--- a/T620X_IO.xlsx
+++ b/T620X_IO.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PLC_DEV\MTech\Mtech_T620X_Trommel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\dev_plc\MTech\MTech_T620X_Trommel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A0FBAE4-DA39-47A2-9099-4879E8FF8915}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A85BE2FD-ADBE-493C-9E30-B61AFBF7D8BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="23520" tabRatio="857" activeTab="8" xr2:uid="{2FCBBB71-3591-49CF-88C3-9E3184A7626E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="857" activeTab="7" xr2:uid="{2FCBBB71-3591-49CF-88C3-9E3184A7626E}"/>
   </bookViews>
   <sheets>
     <sheet name="IO" sheetId="11" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2617" uniqueCount="1008">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3124" uniqueCount="1187">
   <si>
     <t>PLC Name</t>
   </si>
@@ -3073,6 +3073,543 @@
   </si>
   <si>
     <t>UDINT</t>
+  </si>
+  <si>
+    <t>AccelPedal1LowIdleSwitch</t>
+  </si>
+  <si>
+    <t>AccelPedalKickdownSwitch</t>
+  </si>
+  <si>
+    <t>RoadSpeedLimitStatus</t>
+  </si>
+  <si>
+    <t>AccelPedal2LowIdleSwitch</t>
+  </si>
+  <si>
+    <t>AccelPedalPos1</t>
+  </si>
+  <si>
+    <t>EngPercentLoadAtCurrentSpeed</t>
+  </si>
+  <si>
+    <t>RemoteAccelPedalPos</t>
+  </si>
+  <si>
+    <t>AccelPedalPos2</t>
+  </si>
+  <si>
+    <t>VhclAccelerationRateLimitStatus</t>
+  </si>
+  <si>
+    <t>MmntryEngMaxPowerEnableFeedback</t>
+  </si>
+  <si>
+    <t>DPFThermalManagementActive</t>
+  </si>
+  <si>
+    <t>SCRThermalManagementActive</t>
+  </si>
+  <si>
+    <t>ActlMxAvailableEngPercentTorque</t>
+  </si>
+  <si>
+    <t>EstPumpingPercentTorque</t>
+  </si>
+  <si>
+    <t>NominalFrictionPercentTorque</t>
+  </si>
+  <si>
+    <t>EngsDesiredOperatingSpeed</t>
+  </si>
+  <si>
+    <t>EngsDsrdOprtngSpdAsymmtryAdjstmn</t>
+  </si>
+  <si>
+    <t>EstEngPrsticLossesPercentTorque</t>
+  </si>
+  <si>
+    <t>Aftrtratment1ExhaustGasMassFlow</t>
+  </si>
+  <si>
+    <t>Aftertreatment1IntakeDewPoint</t>
+  </si>
+  <si>
+    <t>Aftertreatment1ExhaustDewPoint</t>
+  </si>
+  <si>
+    <t>Aftertreatment2IntakeDewPoint</t>
+  </si>
+  <si>
+    <t>Aftertreatment2ExhaustDewPoint</t>
+  </si>
+  <si>
+    <t>REAl</t>
+  </si>
+  <si>
+    <t>EngTrb1ClcltedTurbineIntakeTemp</t>
+  </si>
+  <si>
+    <t>EngTrb1ClcltedTurbineOutletTemp</t>
+  </si>
+  <si>
+    <t>EngExhstGsRcrculation1ValveCtrl</t>
+  </si>
+  <si>
+    <t>EngVrblGmtryTrbArCtrlShtffValve</t>
+  </si>
+  <si>
+    <t>EngVrableGeometryTurbo1CtrlMode</t>
+  </si>
+  <si>
+    <t>EngVrblGometryTurbo1ActuatorPos</t>
+  </si>
+  <si>
+    <t>EngCoolantTemp</t>
+  </si>
+  <si>
+    <t>EngFuelTemp1</t>
+  </si>
+  <si>
+    <t>EngOilTemp1</t>
+  </si>
+  <si>
+    <t>EngTurboOilTemp</t>
+  </si>
+  <si>
+    <t>EngIntercoolerTemp</t>
+  </si>
+  <si>
+    <t>EngIntercoolerThermostatOpening</t>
+  </si>
+  <si>
+    <t>EngFuelDeliveryPress</t>
+  </si>
+  <si>
+    <t>EngExCrankcaseBlowbyPress</t>
+  </si>
+  <si>
+    <t>EngOilLevel</t>
+  </si>
+  <si>
+    <t>EngOilPress</t>
+  </si>
+  <si>
+    <t>EngCrankcasePress</t>
+  </si>
+  <si>
+    <t>EngCoolantPress</t>
+  </si>
+  <si>
+    <t>EngCoolantLevel</t>
+  </si>
+  <si>
+    <t>UINT</t>
+  </si>
+  <si>
+    <t>EFL_P1</t>
+  </si>
+  <si>
+    <t>EngInjectionCtrlPress</t>
+  </si>
+  <si>
+    <t>EngInjectorMeteringRail1Press</t>
+  </si>
+  <si>
+    <t>EngInjectorTimingRail1Press</t>
+  </si>
+  <si>
+    <t>EngInjectorMeteringRail2Press</t>
+  </si>
+  <si>
+    <t>LREAL</t>
+  </si>
+  <si>
+    <t>EngTripFuel</t>
+  </si>
+  <si>
+    <t>EngTotalFuelUsed</t>
+  </si>
+  <si>
+    <t>BarometricPress</t>
+  </si>
+  <si>
+    <t>CabInteriorTemp</t>
+  </si>
+  <si>
+    <t>AmbientAirTemp</t>
+  </si>
+  <si>
+    <t>EngAirIntakeTemp</t>
+  </si>
+  <si>
+    <t>RoadSurfaceTemp</t>
+  </si>
+  <si>
+    <t>EngDslPrtclateFilterIntakePress</t>
+  </si>
+  <si>
+    <t>EngIntakeManifold1Press</t>
+  </si>
+  <si>
+    <t>EngIntakeManifold1Temp</t>
+  </si>
+  <si>
+    <t>EngAirIntakePress</t>
+  </si>
+  <si>
+    <t>EngAirFilter1DiffPress</t>
+  </si>
+  <si>
+    <t>EngExhaustGasTemp</t>
+  </si>
+  <si>
+    <t>EngCoolantFilterDiffPress</t>
+  </si>
+  <si>
+    <t>IC1</t>
+  </si>
+  <si>
+    <t>NetBatteryCurrent</t>
+  </si>
+  <si>
+    <t>AltCurrent</t>
+  </si>
+  <si>
+    <t>ChargingSystemPotential</t>
+  </si>
+  <si>
+    <t>BatteryPotential_PowerInput1</t>
+  </si>
+  <si>
+    <t>KeyswitchBatteryPotential</t>
+  </si>
+  <si>
+    <t>EngOilLevelRemoteReservoir</t>
+  </si>
+  <si>
+    <t>EngFuelSupplyPumpIntakePress</t>
+  </si>
+  <si>
+    <t>EngFuelFilterDiffPress</t>
+  </si>
+  <si>
+    <t>EngWasteOilReservoirLevel</t>
+  </si>
+  <si>
+    <t>EngOilFilterOutletPress</t>
+  </si>
+  <si>
+    <t>EngOilPrimingPumpSwitch</t>
+  </si>
+  <si>
+    <t>EngOilPrimingState</t>
+  </si>
+  <si>
+    <t>EngOilPreHeatedState</t>
+  </si>
+  <si>
+    <t>EngCoolantPreheatedState</t>
+  </si>
+  <si>
+    <t>EngVentilationStatus</t>
+  </si>
+  <si>
+    <t>FuelPumpPrimerStatus</t>
+  </si>
+  <si>
+    <t>DieselParticulateFilterLampCmd</t>
+  </si>
+  <si>
+    <t>DslPrtcltFltrPssvRgnrtionStatus</t>
+  </si>
+  <si>
+    <t>DslPrtcltFltrActvRgnrtionStatus</t>
+  </si>
+  <si>
+    <t>DieselParticulateFilterStatus</t>
+  </si>
+  <si>
+    <t>DslPrtcltFltrActvRgnrtnInhbtdStt</t>
+  </si>
+  <si>
+    <t>DslPrtcltFltrActvRgnrtnInhbtdDTI</t>
+  </si>
+  <si>
+    <t>DslPrtcltFltrActvRgnrtnInhbtdDTC</t>
+  </si>
+  <si>
+    <t>DslPrtcltFltrActvRgnrtnInhb_0004</t>
+  </si>
+  <si>
+    <t>DslPrtcltFltrActvRgnrtnInhb_0003</t>
+  </si>
+  <si>
+    <t>DslPrtcltFltrActvRgnrtnInhbtdDTA</t>
+  </si>
+  <si>
+    <t>DslPrtcltFltrActvRgnrtnInhbtdDTO</t>
+  </si>
+  <si>
+    <t>DslPrtcltFltrActvRgnrtnInhb_0002</t>
+  </si>
+  <si>
+    <t>DslPrtcltFltrActvRgnrtnInhb_0001</t>
+  </si>
+  <si>
+    <t>DslPrtcltFltrActvRgnrtnInhbtdDTL</t>
+  </si>
+  <si>
+    <t>DslPrtcltFltrActvRgnrtnInhb_0000</t>
+  </si>
+  <si>
+    <t>DslPrtcltFltrActvRgnrtnInhbtdDTS</t>
+  </si>
+  <si>
+    <t>DslPrtcltFltrActvRgnrtnInhbtdDTT</t>
+  </si>
+  <si>
+    <t>DslPrtcltFltrActvRgnrtnInhbtdDTP</t>
+  </si>
+  <si>
+    <t>DslPrtcltFltrActvRgnrtnInhbtdDTE</t>
+  </si>
+  <si>
+    <t>DslPrtcltFltrActvRgnrtnInhbtdDTV</t>
+  </si>
+  <si>
+    <t>DslPrtcltFltrAtmtcActvRgnrtnIntt</t>
+  </si>
+  <si>
+    <t>ExhaustSystemHighTempLampCmd</t>
+  </si>
+  <si>
+    <t>DslPrtcltFltrActvRgnrtnFrcdStts</t>
+  </si>
+  <si>
+    <t>Aftertreatment1ExhaustGasTemp1</t>
+  </si>
+  <si>
+    <t>Aftrtrtmnt1DslPrtcltFltrInt_0000</t>
+  </si>
+  <si>
+    <t>Aftrtrtmnt1ExhstGsTmp1PrlmnryFMI</t>
+  </si>
+  <si>
+    <t>Aftrtrtmnt1DslPrtcltFltrIntkGsTm</t>
+  </si>
+  <si>
+    <t>Aftrtrtmnt1SCRCatalystTankLevel</t>
+  </si>
+  <si>
+    <t>Aftrtrtment1SCRCatalystTankTemp</t>
+  </si>
+  <si>
+    <t>Aftrtrtmnt1SCRCtalystTankLevel2</t>
+  </si>
+  <si>
+    <t>Aftrtrtmnt1SCRCtlystTnkLvlPrlmnr</t>
+  </si>
+  <si>
+    <t>Aftrtrtmnt1DEFTnkLwLvlIndicator</t>
+  </si>
+  <si>
+    <t>Aftrtrtmnt1SCRCtlystRgntTnk1TmpP</t>
+  </si>
+  <si>
+    <t>AftrtrtmntSCROprtrIndcmntSvrity</t>
+  </si>
+  <si>
+    <t>Aftrtrtmnt1SCRCtalystTankHeater</t>
+  </si>
+  <si>
+    <t>Aftrtrtmnt1SCRCtlystRgntTnk1HtrP</t>
+  </si>
+  <si>
+    <t>Aftrtrtmnt1SCRCatalystTankLevel_1</t>
+  </si>
+  <si>
+    <t>Aftrtrtment1SCRCatalystTankTemp_1</t>
+  </si>
+  <si>
+    <t>Aftrtrtmnt1SCRCtalystTankLevel2_1</t>
+  </si>
+  <si>
+    <t>Aftrtrtmnt1SCRCtlystTnkLvlPrlmnr_1</t>
+  </si>
+  <si>
+    <t>Aftrtrtmnt1DEFTnkLwLvlIndicator_1</t>
+  </si>
+  <si>
+    <t>Aftrtrtmnt1SCRCtlystRgntTnk1TmpP_1</t>
+  </si>
+  <si>
+    <t>AftrtrtmntSCROprtrIndcmntSvrity_1</t>
+  </si>
+  <si>
+    <t>Aftrtrtmnt1SCRCtalystTankHeater_1</t>
+  </si>
+  <si>
+    <t>Aftrtrtmnt1SCRCtlystRgntTnk1HtrP_1</t>
+  </si>
+  <si>
+    <t>AT1T1I</t>
+  </si>
+  <si>
+    <t>Aftrtrtmnt1SCRActlDsngRgntQntty</t>
+  </si>
+  <si>
+    <t>Aftertreatment1SCRSystemState</t>
+  </si>
+  <si>
+    <t>Aftrtrtmnt1SCRActlRgntQnttyOfInt</t>
+  </si>
+  <si>
+    <t>Aftrtrtmnt1SCRDsngRgentAbsPress</t>
+  </si>
+  <si>
+    <t>A1SCREGT</t>
+  </si>
+  <si>
+    <t>Aftrtrtmnt1SCRCtlystIntkGasTemp</t>
+  </si>
+  <si>
+    <t>Aftrtrtmnt1SCRCtlystIntkGsTmpPrl</t>
+  </si>
+  <si>
+    <t>Aftrtrtmnt1SCRCtlystOtltGasTemp</t>
+  </si>
+  <si>
+    <t>Aftrtrtmnt1SCRCtlystOtltGsTmpPrl</t>
+  </si>
+  <si>
+    <t>Aftrtrtmnt1DslOxdtnCtlystIn_0000</t>
+  </si>
+  <si>
+    <t>Aftrtrtmnt1DslOxdtnCtlystOt_0000</t>
+  </si>
+  <si>
+    <t>Aftrtrtmnt1DslOxdtnCtlystDffPrss</t>
+  </si>
+  <si>
+    <t>Aftrtrtmnt1DslOxdtnCtlystIntkGsT</t>
+  </si>
+  <si>
+    <t>Aftrtrtmnt1DslOxdtnCtlystOtltGsT</t>
+  </si>
+  <si>
+    <t>Aftrtrtmnt1DslOxdtnCtlystDf_0000</t>
+  </si>
+  <si>
+    <t>WFI</t>
+  </si>
+  <si>
+    <t>WaterInFuelIndicator</t>
+  </si>
+  <si>
+    <t>EngProtectLampCmd</t>
+  </si>
+  <si>
+    <t>EngAmberWarningLampCmd</t>
+  </si>
+  <si>
+    <t>EngRedStopLampCmd</t>
+  </si>
+  <si>
+    <t>OBDMalfunctionIndicatorLampCmd</t>
+  </si>
+  <si>
+    <t>EngBrakeActiveLampCmd</t>
+  </si>
+  <si>
+    <t>CmprssnBrkEnblSwtchIndctrLmpCmd</t>
+  </si>
+  <si>
+    <t>EngOilPressLowLampCmd</t>
+  </si>
+  <si>
+    <t>EngCoolantTempHighLampCmd</t>
+  </si>
+  <si>
+    <t>EngCoolantLevelLowLampCmd</t>
+  </si>
+  <si>
+    <t>EngIdleManagementActiveLampCmd</t>
+  </si>
+  <si>
+    <t>EngAirFilterRestrictionLampCmd</t>
+  </si>
+  <si>
+    <t>EngFuelFilterRestrictedLampCmd</t>
+  </si>
+  <si>
+    <t>DLCD1</t>
+  </si>
+  <si>
+    <t>EngProtectLampData</t>
+  </si>
+  <si>
+    <t>EngAmberWarningLampData</t>
+  </si>
+  <si>
+    <t>EngRedStopLampData</t>
+  </si>
+  <si>
+    <t>OBDMalfunctionIndicatorLampData</t>
+  </si>
+  <si>
+    <t>EngBrakeActiveLampData</t>
+  </si>
+  <si>
+    <t>CmprssnBrkEnblSwtchIndctrLmpDta</t>
+  </si>
+  <si>
+    <t>EngOilPressLowLampData</t>
+  </si>
+  <si>
+    <t>EngCoolantTempHighLampData</t>
+  </si>
+  <si>
+    <t>EngCoolantLevelLowLampData</t>
+  </si>
+  <si>
+    <t>EngIdleManagementActiveLampData</t>
+  </si>
+  <si>
+    <t>EngAirFilterRestrictionLampData</t>
+  </si>
+  <si>
+    <t>EngFuelFilterRestrictedLampData</t>
+  </si>
+  <si>
+    <t>EngWaitToStartLampData</t>
+  </si>
+  <si>
+    <t>ENGINE SPEED SENSOR INFORMATION</t>
+  </si>
+  <si>
+    <t>0,1,2</t>
+  </si>
+  <si>
+    <t>0,1</t>
+  </si>
+  <si>
+    <t>2,3</t>
+  </si>
+  <si>
+    <t>4,5,6</t>
+  </si>
+  <si>
+    <t>4,5</t>
+  </si>
+  <si>
+    <t>6,7</t>
+  </si>
+  <si>
+    <t>2,3,4</t>
+  </si>
+  <si>
+    <t>5,6,7</t>
   </si>
 </sst>
 </file>
@@ -24520,6 +25057,14 @@
         <v>936</v>
       </c>
     </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>1178</v>
+      </c>
+      <c r="D42" s="26">
+        <v>61473</v>
+      </c>
+    </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" s="36"/>
       <c r="B49" s="36"/>
@@ -24539,406 +25084,3389 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67835F87-8E16-4012-B1FC-4AA8A57E1B78}">
-  <dimension ref="B3:H38"/>
+  <dimension ref="B3:S203"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="31.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="34.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.85546875" customWidth="1"/>
+    <col min="3" max="3" width="35.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="2" style="26" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.140625" style="26" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="2" style="26" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.140625" style="26" customWidth="1"/>
+    <col min="10" max="10" width="43.28515625" customWidth="1"/>
+    <col min="11" max="11" width="38.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>871</v>
       </c>
       <c r="C3" t="s">
         <v>974</v>
       </c>
-      <c r="E3" t="s">
+      <c r="H3" t="s">
         <v>983</v>
       </c>
-      <c r="H3" t="str">
-        <f>_xlfn.CONCAT(B3,C3,":",E3,";")</f>
+      <c r="J3" t="str">
+        <f>IF(C3&lt;&gt;"",_xlfn.CONCAT(C3,";"),"")</f>
+        <v>EngOverrideCtrlMode;</v>
+      </c>
+      <c r="K3" t="str">
+        <f>_xlfn.CONCAT(B3,C3,":",H3,";")</f>
         <v>TSC1EngOverrideCtrlMode:USINT;</v>
       </c>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>871</v>
       </c>
       <c r="C4" t="s">
         <v>973</v>
       </c>
-      <c r="E4" t="s">
+      <c r="H4" t="s">
         <v>983</v>
       </c>
-      <c r="H4" t="str">
-        <f t="shared" ref="H4:H12" si="0">_xlfn.CONCAT(B4,C4,":",E4,";")</f>
+      <c r="J4" t="str">
+        <f t="shared" ref="J4:J67" si="0">IF(C4&lt;&gt;"",_xlfn.CONCAT(C4,";"),"")</f>
+        <v>EngRqedSpeedCtrlConditions;</v>
+      </c>
+      <c r="K4" t="str">
+        <f t="shared" ref="K4:K12" si="1">_xlfn.CONCAT(B4,C4,":",H4,";")</f>
         <v>TSC1EngRqedSpeedCtrlConditions:USINT;</v>
       </c>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>871</v>
       </c>
       <c r="C5" t="s">
         <v>975</v>
       </c>
-      <c r="E5" t="s">
+      <c r="H5" t="s">
         <v>983</v>
       </c>
-      <c r="H5" t="str">
+      <c r="J5" t="str">
         <f t="shared" si="0"/>
+        <v>OverrideCtrlModePriority;</v>
+      </c>
+      <c r="K5" t="str">
+        <f t="shared" si="1"/>
         <v>TSC1OverrideCtrlModePriority:USINT;</v>
       </c>
     </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>871</v>
       </c>
       <c r="C6" t="s">
         <v>976</v>
       </c>
-      <c r="E6" t="s">
+      <c r="H6" t="s">
         <v>984</v>
       </c>
-      <c r="H6" t="str">
+      <c r="J6" t="str">
         <f t="shared" si="0"/>
+        <v>EngRqedSpeed_SpeedLimit;</v>
+      </c>
+      <c r="K6" t="str">
+        <f t="shared" si="1"/>
         <v>TSC1EngRqedSpeed_SpeedLimit:REAL;</v>
       </c>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>871</v>
       </c>
       <c r="C7" t="s">
         <v>977</v>
       </c>
-      <c r="E7" t="s">
+      <c r="H7" t="s">
         <v>985</v>
       </c>
-      <c r="H7" t="str">
+      <c r="J7" t="str">
         <f t="shared" si="0"/>
+        <v>EngRqedTorque_TorqueLimit;</v>
+      </c>
+      <c r="K7" t="str">
+        <f t="shared" si="1"/>
         <v>TSC1EngRqedTorque_TorqueLimit:INT;</v>
       </c>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>871</v>
       </c>
       <c r="C8" t="s">
         <v>978</v>
       </c>
-      <c r="E8" t="s">
+      <c r="H8" t="s">
         <v>983</v>
       </c>
-      <c r="H8" t="str">
+      <c r="J8" t="str">
         <f t="shared" si="0"/>
+        <v>TransmissionRate;</v>
+      </c>
+      <c r="K8" t="str">
+        <f t="shared" si="1"/>
         <v>TSC1TransmissionRate:USINT;</v>
       </c>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>871</v>
       </c>
       <c r="C9" t="s">
         <v>979</v>
       </c>
-      <c r="E9" t="s">
+      <c r="H9" t="s">
         <v>983</v>
       </c>
-      <c r="H9" t="str">
+      <c r="J9" t="str">
         <f t="shared" si="0"/>
+        <v>ControlPurpose;</v>
+      </c>
+      <c r="K9" t="str">
+        <f t="shared" si="1"/>
         <v>TSC1ControlPurpose:USINT;</v>
       </c>
-    </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="P9" t="s">
+        <v>564</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>994</v>
+      </c>
+      <c r="S9" t="s">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="10" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>871</v>
       </c>
       <c r="C10" t="s">
         <v>980</v>
       </c>
-      <c r="E10" t="s">
+      <c r="H10" t="s">
         <v>984</v>
       </c>
-      <c r="H10" t="str">
+      <c r="J10" t="str">
         <f t="shared" si="0"/>
+        <v>EngineRequestedTorqueHiRes;</v>
+      </c>
+      <c r="K10" t="str">
+        <f t="shared" si="1"/>
         <v>TSC1EngineRequestedTorqueHiRes:REAL;</v>
       </c>
-    </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="P10" t="s">
+        <v>564</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>995</v>
+      </c>
+      <c r="S10" t="s">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="11" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>871</v>
       </c>
       <c r="C11" t="s">
         <v>981</v>
       </c>
-      <c r="E11" t="s">
+      <c r="H11" t="s">
         <v>983</v>
       </c>
-      <c r="H11" t="str">
+      <c r="J11" t="str">
         <f t="shared" si="0"/>
+        <v>MessageCounter;</v>
+      </c>
+      <c r="K11" t="str">
+        <f t="shared" si="1"/>
         <v>TSC1MessageCounter:USINT;</v>
       </c>
-    </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="P11" t="s">
+        <v>564</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>996</v>
+      </c>
+      <c r="S11" t="s">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="12" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>871</v>
       </c>
       <c r="C12" t="s">
         <v>982</v>
       </c>
-      <c r="E12" t="s">
+      <c r="H12" t="s">
         <v>983</v>
       </c>
-      <c r="H12" t="str">
+      <c r="J12" t="str">
         <f t="shared" si="0"/>
+        <v>MessageChecksum;</v>
+      </c>
+      <c r="K12" t="str">
+        <f t="shared" si="1"/>
         <v>TSC1MessageChecksum:USINT;</v>
       </c>
-    </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="P12" t="s">
+        <v>564</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>997</v>
+      </c>
+      <c r="S12" t="s">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="13" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="J13" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="P13" t="s">
+        <v>564</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>998</v>
+      </c>
+      <c r="S13" t="s">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="14" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="J14" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="P14" t="s">
+        <v>564</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>999</v>
+      </c>
+      <c r="S14" t="s">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="15" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>895</v>
       </c>
       <c r="C15" t="s">
         <v>986</v>
       </c>
-      <c r="E15" t="s">
+      <c r="H15" t="s">
         <v>983</v>
       </c>
-    </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="J15" t="str">
+        <f t="shared" si="0"/>
+        <v>EngTorqueMode;</v>
+      </c>
+      <c r="P15" t="s">
+        <v>564</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>1000</v>
+      </c>
+      <c r="S15" t="s">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="16" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>895</v>
       </c>
       <c r="C16" t="s">
         <v>987</v>
       </c>
-      <c r="E16" t="s">
+      <c r="H16" t="s">
         <v>984</v>
       </c>
-    </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="J16" t="str">
+        <f t="shared" si="0"/>
+        <v>ActlEngPrcntTrqueHighResolution;</v>
+      </c>
+      <c r="P16" t="s">
+        <v>564</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>1001</v>
+      </c>
+      <c r="S16" t="s">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="17" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>895</v>
       </c>
       <c r="C17" t="s">
         <v>988</v>
       </c>
-      <c r="E17" t="s">
+      <c r="H17" t="s">
         <v>985</v>
       </c>
-    </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="J17" t="str">
+        <f t="shared" si="0"/>
+        <v>DriversDemandEngPercentTorque;</v>
+      </c>
+      <c r="P17" t="s">
+        <v>564</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>1002</v>
+      </c>
+      <c r="S17" t="s">
+        <v>1007</v>
+      </c>
+    </row>
+    <row r="18" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>895</v>
       </c>
       <c r="C18" t="s">
         <v>989</v>
       </c>
-      <c r="E18" t="s">
+      <c r="H18" t="s">
         <v>985</v>
       </c>
-    </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="J18" t="str">
+        <f t="shared" si="0"/>
+        <v>ActualEngPercentTorque;</v>
+      </c>
+      <c r="P18" t="s">
+        <v>564</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>1003</v>
+      </c>
+      <c r="S18" t="s">
+        <v>1007</v>
+      </c>
+    </row>
+    <row r="19" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>895</v>
       </c>
       <c r="C19" t="s">
         <v>990</v>
       </c>
-      <c r="E19" t="s">
+      <c r="H19" t="s">
         <v>984</v>
       </c>
-    </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="J19" t="str">
+        <f t="shared" si="0"/>
+        <v>EngSpeed;</v>
+      </c>
+      <c r="P19" t="s">
+        <v>564</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>1004</v>
+      </c>
+      <c r="S19" t="s">
+        <v>1007</v>
+      </c>
+    </row>
+    <row r="20" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>895</v>
       </c>
       <c r="C20" t="s">
         <v>991</v>
       </c>
-      <c r="E20" t="s">
+      <c r="H20" t="s">
         <v>983</v>
       </c>
-    </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="J20" t="str">
+        <f t="shared" si="0"/>
+        <v>SrcAddrssOfCtrllngDvcFrEngCntrl;</v>
+      </c>
+      <c r="P20" t="s">
+        <v>564</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>1005</v>
+      </c>
+      <c r="S20" t="s">
+        <v>1007</v>
+      </c>
+    </row>
+    <row r="21" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>895</v>
       </c>
       <c r="C21" t="s">
         <v>992</v>
       </c>
-      <c r="E21" t="s">
+      <c r="H21" t="s">
         <v>983</v>
       </c>
-    </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="J21" t="str">
+        <f t="shared" si="0"/>
+        <v>EngStarterMode;</v>
+      </c>
+      <c r="P21" t="s">
+        <v>564</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>1006</v>
+      </c>
+      <c r="S21" t="s">
+        <v>1007</v>
+      </c>
+    </row>
+    <row r="22" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>895</v>
       </c>
       <c r="C22" t="s">
         <v>993</v>
       </c>
-      <c r="E22" t="s">
+      <c r="H22" t="s">
         <v>985</v>
       </c>
-    </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="J22" t="str">
+        <f t="shared" si="0"/>
+        <v>EngDemandPercentTorque;</v>
+      </c>
+    </row>
+    <row r="23" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="J23" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="24" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B24" t="s">
+        <v>958</v>
+      </c>
+      <c r="C24" t="s">
+        <v>1008</v>
+      </c>
+      <c r="H24" t="s">
+        <v>983</v>
+      </c>
+      <c r="J24" t="str">
+        <f t="shared" si="0"/>
+        <v>AccelPedal1LowIdleSwitch;</v>
+      </c>
+    </row>
+    <row r="25" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B25" t="s">
+        <v>958</v>
+      </c>
+      <c r="C25" t="s">
+        <v>1009</v>
+      </c>
+      <c r="H25" t="s">
+        <v>983</v>
+      </c>
+      <c r="J25" t="str">
+        <f t="shared" si="0"/>
+        <v>AccelPedalKickdownSwitch;</v>
+      </c>
+    </row>
+    <row r="26" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
-        <v>564</v>
+        <v>958</v>
       </c>
       <c r="C26" t="s">
-        <v>994</v>
-      </c>
-      <c r="E26" t="s">
+        <v>1010</v>
+      </c>
+      <c r="H26" t="s">
         <v>983</v>
       </c>
-    </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="J26" t="str">
+        <f t="shared" si="0"/>
+        <v>RoadSpeedLimitStatus;</v>
+      </c>
+    </row>
+    <row r="27" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
-        <v>564</v>
+        <v>958</v>
       </c>
       <c r="C27" t="s">
-        <v>995</v>
-      </c>
-      <c r="E27" t="s">
+        <v>1011</v>
+      </c>
+      <c r="H27" t="s">
         <v>983</v>
       </c>
-    </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="J27" t="str">
+        <f t="shared" si="0"/>
+        <v>AccelPedal2LowIdleSwitch;</v>
+      </c>
+    </row>
+    <row r="28" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
-        <v>564</v>
+        <v>958</v>
       </c>
       <c r="C28" t="s">
-        <v>996</v>
-      </c>
-      <c r="E28" t="s">
+        <v>1012</v>
+      </c>
+      <c r="H28" t="s">
+        <v>984</v>
+      </c>
+      <c r="J28" t="str">
+        <f t="shared" si="0"/>
+        <v>AccelPedalPos1;</v>
+      </c>
+    </row>
+    <row r="29" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B29" t="s">
+        <v>958</v>
+      </c>
+      <c r="C29" t="s">
+        <v>1013</v>
+      </c>
+      <c r="H29" t="s">
         <v>983</v>
       </c>
-    </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B29" t="s">
-        <v>564</v>
-      </c>
-      <c r="C29" t="s">
-        <v>997</v>
-      </c>
-      <c r="E29" t="s">
+      <c r="J29" t="str">
+        <f t="shared" si="0"/>
+        <v>EngPercentLoadAtCurrentSpeed;</v>
+      </c>
+    </row>
+    <row r="30" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B30" t="s">
+        <v>958</v>
+      </c>
+      <c r="C30" t="s">
+        <v>1014</v>
+      </c>
+      <c r="H30" t="s">
+        <v>984</v>
+      </c>
+      <c r="J30" t="str">
+        <f t="shared" si="0"/>
+        <v>RemoteAccelPedalPos;</v>
+      </c>
+    </row>
+    <row r="31" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B31" t="s">
+        <v>958</v>
+      </c>
+      <c r="C31" t="s">
+        <v>1015</v>
+      </c>
+      <c r="H31" t="s">
+        <v>984</v>
+      </c>
+      <c r="J31" t="str">
+        <f t="shared" si="0"/>
+        <v>AccelPedalPos2;</v>
+      </c>
+    </row>
+    <row r="32" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B32" t="s">
+        <v>958</v>
+      </c>
+      <c r="C32" t="s">
+        <v>1016</v>
+      </c>
+      <c r="H32" t="s">
         <v>983</v>
       </c>
-    </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B30" t="s">
-        <v>564</v>
-      </c>
-      <c r="C30" t="s">
-        <v>998</v>
-      </c>
-      <c r="E30" t="s">
+      <c r="J32" t="str">
+        <f t="shared" si="0"/>
+        <v>VhclAccelerationRateLimitStatus;</v>
+      </c>
+    </row>
+    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B33" t="s">
+        <v>958</v>
+      </c>
+      <c r="C33" t="s">
+        <v>1017</v>
+      </c>
+      <c r="H33" t="s">
         <v>983</v>
       </c>
-    </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B31" t="s">
-        <v>564</v>
-      </c>
-      <c r="C31" t="s">
-        <v>999</v>
-      </c>
-      <c r="E31" t="s">
+      <c r="J33" t="str">
+        <f t="shared" si="0"/>
+        <v>MmntryEngMaxPowerEnableFeedback;</v>
+      </c>
+    </row>
+    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B34" t="s">
+        <v>958</v>
+      </c>
+      <c r="C34" t="s">
+        <v>1018</v>
+      </c>
+      <c r="H34" t="s">
         <v>983</v>
       </c>
-    </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B32" t="s">
-        <v>564</v>
-      </c>
-      <c r="C32" t="s">
-        <v>1000</v>
-      </c>
-      <c r="E32" t="s">
+      <c r="J34" t="str">
+        <f t="shared" si="0"/>
+        <v>DPFThermalManagementActive;</v>
+      </c>
+    </row>
+    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B35" t="s">
+        <v>958</v>
+      </c>
+      <c r="C35" t="s">
+        <v>1019</v>
+      </c>
+      <c r="H35" t="s">
         <v>983</v>
       </c>
-    </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B33" t="s">
-        <v>564</v>
-      </c>
-      <c r="C33" t="s">
-        <v>1001</v>
-      </c>
-      <c r="E33" t="s">
+      <c r="J35" t="str">
+        <f t="shared" si="0"/>
+        <v>SCRThermalManagementActive;</v>
+      </c>
+    </row>
+    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B36" t="s">
+        <v>958</v>
+      </c>
+      <c r="C36" t="s">
+        <v>1020</v>
+      </c>
+      <c r="H36" t="s">
+        <v>984</v>
+      </c>
+      <c r="J36" t="str">
+        <f t="shared" si="0"/>
+        <v>ActlMxAvailableEngPercentTorque;</v>
+      </c>
+    </row>
+    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B37" t="s">
+        <v>958</v>
+      </c>
+      <c r="C37" t="s">
+        <v>1021</v>
+      </c>
+      <c r="H37" t="s">
+        <v>985</v>
+      </c>
+      <c r="J37" t="str">
+        <f t="shared" si="0"/>
+        <v>EstPumpingPercentTorque;</v>
+      </c>
+    </row>
+    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J38" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B39" t="s">
+        <v>898</v>
+      </c>
+      <c r="C39" t="s">
+        <v>1022</v>
+      </c>
+      <c r="H39" t="s">
+        <v>985</v>
+      </c>
+      <c r="J39" t="str">
+        <f t="shared" si="0"/>
+        <v>NominalFrictionPercentTorque;</v>
+      </c>
+    </row>
+    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B40" t="s">
+        <v>898</v>
+      </c>
+      <c r="C40" t="s">
+        <v>1023</v>
+      </c>
+      <c r="H40" t="s">
+        <v>1031</v>
+      </c>
+      <c r="J40" t="str">
+        <f t="shared" si="0"/>
+        <v>EngsDesiredOperatingSpeed;</v>
+      </c>
+    </row>
+    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B41" t="s">
+        <v>898</v>
+      </c>
+      <c r="C41" t="s">
+        <v>1024</v>
+      </c>
+      <c r="H41" t="s">
         <v>983</v>
       </c>
-    </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B34" t="s">
-        <v>564</v>
-      </c>
-      <c r="C34" t="s">
-        <v>1002</v>
-      </c>
-      <c r="E34" t="s">
-        <v>1007</v>
-      </c>
-    </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B35" t="s">
-        <v>564</v>
-      </c>
-      <c r="C35" t="s">
-        <v>1003</v>
-      </c>
-      <c r="E35" t="s">
-        <v>1007</v>
-      </c>
-    </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B36" t="s">
-        <v>564</v>
-      </c>
-      <c r="C36" t="s">
-        <v>1004</v>
-      </c>
-      <c r="E36" t="s">
-        <v>1007</v>
-      </c>
-    </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B37" t="s">
-        <v>564</v>
-      </c>
-      <c r="C37" t="s">
-        <v>1005</v>
-      </c>
-      <c r="E37" t="s">
-        <v>1007</v>
-      </c>
-    </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B38" t="s">
-        <v>564</v>
-      </c>
-      <c r="C38" t="s">
-        <v>1006</v>
-      </c>
-      <c r="E38" t="s">
-        <v>1007</v>
+      <c r="J41" t="str">
+        <f t="shared" si="0"/>
+        <v>EngsDsrdOprtngSpdAsymmtryAdjstmn;</v>
+      </c>
+    </row>
+    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B42" t="s">
+        <v>898</v>
+      </c>
+      <c r="C42" t="s">
+        <v>1025</v>
+      </c>
+      <c r="H42" t="s">
+        <v>985</v>
+      </c>
+      <c r="J42" t="str">
+        <f t="shared" si="0"/>
+        <v>EstEngPrsticLossesPercentTorque;</v>
+      </c>
+    </row>
+    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B43" t="s">
+        <v>898</v>
+      </c>
+      <c r="C43" t="s">
+        <v>1026</v>
+      </c>
+      <c r="H43" t="s">
+        <v>984</v>
+      </c>
+      <c r="J43" t="str">
+        <f t="shared" si="0"/>
+        <v>Aftrtratment1ExhaustGasMassFlow;</v>
+      </c>
+    </row>
+    <row r="44" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B44" t="s">
+        <v>898</v>
+      </c>
+      <c r="C44" t="s">
+        <v>1027</v>
+      </c>
+      <c r="H44" t="s">
+        <v>983</v>
+      </c>
+      <c r="J44" t="str">
+        <f t="shared" si="0"/>
+        <v>Aftertreatment1IntakeDewPoint;</v>
+      </c>
+    </row>
+    <row r="45" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B45" t="s">
+        <v>898</v>
+      </c>
+      <c r="C45" t="s">
+        <v>1028</v>
+      </c>
+      <c r="H45" t="s">
+        <v>983</v>
+      </c>
+      <c r="J45" t="str">
+        <f t="shared" si="0"/>
+        <v>Aftertreatment1ExhaustDewPoint;</v>
+      </c>
+    </row>
+    <row r="46" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B46" t="s">
+        <v>898</v>
+      </c>
+      <c r="C46" t="s">
+        <v>1029</v>
+      </c>
+      <c r="H46" t="s">
+        <v>983</v>
+      </c>
+      <c r="J46" t="str">
+        <f t="shared" si="0"/>
+        <v>Aftertreatment2IntakeDewPoint;</v>
+      </c>
+    </row>
+    <row r="47" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B47" t="s">
+        <v>898</v>
+      </c>
+      <c r="C47" t="s">
+        <v>1030</v>
+      </c>
+      <c r="H47" t="s">
+        <v>983</v>
+      </c>
+      <c r="J47" t="str">
+        <f t="shared" si="0"/>
+        <v>Aftertreatment2ExhaustDewPoint;</v>
+      </c>
+    </row>
+    <row r="48" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J48" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="49" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B49" t="s">
+        <v>946</v>
+      </c>
+      <c r="C49" t="s">
+        <v>1032</v>
+      </c>
+      <c r="H49" t="s">
+        <v>984</v>
+      </c>
+      <c r="J49" t="str">
+        <f t="shared" si="0"/>
+        <v>EngTrb1ClcltedTurbineIntakeTemp;</v>
+      </c>
+    </row>
+    <row r="50" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B50" t="s">
+        <v>946</v>
+      </c>
+      <c r="C50" t="s">
+        <v>1033</v>
+      </c>
+      <c r="H50" t="s">
+        <v>984</v>
+      </c>
+      <c r="J50" t="str">
+        <f t="shared" si="0"/>
+        <v>EngTrb1ClcltedTurbineOutletTemp;</v>
+      </c>
+    </row>
+    <row r="51" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B51" t="s">
+        <v>946</v>
+      </c>
+      <c r="C51" t="s">
+        <v>1034</v>
+      </c>
+      <c r="H51" t="s">
+        <v>984</v>
+      </c>
+      <c r="J51" t="str">
+        <f t="shared" si="0"/>
+        <v>EngExhstGsRcrculation1ValveCtrl;</v>
+      </c>
+    </row>
+    <row r="52" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B52" t="s">
+        <v>946</v>
+      </c>
+      <c r="C52" t="s">
+        <v>1035</v>
+      </c>
+      <c r="H52" t="s">
+        <v>983</v>
+      </c>
+      <c r="J52" t="str">
+        <f t="shared" si="0"/>
+        <v>EngVrblGmtryTrbArCtrlShtffValve;</v>
+      </c>
+    </row>
+    <row r="53" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B53" t="s">
+        <v>946</v>
+      </c>
+      <c r="C53" t="s">
+        <v>1036</v>
+      </c>
+      <c r="H53" t="s">
+        <v>983</v>
+      </c>
+      <c r="J53" t="str">
+        <f t="shared" si="0"/>
+        <v>EngVrableGeometryTurbo1CtrlMode;</v>
+      </c>
+    </row>
+    <row r="54" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B54" t="s">
+        <v>946</v>
+      </c>
+      <c r="C54" t="s">
+        <v>1037</v>
+      </c>
+      <c r="H54" t="s">
+        <v>984</v>
+      </c>
+      <c r="J54" t="str">
+        <f t="shared" si="0"/>
+        <v>EngVrblGometryTurbo1ActuatorPos;</v>
+      </c>
+    </row>
+    <row r="55" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J55" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="56" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B56" t="s">
+        <v>900</v>
+      </c>
+      <c r="C56" t="s">
+        <v>1038</v>
+      </c>
+      <c r="H56" t="s">
+        <v>984</v>
+      </c>
+      <c r="J56" t="str">
+        <f t="shared" si="0"/>
+        <v>EngCoolantTemp;</v>
+      </c>
+    </row>
+    <row r="57" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B57" t="s">
+        <v>900</v>
+      </c>
+      <c r="C57" t="s">
+        <v>1039</v>
+      </c>
+      <c r="H57" t="s">
+        <v>985</v>
+      </c>
+      <c r="J57" t="str">
+        <f t="shared" si="0"/>
+        <v>EngFuelTemp1;</v>
+      </c>
+    </row>
+    <row r="58" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B58" t="s">
+        <v>900</v>
+      </c>
+      <c r="C58" t="s">
+        <v>1040</v>
+      </c>
+      <c r="H58" t="s">
+        <v>984</v>
+      </c>
+      <c r="J58" t="str">
+        <f t="shared" si="0"/>
+        <v>EngOilTemp1;</v>
+      </c>
+    </row>
+    <row r="59" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B59" t="s">
+        <v>900</v>
+      </c>
+      <c r="C59" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H59" t="s">
+        <v>984</v>
+      </c>
+      <c r="J59" t="str">
+        <f t="shared" si="0"/>
+        <v>EngTurboOilTemp;</v>
+      </c>
+    </row>
+    <row r="60" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B60" t="s">
+        <v>900</v>
+      </c>
+      <c r="C60" t="s">
+        <v>1042</v>
+      </c>
+      <c r="H60" t="s">
+        <v>985</v>
+      </c>
+      <c r="J60" t="str">
+        <f t="shared" si="0"/>
+        <v>EngIntercoolerTemp;</v>
+      </c>
+    </row>
+    <row r="61" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B61" t="s">
+        <v>900</v>
+      </c>
+      <c r="C61" t="s">
+        <v>1043</v>
+      </c>
+      <c r="H61" t="s">
+        <v>984</v>
+      </c>
+      <c r="J61" t="str">
+        <f t="shared" si="0"/>
+        <v>EngIntercoolerThermostatOpening;</v>
+      </c>
+    </row>
+    <row r="62" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J62" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="63" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B63" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C63" t="s">
+        <v>1044</v>
+      </c>
+      <c r="H63" t="s">
+        <v>1051</v>
+      </c>
+      <c r="J63" t="str">
+        <f t="shared" si="0"/>
+        <v>EngFuelDeliveryPress;</v>
+      </c>
+    </row>
+    <row r="64" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B64" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C64" t="s">
+        <v>1045</v>
+      </c>
+      <c r="H64" t="s">
+        <v>984</v>
+      </c>
+      <c r="J64" t="str">
+        <f t="shared" si="0"/>
+        <v>EngExCrankcaseBlowbyPress;</v>
+      </c>
+    </row>
+    <row r="65" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B65" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C65" t="s">
+        <v>1046</v>
+      </c>
+      <c r="H65" t="s">
+        <v>984</v>
+      </c>
+      <c r="J65" t="str">
+        <f t="shared" si="0"/>
+        <v>EngOilLevel;</v>
+      </c>
+    </row>
+    <row r="66" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B66" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C66" t="s">
+        <v>1047</v>
+      </c>
+      <c r="H66" t="s">
+        <v>1051</v>
+      </c>
+      <c r="J66" t="str">
+        <f t="shared" si="0"/>
+        <v>EngOilPress;</v>
+      </c>
+    </row>
+    <row r="67" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B67" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C67" t="s">
+        <v>1048</v>
+      </c>
+      <c r="H67" t="s">
+        <v>1031</v>
+      </c>
+      <c r="J67" t="str">
+        <f t="shared" si="0"/>
+        <v>EngCrankcasePress;</v>
+      </c>
+    </row>
+    <row r="68" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B68" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C68" t="s">
+        <v>1049</v>
+      </c>
+      <c r="H68" t="s">
+        <v>1051</v>
+      </c>
+      <c r="J68" t="str">
+        <f t="shared" ref="J68:J131" si="2">IF(C68&lt;&gt;"",_xlfn.CONCAT(C68,";"),"")</f>
+        <v>EngCoolantPress;</v>
+      </c>
+    </row>
+    <row r="69" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B69" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C69" t="s">
+        <v>1050</v>
+      </c>
+      <c r="H69" t="s">
+        <v>984</v>
+      </c>
+      <c r="J69" t="str">
+        <f t="shared" si="2"/>
+        <v>EngCoolantLevel;</v>
+      </c>
+    </row>
+    <row r="70" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J70" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="71" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B71" t="s">
+        <v>972</v>
+      </c>
+      <c r="C71" t="s">
+        <v>1053</v>
+      </c>
+      <c r="H71" t="s">
+        <v>1057</v>
+      </c>
+      <c r="J71" t="str">
+        <f t="shared" si="2"/>
+        <v>EngInjectionCtrlPress;</v>
+      </c>
+    </row>
+    <row r="72" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B72" t="s">
+        <v>972</v>
+      </c>
+      <c r="C72" t="s">
+        <v>1054</v>
+      </c>
+      <c r="H72" t="s">
+        <v>1057</v>
+      </c>
+      <c r="J72" t="str">
+        <f t="shared" si="2"/>
+        <v>EngInjectorMeteringRail1Press;</v>
+      </c>
+    </row>
+    <row r="73" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B73" t="s">
+        <v>972</v>
+      </c>
+      <c r="C73" t="s">
+        <v>1055</v>
+      </c>
+      <c r="H73" t="s">
+        <v>1057</v>
+      </c>
+      <c r="J73" t="str">
+        <f t="shared" si="2"/>
+        <v>EngInjectorTimingRail1Press;</v>
+      </c>
+    </row>
+    <row r="74" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B74" t="s">
+        <v>972</v>
+      </c>
+      <c r="C74" t="s">
+        <v>1056</v>
+      </c>
+      <c r="H74" t="s">
+        <v>1057</v>
+      </c>
+      <c r="J74" t="str">
+        <f t="shared" si="2"/>
+        <v>EngInjectorMeteringRail2Press;</v>
+      </c>
+    </row>
+    <row r="75" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J75" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="76" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B76" t="s">
+        <v>903</v>
+      </c>
+      <c r="C76" t="s">
+        <v>1058</v>
+      </c>
+      <c r="H76" t="s">
+        <v>984</v>
+      </c>
+      <c r="J76" t="str">
+        <f t="shared" si="2"/>
+        <v>EngTripFuel;</v>
+      </c>
+    </row>
+    <row r="77" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B77" t="s">
+        <v>903</v>
+      </c>
+      <c r="C77" t="s">
+        <v>1059</v>
+      </c>
+      <c r="H77" t="s">
+        <v>984</v>
+      </c>
+      <c r="J77" t="str">
+        <f t="shared" si="2"/>
+        <v>EngTotalFuelUsed;</v>
+      </c>
+    </row>
+    <row r="78" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J78" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="79" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B79" t="s">
+        <v>930</v>
+      </c>
+      <c r="C79" t="s">
+        <v>1060</v>
+      </c>
+      <c r="H79" t="s">
+        <v>984</v>
+      </c>
+      <c r="J79" t="str">
+        <f t="shared" si="2"/>
+        <v>BarometricPress;</v>
+      </c>
+    </row>
+    <row r="80" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B80" t="s">
+        <v>930</v>
+      </c>
+      <c r="C80" t="s">
+        <v>1061</v>
+      </c>
+      <c r="H80" t="s">
+        <v>984</v>
+      </c>
+      <c r="J80" t="str">
+        <f t="shared" si="2"/>
+        <v>CabInteriorTemp;</v>
+      </c>
+    </row>
+    <row r="81" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B81" t="s">
+        <v>930</v>
+      </c>
+      <c r="C81" t="s">
+        <v>1062</v>
+      </c>
+      <c r="H81" t="s">
+        <v>984</v>
+      </c>
+      <c r="J81" t="str">
+        <f t="shared" si="2"/>
+        <v>AmbientAirTemp;</v>
+      </c>
+    </row>
+    <row r="82" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B82" t="s">
+        <v>930</v>
+      </c>
+      <c r="C82" t="s">
+        <v>1063</v>
+      </c>
+      <c r="H82" t="s">
+        <v>985</v>
+      </c>
+      <c r="J82" t="str">
+        <f t="shared" si="2"/>
+        <v>EngAirIntakeTemp;</v>
+      </c>
+    </row>
+    <row r="83" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B83" t="s">
+        <v>930</v>
+      </c>
+      <c r="C83" t="s">
+        <v>1064</v>
+      </c>
+      <c r="H83" t="s">
+        <v>984</v>
+      </c>
+      <c r="J83" t="str">
+        <f t="shared" si="2"/>
+        <v>RoadSurfaceTemp;</v>
+      </c>
+    </row>
+    <row r="84" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J84" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="85" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B85" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C85" t="s">
+        <v>1065</v>
+      </c>
+      <c r="H85" t="s">
+        <v>984</v>
+      </c>
+      <c r="J85" t="str">
+        <f t="shared" si="2"/>
+        <v>EngDslPrtclateFilterIntakePress;</v>
+      </c>
+    </row>
+    <row r="86" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B86" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C86" t="s">
+        <v>1066</v>
+      </c>
+      <c r="H86" t="s">
+        <v>1051</v>
+      </c>
+      <c r="J86" t="str">
+        <f t="shared" si="2"/>
+        <v>EngIntakeManifold1Press;</v>
+      </c>
+    </row>
+    <row r="87" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B87" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C87" t="s">
+        <v>1067</v>
+      </c>
+      <c r="H87" t="s">
+        <v>985</v>
+      </c>
+      <c r="J87" t="str">
+        <f t="shared" si="2"/>
+        <v>EngIntakeManifold1Temp;</v>
+      </c>
+    </row>
+    <row r="88" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B88" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C88" t="s">
+        <v>1068</v>
+      </c>
+      <c r="H88" t="s">
+        <v>1051</v>
+      </c>
+      <c r="J88" t="str">
+        <f t="shared" si="2"/>
+        <v>EngAirIntakePress;</v>
+      </c>
+    </row>
+    <row r="89" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B89" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C89" t="s">
+        <v>1069</v>
+      </c>
+      <c r="H89" t="s">
+        <v>984</v>
+      </c>
+      <c r="J89" t="str">
+        <f t="shared" si="2"/>
+        <v>EngAirFilter1DiffPress;</v>
+      </c>
+    </row>
+    <row r="90" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B90" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C90" t="s">
+        <v>1070</v>
+      </c>
+      <c r="H90" t="s">
+        <v>984</v>
+      </c>
+      <c r="J90" t="str">
+        <f t="shared" si="2"/>
+        <v>EngExhaustGasTemp;</v>
+      </c>
+    </row>
+    <row r="91" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B91" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C91" t="s">
+        <v>1071</v>
+      </c>
+      <c r="H91" t="s">
+        <v>984</v>
+      </c>
+      <c r="J91" t="str">
+        <f t="shared" si="2"/>
+        <v>EngCoolantFilterDiffPress;</v>
+      </c>
+    </row>
+    <row r="92" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J92" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="93" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B93" t="s">
+        <v>928</v>
+      </c>
+      <c r="C93" t="s">
+        <v>1073</v>
+      </c>
+      <c r="H93" t="s">
+        <v>985</v>
+      </c>
+      <c r="J93" t="str">
+        <f t="shared" si="2"/>
+        <v>NetBatteryCurrent;</v>
+      </c>
+    </row>
+    <row r="94" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B94" t="s">
+        <v>928</v>
+      </c>
+      <c r="C94" t="s">
+        <v>1074</v>
+      </c>
+      <c r="H94" t="s">
+        <v>983</v>
+      </c>
+      <c r="J94" t="str">
+        <f t="shared" si="2"/>
+        <v>AltCurrent;</v>
+      </c>
+    </row>
+    <row r="95" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B95" t="s">
+        <v>928</v>
+      </c>
+      <c r="C95" t="s">
+        <v>1075</v>
+      </c>
+      <c r="H95" t="s">
+        <v>1031</v>
+      </c>
+      <c r="J95" t="str">
+        <f t="shared" si="2"/>
+        <v>ChargingSystemPotential;</v>
+      </c>
+    </row>
+    <row r="96" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B96" t="s">
+        <v>928</v>
+      </c>
+      <c r="C96" t="s">
+        <v>1076</v>
+      </c>
+      <c r="H96" t="s">
+        <v>984</v>
+      </c>
+      <c r="J96" t="str">
+        <f t="shared" si="2"/>
+        <v>BatteryPotential_PowerInput1;</v>
+      </c>
+    </row>
+    <row r="97" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B97" t="s">
+        <v>928</v>
+      </c>
+      <c r="C97" t="s">
+        <v>1077</v>
+      </c>
+      <c r="H97" t="s">
+        <v>984</v>
+      </c>
+      <c r="J97" t="str">
+        <f t="shared" si="2"/>
+        <v>KeyswitchBatteryPotential;</v>
+      </c>
+    </row>
+    <row r="98" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J98" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="99" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B99" t="s">
+        <v>938</v>
+      </c>
+      <c r="C99" t="s">
+        <v>1078</v>
+      </c>
+      <c r="H99" t="s">
+        <v>984</v>
+      </c>
+      <c r="J99" t="str">
+        <f t="shared" si="2"/>
+        <v>EngOilLevelRemoteReservoir;</v>
+      </c>
+    </row>
+    <row r="100" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B100" t="s">
+        <v>938</v>
+      </c>
+      <c r="C100" t="s">
+        <v>1079</v>
+      </c>
+      <c r="H100" t="s">
+        <v>1051</v>
+      </c>
+      <c r="J100" t="str">
+        <f t="shared" si="2"/>
+        <v>EngFuelSupplyPumpIntakePress;</v>
+      </c>
+    </row>
+    <row r="101" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B101" t="s">
+        <v>938</v>
+      </c>
+      <c r="C101" t="s">
+        <v>1080</v>
+      </c>
+      <c r="H101" t="s">
+        <v>1051</v>
+      </c>
+      <c r="J101" t="str">
+        <f t="shared" si="2"/>
+        <v>EngFuelFilterDiffPress;</v>
+      </c>
+    </row>
+    <row r="102" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B102" t="s">
+        <v>938</v>
+      </c>
+      <c r="C102" t="s">
+        <v>1081</v>
+      </c>
+      <c r="H102" t="s">
+        <v>984</v>
+      </c>
+      <c r="J102" t="str">
+        <f t="shared" si="2"/>
+        <v>EngWasteOilReservoirLevel;</v>
+      </c>
+    </row>
+    <row r="103" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B103" t="s">
+        <v>938</v>
+      </c>
+      <c r="C103" t="s">
+        <v>1082</v>
+      </c>
+      <c r="H103" t="s">
+        <v>1051</v>
+      </c>
+      <c r="J103" t="str">
+        <f t="shared" si="2"/>
+        <v>EngOilFilterOutletPress;</v>
+      </c>
+    </row>
+    <row r="104" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B104" t="s">
+        <v>938</v>
+      </c>
+      <c r="C104" t="s">
+        <v>1083</v>
+      </c>
+      <c r="H104" t="s">
+        <v>983</v>
+      </c>
+      <c r="J104" t="str">
+        <f t="shared" si="2"/>
+        <v>EngOilPrimingPumpSwitch;</v>
+      </c>
+    </row>
+    <row r="105" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B105" t="s">
+        <v>938</v>
+      </c>
+      <c r="C105" t="s">
+        <v>1084</v>
+      </c>
+      <c r="H105" t="s">
+        <v>983</v>
+      </c>
+      <c r="J105" t="str">
+        <f t="shared" si="2"/>
+        <v>EngOilPrimingState;</v>
+      </c>
+    </row>
+    <row r="106" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B106" t="s">
+        <v>938</v>
+      </c>
+      <c r="C106" t="s">
+        <v>1085</v>
+      </c>
+      <c r="H106" t="s">
+        <v>983</v>
+      </c>
+      <c r="J106" t="str">
+        <f t="shared" si="2"/>
+        <v>EngOilPreHeatedState;</v>
+      </c>
+    </row>
+    <row r="107" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B107" t="s">
+        <v>938</v>
+      </c>
+      <c r="C107" t="s">
+        <v>1086</v>
+      </c>
+      <c r="H107" t="s">
+        <v>983</v>
+      </c>
+      <c r="J107" t="str">
+        <f t="shared" si="2"/>
+        <v>EngCoolantPreheatedState;</v>
+      </c>
+    </row>
+    <row r="108" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B108" t="s">
+        <v>938</v>
+      </c>
+      <c r="C108" t="s">
+        <v>1087</v>
+      </c>
+      <c r="H108" t="s">
+        <v>983</v>
+      </c>
+      <c r="J108" t="str">
+        <f t="shared" si="2"/>
+        <v>EngVentilationStatus;</v>
+      </c>
+    </row>
+    <row r="109" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B109" t="s">
+        <v>938</v>
+      </c>
+      <c r="C109" t="s">
+        <v>1088</v>
+      </c>
+      <c r="H109" t="s">
+        <v>983</v>
+      </c>
+      <c r="J109" t="str">
+        <f t="shared" si="2"/>
+        <v>FuelPumpPrimerStatus;</v>
+      </c>
+    </row>
+    <row r="110" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J110" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="111" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B111" t="s">
+        <v>888</v>
+      </c>
+      <c r="C111" s="33" t="s">
+        <v>1089</v>
+      </c>
+      <c r="D111" s="26">
+        <v>0</v>
+      </c>
+      <c r="E111" s="26" t="s">
+        <v>1179</v>
+      </c>
+      <c r="F111" s="26">
+        <v>0</v>
+      </c>
+      <c r="G111" s="26" t="str">
+        <f>_xlfn.CONCAT(D111+1,",",F111+1)</f>
+        <v>1,1</v>
+      </c>
+      <c r="H111" t="s">
+        <v>983</v>
+      </c>
+      <c r="J111" t="str">
+        <f t="shared" si="2"/>
+        <v>DieselParticulateFilterLampCmd;</v>
+      </c>
+    </row>
+    <row r="112" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B112" t="s">
+        <v>888</v>
+      </c>
+      <c r="C112" t="s">
+        <v>1090</v>
+      </c>
+      <c r="D112" s="26">
+        <v>1</v>
+      </c>
+      <c r="E112" s="26" t="s">
+        <v>1180</v>
+      </c>
+      <c r="F112" s="26">
+        <v>0</v>
+      </c>
+      <c r="G112" s="26" t="str">
+        <f t="shared" ref="G112:G133" si="3">_xlfn.CONCAT(D112+1,",",F112+1)</f>
+        <v>2,1</v>
+      </c>
+      <c r="H112" t="s">
+        <v>983</v>
+      </c>
+      <c r="J112" t="str">
+        <f t="shared" si="2"/>
+        <v>DslPrtcltFltrPssvRgnrtionStatus;</v>
+      </c>
+    </row>
+    <row r="113" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B113" t="s">
+        <v>888</v>
+      </c>
+      <c r="C113" s="33" t="s">
+        <v>1091</v>
+      </c>
+      <c r="D113" s="26">
+        <v>1</v>
+      </c>
+      <c r="E113" s="26" t="s">
+        <v>1181</v>
+      </c>
+      <c r="F113" s="26">
+        <v>2</v>
+      </c>
+      <c r="G113" s="26" t="str">
+        <f t="shared" si="3"/>
+        <v>2,3</v>
+      </c>
+      <c r="H113" t="s">
+        <v>983</v>
+      </c>
+      <c r="J113" t="str">
+        <f t="shared" si="2"/>
+        <v>DslPrtcltFltrActvRgnrtionStatus;</v>
+      </c>
+    </row>
+    <row r="114" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B114" t="s">
+        <v>888</v>
+      </c>
+      <c r="C114" s="33" t="s">
+        <v>1092</v>
+      </c>
+      <c r="D114" s="26">
+        <v>1</v>
+      </c>
+      <c r="E114" s="26" t="s">
+        <v>1182</v>
+      </c>
+      <c r="F114" s="26">
+        <v>4</v>
+      </c>
+      <c r="G114" s="26" t="str">
+        <f t="shared" si="3"/>
+        <v>2,5</v>
+      </c>
+      <c r="H114" t="s">
+        <v>983</v>
+      </c>
+      <c r="J114" t="str">
+        <f t="shared" si="2"/>
+        <v>DieselParticulateFilterStatus;</v>
+      </c>
+    </row>
+    <row r="115" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B115" t="s">
+        <v>888</v>
+      </c>
+      <c r="C115" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D115" s="26">
+        <v>2</v>
+      </c>
+      <c r="E115" s="26" t="s">
+        <v>1180</v>
+      </c>
+      <c r="F115" s="26">
+        <v>0</v>
+      </c>
+      <c r="G115" s="26" t="str">
+        <f t="shared" si="3"/>
+        <v>3,1</v>
+      </c>
+      <c r="H115" t="s">
+        <v>983</v>
+      </c>
+      <c r="J115" t="str">
+        <f t="shared" si="2"/>
+        <v>DslPrtcltFltrActvRgnrtnInhbtdStt;</v>
+      </c>
+    </row>
+    <row r="116" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B116" t="s">
+        <v>888</v>
+      </c>
+      <c r="C116" s="33" t="s">
+        <v>1094</v>
+      </c>
+      <c r="D116" s="26">
+        <v>2</v>
+      </c>
+      <c r="E116" s="26" t="s">
+        <v>1181</v>
+      </c>
+      <c r="F116" s="26">
+        <v>2</v>
+      </c>
+      <c r="G116" s="26" t="str">
+        <f t="shared" si="3"/>
+        <v>3,3</v>
+      </c>
+      <c r="H116" t="s">
+        <v>983</v>
+      </c>
+      <c r="J116" t="str">
+        <f t="shared" si="2"/>
+        <v>DslPrtcltFltrActvRgnrtnInhbtdDTI;</v>
+      </c>
+    </row>
+    <row r="117" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B117" t="s">
+        <v>888</v>
+      </c>
+      <c r="C117" t="s">
+        <v>1095</v>
+      </c>
+      <c r="D117" s="26">
+        <v>2</v>
+      </c>
+      <c r="E117" s="26" t="s">
+        <v>1183</v>
+      </c>
+      <c r="F117" s="26">
+        <v>4</v>
+      </c>
+      <c r="G117" s="26" t="str">
+        <f t="shared" si="3"/>
+        <v>3,5</v>
+      </c>
+      <c r="H117" t="s">
+        <v>983</v>
+      </c>
+      <c r="J117" t="str">
+        <f t="shared" si="2"/>
+        <v>DslPrtcltFltrActvRgnrtnInhbtdDTC;</v>
+      </c>
+    </row>
+    <row r="118" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B118" t="s">
+        <v>888</v>
+      </c>
+      <c r="C118" t="s">
+        <v>1096</v>
+      </c>
+      <c r="D118" s="26">
+        <v>2</v>
+      </c>
+      <c r="E118" s="26" t="s">
+        <v>1184</v>
+      </c>
+      <c r="F118" s="26">
+        <v>6</v>
+      </c>
+      <c r="G118" s="26" t="str">
+        <f t="shared" si="3"/>
+        <v>3,7</v>
+      </c>
+      <c r="H118" t="s">
+        <v>983</v>
+      </c>
+      <c r="J118" t="str">
+        <f t="shared" si="2"/>
+        <v>DslPrtcltFltrActvRgnrtnInhb_0004;</v>
+      </c>
+    </row>
+    <row r="119" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B119" t="s">
+        <v>888</v>
+      </c>
+      <c r="C119" t="s">
+        <v>1097</v>
+      </c>
+      <c r="D119" s="26">
+        <v>3</v>
+      </c>
+      <c r="E119" s="26" t="s">
+        <v>1180</v>
+      </c>
+      <c r="F119" s="26">
+        <v>0</v>
+      </c>
+      <c r="G119" s="26" t="str">
+        <f t="shared" si="3"/>
+        <v>4,1</v>
+      </c>
+      <c r="H119" t="s">
+        <v>983</v>
+      </c>
+      <c r="J119" t="str">
+        <f t="shared" si="2"/>
+        <v>DslPrtcltFltrActvRgnrtnInhb_0003;</v>
+      </c>
+    </row>
+    <row r="120" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B120" t="s">
+        <v>888</v>
+      </c>
+      <c r="C120" t="s">
+        <v>1098</v>
+      </c>
+      <c r="D120" s="26">
+        <v>3</v>
+      </c>
+      <c r="E120" s="26" t="s">
+        <v>1181</v>
+      </c>
+      <c r="F120" s="26">
+        <v>2</v>
+      </c>
+      <c r="G120" s="26" t="str">
+        <f t="shared" si="3"/>
+        <v>4,3</v>
+      </c>
+      <c r="H120" t="s">
+        <v>983</v>
+      </c>
+      <c r="J120" t="str">
+        <f t="shared" si="2"/>
+        <v>DslPrtcltFltrActvRgnrtnInhbtdDTA;</v>
+      </c>
+    </row>
+    <row r="121" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B121" t="s">
+        <v>888</v>
+      </c>
+      <c r="C121" t="s">
+        <v>1099</v>
+      </c>
+      <c r="D121" s="26">
+        <v>3</v>
+      </c>
+      <c r="E121" s="26" t="s">
+        <v>1183</v>
+      </c>
+      <c r="F121" s="26">
+        <v>4</v>
+      </c>
+      <c r="G121" s="26" t="str">
+        <f t="shared" si="3"/>
+        <v>4,5</v>
+      </c>
+      <c r="H121" t="s">
+        <v>983</v>
+      </c>
+      <c r="J121" t="str">
+        <f t="shared" si="2"/>
+        <v>DslPrtcltFltrActvRgnrtnInhbtdDTO;</v>
+      </c>
+    </row>
+    <row r="122" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B122" t="s">
+        <v>888</v>
+      </c>
+      <c r="C122" t="s">
+        <v>1100</v>
+      </c>
+      <c r="D122" s="26">
+        <v>3</v>
+      </c>
+      <c r="E122" s="26" t="s">
+        <v>1184</v>
+      </c>
+      <c r="F122" s="26">
+        <v>6</v>
+      </c>
+      <c r="G122" s="26" t="str">
+        <f t="shared" si="3"/>
+        <v>4,7</v>
+      </c>
+      <c r="H122" t="s">
+        <v>983</v>
+      </c>
+      <c r="J122" t="str">
+        <f t="shared" si="2"/>
+        <v>DslPrtcltFltrActvRgnrtnInhb_0002;</v>
+      </c>
+    </row>
+    <row r="123" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B123" t="s">
+        <v>888</v>
+      </c>
+      <c r="C123" t="s">
+        <v>1101</v>
+      </c>
+      <c r="D123" s="26">
+        <v>4</v>
+      </c>
+      <c r="E123" s="26" t="s">
+        <v>1180</v>
+      </c>
+      <c r="F123" s="26">
+        <v>0</v>
+      </c>
+      <c r="G123" s="26" t="str">
+        <f t="shared" si="3"/>
+        <v>5,1</v>
+      </c>
+      <c r="H123" t="s">
+        <v>983</v>
+      </c>
+      <c r="J123" t="str">
+        <f t="shared" si="2"/>
+        <v>DslPrtcltFltrActvRgnrtnInhb_0001;</v>
+      </c>
+    </row>
+    <row r="124" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B124" t="s">
+        <v>888</v>
+      </c>
+      <c r="C124" t="s">
+        <v>1102</v>
+      </c>
+      <c r="D124" s="26">
+        <v>4</v>
+      </c>
+      <c r="E124" s="26" t="s">
+        <v>1181</v>
+      </c>
+      <c r="F124" s="26">
+        <v>2</v>
+      </c>
+      <c r="G124" s="26" t="str">
+        <f t="shared" si="3"/>
+        <v>5,3</v>
+      </c>
+      <c r="H124" t="s">
+        <v>983</v>
+      </c>
+      <c r="J124" t="str">
+        <f t="shared" si="2"/>
+        <v>DslPrtcltFltrActvRgnrtnInhbtdDTL;</v>
+      </c>
+    </row>
+    <row r="125" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B125" t="s">
+        <v>888</v>
+      </c>
+      <c r="C125" t="s">
+        <v>1103</v>
+      </c>
+      <c r="D125" s="26">
+        <v>4</v>
+      </c>
+      <c r="E125" s="26" t="s">
+        <v>1183</v>
+      </c>
+      <c r="F125" s="26">
+        <v>4</v>
+      </c>
+      <c r="G125" s="26" t="str">
+        <f t="shared" si="3"/>
+        <v>5,5</v>
+      </c>
+      <c r="H125" t="s">
+        <v>983</v>
+      </c>
+      <c r="J125" t="str">
+        <f t="shared" si="2"/>
+        <v>DslPrtcltFltrActvRgnrtnInhb_0000;</v>
+      </c>
+    </row>
+    <row r="126" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B126" t="s">
+        <v>888</v>
+      </c>
+      <c r="C126" t="s">
+        <v>1104</v>
+      </c>
+      <c r="D126" s="26">
+        <v>4</v>
+      </c>
+      <c r="E126" s="26" t="s">
+        <v>1184</v>
+      </c>
+      <c r="F126" s="26">
+        <v>6</v>
+      </c>
+      <c r="G126" s="26" t="str">
+        <f t="shared" si="3"/>
+        <v>5,7</v>
+      </c>
+      <c r="H126" t="s">
+        <v>983</v>
+      </c>
+      <c r="J126" t="str">
+        <f t="shared" si="2"/>
+        <v>DslPrtcltFltrActvRgnrtnInhbtdDTS;</v>
+      </c>
+    </row>
+    <row r="127" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B127" t="s">
+        <v>888</v>
+      </c>
+      <c r="C127" s="33" t="s">
+        <v>1105</v>
+      </c>
+      <c r="D127" s="26">
+        <v>5</v>
+      </c>
+      <c r="E127" s="26" t="s">
+        <v>1180</v>
+      </c>
+      <c r="F127" s="26">
+        <v>0</v>
+      </c>
+      <c r="G127" s="26" t="str">
+        <f t="shared" si="3"/>
+        <v>6,1</v>
+      </c>
+      <c r="H127" t="s">
+        <v>983</v>
+      </c>
+      <c r="J127" t="str">
+        <f t="shared" si="2"/>
+        <v>DslPrtcltFltrActvRgnrtnInhbtdDTT;</v>
+      </c>
+    </row>
+    <row r="128" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B128" t="s">
+        <v>888</v>
+      </c>
+      <c r="C128" s="33" t="s">
+        <v>1106</v>
+      </c>
+      <c r="D128" s="26">
+        <v>5</v>
+      </c>
+      <c r="E128" s="26" t="s">
+        <v>1181</v>
+      </c>
+      <c r="F128" s="26">
+        <v>2</v>
+      </c>
+      <c r="G128" s="26" t="str">
+        <f t="shared" si="3"/>
+        <v>6,3</v>
+      </c>
+      <c r="H128" t="s">
+        <v>983</v>
+      </c>
+      <c r="J128" t="str">
+        <f t="shared" si="2"/>
+        <v>DslPrtcltFltrActvRgnrtnInhbtdDTP;</v>
+      </c>
+    </row>
+    <row r="129" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B129" t="s">
+        <v>888</v>
+      </c>
+      <c r="C129" t="s">
+        <v>1107</v>
+      </c>
+      <c r="D129" s="26">
+        <v>5</v>
+      </c>
+      <c r="E129" s="26" t="s">
+        <v>1183</v>
+      </c>
+      <c r="F129" s="26">
+        <v>4</v>
+      </c>
+      <c r="G129" s="26" t="str">
+        <f t="shared" si="3"/>
+        <v>6,5</v>
+      </c>
+      <c r="H129" t="s">
+        <v>983</v>
+      </c>
+      <c r="J129" t="str">
+        <f t="shared" si="2"/>
+        <v>DslPrtcltFltrActvRgnrtnInhbtdDTE;</v>
+      </c>
+    </row>
+    <row r="130" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B130" t="s">
+        <v>888</v>
+      </c>
+      <c r="C130" t="s">
+        <v>1108</v>
+      </c>
+      <c r="D130" s="26">
+        <v>5</v>
+      </c>
+      <c r="E130" s="26" t="s">
+        <v>1184</v>
+      </c>
+      <c r="F130" s="26">
+        <v>6</v>
+      </c>
+      <c r="G130" s="26" t="str">
+        <f t="shared" si="3"/>
+        <v>6,7</v>
+      </c>
+      <c r="H130" t="s">
+        <v>983</v>
+      </c>
+      <c r="J130" t="str">
+        <f t="shared" si="2"/>
+        <v>DslPrtcltFltrActvRgnrtnInhbtdDTV;</v>
+      </c>
+    </row>
+    <row r="131" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B131" t="s">
+        <v>888</v>
+      </c>
+      <c r="C131" t="s">
+        <v>1109</v>
+      </c>
+      <c r="D131" s="26">
+        <v>6</v>
+      </c>
+      <c r="E131" s="26" t="s">
+        <v>1180</v>
+      </c>
+      <c r="F131" s="26">
+        <v>0</v>
+      </c>
+      <c r="G131" s="26" t="str">
+        <f t="shared" si="3"/>
+        <v>7,1</v>
+      </c>
+      <c r="H131" t="s">
+        <v>983</v>
+      </c>
+      <c r="J131" t="str">
+        <f t="shared" si="2"/>
+        <v>DslPrtcltFltrAtmtcActvRgnrtnIntt;</v>
+      </c>
+    </row>
+    <row r="132" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B132" t="s">
+        <v>888</v>
+      </c>
+      <c r="C132" t="s">
+        <v>1110</v>
+      </c>
+      <c r="D132" s="26">
+        <v>6</v>
+      </c>
+      <c r="E132" s="26" t="s">
+        <v>1185</v>
+      </c>
+      <c r="F132" s="26">
+        <v>2</v>
+      </c>
+      <c r="G132" s="26" t="str">
+        <f t="shared" si="3"/>
+        <v>7,3</v>
+      </c>
+      <c r="H132" t="s">
+        <v>983</v>
+      </c>
+      <c r="J132" t="str">
+        <f t="shared" ref="J132:J195" si="4">IF(C132&lt;&gt;"",_xlfn.CONCAT(C132,";"),"")</f>
+        <v>ExhaustSystemHighTempLampCmd;</v>
+      </c>
+    </row>
+    <row r="133" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B133" t="s">
+        <v>888</v>
+      </c>
+      <c r="C133" t="s">
+        <v>1111</v>
+      </c>
+      <c r="D133" s="26">
+        <v>6</v>
+      </c>
+      <c r="E133" s="26" t="s">
+        <v>1186</v>
+      </c>
+      <c r="F133" s="26">
+        <v>5</v>
+      </c>
+      <c r="G133" s="26" t="str">
+        <f t="shared" si="3"/>
+        <v>7,6</v>
+      </c>
+      <c r="H133" t="s">
+        <v>983</v>
+      </c>
+      <c r="J133" t="str">
+        <f t="shared" si="4"/>
+        <v>DslPrtcltFltrActvRgnrtnFrcdStts;</v>
+      </c>
+    </row>
+    <row r="134" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J134" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="135" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B135" t="s">
+        <v>935</v>
+      </c>
+      <c r="C135" t="s">
+        <v>1112</v>
+      </c>
+      <c r="H135" t="s">
+        <v>984</v>
+      </c>
+      <c r="J135" t="str">
+        <f t="shared" si="4"/>
+        <v>Aftertreatment1ExhaustGasTemp1;</v>
+      </c>
+    </row>
+    <row r="136" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B136" t="s">
+        <v>935</v>
+      </c>
+      <c r="C136" t="s">
+        <v>1113</v>
+      </c>
+      <c r="H136" t="s">
+        <v>984</v>
+      </c>
+      <c r="J136" t="str">
+        <f t="shared" si="4"/>
+        <v>Aftrtrtmnt1DslPrtcltFltrInt_0000;</v>
+      </c>
+    </row>
+    <row r="137" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B137" t="s">
+        <v>935</v>
+      </c>
+      <c r="C137" t="s">
+        <v>1114</v>
+      </c>
+      <c r="H137" t="s">
+        <v>983</v>
+      </c>
+      <c r="J137" t="str">
+        <f t="shared" si="4"/>
+        <v>Aftrtrtmnt1ExhstGsTmp1PrlmnryFMI;</v>
+      </c>
+    </row>
+    <row r="138" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B138" t="s">
+        <v>935</v>
+      </c>
+      <c r="C138" t="s">
+        <v>1115</v>
+      </c>
+      <c r="H138" t="s">
+        <v>983</v>
+      </c>
+      <c r="J138" t="str">
+        <f t="shared" si="4"/>
+        <v>Aftrtrtmnt1DslPrtcltFltrIntkGsTm;</v>
+      </c>
+    </row>
+    <row r="139" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J139" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="140" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B140" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C140" t="s">
+        <v>1116</v>
+      </c>
+      <c r="H140" t="s">
+        <v>984</v>
+      </c>
+      <c r="J140" t="str">
+        <f t="shared" si="4"/>
+        <v>Aftrtrtmnt1SCRCatalystTankLevel;</v>
+      </c>
+    </row>
+    <row r="141" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B141" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C141" t="s">
+        <v>1117</v>
+      </c>
+      <c r="H141" t="s">
+        <v>985</v>
+      </c>
+      <c r="J141" t="str">
+        <f t="shared" si="4"/>
+        <v>Aftrtrtment1SCRCatalystTankTemp;</v>
+      </c>
+    </row>
+    <row r="142" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B142" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C142" t="s">
+        <v>1118</v>
+      </c>
+      <c r="H142" t="s">
+        <v>984</v>
+      </c>
+      <c r="J142" t="str">
+        <f t="shared" si="4"/>
+        <v>Aftrtrtmnt1SCRCtalystTankLevel2;</v>
+      </c>
+    </row>
+    <row r="143" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B143" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C143" t="s">
+        <v>1119</v>
+      </c>
+      <c r="H143" t="s">
+        <v>983</v>
+      </c>
+      <c r="J143" t="str">
+        <f t="shared" si="4"/>
+        <v>Aftrtrtmnt1SCRCtlystTnkLvlPrlmnr;</v>
+      </c>
+    </row>
+    <row r="144" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B144" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C144" t="s">
+        <v>1120</v>
+      </c>
+      <c r="H144" t="s">
+        <v>983</v>
+      </c>
+      <c r="J144" t="str">
+        <f t="shared" si="4"/>
+        <v>Aftrtrtmnt1DEFTnkLwLvlIndicator;</v>
+      </c>
+    </row>
+    <row r="145" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B145" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C145" t="s">
+        <v>1121</v>
+      </c>
+      <c r="H145" t="s">
+        <v>983</v>
+      </c>
+      <c r="J145" t="str">
+        <f t="shared" si="4"/>
+        <v>Aftrtrtmnt1SCRCtlystRgntTnk1TmpP;</v>
+      </c>
+    </row>
+    <row r="146" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B146" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C146" t="s">
+        <v>1122</v>
+      </c>
+      <c r="H146" t="s">
+        <v>983</v>
+      </c>
+      <c r="J146" t="str">
+        <f t="shared" si="4"/>
+        <v>AftrtrtmntSCROprtrIndcmntSvrity;</v>
+      </c>
+    </row>
+    <row r="147" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B147" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C147" t="s">
+        <v>1123</v>
+      </c>
+      <c r="H147" t="s">
+        <v>984</v>
+      </c>
+      <c r="J147" t="str">
+        <f t="shared" si="4"/>
+        <v>Aftrtrtmnt1SCRCtalystTankHeater;</v>
+      </c>
+    </row>
+    <row r="148" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B148" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C148" t="s">
+        <v>1124</v>
+      </c>
+      <c r="H148" t="s">
+        <v>983</v>
+      </c>
+      <c r="J148" t="str">
+        <f t="shared" si="4"/>
+        <v>Aftrtrtmnt1SCRCtlystRgntTnk1HtrP;</v>
+      </c>
+    </row>
+    <row r="149" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B149" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C149" t="s">
+        <v>1125</v>
+      </c>
+      <c r="H149" t="s">
+        <v>984</v>
+      </c>
+      <c r="J149" t="str">
+        <f t="shared" si="4"/>
+        <v>Aftrtrtmnt1SCRCatalystTankLevel_1;</v>
+      </c>
+    </row>
+    <row r="150" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B150" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C150" t="s">
+        <v>1126</v>
+      </c>
+      <c r="H150" t="s">
+        <v>985</v>
+      </c>
+      <c r="J150" t="str">
+        <f t="shared" si="4"/>
+        <v>Aftrtrtment1SCRCatalystTankTemp_1;</v>
+      </c>
+    </row>
+    <row r="151" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B151" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C151" t="s">
+        <v>1127</v>
+      </c>
+      <c r="H151" t="s">
+        <v>984</v>
+      </c>
+      <c r="J151" t="str">
+        <f t="shared" si="4"/>
+        <v>Aftrtrtmnt1SCRCtalystTankLevel2_1;</v>
+      </c>
+    </row>
+    <row r="152" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B152" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C152" t="s">
+        <v>1128</v>
+      </c>
+      <c r="H152" t="s">
+        <v>983</v>
+      </c>
+      <c r="J152" t="str">
+        <f t="shared" si="4"/>
+        <v>Aftrtrtmnt1SCRCtlystTnkLvlPrlmnr_1;</v>
+      </c>
+    </row>
+    <row r="153" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B153" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C153" t="s">
+        <v>1129</v>
+      </c>
+      <c r="H153" t="s">
+        <v>983</v>
+      </c>
+      <c r="J153" t="str">
+        <f t="shared" si="4"/>
+        <v>Aftrtrtmnt1DEFTnkLwLvlIndicator_1;</v>
+      </c>
+    </row>
+    <row r="154" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B154" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C154" t="s">
+        <v>1130</v>
+      </c>
+      <c r="H154" t="s">
+        <v>983</v>
+      </c>
+      <c r="J154" t="str">
+        <f t="shared" si="4"/>
+        <v>Aftrtrtmnt1SCRCtlystRgntTnk1TmpP_1;</v>
+      </c>
+    </row>
+    <row r="155" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B155" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C155" t="s">
+        <v>1131</v>
+      </c>
+      <c r="H155" t="s">
+        <v>983</v>
+      </c>
+      <c r="J155" t="str">
+        <f t="shared" si="4"/>
+        <v>AftrtrtmntSCROprtrIndcmntSvrity_1;</v>
+      </c>
+    </row>
+    <row r="156" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B156" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C156" t="s">
+        <v>1132</v>
+      </c>
+      <c r="H156" t="s">
+        <v>984</v>
+      </c>
+      <c r="J156" t="str">
+        <f t="shared" si="4"/>
+        <v>Aftrtrtmnt1SCRCtalystTankHeater_1;</v>
+      </c>
+    </row>
+    <row r="157" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B157" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C157" t="s">
+        <v>1133</v>
+      </c>
+      <c r="H157" t="s">
+        <v>983</v>
+      </c>
+      <c r="J157" t="str">
+        <f t="shared" si="4"/>
+        <v>Aftrtrtmnt1SCRCtlystRgntTnk1HtrP_1;</v>
+      </c>
+    </row>
+    <row r="158" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J158" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="159" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B159" t="s">
+        <v>940</v>
+      </c>
+      <c r="C159" t="s">
+        <v>1135</v>
+      </c>
+      <c r="H159" t="s">
+        <v>984</v>
+      </c>
+      <c r="J159" t="str">
+        <f t="shared" si="4"/>
+        <v>Aftrtrtmnt1SCRActlDsngRgntQntty;</v>
+      </c>
+    </row>
+    <row r="160" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B160" t="s">
+        <v>940</v>
+      </c>
+      <c r="C160" t="s">
+        <v>1136</v>
+      </c>
+      <c r="H160" t="s">
+        <v>983</v>
+      </c>
+      <c r="J160" t="str">
+        <f t="shared" si="4"/>
+        <v>Aftertreatment1SCRSystemState;</v>
+      </c>
+    </row>
+    <row r="161" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B161" t="s">
+        <v>940</v>
+      </c>
+      <c r="C161" t="s">
+        <v>1137</v>
+      </c>
+      <c r="H161" t="s">
+        <v>984</v>
+      </c>
+      <c r="J161" t="str">
+        <f t="shared" si="4"/>
+        <v>Aftrtrtmnt1SCRActlRgntQnttyOfInt;</v>
+      </c>
+    </row>
+    <row r="162" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B162" t="s">
+        <v>940</v>
+      </c>
+      <c r="C162" t="s">
+        <v>1138</v>
+      </c>
+      <c r="H162" t="s">
+        <v>1051</v>
+      </c>
+      <c r="J162" t="str">
+        <f t="shared" si="4"/>
+        <v>Aftrtrtmnt1SCRDsngRgentAbsPress;</v>
+      </c>
+    </row>
+    <row r="163" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J163" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="164" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B164" t="s">
+        <v>1139</v>
+      </c>
+      <c r="C164" t="s">
+        <v>1140</v>
+      </c>
+      <c r="H164" t="s">
+        <v>984</v>
+      </c>
+      <c r="J164" t="str">
+        <f t="shared" si="4"/>
+        <v>Aftrtrtmnt1SCRCtlystIntkGasTemp;</v>
+      </c>
+    </row>
+    <row r="165" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B165" t="s">
+        <v>1139</v>
+      </c>
+      <c r="C165" t="s">
+        <v>1141</v>
+      </c>
+      <c r="H165" t="s">
+        <v>983</v>
+      </c>
+      <c r="J165" t="str">
+        <f t="shared" si="4"/>
+        <v>Aftrtrtmnt1SCRCtlystIntkGsTmpPrl;</v>
+      </c>
+    </row>
+    <row r="166" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B166" t="s">
+        <v>1139</v>
+      </c>
+      <c r="C166" t="s">
+        <v>1142</v>
+      </c>
+      <c r="H166" t="s">
+        <v>984</v>
+      </c>
+      <c r="J166" t="str">
+        <f t="shared" si="4"/>
+        <v>Aftrtrtmnt1SCRCtlystOtltGasTemp;</v>
+      </c>
+    </row>
+    <row r="167" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B167" t="s">
+        <v>1139</v>
+      </c>
+      <c r="C167" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H167" t="s">
+        <v>983</v>
+      </c>
+      <c r="J167" t="str">
+        <f t="shared" si="4"/>
+        <v>Aftrtrtmnt1SCRCtlystOtltGsTmpPrl;</v>
+      </c>
+    </row>
+    <row r="168" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J168" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="169" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B169" t="s">
+        <v>950</v>
+      </c>
+      <c r="C169" t="s">
+        <v>1144</v>
+      </c>
+      <c r="H169" t="s">
+        <v>984</v>
+      </c>
+      <c r="J169" t="str">
+        <f t="shared" si="4"/>
+        <v>Aftrtrtmnt1DslOxdtnCtlystIn_0000;</v>
+      </c>
+    </row>
+    <row r="170" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B170" t="s">
+        <v>950</v>
+      </c>
+      <c r="C170" t="s">
+        <v>1145</v>
+      </c>
+      <c r="H170" t="s">
+        <v>984</v>
+      </c>
+      <c r="J170" t="str">
+        <f t="shared" si="4"/>
+        <v>Aftrtrtmnt1DslOxdtnCtlystOt_0000;</v>
+      </c>
+    </row>
+    <row r="171" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B171" t="s">
+        <v>950</v>
+      </c>
+      <c r="C171" t="s">
+        <v>1146</v>
+      </c>
+      <c r="H171" t="s">
+        <v>984</v>
+      </c>
+      <c r="J171" t="str">
+        <f t="shared" si="4"/>
+        <v>Aftrtrtmnt1DslOxdtnCtlystDffPrss;</v>
+      </c>
+    </row>
+    <row r="172" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B172" t="s">
+        <v>950</v>
+      </c>
+      <c r="C172" t="s">
+        <v>1147</v>
+      </c>
+      <c r="H172" t="s">
+        <v>983</v>
+      </c>
+      <c r="J172" t="str">
+        <f t="shared" si="4"/>
+        <v>Aftrtrtmnt1DslOxdtnCtlystIntkGsT;</v>
+      </c>
+    </row>
+    <row r="173" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B173" t="s">
+        <v>950</v>
+      </c>
+      <c r="C173" t="s">
+        <v>1148</v>
+      </c>
+      <c r="H173" t="s">
+        <v>983</v>
+      </c>
+      <c r="J173" t="str">
+        <f t="shared" si="4"/>
+        <v>Aftrtrtmnt1DslOxdtnCtlystOtltGsT;</v>
+      </c>
+    </row>
+    <row r="174" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B174" t="s">
+        <v>950</v>
+      </c>
+      <c r="C174" t="s">
+        <v>1149</v>
+      </c>
+      <c r="H174" t="s">
+        <v>983</v>
+      </c>
+      <c r="J174" t="str">
+        <f t="shared" si="4"/>
+        <v>Aftrtrtmnt1DslOxdtnCtlystDf_0000;</v>
+      </c>
+    </row>
+    <row r="175" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J175" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="176" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B176" t="s">
+        <v>1150</v>
+      </c>
+      <c r="C176" t="s">
+        <v>1151</v>
+      </c>
+      <c r="H176" t="s">
+        <v>983</v>
+      </c>
+      <c r="J176" t="str">
+        <f t="shared" si="4"/>
+        <v>WaterInFuelIndicator;</v>
+      </c>
+    </row>
+    <row r="177" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J177" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="178" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B178" t="s">
+        <v>961</v>
+      </c>
+      <c r="C178" t="s">
+        <v>1152</v>
+      </c>
+      <c r="H178" t="s">
+        <v>983</v>
+      </c>
+      <c r="I178">
+        <v>1</v>
+      </c>
+      <c r="J178" t="str">
+        <f t="shared" si="4"/>
+        <v>EngProtectLampCmd;</v>
+      </c>
+    </row>
+    <row r="179" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B179" t="s">
+        <v>961</v>
+      </c>
+      <c r="C179" t="s">
+        <v>1153</v>
+      </c>
+      <c r="H179" t="s">
+        <v>983</v>
+      </c>
+      <c r="I179">
+        <v>2</v>
+      </c>
+      <c r="J179" t="str">
+        <f t="shared" si="4"/>
+        <v>EngAmberWarningLampCmd;</v>
+      </c>
+    </row>
+    <row r="180" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B180" t="s">
+        <v>961</v>
+      </c>
+      <c r="C180" t="s">
+        <v>1154</v>
+      </c>
+      <c r="H180" t="s">
+        <v>983</v>
+      </c>
+      <c r="I180">
+        <v>3</v>
+      </c>
+      <c r="J180" t="str">
+        <f t="shared" si="4"/>
+        <v>EngRedStopLampCmd;</v>
+      </c>
+    </row>
+    <row r="181" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B181" t="s">
+        <v>961</v>
+      </c>
+      <c r="C181" t="s">
+        <v>1155</v>
+      </c>
+      <c r="H181" t="s">
+        <v>983</v>
+      </c>
+      <c r="I181">
+        <v>4</v>
+      </c>
+      <c r="J181" t="str">
+        <f t="shared" si="4"/>
+        <v>OBDMalfunctionIndicatorLampCmd;</v>
+      </c>
+    </row>
+    <row r="182" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B182" t="s">
+        <v>961</v>
+      </c>
+      <c r="C182" t="s">
+        <v>1156</v>
+      </c>
+      <c r="H182" t="s">
+        <v>983</v>
+      </c>
+      <c r="I182">
+        <v>5</v>
+      </c>
+      <c r="J182" t="str">
+        <f t="shared" si="4"/>
+        <v>EngBrakeActiveLampCmd;</v>
+      </c>
+    </row>
+    <row r="183" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B183" t="s">
+        <v>961</v>
+      </c>
+      <c r="C183" t="s">
+        <v>1157</v>
+      </c>
+      <c r="H183" t="s">
+        <v>983</v>
+      </c>
+      <c r="I183">
+        <v>6</v>
+      </c>
+      <c r="J183" t="str">
+        <f t="shared" si="4"/>
+        <v>CmprssnBrkEnblSwtchIndctrLmpCmd;</v>
+      </c>
+    </row>
+    <row r="184" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B184" t="s">
+        <v>961</v>
+      </c>
+      <c r="C184" t="s">
+        <v>1158</v>
+      </c>
+      <c r="H184" t="s">
+        <v>983</v>
+      </c>
+      <c r="I184">
+        <v>7</v>
+      </c>
+      <c r="J184" t="str">
+        <f t="shared" si="4"/>
+        <v>EngOilPressLowLampCmd;</v>
+      </c>
+    </row>
+    <row r="185" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B185" t="s">
+        <v>961</v>
+      </c>
+      <c r="C185" t="s">
+        <v>1159</v>
+      </c>
+      <c r="H185" t="s">
+        <v>983</v>
+      </c>
+      <c r="I185">
+        <v>8</v>
+      </c>
+      <c r="J185" t="str">
+        <f t="shared" si="4"/>
+        <v>EngCoolantTempHighLampCmd;</v>
+      </c>
+    </row>
+    <row r="186" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B186" t="s">
+        <v>961</v>
+      </c>
+      <c r="C186" t="s">
+        <v>1160</v>
+      </c>
+      <c r="H186" t="s">
+        <v>983</v>
+      </c>
+      <c r="I186">
+        <v>9</v>
+      </c>
+      <c r="J186" t="str">
+        <f t="shared" si="4"/>
+        <v>EngCoolantLevelLowLampCmd;</v>
+      </c>
+    </row>
+    <row r="187" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B187" t="s">
+        <v>961</v>
+      </c>
+      <c r="C187" t="s">
+        <v>1161</v>
+      </c>
+      <c r="H187" t="s">
+        <v>983</v>
+      </c>
+      <c r="I187">
+        <v>10</v>
+      </c>
+      <c r="J187" t="str">
+        <f t="shared" si="4"/>
+        <v>EngIdleManagementActiveLampCmd;</v>
+      </c>
+    </row>
+    <row r="188" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B188" t="s">
+        <v>961</v>
+      </c>
+      <c r="C188" t="s">
+        <v>1162</v>
+      </c>
+      <c r="H188" t="s">
+        <v>983</v>
+      </c>
+      <c r="I188">
+        <v>11</v>
+      </c>
+      <c r="J188" t="str">
+        <f t="shared" si="4"/>
+        <v>EngAirFilterRestrictionLampCmd;</v>
+      </c>
+    </row>
+    <row r="189" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B189" t="s">
+        <v>961</v>
+      </c>
+      <c r="C189" t="s">
+        <v>1163</v>
+      </c>
+      <c r="H189" t="s">
+        <v>983</v>
+      </c>
+      <c r="I189">
+        <v>12</v>
+      </c>
+      <c r="J189" t="str">
+        <f t="shared" si="4"/>
+        <v>EngFuelFilterRestrictedLampCmd;</v>
+      </c>
+    </row>
+    <row r="190" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J190" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="191" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B191" t="s">
+        <v>1164</v>
+      </c>
+      <c r="C191" t="s">
+        <v>1165</v>
+      </c>
+      <c r="H191" t="s">
+        <v>983</v>
+      </c>
+      <c r="I191">
+        <v>1</v>
+      </c>
+      <c r="J191" t="str">
+        <f t="shared" si="4"/>
+        <v>EngProtectLampData;</v>
+      </c>
+    </row>
+    <row r="192" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B192" t="s">
+        <v>1164</v>
+      </c>
+      <c r="C192" t="s">
+        <v>1166</v>
+      </c>
+      <c r="H192" t="s">
+        <v>983</v>
+      </c>
+      <c r="I192">
+        <v>2</v>
+      </c>
+      <c r="J192" t="str">
+        <f t="shared" si="4"/>
+        <v>EngAmberWarningLampData;</v>
+      </c>
+    </row>
+    <row r="193" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B193" t="s">
+        <v>1164</v>
+      </c>
+      <c r="C193" t="s">
+        <v>1167</v>
+      </c>
+      <c r="H193" t="s">
+        <v>983</v>
+      </c>
+      <c r="I193">
+        <v>3</v>
+      </c>
+      <c r="J193" t="str">
+        <f t="shared" si="4"/>
+        <v>EngRedStopLampData;</v>
+      </c>
+    </row>
+    <row r="194" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B194" t="s">
+        <v>1164</v>
+      </c>
+      <c r="C194" t="s">
+        <v>1168</v>
+      </c>
+      <c r="H194" t="s">
+        <v>983</v>
+      </c>
+      <c r="I194">
+        <v>4</v>
+      </c>
+      <c r="J194" t="str">
+        <f t="shared" si="4"/>
+        <v>OBDMalfunctionIndicatorLampData;</v>
+      </c>
+    </row>
+    <row r="195" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B195" t="s">
+        <v>1164</v>
+      </c>
+      <c r="C195" t="s">
+        <v>1169</v>
+      </c>
+      <c r="H195" t="s">
+        <v>983</v>
+      </c>
+      <c r="I195">
+        <v>5</v>
+      </c>
+      <c r="J195" t="str">
+        <f t="shared" si="4"/>
+        <v>EngBrakeActiveLampData;</v>
+      </c>
+    </row>
+    <row r="196" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B196" t="s">
+        <v>1164</v>
+      </c>
+      <c r="C196" t="s">
+        <v>1170</v>
+      </c>
+      <c r="H196" t="s">
+        <v>983</v>
+      </c>
+      <c r="I196">
+        <v>6</v>
+      </c>
+      <c r="J196" t="str">
+        <f t="shared" ref="J196:J203" si="5">IF(C196&lt;&gt;"",_xlfn.CONCAT(C196,";"),"")</f>
+        <v>CmprssnBrkEnblSwtchIndctrLmpDta;</v>
+      </c>
+    </row>
+    <row r="197" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B197" t="s">
+        <v>1164</v>
+      </c>
+      <c r="C197" t="s">
+        <v>1171</v>
+      </c>
+      <c r="H197" t="s">
+        <v>983</v>
+      </c>
+      <c r="I197">
+        <v>7</v>
+      </c>
+      <c r="J197" t="str">
+        <f t="shared" si="5"/>
+        <v>EngOilPressLowLampData;</v>
+      </c>
+    </row>
+    <row r="198" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B198" t="s">
+        <v>1164</v>
+      </c>
+      <c r="C198" t="s">
+        <v>1172</v>
+      </c>
+      <c r="H198" t="s">
+        <v>983</v>
+      </c>
+      <c r="I198">
+        <v>8</v>
+      </c>
+      <c r="J198" t="str">
+        <f t="shared" si="5"/>
+        <v>EngCoolantTempHighLampData;</v>
+      </c>
+    </row>
+    <row r="199" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B199" t="s">
+        <v>1164</v>
+      </c>
+      <c r="C199" t="s">
+        <v>1173</v>
+      </c>
+      <c r="H199" t="s">
+        <v>983</v>
+      </c>
+      <c r="I199">
+        <v>9</v>
+      </c>
+      <c r="J199" t="str">
+        <f t="shared" si="5"/>
+        <v>EngCoolantLevelLowLampData;</v>
+      </c>
+    </row>
+    <row r="200" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B200" t="s">
+        <v>1164</v>
+      </c>
+      <c r="C200" t="s">
+        <v>1174</v>
+      </c>
+      <c r="H200" t="s">
+        <v>983</v>
+      </c>
+      <c r="I200">
+        <v>10</v>
+      </c>
+      <c r="J200" t="str">
+        <f t="shared" si="5"/>
+        <v>EngIdleManagementActiveLampData;</v>
+      </c>
+    </row>
+    <row r="201" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B201" t="s">
+        <v>1164</v>
+      </c>
+      <c r="C201" t="s">
+        <v>1175</v>
+      </c>
+      <c r="H201" t="s">
+        <v>983</v>
+      </c>
+      <c r="I201">
+        <v>11</v>
+      </c>
+      <c r="J201" t="str">
+        <f t="shared" si="5"/>
+        <v>EngAirFilterRestrictionLampData;</v>
+      </c>
+    </row>
+    <row r="202" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B202" t="s">
+        <v>1164</v>
+      </c>
+      <c r="C202" t="s">
+        <v>1176</v>
+      </c>
+      <c r="H202" t="s">
+        <v>983</v>
+      </c>
+      <c r="I202">
+        <v>12</v>
+      </c>
+      <c r="J202" t="str">
+        <f t="shared" si="5"/>
+        <v>EngFuelFilterRestrictedLampData;</v>
+      </c>
+    </row>
+    <row r="203" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B203" t="s">
+        <v>1164</v>
+      </c>
+      <c r="C203" t="s">
+        <v>1177</v>
+      </c>
+      <c r="H203" t="s">
+        <v>983</v>
+      </c>
+      <c r="I203">
+        <v>13</v>
+      </c>
+      <c r="J203" t="str">
+        <f t="shared" si="5"/>
+        <v>EngWaitToStartLampData;</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c96d9849-7071-4555-8535-ee11c374d0f7">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3f324c86-ae15-4ed4-b4a2-09335a7d28ef" xsi:nil="true"/>
+    <SharedWithUsers xmlns="3f324c86-ae15-4ed4-b4a2-09335a7d28ef">
+      <UserInfo>
+        <DisplayName>Noel Loughran</DisplayName>
+        <AccountId>19</AccountId>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -25165,27 +28693,27 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c96d9849-7071-4555-8535-ee11c374d0f7">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3f324c86-ae15-4ed4-b4a2-09335a7d28ef" xsi:nil="true"/>
-    <SharedWithUsers xmlns="3f324c86-ae15-4ed4-b4a2-09335a7d28ef">
-      <UserInfo>
-        <DisplayName>Noel Loughran</DisplayName>
-        <AccountId>19</AccountId>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3E59E7C-5896-4162-AB70-9CA3CEB6A0FE}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7DE4EA8D-9182-4C6A-B31C-49373749A7AE}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="3f324c86-ae15-4ed4-b4a2-09335a7d28ef"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="c96d9849-7071-4555-8535-ee11c374d0f7"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -25210,18 +28738,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7DE4EA8D-9182-4C6A-B31C-49373749A7AE}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3E59E7C-5896-4162-AB70-9CA3CEB6A0FE}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="3f324c86-ae15-4ed4-b4a2-09335a7d28ef"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="c96d9849-7071-4555-8535-ee11c374d0f7"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/T620X_IO.xlsx
+++ b/T620X_IO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\dev_plc\MTech\MTech_T620X_Trommel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A85BE2FD-ADBE-493C-9E30-B61AFBF7D8BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF9BDA27-FBA0-4566-B69E-7507CE4F3C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="857" activeTab="7" xr2:uid="{2FCBBB71-3591-49CF-88C3-9E3184A7626E}"/>
+    <workbookView xWindow="38280" yWindow="5280" windowWidth="29040" windowHeight="15720" tabRatio="857" activeTab="8" xr2:uid="{2FCBBB71-3591-49CF-88C3-9E3184A7626E}"/>
   </bookViews>
   <sheets>
     <sheet name="IO" sheetId="11" r:id="rId1"/>
@@ -26,6 +26,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">ALARMS_IO!$A$1:$K$48</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">IO!$A$1:$AP$78</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">Sheet3!$A$1:$W$171</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">SNAGS!$A$1:$E$91</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
@@ -49,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3124" uniqueCount="1187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3139" uniqueCount="1182">
   <si>
     <t>PLC Name</t>
   </si>
@@ -3045,12 +3046,6 @@
     <t>MalfunctionIndicatorLampStatus</t>
   </si>
   <si>
-    <t>FlashProtectLamp</t>
-  </si>
-  <si>
-    <t>FlashAmberWarningLamp</t>
-  </si>
-  <si>
     <t>FlashRedStopLamp</t>
   </si>
   <si>
@@ -3426,33 +3421,6 @@
     <t>Aftrtrtmnt1SCRCtlystRgntTnk1HtrP</t>
   </si>
   <si>
-    <t>Aftrtrtmnt1SCRCatalystTankLevel_1</t>
-  </si>
-  <si>
-    <t>Aftrtrtment1SCRCatalystTankTemp_1</t>
-  </si>
-  <si>
-    <t>Aftrtrtmnt1SCRCtalystTankLevel2_1</t>
-  </si>
-  <si>
-    <t>Aftrtrtmnt1SCRCtlystTnkLvlPrlmnr_1</t>
-  </si>
-  <si>
-    <t>Aftrtrtmnt1DEFTnkLwLvlIndicator_1</t>
-  </si>
-  <si>
-    <t>Aftrtrtmnt1SCRCtlystRgntTnk1TmpP_1</t>
-  </si>
-  <si>
-    <t>AftrtrtmntSCROprtrIndcmntSvrity_1</t>
-  </si>
-  <si>
-    <t>Aftrtrtmnt1SCRCtalystTankHeater_1</t>
-  </si>
-  <si>
-    <t>Aftrtrtmnt1SCRCtlystRgntTnk1HtrP_1</t>
-  </si>
-  <si>
     <t>AT1T1I</t>
   </si>
   <si>
@@ -3610,6 +3578,24 @@
   </si>
   <si>
     <t>5,6,7</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>SPN</t>
+  </si>
+  <si>
+    <t>PGN</t>
+  </si>
+  <si>
+    <t>DATA</t>
+  </si>
+  <si>
+    <t>GVL_J1939.</t>
+  </si>
+  <si>
+    <t>C3.6</t>
   </si>
 </sst>
 </file>
@@ -3804,7 +3790,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3912,6 +3898,9 @@
     </xf>
     <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -25059,7 +25048,7 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>1178</v>
+        <v>1167</v>
       </c>
       <c r="D42" s="26">
         <v>61473</v>
@@ -25084,3389 +25073,6247 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67835F87-8E16-4012-B1FC-4AA8A57E1B78}">
-  <dimension ref="B3:S203"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:W171"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="12.85546875" customWidth="1"/>
+    <col min="2" max="2" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="35.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="2" style="26" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.140625" style="26" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.85546875" style="35" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="2" style="26" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.140625" style="26" customWidth="1"/>
-    <col min="10" max="10" width="43.28515625" customWidth="1"/>
-    <col min="11" max="11" width="38.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.140625" style="26" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="2" style="26" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.140625" style="26" customWidth="1"/>
+    <col min="12" max="12" width="43.28515625" customWidth="1"/>
+    <col min="13" max="13" width="50.28515625" customWidth="1"/>
+    <col min="14" max="14" width="44" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="49" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" s="27" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="27" t="s">
+        <v>1178</v>
+      </c>
+      <c r="D1" s="46" t="s">
+        <v>1177</v>
+      </c>
+      <c r="E1" s="27" t="s">
+        <v>1181</v>
+      </c>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="27" t="s">
+        <v>1179</v>
+      </c>
+      <c r="M1" s="27" t="s">
+        <v>1180</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>871</v>
+      </c>
+      <c r="C2" t="s">
+        <v>974</v>
+      </c>
+      <c r="J2" t="s">
+        <v>983</v>
+      </c>
+      <c r="L2" t="str">
+        <f>IF(C2&lt;&gt;"",_xlfn.CONCAT(B2,"_",C2),"")</f>
+        <v>TSC1_EngOverrideCtrlMode</v>
+      </c>
+      <c r="M2" t="str">
+        <f>_xlfn.CONCAT($M$1,L2)</f>
+        <v>GVL_J1939.TSC1_EngOverrideCtrlMode</v>
+      </c>
+      <c r="N2" t="str">
+        <f>_xlfn.CONCAT(M2,";")</f>
+        <v>GVL_J1939.TSC1_EngOverrideCtrlMode;</v>
+      </c>
+      <c r="O2" t="str">
+        <f>_xlfn.CONCAT(L2,":",J2,"; // SPN:",D2)</f>
+        <v>TSC1_EngOverrideCtrlMode:USINT; // SPN:</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
       <c r="B3" t="s">
         <v>871</v>
       </c>
       <c r="C3" t="s">
-        <v>974</v>
-      </c>
-      <c r="H3" t="s">
+        <v>973</v>
+      </c>
+      <c r="J3" t="s">
         <v>983</v>
       </c>
-      <c r="J3" t="str">
-        <f>IF(C3&lt;&gt;"",_xlfn.CONCAT(C3,";"),"")</f>
-        <v>EngOverrideCtrlMode;</v>
-      </c>
-      <c r="K3" t="str">
-        <f>_xlfn.CONCAT(B3,C3,":",H3,";")</f>
-        <v>TSC1EngOverrideCtrlMode:USINT;</v>
-      </c>
-    </row>
-    <row r="4" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="L3" t="str">
+        <f t="shared" ref="L3:L66" si="0">IF(C3&lt;&gt;"",_xlfn.CONCAT(B3,"_",C3),"")</f>
+        <v>TSC1_EngRqedSpeedCtrlConditions</v>
+      </c>
+      <c r="M3" t="str">
+        <f t="shared" ref="M3:M66" si="1">_xlfn.CONCAT($M$1,L3)</f>
+        <v>GVL_J1939.TSC1_EngRqedSpeedCtrlConditions</v>
+      </c>
+      <c r="N3" t="str">
+        <f t="shared" ref="N3:N66" si="2">_xlfn.CONCAT(M3,";")</f>
+        <v>GVL_J1939.TSC1_EngRqedSpeedCtrlConditions;</v>
+      </c>
+      <c r="O3" t="str">
+        <f t="shared" ref="O3:O66" si="3">_xlfn.CONCAT(L3,":",J3,"; // SPN:",D3)</f>
+        <v>TSC1_EngRqedSpeedCtrlConditions:USINT; // SPN:</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
       <c r="B4" t="s">
         <v>871</v>
       </c>
       <c r="C4" t="s">
-        <v>973</v>
-      </c>
-      <c r="H4" t="s">
+        <v>975</v>
+      </c>
+      <c r="J4" t="s">
         <v>983</v>
       </c>
-      <c r="J4" t="str">
-        <f t="shared" ref="J4:J67" si="0">IF(C4&lt;&gt;"",_xlfn.CONCAT(C4,";"),"")</f>
-        <v>EngRqedSpeedCtrlConditions;</v>
-      </c>
-      <c r="K4" t="str">
-        <f t="shared" ref="K4:K12" si="1">_xlfn.CONCAT(B4,C4,":",H4,";")</f>
-        <v>TSC1EngRqedSpeedCtrlConditions:USINT;</v>
-      </c>
-    </row>
-    <row r="5" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="L4" t="str">
+        <f t="shared" si="0"/>
+        <v>TSC1_OverrideCtrlModePriority</v>
+      </c>
+      <c r="M4" t="str">
+        <f t="shared" si="1"/>
+        <v>GVL_J1939.TSC1_OverrideCtrlModePriority</v>
+      </c>
+      <c r="N4" t="str">
+        <f t="shared" si="2"/>
+        <v>GVL_J1939.TSC1_OverrideCtrlModePriority;</v>
+      </c>
+      <c r="O4" t="str">
+        <f t="shared" si="3"/>
+        <v>TSC1_OverrideCtrlModePriority:USINT; // SPN:</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
       <c r="B5" t="s">
         <v>871</v>
       </c>
       <c r="C5" t="s">
-        <v>975</v>
-      </c>
-      <c r="H5" t="s">
-        <v>983</v>
-      </c>
-      <c r="J5" t="str">
+        <v>976</v>
+      </c>
+      <c r="J5" t="s">
+        <v>984</v>
+      </c>
+      <c r="L5" t="str">
         <f t="shared" si="0"/>
-        <v>OverrideCtrlModePriority;</v>
-      </c>
-      <c r="K5" t="str">
-        <f t="shared" si="1"/>
-        <v>TSC1OverrideCtrlModePriority:USINT;</v>
-      </c>
-    </row>
-    <row r="6" spans="2:19" x14ac:dyDescent="0.25">
+        <v>TSC1_EngRqedSpeed_SpeedLimit</v>
+      </c>
+      <c r="M5" t="str">
+        <f t="shared" si="1"/>
+        <v>GVL_J1939.TSC1_EngRqedSpeed_SpeedLimit</v>
+      </c>
+      <c r="N5" t="str">
+        <f t="shared" si="2"/>
+        <v>GVL_J1939.TSC1_EngRqedSpeed_SpeedLimit;</v>
+      </c>
+      <c r="O5" t="str">
+        <f t="shared" si="3"/>
+        <v>TSC1_EngRqedSpeed_SpeedLimit:REAL; // SPN:</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
       <c r="B6" t="s">
         <v>871</v>
       </c>
       <c r="C6" t="s">
-        <v>976</v>
-      </c>
-      <c r="H6" t="s">
-        <v>984</v>
-      </c>
-      <c r="J6" t="str">
+        <v>977</v>
+      </c>
+      <c r="J6" t="s">
+        <v>985</v>
+      </c>
+      <c r="L6" t="str">
         <f t="shared" si="0"/>
-        <v>EngRqedSpeed_SpeedLimit;</v>
-      </c>
-      <c r="K6" t="str">
-        <f t="shared" si="1"/>
-        <v>TSC1EngRqedSpeed_SpeedLimit:REAL;</v>
-      </c>
-    </row>
-    <row r="7" spans="2:19" x14ac:dyDescent="0.25">
+        <v>TSC1_EngRqedTorque_TorqueLimit</v>
+      </c>
+      <c r="M6" t="str">
+        <f t="shared" si="1"/>
+        <v>GVL_J1939.TSC1_EngRqedTorque_TorqueLimit</v>
+      </c>
+      <c r="N6" t="str">
+        <f t="shared" si="2"/>
+        <v>GVL_J1939.TSC1_EngRqedTorque_TorqueLimit;</v>
+      </c>
+      <c r="O6" t="str">
+        <f t="shared" si="3"/>
+        <v>TSC1_EngRqedTorque_TorqueLimit:INT; // SPN:</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
       <c r="B7" t="s">
         <v>871</v>
       </c>
       <c r="C7" t="s">
-        <v>977</v>
-      </c>
-      <c r="H7" t="s">
-        <v>985</v>
-      </c>
-      <c r="J7" t="str">
+        <v>978</v>
+      </c>
+      <c r="J7" t="s">
+        <v>983</v>
+      </c>
+      <c r="L7" t="str">
         <f t="shared" si="0"/>
-        <v>EngRqedTorque_TorqueLimit;</v>
-      </c>
-      <c r="K7" t="str">
-        <f t="shared" si="1"/>
-        <v>TSC1EngRqedTorque_TorqueLimit:INT;</v>
-      </c>
-    </row>
-    <row r="8" spans="2:19" x14ac:dyDescent="0.25">
+        <v>TSC1_TransmissionRate</v>
+      </c>
+      <c r="M7" t="str">
+        <f t="shared" si="1"/>
+        <v>GVL_J1939.TSC1_TransmissionRate</v>
+      </c>
+      <c r="N7" t="str">
+        <f t="shared" si="2"/>
+        <v>GVL_J1939.TSC1_TransmissionRate;</v>
+      </c>
+      <c r="O7" t="str">
+        <f t="shared" si="3"/>
+        <v>TSC1_TransmissionRate:USINT; // SPN:</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
       <c r="B8" t="s">
         <v>871</v>
       </c>
       <c r="C8" t="s">
-        <v>978</v>
-      </c>
-      <c r="H8" t="s">
+        <v>979</v>
+      </c>
+      <c r="J8" t="s">
         <v>983</v>
       </c>
-      <c r="J8" t="str">
+      <c r="L8" t="str">
         <f t="shared" si="0"/>
-        <v>TransmissionRate;</v>
-      </c>
-      <c r="K8" t="str">
-        <f t="shared" si="1"/>
-        <v>TSC1TransmissionRate:USINT;</v>
-      </c>
-    </row>
-    <row r="9" spans="2:19" x14ac:dyDescent="0.25">
+        <v>TSC1_ControlPurpose</v>
+      </c>
+      <c r="M8" t="str">
+        <f t="shared" si="1"/>
+        <v>GVL_J1939.TSC1_ControlPurpose</v>
+      </c>
+      <c r="N8" t="str">
+        <f t="shared" si="2"/>
+        <v>GVL_J1939.TSC1_ControlPurpose;</v>
+      </c>
+      <c r="O8" t="str">
+        <f t="shared" si="3"/>
+        <v>TSC1_ControlPurpose:USINT; // SPN:</v>
+      </c>
+      <c r="T8" t="s">
+        <v>564</v>
+      </c>
+      <c r="U8" t="s">
+        <v>994</v>
+      </c>
+      <c r="W8" t="s">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
       <c r="B9" t="s">
         <v>871</v>
       </c>
       <c r="C9" t="s">
-        <v>979</v>
-      </c>
-      <c r="H9" t="s">
+        <v>980</v>
+      </c>
+      <c r="J9" t="s">
+        <v>984</v>
+      </c>
+      <c r="L9" t="str">
+        <f t="shared" si="0"/>
+        <v>TSC1_EngineRequestedTorqueHiRes</v>
+      </c>
+      <c r="M9" t="str">
+        <f t="shared" si="1"/>
+        <v>GVL_J1939.TSC1_EngineRequestedTorqueHiRes</v>
+      </c>
+      <c r="N9" t="str">
+        <f t="shared" si="2"/>
+        <v>GVL_J1939.TSC1_EngineRequestedTorqueHiRes;</v>
+      </c>
+      <c r="O9" t="str">
+        <f t="shared" si="3"/>
+        <v>TSC1_EngineRequestedTorqueHiRes:REAL; // SPN:</v>
+      </c>
+      <c r="T9" t="s">
+        <v>564</v>
+      </c>
+      <c r="U9" t="s">
+        <v>995</v>
+      </c>
+      <c r="W9" t="s">
         <v>983</v>
       </c>
-      <c r="J9" t="str">
-        <f t="shared" si="0"/>
-        <v>ControlPurpose;</v>
-      </c>
-      <c r="K9" t="str">
-        <f t="shared" si="1"/>
-        <v>TSC1ControlPurpose:USINT;</v>
-      </c>
-      <c r="P9" t="s">
-        <v>564</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>994</v>
-      </c>
-      <c r="S9" t="s">
-        <v>983</v>
-      </c>
-    </row>
-    <row r="10" spans="2:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
       <c r="B10" t="s">
         <v>871</v>
       </c>
       <c r="C10" t="s">
-        <v>980</v>
-      </c>
-      <c r="H10" t="s">
-        <v>984</v>
-      </c>
-      <c r="J10" t="str">
+        <v>981</v>
+      </c>
+      <c r="J10" t="s">
+        <v>983</v>
+      </c>
+      <c r="L10" t="str">
         <f t="shared" si="0"/>
-        <v>EngineRequestedTorqueHiRes;</v>
-      </c>
-      <c r="K10" t="str">
-        <f t="shared" si="1"/>
-        <v>TSC1EngineRequestedTorqueHiRes:REAL;</v>
-      </c>
-      <c r="P10" t="s">
+        <v>TSC1_MessageCounter</v>
+      </c>
+      <c r="M10" t="str">
+        <f t="shared" si="1"/>
+        <v>GVL_J1939.TSC1_MessageCounter</v>
+      </c>
+      <c r="N10" t="str">
+        <f t="shared" si="2"/>
+        <v>GVL_J1939.TSC1_MessageCounter;</v>
+      </c>
+      <c r="O10" t="str">
+        <f t="shared" si="3"/>
+        <v>TSC1_MessageCounter:USINT; // SPN:</v>
+      </c>
+      <c r="T10" t="s">
         <v>564</v>
       </c>
-      <c r="Q10" t="s">
-        <v>995</v>
-      </c>
-      <c r="S10" t="s">
+      <c r="U10" t="s">
+        <v>996</v>
+      </c>
+      <c r="W10" t="s">
         <v>983</v>
       </c>
     </row>
-    <row r="11" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
       <c r="B11" t="s">
         <v>871</v>
       </c>
       <c r="C11" t="s">
-        <v>981</v>
-      </c>
-      <c r="H11" t="s">
+        <v>982</v>
+      </c>
+      <c r="J11" t="s">
         <v>983</v>
       </c>
-      <c r="J11" t="str">
+      <c r="L11" t="str">
         <f t="shared" si="0"/>
-        <v>MessageCounter;</v>
-      </c>
-      <c r="K11" t="str">
-        <f t="shared" si="1"/>
-        <v>TSC1MessageCounter:USINT;</v>
-      </c>
-      <c r="P11" t="s">
+        <v>TSC1_MessageChecksum</v>
+      </c>
+      <c r="M11" t="str">
+        <f t="shared" si="1"/>
+        <v>GVL_J1939.TSC1_MessageChecksum</v>
+      </c>
+      <c r="N11" t="str">
+        <f t="shared" si="2"/>
+        <v>GVL_J1939.TSC1_MessageChecksum;</v>
+      </c>
+      <c r="O11" t="str">
+        <f t="shared" si="3"/>
+        <v>TSC1_MessageChecksum:USINT; // SPN:</v>
+      </c>
+      <c r="T11" t="s">
         <v>564</v>
       </c>
-      <c r="Q11" t="s">
-        <v>996</v>
-      </c>
-      <c r="S11" t="s">
+      <c r="U11" t="s">
+        <v>997</v>
+      </c>
+      <c r="W11" t="s">
         <v>983</v>
       </c>
     </row>
-    <row r="12" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>11</v>
+      </c>
       <c r="B12" t="s">
-        <v>871</v>
+        <v>895</v>
       </c>
       <c r="C12" t="s">
-        <v>982</v>
-      </c>
-      <c r="H12" t="s">
+        <v>986</v>
+      </c>
+      <c r="D12" s="35">
+        <v>899</v>
+      </c>
+      <c r="J12" t="s">
         <v>983</v>
       </c>
-      <c r="J12" t="str">
+      <c r="L12" t="str">
         <f t="shared" si="0"/>
-        <v>MessageChecksum;</v>
-      </c>
-      <c r="K12" t="str">
-        <f t="shared" si="1"/>
-        <v>TSC1MessageChecksum:USINT;</v>
-      </c>
-      <c r="P12" t="s">
+        <v>EEC1_EngTorqueMode</v>
+      </c>
+      <c r="M12" t="str">
+        <f t="shared" si="1"/>
+        <v>GVL_J1939.EEC1_EngTorqueMode</v>
+      </c>
+      <c r="N12" t="str">
+        <f t="shared" si="2"/>
+        <v>GVL_J1939.EEC1_EngTorqueMode;</v>
+      </c>
+      <c r="O12" t="str">
+        <f t="shared" si="3"/>
+        <v>EEC1_EngTorqueMode:USINT; // SPN:899</v>
+      </c>
+      <c r="T12" t="s">
         <v>564</v>
       </c>
-      <c r="Q12" t="s">
-        <v>997</v>
-      </c>
-      <c r="S12" t="s">
+      <c r="U12" t="s">
+        <v>998</v>
+      </c>
+      <c r="W12" t="s">
         <v>983</v>
       </c>
     </row>
-    <row r="13" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="J13" t="str">
+    <row r="13" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>895</v>
+      </c>
+      <c r="C13" t="s">
+        <v>987</v>
+      </c>
+      <c r="D13" s="35">
+        <v>4154</v>
+      </c>
+      <c r="J13" t="s">
+        <v>984</v>
+      </c>
+      <c r="L13" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="P13" t="s">
+        <v>EEC1_ActlEngPrcntTrqueHighResolution</v>
+      </c>
+      <c r="M13" t="str">
+        <f t="shared" si="1"/>
+        <v>GVL_J1939.EEC1_ActlEngPrcntTrqueHighResolution</v>
+      </c>
+      <c r="N13" t="str">
+        <f t="shared" si="2"/>
+        <v>GVL_J1939.EEC1_ActlEngPrcntTrqueHighResolution;</v>
+      </c>
+      <c r="O13" t="str">
+        <f t="shared" si="3"/>
+        <v>EEC1_ActlEngPrcntTrqueHighResolution:REAL; // SPN:4154</v>
+      </c>
+      <c r="T13" t="s">
         <v>564</v>
       </c>
-      <c r="Q13" t="s">
-        <v>998</v>
-      </c>
-      <c r="S13" t="s">
+      <c r="U13" t="s">
+        <v>999</v>
+      </c>
+      <c r="W13" t="s">
         <v>983</v>
       </c>
     </row>
-    <row r="14" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="J14" t="str">
+    <row r="14" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>895</v>
+      </c>
+      <c r="C14" t="s">
+        <v>988</v>
+      </c>
+      <c r="D14" s="35">
+        <v>512</v>
+      </c>
+      <c r="J14" t="s">
+        <v>985</v>
+      </c>
+      <c r="L14" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="P14" t="s">
+        <v>EEC1_DriversDemandEngPercentTorque</v>
+      </c>
+      <c r="M14" t="str">
+        <f t="shared" si="1"/>
+        <v>GVL_J1939.EEC1_DriversDemandEngPercentTorque</v>
+      </c>
+      <c r="N14" t="str">
+        <f t="shared" si="2"/>
+        <v>GVL_J1939.EEC1_DriversDemandEngPercentTorque;</v>
+      </c>
+      <c r="O14" t="str">
+        <f t="shared" si="3"/>
+        <v>EEC1_DriversDemandEngPercentTorque:INT; // SPN:512</v>
+      </c>
+      <c r="T14" t="s">
         <v>564</v>
       </c>
-      <c r="Q14" t="s">
-        <v>999</v>
-      </c>
-      <c r="S14" t="s">
-        <v>983</v>
-      </c>
-    </row>
-    <row r="15" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="U14" t="s">
+        <v>1000</v>
+      </c>
+      <c r="W14" t="s">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>14</v>
+      </c>
       <c r="B15" t="s">
         <v>895</v>
       </c>
       <c r="C15" t="s">
-        <v>986</v>
-      </c>
-      <c r="H15" t="s">
-        <v>983</v>
-      </c>
-      <c r="J15" t="str">
+        <v>989</v>
+      </c>
+      <c r="D15" s="35">
+        <v>513</v>
+      </c>
+      <c r="E15" t="s">
+        <v>682</v>
+      </c>
+      <c r="J15" t="s">
+        <v>985</v>
+      </c>
+      <c r="L15" t="str">
         <f t="shared" si="0"/>
-        <v>EngTorqueMode;</v>
-      </c>
-      <c r="P15" t="s">
+        <v>EEC1_ActualEngPercentTorque</v>
+      </c>
+      <c r="M15" t="str">
+        <f t="shared" si="1"/>
+        <v>GVL_J1939.EEC1_ActualEngPercentTorque</v>
+      </c>
+      <c r="N15" t="str">
+        <f t="shared" si="2"/>
+        <v>GVL_J1939.EEC1_ActualEngPercentTorque;</v>
+      </c>
+      <c r="O15" t="str">
+        <f t="shared" si="3"/>
+        <v>EEC1_ActualEngPercentTorque:INT; // SPN:513</v>
+      </c>
+      <c r="T15" t="s">
         <v>564</v>
       </c>
-      <c r="Q15" t="s">
-        <v>1000</v>
-      </c>
-      <c r="S15" t="s">
-        <v>983</v>
-      </c>
-    </row>
-    <row r="16" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="U15" t="s">
+        <v>1001</v>
+      </c>
+      <c r="W15" t="s">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>15</v>
+      </c>
       <c r="B16" t="s">
         <v>895</v>
       </c>
       <c r="C16" t="s">
-        <v>987</v>
-      </c>
-      <c r="H16" t="s">
+        <v>990</v>
+      </c>
+      <c r="D16" s="35">
+        <v>190</v>
+      </c>
+      <c r="E16" t="s">
+        <v>682</v>
+      </c>
+      <c r="J16" t="s">
         <v>984</v>
       </c>
-      <c r="J16" t="str">
+      <c r="L16" t="str">
         <f t="shared" si="0"/>
-        <v>ActlEngPrcntTrqueHighResolution;</v>
-      </c>
-      <c r="P16" t="s">
+        <v>EEC1_EngSpeed</v>
+      </c>
+      <c r="M16" t="str">
+        <f t="shared" si="1"/>
+        <v>GVL_J1939.EEC1_EngSpeed</v>
+      </c>
+      <c r="N16" t="str">
+        <f t="shared" si="2"/>
+        <v>GVL_J1939.EEC1_EngSpeed;</v>
+      </c>
+      <c r="O16" t="str">
+        <f t="shared" si="3"/>
+        <v>EEC1_EngSpeed:REAL; // SPN:190</v>
+      </c>
+      <c r="T16" t="s">
         <v>564</v>
       </c>
-      <c r="Q16" t="s">
-        <v>1001</v>
-      </c>
-      <c r="S16" t="s">
-        <v>983</v>
-      </c>
-    </row>
-    <row r="17" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="U16" t="s">
+        <v>1002</v>
+      </c>
+      <c r="W16" t="s">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>16</v>
+      </c>
       <c r="B17" t="s">
         <v>895</v>
       </c>
       <c r="C17" t="s">
-        <v>988</v>
-      </c>
-      <c r="H17" t="s">
-        <v>985</v>
-      </c>
-      <c r="J17" t="str">
+        <v>991</v>
+      </c>
+      <c r="D17" s="35">
+        <v>1483</v>
+      </c>
+      <c r="J17" t="s">
+        <v>983</v>
+      </c>
+      <c r="L17" t="str">
         <f t="shared" si="0"/>
-        <v>DriversDemandEngPercentTorque;</v>
-      </c>
-      <c r="P17" t="s">
+        <v>EEC1_SrcAddrssOfCtrllngDvcFrEngCntrl</v>
+      </c>
+      <c r="M17" t="str">
+        <f t="shared" si="1"/>
+        <v>GVL_J1939.EEC1_SrcAddrssOfCtrllngDvcFrEngCntrl</v>
+      </c>
+      <c r="N17" t="str">
+        <f t="shared" si="2"/>
+        <v>GVL_J1939.EEC1_SrcAddrssOfCtrllngDvcFrEngCntrl;</v>
+      </c>
+      <c r="O17" t="str">
+        <f t="shared" si="3"/>
+        <v>EEC1_SrcAddrssOfCtrllngDvcFrEngCntrl:USINT; // SPN:1483</v>
+      </c>
+      <c r="T17" t="s">
         <v>564</v>
       </c>
-      <c r="Q17" t="s">
-        <v>1002</v>
-      </c>
-      <c r="S17" t="s">
-        <v>1007</v>
-      </c>
-    </row>
-    <row r="18" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="U17" t="s">
+        <v>1003</v>
+      </c>
+      <c r="W17" t="s">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>17</v>
+      </c>
       <c r="B18" t="s">
         <v>895</v>
       </c>
       <c r="C18" t="s">
-        <v>989</v>
-      </c>
-      <c r="H18" t="s">
-        <v>985</v>
-      </c>
-      <c r="J18" t="str">
+        <v>992</v>
+      </c>
+      <c r="D18" s="35">
+        <v>1675</v>
+      </c>
+      <c r="J18" t="s">
+        <v>983</v>
+      </c>
+      <c r="L18" t="str">
         <f t="shared" si="0"/>
-        <v>ActualEngPercentTorque;</v>
-      </c>
-      <c r="P18" t="s">
+        <v>EEC1_EngStarterMode</v>
+      </c>
+      <c r="M18" t="str">
+        <f t="shared" si="1"/>
+        <v>GVL_J1939.EEC1_EngStarterMode</v>
+      </c>
+      <c r="N18" t="str">
+        <f t="shared" si="2"/>
+        <v>GVL_J1939.EEC1_EngStarterMode;</v>
+      </c>
+      <c r="O18" t="str">
+        <f t="shared" si="3"/>
+        <v>EEC1_EngStarterMode:USINT; // SPN:1675</v>
+      </c>
+      <c r="T18" t="s">
         <v>564</v>
       </c>
-      <c r="Q18" t="s">
-        <v>1003</v>
-      </c>
-      <c r="S18" t="s">
-        <v>1007</v>
-      </c>
-    </row>
-    <row r="19" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="U18" t="s">
+        <v>1004</v>
+      </c>
+      <c r="W18" t="s">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>18</v>
+      </c>
       <c r="B19" t="s">
         <v>895</v>
       </c>
       <c r="C19" t="s">
-        <v>990</v>
-      </c>
-      <c r="H19" t="s">
-        <v>984</v>
-      </c>
-      <c r="J19" t="str">
+        <v>993</v>
+      </c>
+      <c r="D19" s="35">
+        <v>2432</v>
+      </c>
+      <c r="J19" t="s">
+        <v>985</v>
+      </c>
+      <c r="L19" t="str">
         <f t="shared" si="0"/>
-        <v>EngSpeed;</v>
-      </c>
-      <c r="P19" t="s">
-        <v>564</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>1004</v>
-      </c>
-      <c r="S19" t="s">
+        <v>EEC1_EngDemandPercentTorque</v>
+      </c>
+      <c r="M19" t="str">
+        <f t="shared" si="1"/>
+        <v>GVL_J1939.EEC1_EngDemandPercentTorque</v>
+      </c>
+      <c r="N19" t="str">
+        <f t="shared" si="2"/>
+        <v>GVL_J1939.EEC1_EngDemandPercentTorque;</v>
+      </c>
+      <c r="O19" t="str">
+        <f t="shared" si="3"/>
+        <v>EEC1_EngDemandPercentTorque:INT; // SPN:2432</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>958</v>
+      </c>
+      <c r="C20" t="s">
+        <v>1006</v>
+      </c>
+      <c r="D20" s="35">
+        <v>588</v>
+      </c>
+      <c r="J20" t="s">
+        <v>983</v>
+      </c>
+      <c r="L20" t="str">
+        <f t="shared" si="0"/>
+        <v>EEC2_AccelPedal1LowIdleSwitch</v>
+      </c>
+      <c r="M20" t="str">
+        <f t="shared" si="1"/>
+        <v>GVL_J1939.EEC2_AccelPedal1LowIdleSwitch</v>
+      </c>
+      <c r="N20" t="str">
+        <f t="shared" si="2"/>
+        <v>GVL_J1939.EEC2_AccelPedal1LowIdleSwitch;</v>
+      </c>
+      <c r="O20" t="str">
+        <f t="shared" si="3"/>
+        <v>EEC2_AccelPedal1LowIdleSwitch:USINT; // SPN:588</v>
+      </c>
+    </row>
+    <row r="21" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>958</v>
+      </c>
+      <c r="C21" t="s">
         <v>1007</v>
       </c>
-    </row>
-    <row r="20" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B20" t="s">
-        <v>895</v>
-      </c>
-      <c r="C20" t="s">
-        <v>991</v>
-      </c>
-      <c r="H20" t="s">
+      <c r="D21" s="35">
+        <v>559</v>
+      </c>
+      <c r="J21" t="s">
         <v>983</v>
       </c>
-      <c r="J20" t="str">
+      <c r="L21" t="str">
         <f t="shared" si="0"/>
-        <v>SrcAddrssOfCtrllngDvcFrEngCntrl;</v>
-      </c>
-      <c r="P20" t="s">
-        <v>564</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>1005</v>
-      </c>
-      <c r="S20" t="s">
-        <v>1007</v>
-      </c>
-    </row>
-    <row r="21" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B21" t="s">
-        <v>895</v>
-      </c>
-      <c r="C21" t="s">
-        <v>992</v>
-      </c>
-      <c r="H21" t="s">
+        <v>EEC2_AccelPedalKickdownSwitch</v>
+      </c>
+      <c r="M21" t="str">
+        <f t="shared" si="1"/>
+        <v>GVL_J1939.EEC2_AccelPedalKickdownSwitch</v>
+      </c>
+      <c r="N21" t="str">
+        <f t="shared" si="2"/>
+        <v>GVL_J1939.EEC2_AccelPedalKickdownSwitch;</v>
+      </c>
+      <c r="O21" t="str">
+        <f t="shared" si="3"/>
+        <v>EEC2_AccelPedalKickdownSwitch:USINT; // SPN:559</v>
+      </c>
+    </row>
+    <row r="22" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>958</v>
+      </c>
+      <c r="C22" t="s">
+        <v>1008</v>
+      </c>
+      <c r="D22" s="35">
+        <v>1437</v>
+      </c>
+      <c r="J22" t="s">
         <v>983</v>
       </c>
-      <c r="J21" t="str">
+      <c r="L22" t="str">
         <f t="shared" si="0"/>
-        <v>EngStarterMode;</v>
-      </c>
-      <c r="P21" t="s">
-        <v>564</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>1006</v>
-      </c>
-      <c r="S21" t="s">
-        <v>1007</v>
-      </c>
-    </row>
-    <row r="22" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B22" t="s">
-        <v>895</v>
-      </c>
-      <c r="C22" t="s">
-        <v>993</v>
-      </c>
-      <c r="H22" t="s">
-        <v>985</v>
-      </c>
-      <c r="J22" t="str">
+        <v>EEC2_RoadSpeedLimitStatus</v>
+      </c>
+      <c r="M22" t="str">
+        <f t="shared" si="1"/>
+        <v>GVL_J1939.EEC2_RoadSpeedLimitStatus</v>
+      </c>
+      <c r="N22" t="str">
+        <f t="shared" si="2"/>
+        <v>GVL_J1939.EEC2_RoadSpeedLimitStatus;</v>
+      </c>
+      <c r="O22" t="str">
+        <f t="shared" si="3"/>
+        <v>EEC2_RoadSpeedLimitStatus:USINT; // SPN:1437</v>
+      </c>
+    </row>
+    <row r="23" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>958</v>
+      </c>
+      <c r="C23" t="s">
+        <v>1009</v>
+      </c>
+      <c r="D23" s="35">
+        <v>2970</v>
+      </c>
+      <c r="J23" t="s">
+        <v>983</v>
+      </c>
+      <c r="L23" t="str">
         <f t="shared" si="0"/>
-        <v>EngDemandPercentTorque;</v>
-      </c>
-    </row>
-    <row r="23" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="J23" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="24" spans="2:19" x14ac:dyDescent="0.25">
+        <v>EEC2_AccelPedal2LowIdleSwitch</v>
+      </c>
+      <c r="M23" t="str">
+        <f t="shared" si="1"/>
+        <v>GVL_J1939.EEC2_AccelPedal2LowIdleSwitch</v>
+      </c>
+      <c r="N23" t="str">
+        <f t="shared" si="2"/>
+        <v>GVL_J1939.EEC2_AccelPedal2LowIdleSwitch;</v>
+      </c>
+      <c r="O23" t="str">
+        <f t="shared" si="3"/>
+        <v>EEC2_AccelPedal2LowIdleSwitch:USINT; // SPN:2970</v>
+      </c>
+    </row>
+    <row r="24" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>23</v>
+      </c>
       <c r="B24" t="s">
         <v>958</v>
       </c>
       <c r="C24" t="s">
-        <v>1008</v>
-      </c>
-      <c r="H24" t="s">
-        <v>983</v>
-      </c>
-      <c r="J24" t="str">
+        <v>1010</v>
+      </c>
+      <c r="D24" s="35">
+        <v>91</v>
+      </c>
+      <c r="J24" t="s">
+        <v>984</v>
+      </c>
+      <c r="L24" t="str">
         <f t="shared" si="0"/>
-        <v>AccelPedal1LowIdleSwitch;</v>
-      </c>
-    </row>
-    <row r="25" spans="2:19" x14ac:dyDescent="0.25">
+        <v>EEC2_AccelPedalPos1</v>
+      </c>
+      <c r="M24" t="str">
+        <f t="shared" si="1"/>
+        <v>GVL_J1939.EEC2_AccelPedalPos1</v>
+      </c>
+      <c r="N24" t="str">
+        <f t="shared" si="2"/>
+        <v>GVL_J1939.EEC2_AccelPedalPos1;</v>
+      </c>
+      <c r="O24" t="str">
+        <f t="shared" si="3"/>
+        <v>EEC2_AccelPedalPos1:REAL; // SPN:91</v>
+      </c>
+    </row>
+    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>24</v>
+      </c>
       <c r="B25" t="s">
         <v>958</v>
       </c>
       <c r="C25" t="s">
-        <v>1009</v>
-      </c>
-      <c r="H25" t="s">
+        <v>1011</v>
+      </c>
+      <c r="D25" s="35">
+        <v>92</v>
+      </c>
+      <c r="E25" t="s">
+        <v>1176</v>
+      </c>
+      <c r="J25" t="s">
         <v>983</v>
       </c>
-      <c r="J25" t="str">
+      <c r="L25" t="str">
         <f t="shared" si="0"/>
-        <v>AccelPedalKickdownSwitch;</v>
-      </c>
-    </row>
-    <row r="26" spans="2:19" x14ac:dyDescent="0.25">
+        <v>EEC2_EngPercentLoadAtCurrentSpeed</v>
+      </c>
+      <c r="M25" t="str">
+        <f t="shared" si="1"/>
+        <v>GVL_J1939.EEC2_EngPercentLoadAtCurrentSpeed</v>
+      </c>
+      <c r="N25" t="str">
+        <f t="shared" si="2"/>
+        <v>GVL_J1939.EEC2_EngPercentLoadAtCurrentSpeed;</v>
+      </c>
+      <c r="O25" t="str">
+        <f t="shared" si="3"/>
+        <v>EEC2_EngPercentLoadAtCurrentSpeed:USINT; // SPN:92</v>
+      </c>
+    </row>
+    <row r="26" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>25</v>
+      </c>
       <c r="B26" t="s">
         <v>958</v>
       </c>
       <c r="C26" t="s">
-        <v>1010</v>
-      </c>
-      <c r="H26" t="s">
-        <v>983</v>
-      </c>
-      <c r="J26" t="str">
+        <v>1012</v>
+      </c>
+      <c r="D26" s="35">
+        <v>974</v>
+      </c>
+      <c r="J26" t="s">
+        <v>984</v>
+      </c>
+      <c r="L26" t="str">
         <f t="shared" si="0"/>
-        <v>RoadSpeedLimitStatus;</v>
-      </c>
-    </row>
-    <row r="27" spans="2:19" x14ac:dyDescent="0.25">
+        <v>EEC2_RemoteAccelPedalPos</v>
+      </c>
+      <c r="M26" t="str">
+        <f t="shared" si="1"/>
+        <v>GVL_J1939.EEC2_RemoteAccelPedalPos</v>
+      </c>
+      <c r="N26" t="str">
+        <f t="shared" si="2"/>
+        <v>GVL_J1939.EEC2_RemoteAccelPedalPos;</v>
+      </c>
+      <c r="O26" t="str">
+        <f t="shared" si="3"/>
+        <v>EEC2_RemoteAccelPedalPos:REAL; // SPN:974</v>
+      </c>
+    </row>
+    <row r="27" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>26</v>
+      </c>
       <c r="B27" t="s">
         <v>958</v>
       </c>
       <c r="C27" t="s">
-        <v>1011</v>
-      </c>
-      <c r="H27" t="s">
-        <v>983</v>
-      </c>
-      <c r="J27" t="str">
+        <v>1013</v>
+      </c>
+      <c r="D27" s="35">
+        <v>29</v>
+      </c>
+      <c r="J27" t="s">
+        <v>984</v>
+      </c>
+      <c r="L27" t="str">
         <f t="shared" si="0"/>
-        <v>AccelPedal2LowIdleSwitch;</v>
-      </c>
-    </row>
-    <row r="28" spans="2:19" x14ac:dyDescent="0.25">
+        <v>EEC2_AccelPedalPos2</v>
+      </c>
+      <c r="M27" t="str">
+        <f t="shared" si="1"/>
+        <v>GVL_J1939.EEC2_AccelPedalPos2</v>
+      </c>
+      <c r="N27" t="str">
+        <f t="shared" si="2"/>
+        <v>GVL_J1939.EEC2_AccelPedalPos2;</v>
+      </c>
+      <c r="O27" t="str">
+        <f t="shared" si="3"/>
+        <v>EEC2_AccelPedalPos2:REAL; // SPN:29</v>
+      </c>
+    </row>
+    <row r="28" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>27</v>
+      </c>
       <c r="B28" t="s">
         <v>958</v>
       </c>
       <c r="C28" t="s">
-        <v>1012</v>
-      </c>
-      <c r="H28" t="s">
-        <v>984</v>
-      </c>
-      <c r="J28" t="str">
+        <v>1014</v>
+      </c>
+      <c r="D28" s="35">
+        <v>2979</v>
+      </c>
+      <c r="J28" t="s">
+        <v>983</v>
+      </c>
+      <c r="L28" t="str">
         <f t="shared" si="0"/>
-        <v>AccelPedalPos1;</v>
-      </c>
-    </row>
-    <row r="29" spans="2:19" x14ac:dyDescent="0.25">
+        <v>EEC2_VhclAccelerationRateLimitStatus</v>
+      </c>
+      <c r="M28" t="str">
+        <f t="shared" si="1"/>
+        <v>GVL_J1939.EEC2_VhclAccelerationRateLimitStatus</v>
+      </c>
+      <c r="N28" t="str">
+        <f t="shared" si="2"/>
+        <v>GVL_J1939.EEC2_VhclAccelerationRateLimitStatus;</v>
+      </c>
+      <c r="O28" t="str">
+        <f t="shared" si="3"/>
+        <v>EEC2_VhclAccelerationRateLimitStatus:USINT; // SPN:2979</v>
+      </c>
+    </row>
+    <row r="29" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>28</v>
+      </c>
       <c r="B29" t="s">
         <v>958</v>
       </c>
       <c r="C29" t="s">
-        <v>1013</v>
-      </c>
-      <c r="H29" t="s">
+        <v>1015</v>
+      </c>
+      <c r="D29" s="35">
+        <v>5021</v>
+      </c>
+      <c r="J29" t="s">
         <v>983</v>
       </c>
-      <c r="J29" t="str">
+      <c r="L29" t="str">
         <f t="shared" si="0"/>
-        <v>EngPercentLoadAtCurrentSpeed;</v>
-      </c>
-    </row>
-    <row r="30" spans="2:19" x14ac:dyDescent="0.25">
+        <v>EEC2_MmntryEngMaxPowerEnableFeedback</v>
+      </c>
+      <c r="M29" t="str">
+        <f t="shared" si="1"/>
+        <v>GVL_J1939.EEC2_MmntryEngMaxPowerEnableFeedback</v>
+      </c>
+      <c r="N29" t="str">
+        <f t="shared" si="2"/>
+        <v>GVL_J1939.EEC2_MmntryEngMaxPowerEnableFeedback;</v>
+      </c>
+      <c r="O29" t="str">
+        <f t="shared" si="3"/>
+        <v>EEC2_MmntryEngMaxPowerEnableFeedback:USINT; // SPN:5021</v>
+      </c>
+    </row>
+    <row r="30" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>29</v>
+      </c>
       <c r="B30" t="s">
         <v>958</v>
       </c>
       <c r="C30" t="s">
-        <v>1014</v>
-      </c>
-      <c r="H30" t="s">
-        <v>984</v>
-      </c>
-      <c r="J30" t="str">
+        <v>1016</v>
+      </c>
+      <c r="D30" s="35">
+        <v>5399</v>
+      </c>
+      <c r="J30" t="s">
+        <v>983</v>
+      </c>
+      <c r="L30" t="str">
         <f t="shared" si="0"/>
-        <v>RemoteAccelPedalPos;</v>
-      </c>
-    </row>
-    <row r="31" spans="2:19" x14ac:dyDescent="0.25">
+        <v>EEC2_DPFThermalManagementActive</v>
+      </c>
+      <c r="M30" t="str">
+        <f t="shared" si="1"/>
+        <v>GVL_J1939.EEC2_DPFThermalManagementActive</v>
+      </c>
+      <c r="N30" t="str">
+        <f t="shared" si="2"/>
+        <v>GVL_J1939.EEC2_DPFThermalManagementActive;</v>
+      </c>
+      <c r="O30" t="str">
+        <f t="shared" si="3"/>
+        <v>EEC2_DPFThermalManagementActive:USINT; // SPN:5399</v>
+      </c>
+    </row>
+    <row r="31" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>30</v>
+      </c>
       <c r="B31" t="s">
         <v>958</v>
       </c>
       <c r="C31" t="s">
-        <v>1015</v>
-      </c>
-      <c r="H31" t="s">
-        <v>984</v>
-      </c>
-      <c r="J31" t="str">
+        <v>1017</v>
+      </c>
+      <c r="D31" s="35">
+        <v>5400</v>
+      </c>
+      <c r="E31" t="s">
+        <v>682</v>
+      </c>
+      <c r="J31" t="s">
+        <v>983</v>
+      </c>
+      <c r="L31" t="str">
         <f t="shared" si="0"/>
-        <v>AccelPedalPos2;</v>
-      </c>
-    </row>
-    <row r="32" spans="2:19" x14ac:dyDescent="0.25">
+        <v>EEC2_SCRThermalManagementActive</v>
+      </c>
+      <c r="M31" t="str">
+        <f t="shared" si="1"/>
+        <v>GVL_J1939.EEC2_SCRThermalManagementActive</v>
+      </c>
+      <c r="N31" t="str">
+        <f t="shared" si="2"/>
+        <v>GVL_J1939.EEC2_SCRThermalManagementActive;</v>
+      </c>
+      <c r="O31" t="str">
+        <f t="shared" si="3"/>
+        <v>EEC2_SCRThermalManagementActive:USINT; // SPN:5400</v>
+      </c>
+    </row>
+    <row r="32" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>31</v>
+      </c>
       <c r="B32" t="s">
         <v>958</v>
       </c>
       <c r="C32" t="s">
-        <v>1016</v>
-      </c>
-      <c r="H32" t="s">
-        <v>983</v>
-      </c>
-      <c r="J32" t="str">
+        <v>1018</v>
+      </c>
+      <c r="D32" s="35">
+        <v>3357</v>
+      </c>
+      <c r="E32" t="s">
+        <v>682</v>
+      </c>
+      <c r="J32" t="s">
+        <v>984</v>
+      </c>
+      <c r="L32" t="str">
         <f t="shared" si="0"/>
-        <v>VhclAccelerationRateLimitStatus;</v>
-      </c>
-    </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
+        <v>EEC2_ActlMxAvailableEngPercentTorque</v>
+      </c>
+      <c r="M32" t="str">
+        <f t="shared" si="1"/>
+        <v>GVL_J1939.EEC2_ActlMxAvailableEngPercentTorque</v>
+      </c>
+      <c r="N32" t="str">
+        <f t="shared" si="2"/>
+        <v>GVL_J1939.EEC2_ActlMxAvailableEngPercentTorque;</v>
+      </c>
+      <c r="O32" t="str">
+        <f t="shared" si="3"/>
+        <v>EEC2_ActlMxAvailableEngPercentTorque:REAL; // SPN:3357</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>32</v>
+      </c>
       <c r="B33" t="s">
         <v>958</v>
       </c>
       <c r="C33" t="s">
-        <v>1017</v>
-      </c>
-      <c r="H33" t="s">
+        <v>1019</v>
+      </c>
+      <c r="D33" s="35">
+        <v>5398</v>
+      </c>
+      <c r="J33" t="s">
+        <v>985</v>
+      </c>
+      <c r="L33" t="str">
+        <f t="shared" si="0"/>
+        <v>EEC2_EstPumpingPercentTorque</v>
+      </c>
+      <c r="M33" t="str">
+        <f t="shared" si="1"/>
+        <v>GVL_J1939.EEC2_EstPumpingPercentTorque</v>
+      </c>
+      <c r="N33" t="str">
+        <f t="shared" si="2"/>
+        <v>GVL_J1939.EEC2_EstPumpingPercentTorque;</v>
+      </c>
+      <c r="O33" t="str">
+        <f t="shared" si="3"/>
+        <v>EEC2_EstPumpingPercentTorque:INT; // SPN:5398</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>898</v>
+      </c>
+      <c r="C34" t="s">
+        <v>1020</v>
+      </c>
+      <c r="D34" s="35">
+        <v>514</v>
+      </c>
+      <c r="E34" t="s">
+        <v>682</v>
+      </c>
+      <c r="J34" t="s">
+        <v>985</v>
+      </c>
+      <c r="L34" t="str">
+        <f t="shared" si="0"/>
+        <v>EEC3_NominalFrictionPercentTorque</v>
+      </c>
+      <c r="M34" t="str">
+        <f t="shared" si="1"/>
+        <v>GVL_J1939.EEC3_NominalFrictionPercentTorque</v>
+      </c>
+      <c r="N34" t="str">
+        <f t="shared" si="2"/>
+        <v>GVL_J1939.EEC3_NominalFrictionPercentTorque;</v>
+      </c>
+      <c r="O34" t="str">
+        <f t="shared" si="3"/>
+        <v>EEC3_NominalFrictionPercentTorque:INT; // SPN:514</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
+        <v>898</v>
+      </c>
+      <c r="C35" t="s">
+        <v>1021</v>
+      </c>
+      <c r="D35" s="35">
+        <v>515</v>
+      </c>
+      <c r="E35" t="s">
+        <v>682</v>
+      </c>
+      <c r="J35" t="s">
+        <v>1029</v>
+      </c>
+      <c r="L35" t="str">
+        <f t="shared" si="0"/>
+        <v>EEC3_EngsDesiredOperatingSpeed</v>
+      </c>
+      <c r="M35" t="str">
+        <f t="shared" si="1"/>
+        <v>GVL_J1939.EEC3_EngsDesiredOperatingSpeed</v>
+      </c>
+      <c r="N35" t="str">
+        <f t="shared" si="2"/>
+        <v>GVL_J1939.EEC3_EngsDesiredOperatingSpeed;</v>
+      </c>
+      <c r="O35" t="str">
+        <f t="shared" si="3"/>
+        <v>EEC3_EngsDesiredOperatingSpeed:REAl; // SPN:515</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" t="s">
+        <v>898</v>
+      </c>
+      <c r="C36" t="s">
+        <v>1022</v>
+      </c>
+      <c r="D36" s="35">
+        <v>519</v>
+      </c>
+      <c r="J36" t="s">
         <v>983</v>
       </c>
-      <c r="J33" t="str">
+      <c r="L36" t="str">
         <f t="shared" si="0"/>
-        <v>MmntryEngMaxPowerEnableFeedback;</v>
-      </c>
-    </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B34" t="s">
-        <v>958</v>
-      </c>
-      <c r="C34" t="s">
-        <v>1018</v>
-      </c>
-      <c r="H34" t="s">
-        <v>983</v>
-      </c>
-      <c r="J34" t="str">
+        <v>EEC3_EngsDsrdOprtngSpdAsymmtryAdjstmn</v>
+      </c>
+      <c r="M36" t="str">
+        <f t="shared" si="1"/>
+        <v>GVL_J1939.EEC3_EngsDsrdOprtngSpdAsymmtryAdjstmn</v>
+      </c>
+      <c r="N36" t="str">
+        <f t="shared" si="2"/>
+        <v>GVL_J1939.EEC3_EngsDsrdOprtngSpdAsymmtryAdjstmn;</v>
+      </c>
+      <c r="O36" t="str">
+        <f t="shared" si="3"/>
+        <v>EEC3_EngsDsrdOprtngSpdAsymmtryAdjstmn:USINT; // SPN:519</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" t="s">
+        <v>898</v>
+      </c>
+      <c r="C37" t="s">
+        <v>1023</v>
+      </c>
+      <c r="D37" s="35">
+        <v>2978</v>
+      </c>
+      <c r="J37" t="s">
+        <v>985</v>
+      </c>
+      <c r="L37" t="str">
         <f t="shared" si="0"/>
-        <v>DPFThermalManagementActive;</v>
-      </c>
-    </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B35" t="s">
-        <v>958</v>
-      </c>
-      <c r="C35" t="s">
-        <v>1019</v>
-      </c>
-      <c r="H35" t="s">
-        <v>983</v>
-      </c>
-      <c r="J35" t="str">
+        <v>EEC3_EstEngPrsticLossesPercentTorque</v>
+      </c>
+      <c r="M37" t="str">
+        <f t="shared" si="1"/>
+        <v>GVL_J1939.EEC3_EstEngPrsticLossesPercentTorque</v>
+      </c>
+      <c r="N37" t="str">
+        <f t="shared" si="2"/>
+        <v>GVL_J1939.EEC3_EstEngPrsticLossesPercentTorque;</v>
+      </c>
+      <c r="O37" t="str">
+        <f t="shared" si="3"/>
+        <v>EEC3_EstEngPrsticLossesPercentTorque:INT; // SPN:2978</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" t="s">
+        <v>898</v>
+      </c>
+      <c r="C38" t="s">
+        <v>1024</v>
+      </c>
+      <c r="D38" s="35">
+        <v>3236</v>
+      </c>
+      <c r="J38" t="s">
+        <v>984</v>
+      </c>
+      <c r="L38" t="str">
         <f t="shared" si="0"/>
-        <v>SCRThermalManagementActive;</v>
-      </c>
-    </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B36" t="s">
-        <v>958</v>
-      </c>
-      <c r="C36" t="s">
-        <v>1020</v>
-      </c>
-      <c r="H36" t="s">
-        <v>984</v>
-      </c>
-      <c r="J36" t="str">
-        <f t="shared" si="0"/>
-        <v>ActlMxAvailableEngPercentTorque;</v>
-      </c>
-    </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B37" t="s">
-        <v>958</v>
-      </c>
-      <c r="C37" t="s">
-        <v>1021</v>
-      </c>
-      <c r="H37" t="s">
-        <v>985</v>
-      </c>
-      <c r="J37" t="str">
-        <f t="shared" si="0"/>
-        <v>EstPumpingPercentTorque;</v>
-      </c>
-    </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="J38" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
+        <v>EEC3_Aftrtratment1ExhaustGasMassFlow</v>
+      </c>
+      <c r="M38" t="str">
+        <f t="shared" si="1"/>
+        <v>GVL_J1939.EEC3_Aftrtratment1ExhaustGasMassFlow</v>
+      </c>
+      <c r="N38" t="str">
+        <f t="shared" si="2"/>
+        <v>GVL_J1939.EEC3_Aftrtratment1ExhaustGasMassFlow;</v>
+      </c>
+      <c r="O38" t="str">
+        <f t="shared" si="3"/>
+        <v>EEC3_Aftrtratment1ExhaustGasMassFlow:REAL; // SPN:3236</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>38</v>
+      </c>
       <c r="B39" t="s">
         <v>898</v>
       </c>
       <c r="C39" t="s">
-        <v>1022</v>
-      </c>
-      <c r="H39" t="s">
-        <v>985</v>
-      </c>
-      <c r="J39" t="str">
+        <v>1025</v>
+      </c>
+      <c r="D39" s="35">
+        <v>3237</v>
+      </c>
+      <c r="J39" t="s">
+        <v>983</v>
+      </c>
+      <c r="L39" t="str">
         <f t="shared" si="0"/>
-        <v>NominalFrictionPercentTorque;</v>
-      </c>
-    </row>
-    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
+        <v>EEC3_Aftertreatment1IntakeDewPoint</v>
+      </c>
+      <c r="M39" t="str">
+        <f t="shared" si="1"/>
+        <v>GVL_J1939.EEC3_Aftertreatment1IntakeDewPoint</v>
+      </c>
+      <c r="N39" t="str">
+        <f t="shared" si="2"/>
+        <v>GVL_J1939.EEC3_Aftertreatment1IntakeDewPoint;</v>
+      </c>
+      <c r="O39" t="str">
+        <f t="shared" si="3"/>
+        <v>EEC3_Aftertreatment1IntakeDewPoint:USINT; // SPN:3237</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>39</v>
+      </c>
       <c r="B40" t="s">
         <v>898</v>
       </c>
       <c r="C40" t="s">
-        <v>1023</v>
-      </c>
-      <c r="H40" t="s">
-        <v>1031</v>
-      </c>
-      <c r="J40" t="str">
+        <v>1026</v>
+      </c>
+      <c r="D40" s="35">
+        <v>3238</v>
+      </c>
+      <c r="J40" t="s">
+        <v>983</v>
+      </c>
+      <c r="L40" t="str">
         <f t="shared" si="0"/>
-        <v>EngsDesiredOperatingSpeed;</v>
-      </c>
-    </row>
-    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
+        <v>EEC3_Aftertreatment1ExhaustDewPoint</v>
+      </c>
+      <c r="M40" t="str">
+        <f t="shared" si="1"/>
+        <v>GVL_J1939.EEC3_Aftertreatment1ExhaustDewPoint</v>
+      </c>
+      <c r="N40" t="str">
+        <f t="shared" si="2"/>
+        <v>GVL_J1939.EEC3_Aftertreatment1ExhaustDewPoint;</v>
+      </c>
+      <c r="O40" t="str">
+        <f t="shared" si="3"/>
+        <v>EEC3_Aftertreatment1ExhaustDewPoint:USINT; // SPN:3238</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>40</v>
+      </c>
       <c r="B41" t="s">
         <v>898</v>
       </c>
       <c r="C41" t="s">
-        <v>1024</v>
-      </c>
-      <c r="H41" t="s">
+        <v>1027</v>
+      </c>
+      <c r="D41" s="35">
+        <v>3239</v>
+      </c>
+      <c r="J41" t="s">
         <v>983</v>
       </c>
-      <c r="J41" t="str">
+      <c r="L41" t="str">
         <f t="shared" si="0"/>
-        <v>EngsDsrdOprtngSpdAsymmtryAdjstmn;</v>
-      </c>
-    </row>
-    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
+        <v>EEC3_Aftertreatment2IntakeDewPoint</v>
+      </c>
+      <c r="M41" t="str">
+        <f t="shared" si="1"/>
+        <v>GVL_J1939.EEC3_Aftertreatment2IntakeDewPoint</v>
+      </c>
+      <c r="N41" t="str">
+        <f t="shared" si="2"/>
+        <v>GVL_J1939.EEC3_Aftertreatment2IntakeDewPoint;</v>
+      </c>
+      <c r="O41" t="str">
+        <f t="shared" si="3"/>
+        <v>EEC3_Aftertreatment2IntakeDewPoint:USINT; // SPN:3239</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>41</v>
+      </c>
       <c r="B42" t="s">
         <v>898</v>
       </c>
       <c r="C42" t="s">
-        <v>1025</v>
-      </c>
-      <c r="H42" t="s">
+        <v>1028</v>
+      </c>
+      <c r="D42" s="35">
+        <v>3240</v>
+      </c>
+      <c r="J42" t="s">
+        <v>983</v>
+      </c>
+      <c r="L42" t="str">
+        <f t="shared" si="0"/>
+        <v>EEC3_Aftertreatment2ExhaustDewPoint</v>
+      </c>
+      <c r="M42" t="str">
+        <f t="shared" si="1"/>
+        <v>GVL_J1939.EEC3_Aftertreatment2ExhaustDewPoint</v>
+      </c>
+      <c r="N42" t="str">
+        <f t="shared" si="2"/>
+        <v>GVL_J1939.EEC3_Aftertreatment2ExhaustDewPoint;</v>
+      </c>
+      <c r="O42" t="str">
+        <f t="shared" si="3"/>
+        <v>EEC3_Aftertreatment2ExhaustDewPoint:USINT; // SPN:3240</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" t="s">
+        <v>946</v>
+      </c>
+      <c r="C43" t="s">
+        <v>1030</v>
+      </c>
+      <c r="D43" s="35">
+        <v>2789</v>
+      </c>
+      <c r="J43" t="s">
+        <v>984</v>
+      </c>
+      <c r="L43" t="str">
+        <f t="shared" si="0"/>
+        <v>EEC5_EngTrb1ClcltedTurbineIntakeTemp</v>
+      </c>
+      <c r="M43" t="str">
+        <f t="shared" si="1"/>
+        <v>GVL_J1939.EEC5_EngTrb1ClcltedTurbineIntakeTemp</v>
+      </c>
+      <c r="N43" t="str">
+        <f t="shared" si="2"/>
+        <v>GVL_J1939.EEC5_EngTrb1ClcltedTurbineIntakeTemp;</v>
+      </c>
+      <c r="O43" t="str">
+        <f t="shared" si="3"/>
+        <v>EEC5_EngTrb1ClcltedTurbineIntakeTemp:REAL; // SPN:2789</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44" t="s">
+        <v>946</v>
+      </c>
+      <c r="C44" t="s">
+        <v>1031</v>
+      </c>
+      <c r="D44" s="35">
+        <v>2790</v>
+      </c>
+      <c r="J44" t="s">
+        <v>984</v>
+      </c>
+      <c r="L44" t="str">
+        <f t="shared" si="0"/>
+        <v>EEC5_EngTrb1ClcltedTurbineOutletTemp</v>
+      </c>
+      <c r="M44" t="str">
+        <f t="shared" si="1"/>
+        <v>GVL_J1939.EEC5_EngTrb1ClcltedTurbineOutletTemp</v>
+      </c>
+      <c r="N44" t="str">
+        <f t="shared" si="2"/>
+        <v>GVL_J1939.EEC5_EngTrb1ClcltedTurbineOutletTemp;</v>
+      </c>
+      <c r="O44" t="str">
+        <f t="shared" si="3"/>
+        <v>EEC5_EngTrb1ClcltedTurbineOutletTemp:REAL; // SPN:2790</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45" t="s">
+        <v>946</v>
+      </c>
+      <c r="C45" t="s">
+        <v>1032</v>
+      </c>
+      <c r="D45" s="35">
+        <v>2791</v>
+      </c>
+      <c r="E45" t="s">
+        <v>682</v>
+      </c>
+      <c r="J45" t="s">
+        <v>984</v>
+      </c>
+      <c r="L45" t="str">
+        <f t="shared" si="0"/>
+        <v>EEC5_EngExhstGsRcrculation1ValveCtrl</v>
+      </c>
+      <c r="M45" t="str">
+        <f t="shared" si="1"/>
+        <v>GVL_J1939.EEC5_EngExhstGsRcrculation1ValveCtrl</v>
+      </c>
+      <c r="N45" t="str">
+        <f t="shared" si="2"/>
+        <v>GVL_J1939.EEC5_EngExhstGsRcrculation1ValveCtrl;</v>
+      </c>
+      <c r="O45" t="str">
+        <f t="shared" si="3"/>
+        <v>EEC5_EngExhstGsRcrculation1ValveCtrl:REAL; // SPN:2791</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46" t="s">
+        <v>946</v>
+      </c>
+      <c r="C46" t="s">
+        <v>1033</v>
+      </c>
+      <c r="D46" s="35">
+        <v>2792</v>
+      </c>
+      <c r="J46" t="s">
+        <v>983</v>
+      </c>
+      <c r="L46" t="str">
+        <f t="shared" si="0"/>
+        <v>EEC5_EngVrblGmtryTrbArCtrlShtffValve</v>
+      </c>
+      <c r="M46" t="str">
+        <f t="shared" si="1"/>
+        <v>GVL_J1939.EEC5_EngVrblGmtryTrbArCtrlShtffValve</v>
+      </c>
+      <c r="N46" t="str">
+        <f t="shared" si="2"/>
+        <v>GVL_J1939.EEC5_EngVrblGmtryTrbArCtrlShtffValve;</v>
+      </c>
+      <c r="O46" t="str">
+        <f t="shared" si="3"/>
+        <v>EEC5_EngVrblGmtryTrbArCtrlShtffValve:USINT; // SPN:2792</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47" t="s">
+        <v>946</v>
+      </c>
+      <c r="C47" t="s">
+        <v>1034</v>
+      </c>
+      <c r="D47" s="35">
+        <v>5457</v>
+      </c>
+      <c r="J47" t="s">
+        <v>983</v>
+      </c>
+      <c r="L47" t="str">
+        <f t="shared" si="0"/>
+        <v>EEC5_EngVrableGeometryTurbo1CtrlMode</v>
+      </c>
+      <c r="M47" t="str">
+        <f t="shared" si="1"/>
+        <v>GVL_J1939.EEC5_EngVrableGeometryTurbo1CtrlMode</v>
+      </c>
+      <c r="N47" t="str">
+        <f t="shared" si="2"/>
+        <v>GVL_J1939.EEC5_EngVrableGeometryTurbo1CtrlMode;</v>
+      </c>
+      <c r="O47" t="str">
+        <f t="shared" si="3"/>
+        <v>EEC5_EngVrableGeometryTurbo1CtrlMode:USINT; // SPN:5457</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48" t="s">
+        <v>946</v>
+      </c>
+      <c r="C48" t="s">
+        <v>1035</v>
+      </c>
+      <c r="D48" s="35">
+        <v>2795</v>
+      </c>
+      <c r="J48" t="s">
+        <v>984</v>
+      </c>
+      <c r="L48" t="str">
+        <f t="shared" si="0"/>
+        <v>EEC5_EngVrblGometryTurbo1ActuatorPos</v>
+      </c>
+      <c r="M48" t="str">
+        <f t="shared" si="1"/>
+        <v>GVL_J1939.EEC5_EngVrblGometryTurbo1ActuatorPos</v>
+      </c>
+      <c r="N48" t="str">
+        <f t="shared" si="2"/>
+        <v>GVL_J1939.EEC5_EngVrblGometryTurbo1ActuatorPos;</v>
+      </c>
+      <c r="O48" t="str">
+        <f t="shared" si="3"/>
+        <v>EEC5_EngVrblGometryTurbo1ActuatorPos:REAL; // SPN:2795</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49" t="s">
+        <v>900</v>
+      </c>
+      <c r="C49" t="s">
+        <v>1036</v>
+      </c>
+      <c r="D49" s="35">
+        <v>1637</v>
+      </c>
+      <c r="E49" t="s">
+        <v>682</v>
+      </c>
+      <c r="J49" t="s">
+        <v>984</v>
+      </c>
+      <c r="L49" t="str">
+        <f t="shared" si="0"/>
+        <v>ET1_EngCoolantTemp</v>
+      </c>
+      <c r="M49" t="str">
+        <f t="shared" si="1"/>
+        <v>GVL_J1939.ET1_EngCoolantTemp</v>
+      </c>
+      <c r="N49" t="str">
+        <f t="shared" si="2"/>
+        <v>GVL_J1939.ET1_EngCoolantTemp;</v>
+      </c>
+      <c r="O49" t="str">
+        <f t="shared" si="3"/>
+        <v>ET1_EngCoolantTemp:REAL; // SPN:1637</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50" t="s">
+        <v>900</v>
+      </c>
+      <c r="C50" t="s">
+        <v>1037</v>
+      </c>
+      <c r="D50" s="35">
+        <v>174</v>
+      </c>
+      <c r="E50" t="s">
+        <v>682</v>
+      </c>
+      <c r="J50" t="s">
         <v>985</v>
       </c>
-      <c r="J42" t="str">
+      <c r="L50" t="str">
         <f t="shared" si="0"/>
-        <v>EstEngPrsticLossesPercentTorque;</v>
-      </c>
-    </row>
-    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B43" t="s">
-        <v>898</v>
-      </c>
-      <c r="C43" t="s">
-        <v>1026</v>
-      </c>
-      <c r="H43" t="s">
+        <v>ET1_EngFuelTemp1</v>
+      </c>
+      <c r="M50" t="str">
+        <f t="shared" si="1"/>
+        <v>GVL_J1939.ET1_EngFuelTemp1</v>
+      </c>
+      <c r="N50" t="str">
+        <f t="shared" si="2"/>
+        <v>GVL_J1939.ET1_EngFuelTemp1;</v>
+      </c>
+      <c r="O50" t="str">
+        <f t="shared" si="3"/>
+        <v>ET1_EngFuelTemp1:INT; // SPN:174</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51" t="s">
+        <v>900</v>
+      </c>
+      <c r="C51" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D51" s="35">
+        <v>175</v>
+      </c>
+      <c r="J51" t="s">
         <v>984</v>
       </c>
-      <c r="J43" t="str">
+      <c r="L51" t="str">
         <f t="shared" si="0"/>
-        <v>Aftrtratment1ExhaustGasMassFlow;</v>
-      </c>
-    </row>
-    <row r="44" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B44" t="s">
-        <v>898</v>
-      </c>
-      <c r="C44" t="s">
-        <v>1027</v>
-      </c>
-      <c r="H44" t="s">
+        <v>ET1_EngOilTemp1</v>
+      </c>
+      <c r="M51" t="str">
+        <f t="shared" si="1"/>
+        <v>GVL_J1939.ET1_EngOilTemp1</v>
+      </c>
+      <c r="N51" t="str">
+        <f t="shared" si="2"/>
+        <v>GVL_J1939.ET1_EngOilTemp1;</v>
+      </c>
+      <c r="O51" t="str">
+        <f t="shared" si="3"/>
+        <v>ET1_EngOilTemp1:REAL; // SPN:175</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52" t="s">
+        <v>900</v>
+      </c>
+      <c r="C52" t="s">
+        <v>1039</v>
+      </c>
+      <c r="D52" s="35">
+        <v>176</v>
+      </c>
+      <c r="J52" t="s">
+        <v>984</v>
+      </c>
+      <c r="L52" t="str">
+        <f t="shared" si="0"/>
+        <v>ET1_EngTurboOilTemp</v>
+      </c>
+      <c r="M52" t="str">
+        <f t="shared" si="1"/>
+        <v>GVL_J1939.ET1_EngTurboOilTemp</v>
+      </c>
+      <c r="N52" t="str">
+        <f t="shared" si="2"/>
+        <v>GVL_J1939.ET1_EngTurboOilTemp;</v>
+      </c>
+      <c r="O52" t="str">
+        <f t="shared" si="3"/>
+        <v>ET1_EngTurboOilTemp:REAL; // SPN:176</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53" t="s">
+        <v>900</v>
+      </c>
+      <c r="C53" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D53" s="35">
+        <v>52</v>
+      </c>
+      <c r="J53" t="s">
+        <v>985</v>
+      </c>
+      <c r="L53" t="str">
+        <f t="shared" si="0"/>
+        <v>ET1_EngIntercoolerTemp</v>
+      </c>
+      <c r="M53" t="str">
+        <f t="shared" si="1"/>
+        <v>GVL_J1939.ET1_EngIntercoolerTemp</v>
+      </c>
+      <c r="N53" t="str">
+        <f t="shared" si="2"/>
+        <v>GVL_J1939.ET1_EngIntercoolerTemp;</v>
+      </c>
+      <c r="O53" t="str">
+        <f t="shared" si="3"/>
+        <v>ET1_EngIntercoolerTemp:INT; // SPN:52</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54" t="s">
+        <v>900</v>
+      </c>
+      <c r="C54" t="s">
+        <v>1041</v>
+      </c>
+      <c r="D54" s="35">
+        <v>1134</v>
+      </c>
+      <c r="J54" t="s">
+        <v>984</v>
+      </c>
+      <c r="L54" t="str">
+        <f t="shared" si="0"/>
+        <v>ET1_EngIntercoolerThermostatOpening</v>
+      </c>
+      <c r="M54" t="str">
+        <f t="shared" si="1"/>
+        <v>GVL_J1939.ET1_EngIntercoolerThermostatOpening</v>
+      </c>
+      <c r="N54" t="str">
+        <f t="shared" si="2"/>
+        <v>GVL_J1939.ET1_EngIntercoolerThermostatOpening;</v>
+      </c>
+      <c r="O54" t="str">
+        <f t="shared" si="3"/>
+        <v>ET1_EngIntercoolerThermostatOpening:REAL; // SPN:1134</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55" t="s">
+        <v>1050</v>
+      </c>
+      <c r="C55" t="s">
+        <v>1042</v>
+      </c>
+      <c r="D55" s="35">
+        <v>94</v>
+      </c>
+      <c r="J55" t="s">
+        <v>1049</v>
+      </c>
+      <c r="L55" t="str">
+        <f t="shared" si="0"/>
+        <v>EFL_P1_EngFuelDeliveryPress</v>
+      </c>
+      <c r="M55" t="str">
+        <f t="shared" si="1"/>
+        <v>GVL_J1939.EFL_P1_EngFuelDeliveryPress</v>
+      </c>
+      <c r="N55" t="str">
+        <f t="shared" si="2"/>
+        <v>GVL_J1939.EFL_P1_EngFuelDeliveryPress;</v>
+      </c>
+      <c r="O55" t="str">
+        <f t="shared" si="3"/>
+        <v>EFL_P1_EngFuelDeliveryPress:UINT; // SPN:94</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56" t="s">
+        <v>1050</v>
+      </c>
+      <c r="C56" t="s">
+        <v>1043</v>
+      </c>
+      <c r="D56" s="35">
+        <v>22</v>
+      </c>
+      <c r="J56" t="s">
+        <v>984</v>
+      </c>
+      <c r="L56" t="str">
+        <f t="shared" si="0"/>
+        <v>EFL_P1_EngExCrankcaseBlowbyPress</v>
+      </c>
+      <c r="M56" t="str">
+        <f t="shared" si="1"/>
+        <v>GVL_J1939.EFL_P1_EngExCrankcaseBlowbyPress</v>
+      </c>
+      <c r="N56" t="str">
+        <f t="shared" si="2"/>
+        <v>GVL_J1939.EFL_P1_EngExCrankcaseBlowbyPress;</v>
+      </c>
+      <c r="O56" t="str">
+        <f t="shared" si="3"/>
+        <v>EFL_P1_EngExCrankcaseBlowbyPress:REAL; // SPN:22</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57" t="s">
+        <v>1050</v>
+      </c>
+      <c r="C57" t="s">
+        <v>1044</v>
+      </c>
+      <c r="D57" s="35">
+        <v>98</v>
+      </c>
+      <c r="J57" t="s">
+        <v>984</v>
+      </c>
+      <c r="L57" t="str">
+        <f t="shared" si="0"/>
+        <v>EFL_P1_EngOilLevel</v>
+      </c>
+      <c r="M57" t="str">
+        <f t="shared" si="1"/>
+        <v>GVL_J1939.EFL_P1_EngOilLevel</v>
+      </c>
+      <c r="N57" t="str">
+        <f t="shared" si="2"/>
+        <v>GVL_J1939.EFL_P1_EngOilLevel;</v>
+      </c>
+      <c r="O57" t="str">
+        <f t="shared" si="3"/>
+        <v>EFL_P1_EngOilLevel:REAL; // SPN:98</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58" t="s">
+        <v>1050</v>
+      </c>
+      <c r="C58" t="s">
+        <v>1045</v>
+      </c>
+      <c r="D58" s="35">
+        <v>100</v>
+      </c>
+      <c r="E58" t="s">
+        <v>682</v>
+      </c>
+      <c r="J58" t="s">
+        <v>1049</v>
+      </c>
+      <c r="L58" t="str">
+        <f t="shared" si="0"/>
+        <v>EFL_P1_EngOilPress</v>
+      </c>
+      <c r="M58" t="str">
+        <f t="shared" si="1"/>
+        <v>GVL_J1939.EFL_P1_EngOilPress</v>
+      </c>
+      <c r="N58" t="str">
+        <f t="shared" si="2"/>
+        <v>GVL_J1939.EFL_P1_EngOilPress;</v>
+      </c>
+      <c r="O58" t="str">
+        <f t="shared" si="3"/>
+        <v>EFL_P1_EngOilPress:UINT; // SPN:100</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59" t="s">
+        <v>1050</v>
+      </c>
+      <c r="C59" t="s">
+        <v>1046</v>
+      </c>
+      <c r="D59" s="35">
+        <v>101</v>
+      </c>
+      <c r="J59" t="s">
+        <v>1029</v>
+      </c>
+      <c r="L59" t="str">
+        <f t="shared" si="0"/>
+        <v>EFL_P1_EngCrankcasePress</v>
+      </c>
+      <c r="M59" t="str">
+        <f t="shared" si="1"/>
+        <v>GVL_J1939.EFL_P1_EngCrankcasePress</v>
+      </c>
+      <c r="N59" t="str">
+        <f t="shared" si="2"/>
+        <v>GVL_J1939.EFL_P1_EngCrankcasePress;</v>
+      </c>
+      <c r="O59" t="str">
+        <f t="shared" si="3"/>
+        <v>EFL_P1_EngCrankcasePress:REAl; // SPN:101</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60" t="s">
+        <v>1050</v>
+      </c>
+      <c r="C60" t="s">
+        <v>1047</v>
+      </c>
+      <c r="D60" s="35">
+        <v>109</v>
+      </c>
+      <c r="J60" t="s">
+        <v>1049</v>
+      </c>
+      <c r="L60" t="str">
+        <f t="shared" si="0"/>
+        <v>EFL_P1_EngCoolantPress</v>
+      </c>
+      <c r="M60" t="str">
+        <f t="shared" si="1"/>
+        <v>GVL_J1939.EFL_P1_EngCoolantPress</v>
+      </c>
+      <c r="N60" t="str">
+        <f t="shared" si="2"/>
+        <v>GVL_J1939.EFL_P1_EngCoolantPress;</v>
+      </c>
+      <c r="O60" t="str">
+        <f t="shared" si="3"/>
+        <v>EFL_P1_EngCoolantPress:UINT; // SPN:109</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61" t="s">
+        <v>1050</v>
+      </c>
+      <c r="C61" t="s">
+        <v>1048</v>
+      </c>
+      <c r="D61" s="35">
+        <v>111</v>
+      </c>
+      <c r="E61" t="s">
+        <v>682</v>
+      </c>
+      <c r="J61" t="s">
+        <v>984</v>
+      </c>
+      <c r="L61" t="str">
+        <f t="shared" si="0"/>
+        <v>EFL_P1_EngCoolantLevel</v>
+      </c>
+      <c r="M61" t="str">
+        <f t="shared" si="1"/>
+        <v>GVL_J1939.EFL_P1_EngCoolantLevel</v>
+      </c>
+      <c r="N61" t="str">
+        <f t="shared" si="2"/>
+        <v>GVL_J1939.EFL_P1_EngCoolantLevel;</v>
+      </c>
+      <c r="O61" t="str">
+        <f t="shared" si="3"/>
+        <v>EFL_P1_EngCoolantLevel:REAL; // SPN:111</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62" t="s">
+        <v>972</v>
+      </c>
+      <c r="C62" t="s">
+        <v>1051</v>
+      </c>
+      <c r="D62" s="35">
+        <v>164</v>
+      </c>
+      <c r="J62" t="s">
+        <v>1055</v>
+      </c>
+      <c r="L62" t="str">
+        <f t="shared" si="0"/>
+        <v>EFL_P2_EngInjectionCtrlPress</v>
+      </c>
+      <c r="M62" t="str">
+        <f t="shared" si="1"/>
+        <v>GVL_J1939.EFL_P2_EngInjectionCtrlPress</v>
+      </c>
+      <c r="N62" t="str">
+        <f t="shared" si="2"/>
+        <v>GVL_J1939.EFL_P2_EngInjectionCtrlPress;</v>
+      </c>
+      <c r="O62" t="str">
+        <f t="shared" si="3"/>
+        <v>EFL_P2_EngInjectionCtrlPress:LREAL; // SPN:164</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>62</v>
+      </c>
+      <c r="B63" t="s">
+        <v>972</v>
+      </c>
+      <c r="C63" t="s">
+        <v>1052</v>
+      </c>
+      <c r="D63" s="35">
+        <v>157</v>
+      </c>
+      <c r="E63" t="s">
+        <v>682</v>
+      </c>
+      <c r="J63" t="s">
+        <v>1055</v>
+      </c>
+      <c r="L63" t="str">
+        <f t="shared" si="0"/>
+        <v>EFL_P2_EngInjectorMeteringRail1Press</v>
+      </c>
+      <c r="M63" t="str">
+        <f t="shared" si="1"/>
+        <v>GVL_J1939.EFL_P2_EngInjectorMeteringRail1Press</v>
+      </c>
+      <c r="N63" t="str">
+        <f t="shared" si="2"/>
+        <v>GVL_J1939.EFL_P2_EngInjectorMeteringRail1Press;</v>
+      </c>
+      <c r="O63" t="str">
+        <f t="shared" si="3"/>
+        <v>EFL_P2_EngInjectorMeteringRail1Press:LREAL; // SPN:157</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64" t="s">
+        <v>972</v>
+      </c>
+      <c r="C64" t="s">
+        <v>1053</v>
+      </c>
+      <c r="D64" s="35">
+        <v>156</v>
+      </c>
+      <c r="J64" t="s">
+        <v>1055</v>
+      </c>
+      <c r="L64" t="str">
+        <f t="shared" si="0"/>
+        <v>EFL_P2_EngInjectorTimingRail1Press</v>
+      </c>
+      <c r="M64" t="str">
+        <f t="shared" si="1"/>
+        <v>GVL_J1939.EFL_P2_EngInjectorTimingRail1Press</v>
+      </c>
+      <c r="N64" t="str">
+        <f t="shared" si="2"/>
+        <v>GVL_J1939.EFL_P2_EngInjectorTimingRail1Press;</v>
+      </c>
+      <c r="O64" t="str">
+        <f t="shared" si="3"/>
+        <v>EFL_P2_EngInjectorTimingRail1Press:LREAL; // SPN:156</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65" t="s">
+        <v>972</v>
+      </c>
+      <c r="C65" t="s">
+        <v>1054</v>
+      </c>
+      <c r="D65" s="35">
+        <v>1349</v>
+      </c>
+      <c r="J65" t="s">
+        <v>1055</v>
+      </c>
+      <c r="L65" t="str">
+        <f t="shared" si="0"/>
+        <v>EFL_P2_EngInjectorMeteringRail2Press</v>
+      </c>
+      <c r="M65" t="str">
+        <f t="shared" si="1"/>
+        <v>GVL_J1939.EFL_P2_EngInjectorMeteringRail2Press</v>
+      </c>
+      <c r="N65" t="str">
+        <f t="shared" si="2"/>
+        <v>GVL_J1939.EFL_P2_EngInjectorMeteringRail2Press;</v>
+      </c>
+      <c r="O65" t="str">
+        <f t="shared" si="3"/>
+        <v>EFL_P2_EngInjectorMeteringRail2Press:LREAL; // SPN:1349</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66" t="s">
+        <v>903</v>
+      </c>
+      <c r="C66" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D66" s="35">
+        <v>182</v>
+      </c>
+      <c r="J66" t="s">
+        <v>984</v>
+      </c>
+      <c r="L66" t="str">
+        <f t="shared" si="0"/>
+        <v>LFC_EngTripFuel</v>
+      </c>
+      <c r="M66" t="str">
+        <f t="shared" si="1"/>
+        <v>GVL_J1939.LFC_EngTripFuel</v>
+      </c>
+      <c r="N66" t="str">
+        <f t="shared" si="2"/>
+        <v>GVL_J1939.LFC_EngTripFuel;</v>
+      </c>
+      <c r="O66" t="str">
+        <f t="shared" si="3"/>
+        <v>LFC_EngTripFuel:REAL; // SPN:182</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>66</v>
+      </c>
+      <c r="B67" t="s">
+        <v>903</v>
+      </c>
+      <c r="C67" t="s">
+        <v>1057</v>
+      </c>
+      <c r="D67" s="35">
+        <v>250</v>
+      </c>
+      <c r="E67" t="s">
+        <v>682</v>
+      </c>
+      <c r="J67" t="s">
+        <v>984</v>
+      </c>
+      <c r="L67" t="str">
+        <f t="shared" ref="L67:L130" si="4">IF(C67&lt;&gt;"",_xlfn.CONCAT(B67,"_",C67),"")</f>
+        <v>LFC_EngTotalFuelUsed</v>
+      </c>
+      <c r="M67" t="str">
+        <f t="shared" ref="M67:M130" si="5">_xlfn.CONCAT($M$1,L67)</f>
+        <v>GVL_J1939.LFC_EngTotalFuelUsed</v>
+      </c>
+      <c r="N67" t="str">
+        <f t="shared" ref="N67:N130" si="6">_xlfn.CONCAT(M67,";")</f>
+        <v>GVL_J1939.LFC_EngTotalFuelUsed;</v>
+      </c>
+      <c r="O67" t="str">
+        <f t="shared" ref="O67:O130" si="7">_xlfn.CONCAT(L67,":",J67,"; // SPN:",D67)</f>
+        <v>LFC_EngTotalFuelUsed:REAL; // SPN:250</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>67</v>
+      </c>
+      <c r="B68" t="s">
+        <v>930</v>
+      </c>
+      <c r="C68" t="s">
+        <v>1058</v>
+      </c>
+      <c r="D68" s="35">
+        <v>108</v>
+      </c>
+      <c r="E68" t="s">
+        <v>682</v>
+      </c>
+      <c r="J68" t="s">
+        <v>984</v>
+      </c>
+      <c r="L68" t="str">
+        <f t="shared" si="4"/>
+        <v>AMB_BarometricPress</v>
+      </c>
+      <c r="M68" t="str">
+        <f t="shared" si="5"/>
+        <v>GVL_J1939.AMB_BarometricPress</v>
+      </c>
+      <c r="N68" t="str">
+        <f t="shared" si="6"/>
+        <v>GVL_J1939.AMB_BarometricPress;</v>
+      </c>
+      <c r="O68" t="str">
+        <f t="shared" si="7"/>
+        <v>AMB_BarometricPress:REAL; // SPN:108</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>68</v>
+      </c>
+      <c r="B69" t="s">
+        <v>930</v>
+      </c>
+      <c r="C69" t="s">
+        <v>1059</v>
+      </c>
+      <c r="D69" s="35">
+        <v>170</v>
+      </c>
+      <c r="J69" t="s">
+        <v>984</v>
+      </c>
+      <c r="L69" t="str">
+        <f t="shared" si="4"/>
+        <v>AMB_CabInteriorTemp</v>
+      </c>
+      <c r="M69" t="str">
+        <f t="shared" si="5"/>
+        <v>GVL_J1939.AMB_CabInteriorTemp</v>
+      </c>
+      <c r="N69" t="str">
+        <f t="shared" si="6"/>
+        <v>GVL_J1939.AMB_CabInteriorTemp;</v>
+      </c>
+      <c r="O69" t="str">
+        <f t="shared" si="7"/>
+        <v>AMB_CabInteriorTemp:REAL; // SPN:170</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>69</v>
+      </c>
+      <c r="B70" t="s">
+        <v>930</v>
+      </c>
+      <c r="C70" t="s">
+        <v>1060</v>
+      </c>
+      <c r="D70" s="35">
+        <v>171</v>
+      </c>
+      <c r="E70" t="s">
+        <v>682</v>
+      </c>
+      <c r="J70" t="s">
+        <v>984</v>
+      </c>
+      <c r="L70" t="str">
+        <f t="shared" si="4"/>
+        <v>AMB_AmbientAirTemp</v>
+      </c>
+      <c r="M70" t="str">
+        <f t="shared" si="5"/>
+        <v>GVL_J1939.AMB_AmbientAirTemp</v>
+      </c>
+      <c r="N70" t="str">
+        <f t="shared" si="6"/>
+        <v>GVL_J1939.AMB_AmbientAirTemp;</v>
+      </c>
+      <c r="O70" t="str">
+        <f t="shared" si="7"/>
+        <v>AMB_AmbientAirTemp:REAL; // SPN:171</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>70</v>
+      </c>
+      <c r="B71" t="s">
+        <v>930</v>
+      </c>
+      <c r="C71" t="s">
+        <v>1061</v>
+      </c>
+      <c r="D71" s="35">
+        <v>172</v>
+      </c>
+      <c r="E71" t="s">
+        <v>682</v>
+      </c>
+      <c r="J71" t="s">
+        <v>985</v>
+      </c>
+      <c r="L71" t="str">
+        <f t="shared" si="4"/>
+        <v>AMB_EngAirIntakeTemp</v>
+      </c>
+      <c r="M71" t="str">
+        <f t="shared" si="5"/>
+        <v>GVL_J1939.AMB_EngAirIntakeTemp</v>
+      </c>
+      <c r="N71" t="str">
+        <f t="shared" si="6"/>
+        <v>GVL_J1939.AMB_EngAirIntakeTemp;</v>
+      </c>
+      <c r="O71" t="str">
+        <f t="shared" si="7"/>
+        <v>AMB_EngAirIntakeTemp:INT; // SPN:172</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>71</v>
+      </c>
+      <c r="B72" t="s">
+        <v>930</v>
+      </c>
+      <c r="C72" t="s">
+        <v>1062</v>
+      </c>
+      <c r="D72" s="35">
+        <v>79</v>
+      </c>
+      <c r="J72" t="s">
+        <v>984</v>
+      </c>
+      <c r="L72" t="str">
+        <f t="shared" si="4"/>
+        <v>AMB_RoadSurfaceTemp</v>
+      </c>
+      <c r="M72" t="str">
+        <f t="shared" si="5"/>
+        <v>GVL_J1939.AMB_RoadSurfaceTemp</v>
+      </c>
+      <c r="N72" t="str">
+        <f t="shared" si="6"/>
+        <v>GVL_J1939.AMB_RoadSurfaceTemp;</v>
+      </c>
+      <c r="O72" t="str">
+        <f t="shared" si="7"/>
+        <v>AMB_RoadSurfaceTemp:REAL; // SPN:79</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>72</v>
+      </c>
+      <c r="B73" t="s">
+        <v>1070</v>
+      </c>
+      <c r="C73" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D73" s="35">
+        <v>81</v>
+      </c>
+      <c r="J73" t="s">
+        <v>984</v>
+      </c>
+      <c r="L73" t="str">
+        <f t="shared" si="4"/>
+        <v>IC1_EngDslPrtclateFilterIntakePress</v>
+      </c>
+      <c r="M73" t="str">
+        <f t="shared" si="5"/>
+        <v>GVL_J1939.IC1_EngDslPrtclateFilterIntakePress</v>
+      </c>
+      <c r="N73" t="str">
+        <f t="shared" si="6"/>
+        <v>GVL_J1939.IC1_EngDslPrtclateFilterIntakePress;</v>
+      </c>
+      <c r="O73" t="str">
+        <f t="shared" si="7"/>
+        <v>IC1_EngDslPrtclateFilterIntakePress:REAL; // SPN:81</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>73</v>
+      </c>
+      <c r="B74" t="s">
+        <v>1070</v>
+      </c>
+      <c r="C74" t="s">
+        <v>1064</v>
+      </c>
+      <c r="D74" s="35">
+        <v>102</v>
+      </c>
+      <c r="E74" t="s">
+        <v>682</v>
+      </c>
+      <c r="J74" t="s">
+        <v>1049</v>
+      </c>
+      <c r="L74" t="str">
+        <f t="shared" si="4"/>
+        <v>IC1_EngIntakeManifold1Press</v>
+      </c>
+      <c r="M74" t="str">
+        <f t="shared" si="5"/>
+        <v>GVL_J1939.IC1_EngIntakeManifold1Press</v>
+      </c>
+      <c r="N74" t="str">
+        <f t="shared" si="6"/>
+        <v>GVL_J1939.IC1_EngIntakeManifold1Press;</v>
+      </c>
+      <c r="O74" t="str">
+        <f t="shared" si="7"/>
+        <v>IC1_EngIntakeManifold1Press:UINT; // SPN:102</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>74</v>
+      </c>
+      <c r="B75" t="s">
+        <v>1070</v>
+      </c>
+      <c r="C75" t="s">
+        <v>1065</v>
+      </c>
+      <c r="D75" s="35">
+        <v>105</v>
+      </c>
+      <c r="E75" t="s">
+        <v>682</v>
+      </c>
+      <c r="J75" t="s">
+        <v>985</v>
+      </c>
+      <c r="L75" t="str">
+        <f t="shared" si="4"/>
+        <v>IC1_EngIntakeManifold1Temp</v>
+      </c>
+      <c r="M75" t="str">
+        <f t="shared" si="5"/>
+        <v>GVL_J1939.IC1_EngIntakeManifold1Temp</v>
+      </c>
+      <c r="N75" t="str">
+        <f t="shared" si="6"/>
+        <v>GVL_J1939.IC1_EngIntakeManifold1Temp;</v>
+      </c>
+      <c r="O75" t="str">
+        <f t="shared" si="7"/>
+        <v>IC1_EngIntakeManifold1Temp:INT; // SPN:105</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>75</v>
+      </c>
+      <c r="B76" t="s">
+        <v>1070</v>
+      </c>
+      <c r="C76" t="s">
+        <v>1066</v>
+      </c>
+      <c r="D76" s="35">
+        <v>106</v>
+      </c>
+      <c r="E76" t="s">
+        <v>682</v>
+      </c>
+      <c r="J76" t="s">
+        <v>1049</v>
+      </c>
+      <c r="L76" t="str">
+        <f t="shared" si="4"/>
+        <v>IC1_EngAirIntakePress</v>
+      </c>
+      <c r="M76" t="str">
+        <f t="shared" si="5"/>
+        <v>GVL_J1939.IC1_EngAirIntakePress</v>
+      </c>
+      <c r="N76" t="str">
+        <f t="shared" si="6"/>
+        <v>GVL_J1939.IC1_EngAirIntakePress;</v>
+      </c>
+      <c r="O76" t="str">
+        <f t="shared" si="7"/>
+        <v>IC1_EngAirIntakePress:UINT; // SPN:106</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>76</v>
+      </c>
+      <c r="B77" t="s">
+        <v>1070</v>
+      </c>
+      <c r="C77" t="s">
+        <v>1067</v>
+      </c>
+      <c r="D77" s="35">
+        <v>107</v>
+      </c>
+      <c r="J77" t="s">
+        <v>984</v>
+      </c>
+      <c r="L77" t="str">
+        <f t="shared" si="4"/>
+        <v>IC1_EngAirFilter1DiffPress</v>
+      </c>
+      <c r="M77" t="str">
+        <f t="shared" si="5"/>
+        <v>GVL_J1939.IC1_EngAirFilter1DiffPress</v>
+      </c>
+      <c r="N77" t="str">
+        <f t="shared" si="6"/>
+        <v>GVL_J1939.IC1_EngAirFilter1DiffPress;</v>
+      </c>
+      <c r="O77" t="str">
+        <f t="shared" si="7"/>
+        <v>IC1_EngAirFilter1DiffPress:REAL; // SPN:107</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>77</v>
+      </c>
+      <c r="B78" t="s">
+        <v>1070</v>
+      </c>
+      <c r="C78" t="s">
+        <v>1068</v>
+      </c>
+      <c r="D78" s="35">
+        <v>173</v>
+      </c>
+      <c r="J78" t="s">
+        <v>984</v>
+      </c>
+      <c r="L78" t="str">
+        <f t="shared" si="4"/>
+        <v>IC1_EngExhaustGasTemp</v>
+      </c>
+      <c r="M78" t="str">
+        <f t="shared" si="5"/>
+        <v>GVL_J1939.IC1_EngExhaustGasTemp</v>
+      </c>
+      <c r="N78" t="str">
+        <f t="shared" si="6"/>
+        <v>GVL_J1939.IC1_EngExhaustGasTemp;</v>
+      </c>
+      <c r="O78" t="str">
+        <f t="shared" si="7"/>
+        <v>IC1_EngExhaustGasTemp:REAL; // SPN:173</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>78</v>
+      </c>
+      <c r="B79" t="s">
+        <v>1070</v>
+      </c>
+      <c r="C79" t="s">
+        <v>1069</v>
+      </c>
+      <c r="D79" s="35">
+        <v>112</v>
+      </c>
+      <c r="J79" t="s">
+        <v>984</v>
+      </c>
+      <c r="L79" t="str">
+        <f t="shared" si="4"/>
+        <v>IC1_EngCoolantFilterDiffPress</v>
+      </c>
+      <c r="M79" t="str">
+        <f t="shared" si="5"/>
+        <v>GVL_J1939.IC1_EngCoolantFilterDiffPress</v>
+      </c>
+      <c r="N79" t="str">
+        <f t="shared" si="6"/>
+        <v>GVL_J1939.IC1_EngCoolantFilterDiffPress;</v>
+      </c>
+      <c r="O79" t="str">
+        <f t="shared" si="7"/>
+        <v>IC1_EngCoolantFilterDiffPress:REAL; // SPN:112</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>79</v>
+      </c>
+      <c r="B80" t="s">
+        <v>928</v>
+      </c>
+      <c r="C80" t="s">
+        <v>1071</v>
+      </c>
+      <c r="D80" s="35">
+        <v>114</v>
+      </c>
+      <c r="J80" t="s">
+        <v>985</v>
+      </c>
+      <c r="L80" t="str">
+        <f t="shared" si="4"/>
+        <v>VEP1_NetBatteryCurrent</v>
+      </c>
+      <c r="M80" t="str">
+        <f t="shared" si="5"/>
+        <v>GVL_J1939.VEP1_NetBatteryCurrent</v>
+      </c>
+      <c r="N80" t="str">
+        <f t="shared" si="6"/>
+        <v>GVL_J1939.VEP1_NetBatteryCurrent;</v>
+      </c>
+      <c r="O80" t="str">
+        <f t="shared" si="7"/>
+        <v>VEP1_NetBatteryCurrent:INT; // SPN:114</v>
+      </c>
+    </row>
+    <row r="81" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>80</v>
+      </c>
+      <c r="B81" t="s">
+        <v>928</v>
+      </c>
+      <c r="C81" t="s">
+        <v>1072</v>
+      </c>
+      <c r="D81" s="35">
+        <v>115</v>
+      </c>
+      <c r="J81" t="s">
         <v>983</v>
       </c>
-      <c r="J44" t="str">
-        <f t="shared" si="0"/>
-        <v>Aftertreatment1IntakeDewPoint;</v>
-      </c>
-    </row>
-    <row r="45" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B45" t="s">
-        <v>898</v>
-      </c>
-      <c r="C45" t="s">
-        <v>1028</v>
-      </c>
-      <c r="H45" t="s">
+      <c r="L81" t="str">
+        <f t="shared" si="4"/>
+        <v>VEP1_AltCurrent</v>
+      </c>
+      <c r="M81" t="str">
+        <f t="shared" si="5"/>
+        <v>GVL_J1939.VEP1_AltCurrent</v>
+      </c>
+      <c r="N81" t="str">
+        <f t="shared" si="6"/>
+        <v>GVL_J1939.VEP1_AltCurrent;</v>
+      </c>
+      <c r="O81" t="str">
+        <f t="shared" si="7"/>
+        <v>VEP1_AltCurrent:USINT; // SPN:115</v>
+      </c>
+    </row>
+    <row r="82" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>81</v>
+      </c>
+      <c r="B82" t="s">
+        <v>928</v>
+      </c>
+      <c r="C82" t="s">
+        <v>1073</v>
+      </c>
+      <c r="D82" s="35">
+        <v>167</v>
+      </c>
+      <c r="J82" t="s">
+        <v>1029</v>
+      </c>
+      <c r="L82" t="str">
+        <f t="shared" si="4"/>
+        <v>VEP1_ChargingSystemPotential</v>
+      </c>
+      <c r="M82" t="str">
+        <f t="shared" si="5"/>
+        <v>GVL_J1939.VEP1_ChargingSystemPotential</v>
+      </c>
+      <c r="N82" t="str">
+        <f t="shared" si="6"/>
+        <v>GVL_J1939.VEP1_ChargingSystemPotential;</v>
+      </c>
+      <c r="O82" t="str">
+        <f t="shared" si="7"/>
+        <v>VEP1_ChargingSystemPotential:REAl; // SPN:167</v>
+      </c>
+    </row>
+    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>82</v>
+      </c>
+      <c r="B83" t="s">
+        <v>928</v>
+      </c>
+      <c r="C83" t="s">
+        <v>1074</v>
+      </c>
+      <c r="D83" s="35">
+        <v>168</v>
+      </c>
+      <c r="E83" t="s">
+        <v>682</v>
+      </c>
+      <c r="J83" t="s">
+        <v>984</v>
+      </c>
+      <c r="L83" t="str">
+        <f t="shared" si="4"/>
+        <v>VEP1_BatteryPotential_PowerInput1</v>
+      </c>
+      <c r="M83" t="str">
+        <f t="shared" si="5"/>
+        <v>GVL_J1939.VEP1_BatteryPotential_PowerInput1</v>
+      </c>
+      <c r="N83" t="str">
+        <f t="shared" si="6"/>
+        <v>GVL_J1939.VEP1_BatteryPotential_PowerInput1;</v>
+      </c>
+      <c r="O83" t="str">
+        <f t="shared" si="7"/>
+        <v>VEP1_BatteryPotential_PowerInput1:REAL; // SPN:168</v>
+      </c>
+    </row>
+    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>83</v>
+      </c>
+      <c r="B84" t="s">
+        <v>928</v>
+      </c>
+      <c r="C84" t="s">
+        <v>1075</v>
+      </c>
+      <c r="D84" s="35">
+        <v>158</v>
+      </c>
+      <c r="E84" t="s">
+        <v>682</v>
+      </c>
+      <c r="J84" t="s">
+        <v>984</v>
+      </c>
+      <c r="L84" t="str">
+        <f t="shared" si="4"/>
+        <v>VEP1_KeyswitchBatteryPotential</v>
+      </c>
+      <c r="M84" t="str">
+        <f t="shared" si="5"/>
+        <v>GVL_J1939.VEP1_KeyswitchBatteryPotential</v>
+      </c>
+      <c r="N84" t="str">
+        <f t="shared" si="6"/>
+        <v>GVL_J1939.VEP1_KeyswitchBatteryPotential;</v>
+      </c>
+      <c r="O84" t="str">
+        <f t="shared" si="7"/>
+        <v>VEP1_KeyswitchBatteryPotential:REAL; // SPN:158</v>
+      </c>
+    </row>
+    <row r="85" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>84</v>
+      </c>
+      <c r="B85" t="s">
+        <v>938</v>
+      </c>
+      <c r="C85" t="s">
+        <v>1076</v>
+      </c>
+      <c r="D85" s="35">
+        <v>1380</v>
+      </c>
+      <c r="J85" t="s">
+        <v>984</v>
+      </c>
+      <c r="L85" t="str">
+        <f t="shared" si="4"/>
+        <v>EFS_EngOilLevelRemoteReservoir</v>
+      </c>
+      <c r="M85" t="str">
+        <f t="shared" si="5"/>
+        <v>GVL_J1939.EFS_EngOilLevelRemoteReservoir</v>
+      </c>
+      <c r="N85" t="str">
+        <f t="shared" si="6"/>
+        <v>GVL_J1939.EFS_EngOilLevelRemoteReservoir;</v>
+      </c>
+      <c r="O85" t="str">
+        <f t="shared" si="7"/>
+        <v>EFS_EngOilLevelRemoteReservoir:REAL; // SPN:1380</v>
+      </c>
+    </row>
+    <row r="86" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>85</v>
+      </c>
+      <c r="B86" t="s">
+        <v>938</v>
+      </c>
+      <c r="C86" t="s">
+        <v>1077</v>
+      </c>
+      <c r="D86" s="35">
+        <v>1381</v>
+      </c>
+      <c r="J86" t="s">
+        <v>1049</v>
+      </c>
+      <c r="L86" t="str">
+        <f t="shared" si="4"/>
+        <v>EFS_EngFuelSupplyPumpIntakePress</v>
+      </c>
+      <c r="M86" t="str">
+        <f t="shared" si="5"/>
+        <v>GVL_J1939.EFS_EngFuelSupplyPumpIntakePress</v>
+      </c>
+      <c r="N86" t="str">
+        <f t="shared" si="6"/>
+        <v>GVL_J1939.EFS_EngFuelSupplyPumpIntakePress;</v>
+      </c>
+      <c r="O86" t="str">
+        <f t="shared" si="7"/>
+        <v>EFS_EngFuelSupplyPumpIntakePress:UINT; // SPN:1381</v>
+      </c>
+    </row>
+    <row r="87" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>86</v>
+      </c>
+      <c r="B87" t="s">
+        <v>938</v>
+      </c>
+      <c r="C87" t="s">
+        <v>1078</v>
+      </c>
+      <c r="D87" s="35">
+        <v>1382</v>
+      </c>
+      <c r="J87" t="s">
+        <v>1049</v>
+      </c>
+      <c r="L87" t="str">
+        <f t="shared" si="4"/>
+        <v>EFS_EngFuelFilterDiffPress</v>
+      </c>
+      <c r="M87" t="str">
+        <f t="shared" si="5"/>
+        <v>GVL_J1939.EFS_EngFuelFilterDiffPress</v>
+      </c>
+      <c r="N87" t="str">
+        <f t="shared" si="6"/>
+        <v>GVL_J1939.EFS_EngFuelFilterDiffPress;</v>
+      </c>
+      <c r="O87" t="str">
+        <f t="shared" si="7"/>
+        <v>EFS_EngFuelFilterDiffPress:UINT; // SPN:1382</v>
+      </c>
+    </row>
+    <row r="88" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>87</v>
+      </c>
+      <c r="B88" t="s">
+        <v>938</v>
+      </c>
+      <c r="C88" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D88" s="35">
+        <v>3548</v>
+      </c>
+      <c r="J88" t="s">
+        <v>984</v>
+      </c>
+      <c r="L88" t="str">
+        <f t="shared" si="4"/>
+        <v>EFS_EngWasteOilReservoirLevel</v>
+      </c>
+      <c r="M88" t="str">
+        <f t="shared" si="5"/>
+        <v>GVL_J1939.EFS_EngWasteOilReservoirLevel</v>
+      </c>
+      <c r="N88" t="str">
+        <f t="shared" si="6"/>
+        <v>GVL_J1939.EFS_EngWasteOilReservoirLevel;</v>
+      </c>
+      <c r="O88" t="str">
+        <f t="shared" si="7"/>
+        <v>EFS_EngWasteOilReservoirLevel:REAL; // SPN:3548</v>
+      </c>
+    </row>
+    <row r="89" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>88</v>
+      </c>
+      <c r="B89" t="s">
+        <v>938</v>
+      </c>
+      <c r="C89" t="s">
+        <v>1080</v>
+      </c>
+      <c r="D89" s="35">
+        <v>3549</v>
+      </c>
+      <c r="J89" t="s">
+        <v>1049</v>
+      </c>
+      <c r="L89" t="str">
+        <f t="shared" si="4"/>
+        <v>EFS_EngOilFilterOutletPress</v>
+      </c>
+      <c r="M89" t="str">
+        <f t="shared" si="5"/>
+        <v>GVL_J1939.EFS_EngOilFilterOutletPress</v>
+      </c>
+      <c r="N89" t="str">
+        <f t="shared" si="6"/>
+        <v>GVL_J1939.EFS_EngOilFilterOutletPress;</v>
+      </c>
+      <c r="O89" t="str">
+        <f t="shared" si="7"/>
+        <v>EFS_EngOilFilterOutletPress:UINT; // SPN:3549</v>
+      </c>
+    </row>
+    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>89</v>
+      </c>
+      <c r="B90" t="s">
+        <v>938</v>
+      </c>
+      <c r="C90" t="s">
+        <v>1081</v>
+      </c>
+      <c r="D90" s="35">
+        <v>3550</v>
+      </c>
+      <c r="E90" t="s">
+        <v>682</v>
+      </c>
+      <c r="J90" t="s">
         <v>983</v>
       </c>
-      <c r="J45" t="str">
-        <f t="shared" si="0"/>
-        <v>Aftertreatment1ExhaustDewPoint;</v>
-      </c>
-    </row>
-    <row r="46" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B46" t="s">
-        <v>898</v>
-      </c>
-      <c r="C46" t="s">
-        <v>1029</v>
-      </c>
-      <c r="H46" t="s">
+      <c r="L90" t="str">
+        <f t="shared" si="4"/>
+        <v>EFS_EngOilPrimingPumpSwitch</v>
+      </c>
+      <c r="M90" t="str">
+        <f t="shared" si="5"/>
+        <v>GVL_J1939.EFS_EngOilPrimingPumpSwitch</v>
+      </c>
+      <c r="N90" t="str">
+        <f t="shared" si="6"/>
+        <v>GVL_J1939.EFS_EngOilPrimingPumpSwitch;</v>
+      </c>
+      <c r="O90" t="str">
+        <f t="shared" si="7"/>
+        <v>EFS_EngOilPrimingPumpSwitch:USINT; // SPN:3550</v>
+      </c>
+    </row>
+    <row r="91" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>90</v>
+      </c>
+      <c r="B91" t="s">
+        <v>938</v>
+      </c>
+      <c r="C91" t="s">
+        <v>1082</v>
+      </c>
+      <c r="D91" s="35">
+        <v>3551</v>
+      </c>
+      <c r="J91" t="s">
         <v>983</v>
       </c>
-      <c r="J46" t="str">
-        <f t="shared" si="0"/>
-        <v>Aftertreatment2IntakeDewPoint;</v>
-      </c>
-    </row>
-    <row r="47" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B47" t="s">
-        <v>898</v>
-      </c>
-      <c r="C47" t="s">
-        <v>1030</v>
-      </c>
-      <c r="H47" t="s">
+      <c r="L91" t="str">
+        <f t="shared" si="4"/>
+        <v>EFS_EngOilPrimingState</v>
+      </c>
+      <c r="M91" t="str">
+        <f t="shared" si="5"/>
+        <v>GVL_J1939.EFS_EngOilPrimingState</v>
+      </c>
+      <c r="N91" t="str">
+        <f t="shared" si="6"/>
+        <v>GVL_J1939.EFS_EngOilPrimingState;</v>
+      </c>
+      <c r="O91" t="str">
+        <f t="shared" si="7"/>
+        <v>EFS_EngOilPrimingState:USINT; // SPN:3551</v>
+      </c>
+    </row>
+    <row r="92" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A92">
+        <v>91</v>
+      </c>
+      <c r="B92" t="s">
+        <v>938</v>
+      </c>
+      <c r="C92" t="s">
+        <v>1083</v>
+      </c>
+      <c r="D92" s="35">
+        <v>3552</v>
+      </c>
+      <c r="J92" t="s">
         <v>983</v>
       </c>
-      <c r="J47" t="str">
-        <f t="shared" si="0"/>
-        <v>Aftertreatment2ExhaustDewPoint;</v>
-      </c>
-    </row>
-    <row r="48" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="J48" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="49" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B49" t="s">
-        <v>946</v>
-      </c>
-      <c r="C49" t="s">
-        <v>1032</v>
-      </c>
-      <c r="H49" t="s">
-        <v>984</v>
-      </c>
-      <c r="J49" t="str">
-        <f t="shared" si="0"/>
-        <v>EngTrb1ClcltedTurbineIntakeTemp;</v>
-      </c>
-    </row>
-    <row r="50" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B50" t="s">
-        <v>946</v>
-      </c>
-      <c r="C50" t="s">
-        <v>1033</v>
-      </c>
-      <c r="H50" t="s">
-        <v>984</v>
-      </c>
-      <c r="J50" t="str">
-        <f t="shared" si="0"/>
-        <v>EngTrb1ClcltedTurbineOutletTemp;</v>
-      </c>
-    </row>
-    <row r="51" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B51" t="s">
-        <v>946</v>
-      </c>
-      <c r="C51" t="s">
-        <v>1034</v>
-      </c>
-      <c r="H51" t="s">
-        <v>984</v>
-      </c>
-      <c r="J51" t="str">
-        <f t="shared" si="0"/>
-        <v>EngExhstGsRcrculation1ValveCtrl;</v>
-      </c>
-    </row>
-    <row r="52" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B52" t="s">
-        <v>946</v>
-      </c>
-      <c r="C52" t="s">
-        <v>1035</v>
-      </c>
-      <c r="H52" t="s">
+      <c r="L92" t="str">
+        <f t="shared" si="4"/>
+        <v>EFS_EngOilPreHeatedState</v>
+      </c>
+      <c r="M92" t="str">
+        <f t="shared" si="5"/>
+        <v>GVL_J1939.EFS_EngOilPreHeatedState</v>
+      </c>
+      <c r="N92" t="str">
+        <f t="shared" si="6"/>
+        <v>GVL_J1939.EFS_EngOilPreHeatedState;</v>
+      </c>
+      <c r="O92" t="str">
+        <f t="shared" si="7"/>
+        <v>EFS_EngOilPreHeatedState:USINT; // SPN:3552</v>
+      </c>
+    </row>
+    <row r="93" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A93">
+        <v>92</v>
+      </c>
+      <c r="B93" t="s">
+        <v>938</v>
+      </c>
+      <c r="C93" t="s">
+        <v>1084</v>
+      </c>
+      <c r="D93" s="35">
+        <v>3553</v>
+      </c>
+      <c r="J93" t="s">
         <v>983</v>
       </c>
-      <c r="J52" t="str">
-        <f t="shared" si="0"/>
-        <v>EngVrblGmtryTrbArCtrlShtffValve;</v>
-      </c>
-    </row>
-    <row r="53" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B53" t="s">
-        <v>946</v>
-      </c>
-      <c r="C53" t="s">
-        <v>1036</v>
-      </c>
-      <c r="H53" t="s">
+      <c r="L93" t="str">
+        <f t="shared" si="4"/>
+        <v>EFS_EngCoolantPreheatedState</v>
+      </c>
+      <c r="M93" t="str">
+        <f t="shared" si="5"/>
+        <v>GVL_J1939.EFS_EngCoolantPreheatedState</v>
+      </c>
+      <c r="N93" t="str">
+        <f t="shared" si="6"/>
+        <v>GVL_J1939.EFS_EngCoolantPreheatedState;</v>
+      </c>
+      <c r="O93" t="str">
+        <f t="shared" si="7"/>
+        <v>EFS_EngCoolantPreheatedState:USINT; // SPN:3553</v>
+      </c>
+    </row>
+    <row r="94" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A94">
+        <v>93</v>
+      </c>
+      <c r="B94" t="s">
+        <v>938</v>
+      </c>
+      <c r="C94" t="s">
+        <v>1085</v>
+      </c>
+      <c r="D94" s="35">
+        <v>3554</v>
+      </c>
+      <c r="J94" t="s">
         <v>983</v>
       </c>
-      <c r="J53" t="str">
-        <f t="shared" si="0"/>
-        <v>EngVrableGeometryTurbo1CtrlMode;</v>
-      </c>
-    </row>
-    <row r="54" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B54" t="s">
-        <v>946</v>
-      </c>
-      <c r="C54" t="s">
-        <v>1037</v>
-      </c>
-      <c r="H54" t="s">
-        <v>984</v>
-      </c>
-      <c r="J54" t="str">
-        <f t="shared" si="0"/>
-        <v>EngVrblGometryTurbo1ActuatorPos;</v>
-      </c>
-    </row>
-    <row r="55" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="J55" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="56" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B56" t="s">
-        <v>900</v>
-      </c>
-      <c r="C56" t="s">
-        <v>1038</v>
-      </c>
-      <c r="H56" t="s">
-        <v>984</v>
-      </c>
-      <c r="J56" t="str">
-        <f t="shared" si="0"/>
-        <v>EngCoolantTemp;</v>
-      </c>
-    </row>
-    <row r="57" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B57" t="s">
-        <v>900</v>
-      </c>
-      <c r="C57" t="s">
-        <v>1039</v>
-      </c>
-      <c r="H57" t="s">
-        <v>985</v>
-      </c>
-      <c r="J57" t="str">
-        <f t="shared" si="0"/>
-        <v>EngFuelTemp1;</v>
-      </c>
-    </row>
-    <row r="58" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B58" t="s">
-        <v>900</v>
-      </c>
-      <c r="C58" t="s">
-        <v>1040</v>
-      </c>
-      <c r="H58" t="s">
-        <v>984</v>
-      </c>
-      <c r="J58" t="str">
-        <f t="shared" si="0"/>
-        <v>EngOilTemp1;</v>
-      </c>
-    </row>
-    <row r="59" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B59" t="s">
-        <v>900</v>
-      </c>
-      <c r="C59" t="s">
-        <v>1041</v>
-      </c>
-      <c r="H59" t="s">
-        <v>984</v>
-      </c>
-      <c r="J59" t="str">
-        <f t="shared" si="0"/>
-        <v>EngTurboOilTemp;</v>
-      </c>
-    </row>
-    <row r="60" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B60" t="s">
-        <v>900</v>
-      </c>
-      <c r="C60" t="s">
-        <v>1042</v>
-      </c>
-      <c r="H60" t="s">
-        <v>985</v>
-      </c>
-      <c r="J60" t="str">
-        <f t="shared" si="0"/>
-        <v>EngIntercoolerTemp;</v>
-      </c>
-    </row>
-    <row r="61" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B61" t="s">
-        <v>900</v>
-      </c>
-      <c r="C61" t="s">
-        <v>1043</v>
-      </c>
-      <c r="H61" t="s">
-        <v>984</v>
-      </c>
-      <c r="J61" t="str">
-        <f t="shared" si="0"/>
-        <v>EngIntercoolerThermostatOpening;</v>
-      </c>
-    </row>
-    <row r="62" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="J62" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="63" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B63" t="s">
-        <v>1052</v>
-      </c>
-      <c r="C63" t="s">
-        <v>1044</v>
-      </c>
-      <c r="H63" t="s">
-        <v>1051</v>
-      </c>
-      <c r="J63" t="str">
-        <f t="shared" si="0"/>
-        <v>EngFuelDeliveryPress;</v>
-      </c>
-    </row>
-    <row r="64" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B64" t="s">
-        <v>1052</v>
-      </c>
-      <c r="C64" t="s">
-        <v>1045</v>
-      </c>
-      <c r="H64" t="s">
-        <v>984</v>
-      </c>
-      <c r="J64" t="str">
-        <f t="shared" si="0"/>
-        <v>EngExCrankcaseBlowbyPress;</v>
-      </c>
-    </row>
-    <row r="65" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B65" t="s">
-        <v>1052</v>
-      </c>
-      <c r="C65" t="s">
-        <v>1046</v>
-      </c>
-      <c r="H65" t="s">
-        <v>984</v>
-      </c>
-      <c r="J65" t="str">
-        <f t="shared" si="0"/>
-        <v>EngOilLevel;</v>
-      </c>
-    </row>
-    <row r="66" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B66" t="s">
-        <v>1052</v>
-      </c>
-      <c r="C66" t="s">
-        <v>1047</v>
-      </c>
-      <c r="H66" t="s">
-        <v>1051</v>
-      </c>
-      <c r="J66" t="str">
-        <f t="shared" si="0"/>
-        <v>EngOilPress;</v>
-      </c>
-    </row>
-    <row r="67" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B67" t="s">
-        <v>1052</v>
-      </c>
-      <c r="C67" t="s">
-        <v>1048</v>
-      </c>
-      <c r="H67" t="s">
-        <v>1031</v>
-      </c>
-      <c r="J67" t="str">
-        <f t="shared" si="0"/>
-        <v>EngCrankcasePress;</v>
-      </c>
-    </row>
-    <row r="68" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B68" t="s">
-        <v>1052</v>
-      </c>
-      <c r="C68" t="s">
-        <v>1049</v>
-      </c>
-      <c r="H68" t="s">
-        <v>1051</v>
-      </c>
-      <c r="J68" t="str">
-        <f t="shared" ref="J68:J131" si="2">IF(C68&lt;&gt;"",_xlfn.CONCAT(C68,";"),"")</f>
-        <v>EngCoolantPress;</v>
-      </c>
-    </row>
-    <row r="69" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B69" t="s">
-        <v>1052</v>
-      </c>
-      <c r="C69" t="s">
-        <v>1050</v>
-      </c>
-      <c r="H69" t="s">
-        <v>984</v>
-      </c>
-      <c r="J69" t="str">
-        <f t="shared" si="2"/>
-        <v>EngCoolantLevel;</v>
-      </c>
-    </row>
-    <row r="70" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="J70" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="71" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B71" t="s">
-        <v>972</v>
-      </c>
-      <c r="C71" t="s">
-        <v>1053</v>
-      </c>
-      <c r="H71" t="s">
-        <v>1057</v>
-      </c>
-      <c r="J71" t="str">
-        <f t="shared" si="2"/>
-        <v>EngInjectionCtrlPress;</v>
-      </c>
-    </row>
-    <row r="72" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B72" t="s">
-        <v>972</v>
-      </c>
-      <c r="C72" t="s">
-        <v>1054</v>
-      </c>
-      <c r="H72" t="s">
-        <v>1057</v>
-      </c>
-      <c r="J72" t="str">
-        <f t="shared" si="2"/>
-        <v>EngInjectorMeteringRail1Press;</v>
-      </c>
-    </row>
-    <row r="73" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B73" t="s">
-        <v>972</v>
-      </c>
-      <c r="C73" t="s">
-        <v>1055</v>
-      </c>
-      <c r="H73" t="s">
-        <v>1057</v>
-      </c>
-      <c r="J73" t="str">
-        <f t="shared" si="2"/>
-        <v>EngInjectorTimingRail1Press;</v>
-      </c>
-    </row>
-    <row r="74" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B74" t="s">
-        <v>972</v>
-      </c>
-      <c r="C74" t="s">
-        <v>1056</v>
-      </c>
-      <c r="H74" t="s">
-        <v>1057</v>
-      </c>
-      <c r="J74" t="str">
-        <f t="shared" si="2"/>
-        <v>EngInjectorMeteringRail2Press;</v>
-      </c>
-    </row>
-    <row r="75" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="J75" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="76" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B76" t="s">
-        <v>903</v>
-      </c>
-      <c r="C76" t="s">
-        <v>1058</v>
-      </c>
-      <c r="H76" t="s">
-        <v>984</v>
-      </c>
-      <c r="J76" t="str">
-        <f t="shared" si="2"/>
-        <v>EngTripFuel;</v>
-      </c>
-    </row>
-    <row r="77" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B77" t="s">
-        <v>903</v>
-      </c>
-      <c r="C77" t="s">
-        <v>1059</v>
-      </c>
-      <c r="H77" t="s">
-        <v>984</v>
-      </c>
-      <c r="J77" t="str">
-        <f t="shared" si="2"/>
-        <v>EngTotalFuelUsed;</v>
-      </c>
-    </row>
-    <row r="78" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="J78" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="79" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B79" t="s">
-        <v>930</v>
-      </c>
-      <c r="C79" t="s">
-        <v>1060</v>
-      </c>
-      <c r="H79" t="s">
-        <v>984</v>
-      </c>
-      <c r="J79" t="str">
-        <f t="shared" si="2"/>
-        <v>BarometricPress;</v>
-      </c>
-    </row>
-    <row r="80" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B80" t="s">
-        <v>930</v>
-      </c>
-      <c r="C80" t="s">
-        <v>1061</v>
-      </c>
-      <c r="H80" t="s">
-        <v>984</v>
-      </c>
-      <c r="J80" t="str">
-        <f t="shared" si="2"/>
-        <v>CabInteriorTemp;</v>
-      </c>
-    </row>
-    <row r="81" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B81" t="s">
-        <v>930</v>
-      </c>
-      <c r="C81" t="s">
-        <v>1062</v>
-      </c>
-      <c r="H81" t="s">
-        <v>984</v>
-      </c>
-      <c r="J81" t="str">
-        <f t="shared" si="2"/>
-        <v>AmbientAirTemp;</v>
-      </c>
-    </row>
-    <row r="82" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B82" t="s">
-        <v>930</v>
-      </c>
-      <c r="C82" t="s">
-        <v>1063</v>
-      </c>
-      <c r="H82" t="s">
-        <v>985</v>
-      </c>
-      <c r="J82" t="str">
-        <f t="shared" si="2"/>
-        <v>EngAirIntakeTemp;</v>
-      </c>
-    </row>
-    <row r="83" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B83" t="s">
-        <v>930</v>
-      </c>
-      <c r="C83" t="s">
-        <v>1064</v>
-      </c>
-      <c r="H83" t="s">
-        <v>984</v>
-      </c>
-      <c r="J83" t="str">
-        <f t="shared" si="2"/>
-        <v>RoadSurfaceTemp;</v>
-      </c>
-    </row>
-    <row r="84" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="J84" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="85" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B85" t="s">
-        <v>1072</v>
-      </c>
-      <c r="C85" t="s">
-        <v>1065</v>
-      </c>
-      <c r="H85" t="s">
-        <v>984</v>
-      </c>
-      <c r="J85" t="str">
-        <f t="shared" si="2"/>
-        <v>EngDslPrtclateFilterIntakePress;</v>
-      </c>
-    </row>
-    <row r="86" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B86" t="s">
-        <v>1072</v>
-      </c>
-      <c r="C86" t="s">
-        <v>1066</v>
-      </c>
-      <c r="H86" t="s">
-        <v>1051</v>
-      </c>
-      <c r="J86" t="str">
-        <f t="shared" si="2"/>
-        <v>EngIntakeManifold1Press;</v>
-      </c>
-    </row>
-    <row r="87" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B87" t="s">
-        <v>1072</v>
-      </c>
-      <c r="C87" t="s">
-        <v>1067</v>
-      </c>
-      <c r="H87" t="s">
-        <v>985</v>
-      </c>
-      <c r="J87" t="str">
-        <f t="shared" si="2"/>
-        <v>EngIntakeManifold1Temp;</v>
-      </c>
-    </row>
-    <row r="88" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B88" t="s">
-        <v>1072</v>
-      </c>
-      <c r="C88" t="s">
-        <v>1068</v>
-      </c>
-      <c r="H88" t="s">
-        <v>1051</v>
-      </c>
-      <c r="J88" t="str">
-        <f t="shared" si="2"/>
-        <v>EngAirIntakePress;</v>
-      </c>
-    </row>
-    <row r="89" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B89" t="s">
-        <v>1072</v>
-      </c>
-      <c r="C89" t="s">
-        <v>1069</v>
-      </c>
-      <c r="H89" t="s">
-        <v>984</v>
-      </c>
-      <c r="J89" t="str">
-        <f t="shared" si="2"/>
-        <v>EngAirFilter1DiffPress;</v>
-      </c>
-    </row>
-    <row r="90" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B90" t="s">
-        <v>1072</v>
-      </c>
-      <c r="C90" t="s">
-        <v>1070</v>
-      </c>
-      <c r="H90" t="s">
-        <v>984</v>
-      </c>
-      <c r="J90" t="str">
-        <f t="shared" si="2"/>
-        <v>EngExhaustGasTemp;</v>
-      </c>
-    </row>
-    <row r="91" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B91" t="s">
-        <v>1072</v>
-      </c>
-      <c r="C91" t="s">
-        <v>1071</v>
-      </c>
-      <c r="H91" t="s">
-        <v>984</v>
-      </c>
-      <c r="J91" t="str">
-        <f t="shared" si="2"/>
-        <v>EngCoolantFilterDiffPress;</v>
-      </c>
-    </row>
-    <row r="92" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="J92" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="93" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B93" t="s">
-        <v>928</v>
-      </c>
-      <c r="C93" t="s">
-        <v>1073</v>
-      </c>
-      <c r="H93" t="s">
-        <v>985</v>
-      </c>
-      <c r="J93" t="str">
-        <f t="shared" si="2"/>
-        <v>NetBatteryCurrent;</v>
-      </c>
-    </row>
-    <row r="94" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B94" t="s">
-        <v>928</v>
-      </c>
-      <c r="C94" t="s">
-        <v>1074</v>
-      </c>
-      <c r="H94" t="s">
+      <c r="L94" t="str">
+        <f t="shared" si="4"/>
+        <v>EFS_EngVentilationStatus</v>
+      </c>
+      <c r="M94" t="str">
+        <f t="shared" si="5"/>
+        <v>GVL_J1939.EFS_EngVentilationStatus</v>
+      </c>
+      <c r="N94" t="str">
+        <f t="shared" si="6"/>
+        <v>GVL_J1939.EFS_EngVentilationStatus;</v>
+      </c>
+      <c r="O94" t="str">
+        <f t="shared" si="7"/>
+        <v>EFS_EngVentilationStatus:USINT; // SPN:3554</v>
+      </c>
+    </row>
+    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A95">
+        <v>94</v>
+      </c>
+      <c r="B95" t="s">
+        <v>938</v>
+      </c>
+      <c r="C95" t="s">
+        <v>1086</v>
+      </c>
+      <c r="D95" s="35">
+        <v>4083</v>
+      </c>
+      <c r="E95" t="s">
+        <v>682</v>
+      </c>
+      <c r="J95" t="s">
         <v>983</v>
       </c>
-      <c r="J94" t="str">
-        <f t="shared" si="2"/>
-        <v>AltCurrent;</v>
-      </c>
-    </row>
-    <row r="95" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B95" t="s">
-        <v>928</v>
-      </c>
-      <c r="C95" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H95" t="s">
-        <v>1031</v>
-      </c>
-      <c r="J95" t="str">
-        <f t="shared" si="2"/>
-        <v>ChargingSystemPotential;</v>
-      </c>
-    </row>
-    <row r="96" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="L95" t="str">
+        <f t="shared" si="4"/>
+        <v>EFS_FuelPumpPrimerStatus</v>
+      </c>
+      <c r="M95" t="str">
+        <f t="shared" si="5"/>
+        <v>GVL_J1939.EFS_FuelPumpPrimerStatus</v>
+      </c>
+      <c r="N95" t="str">
+        <f t="shared" si="6"/>
+        <v>GVL_J1939.EFS_FuelPumpPrimerStatus;</v>
+      </c>
+      <c r="O95" t="str">
+        <f t="shared" si="7"/>
+        <v>EFS_FuelPumpPrimerStatus:USINT; // SPN:4083</v>
+      </c>
+    </row>
+    <row r="96" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A96">
+        <v>95</v>
+      </c>
       <c r="B96" t="s">
-        <v>928</v>
-      </c>
-      <c r="C96" t="s">
-        <v>1076</v>
-      </c>
-      <c r="H96" t="s">
-        <v>984</v>
-      </c>
-      <c r="J96" t="str">
-        <f t="shared" si="2"/>
-        <v>BatteryPotential_PowerInput1;</v>
-      </c>
-    </row>
-    <row r="97" spans="2:10" x14ac:dyDescent="0.25">
+        <v>888</v>
+      </c>
+      <c r="C96" s="33" t="s">
+        <v>1087</v>
+      </c>
+      <c r="D96" s="41">
+        <v>3697</v>
+      </c>
+      <c r="E96" t="s">
+        <v>682</v>
+      </c>
+      <c r="F96" s="26">
+        <v>0</v>
+      </c>
+      <c r="G96" s="26" t="s">
+        <v>1168</v>
+      </c>
+      <c r="H96" s="26">
+        <v>0</v>
+      </c>
+      <c r="I96" s="26" t="str">
+        <f>_xlfn.CONCAT(F96+1,",",H96+1)</f>
+        <v>1,1</v>
+      </c>
+      <c r="J96" t="s">
+        <v>983</v>
+      </c>
+      <c r="L96" t="str">
+        <f t="shared" si="4"/>
+        <v>DPFC1_DieselParticulateFilterLampCmd</v>
+      </c>
+      <c r="M96" t="str">
+        <f t="shared" si="5"/>
+        <v>GVL_J1939.DPFC1_DieselParticulateFilterLampCmd</v>
+      </c>
+      <c r="N96" t="str">
+        <f t="shared" si="6"/>
+        <v>GVL_J1939.DPFC1_DieselParticulateFilterLampCmd;</v>
+      </c>
+      <c r="O96" t="str">
+        <f t="shared" si="7"/>
+        <v>DPFC1_DieselParticulateFilterLampCmd:USINT; // SPN:3697</v>
+      </c>
+    </row>
+    <row r="97" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A97">
+        <v>96</v>
+      </c>
       <c r="B97" t="s">
-        <v>928</v>
+        <v>888</v>
       </c>
       <c r="C97" t="s">
-        <v>1077</v>
-      </c>
-      <c r="H97" t="s">
-        <v>984</v>
-      </c>
-      <c r="J97" t="str">
-        <f t="shared" si="2"/>
-        <v>KeyswitchBatteryPotential;</v>
-      </c>
-    </row>
-    <row r="98" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="J98" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="99" spans="2:10" x14ac:dyDescent="0.25">
+        <v>1088</v>
+      </c>
+      <c r="D97" s="35">
+        <v>3699</v>
+      </c>
+      <c r="F97" s="26">
+        <v>1</v>
+      </c>
+      <c r="G97" s="26" t="s">
+        <v>1169</v>
+      </c>
+      <c r="H97" s="26">
+        <v>0</v>
+      </c>
+      <c r="I97" s="26" t="str">
+        <f t="shared" ref="I97:I118" si="8">_xlfn.CONCAT(F97+1,",",H97+1)</f>
+        <v>2,1</v>
+      </c>
+      <c r="J97" t="s">
+        <v>983</v>
+      </c>
+      <c r="L97" t="str">
+        <f t="shared" si="4"/>
+        <v>DPFC1_DslPrtcltFltrPssvRgnrtionStatus</v>
+      </c>
+      <c r="M97" t="str">
+        <f t="shared" si="5"/>
+        <v>GVL_J1939.DPFC1_DslPrtcltFltrPssvRgnrtionStatus</v>
+      </c>
+      <c r="N97" t="str">
+        <f t="shared" si="6"/>
+        <v>GVL_J1939.DPFC1_DslPrtcltFltrPssvRgnrtionStatus;</v>
+      </c>
+      <c r="O97" t="str">
+        <f t="shared" si="7"/>
+        <v>DPFC1_DslPrtcltFltrPssvRgnrtionStatus:USINT; // SPN:3699</v>
+      </c>
+    </row>
+    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A98">
+        <v>97</v>
+      </c>
+      <c r="B98" t="s">
+        <v>888</v>
+      </c>
+      <c r="C98" s="33" t="s">
+        <v>1089</v>
+      </c>
+      <c r="D98" s="35">
+        <v>3700</v>
+      </c>
+      <c r="E98" t="s">
+        <v>682</v>
+      </c>
+      <c r="F98" s="26">
+        <v>1</v>
+      </c>
+      <c r="G98" s="26" t="s">
+        <v>1170</v>
+      </c>
+      <c r="H98" s="26">
+        <v>2</v>
+      </c>
+      <c r="I98" s="26" t="str">
+        <f t="shared" si="8"/>
+        <v>2,3</v>
+      </c>
+      <c r="J98" t="s">
+        <v>983</v>
+      </c>
+      <c r="L98" t="str">
+        <f t="shared" si="4"/>
+        <v>DPFC1_DslPrtcltFltrActvRgnrtionStatus</v>
+      </c>
+      <c r="M98" t="str">
+        <f t="shared" si="5"/>
+        <v>GVL_J1939.DPFC1_DslPrtcltFltrActvRgnrtionStatus</v>
+      </c>
+      <c r="N98" t="str">
+        <f t="shared" si="6"/>
+        <v>GVL_J1939.DPFC1_DslPrtcltFltrActvRgnrtionStatus;</v>
+      </c>
+      <c r="O98" t="str">
+        <f t="shared" si="7"/>
+        <v>DPFC1_DslPrtcltFltrActvRgnrtionStatus:USINT; // SPN:3700</v>
+      </c>
+    </row>
+    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A99">
+        <v>98</v>
+      </c>
       <c r="B99" t="s">
-        <v>938</v>
-      </c>
-      <c r="C99" t="s">
-        <v>1078</v>
-      </c>
-      <c r="H99" t="s">
-        <v>984</v>
-      </c>
-      <c r="J99" t="str">
-        <f t="shared" si="2"/>
-        <v>EngOilLevelRemoteReservoir;</v>
-      </c>
-    </row>
-    <row r="100" spans="2:10" x14ac:dyDescent="0.25">
+        <v>888</v>
+      </c>
+      <c r="C99" s="33" t="s">
+        <v>1090</v>
+      </c>
+      <c r="D99" s="35">
+        <v>3701</v>
+      </c>
+      <c r="E99" t="s">
+        <v>682</v>
+      </c>
+      <c r="F99" s="26">
+        <v>1</v>
+      </c>
+      <c r="G99" s="26" t="s">
+        <v>1171</v>
+      </c>
+      <c r="H99" s="26">
+        <v>4</v>
+      </c>
+      <c r="I99" s="26" t="str">
+        <f t="shared" si="8"/>
+        <v>2,5</v>
+      </c>
+      <c r="J99" t="s">
+        <v>983</v>
+      </c>
+      <c r="L99" t="str">
+        <f t="shared" si="4"/>
+        <v>DPFC1_DieselParticulateFilterStatus</v>
+      </c>
+      <c r="M99" t="str">
+        <f t="shared" si="5"/>
+        <v>GVL_J1939.DPFC1_DieselParticulateFilterStatus</v>
+      </c>
+      <c r="N99" t="str">
+        <f t="shared" si="6"/>
+        <v>GVL_J1939.DPFC1_DieselParticulateFilterStatus;</v>
+      </c>
+      <c r="O99" t="str">
+        <f t="shared" si="7"/>
+        <v>DPFC1_DieselParticulateFilterStatus:USINT; // SPN:3701</v>
+      </c>
+    </row>
+    <row r="100" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A100">
+        <v>99</v>
+      </c>
       <c r="B100" t="s">
-        <v>938</v>
+        <v>888</v>
       </c>
       <c r="C100" t="s">
-        <v>1079</v>
-      </c>
-      <c r="H100" t="s">
-        <v>1051</v>
-      </c>
-      <c r="J100" t="str">
-        <f t="shared" si="2"/>
-        <v>EngFuelSupplyPumpIntakePress;</v>
-      </c>
-    </row>
-    <row r="101" spans="2:10" x14ac:dyDescent="0.25">
+        <v>1091</v>
+      </c>
+      <c r="D100" s="35">
+        <v>3702</v>
+      </c>
+      <c r="F100" s="26">
+        <v>2</v>
+      </c>
+      <c r="G100" s="26" t="s">
+        <v>1169</v>
+      </c>
+      <c r="H100" s="26">
+        <v>0</v>
+      </c>
+      <c r="I100" s="26" t="str">
+        <f t="shared" si="8"/>
+        <v>3,1</v>
+      </c>
+      <c r="J100" t="s">
+        <v>983</v>
+      </c>
+      <c r="L100" t="str">
+        <f t="shared" si="4"/>
+        <v>DPFC1_DslPrtcltFltrActvRgnrtnInhbtdStt</v>
+      </c>
+      <c r="M100" t="str">
+        <f t="shared" si="5"/>
+        <v>GVL_J1939.DPFC1_DslPrtcltFltrActvRgnrtnInhbtdStt</v>
+      </c>
+      <c r="N100" t="str">
+        <f t="shared" si="6"/>
+        <v>GVL_J1939.DPFC1_DslPrtcltFltrActvRgnrtnInhbtdStt;</v>
+      </c>
+      <c r="O100" t="str">
+        <f t="shared" si="7"/>
+        <v>DPFC1_DslPrtcltFltrActvRgnrtnInhbtdStt:USINT; // SPN:3702</v>
+      </c>
+    </row>
+    <row r="101" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A101">
+        <v>100</v>
+      </c>
       <c r="B101" t="s">
-        <v>938</v>
-      </c>
-      <c r="C101" t="s">
-        <v>1080</v>
-      </c>
-      <c r="H101" t="s">
-        <v>1051</v>
-      </c>
-      <c r="J101" t="str">
-        <f t="shared" si="2"/>
-        <v>EngFuelFilterDiffPress;</v>
-      </c>
-    </row>
-    <row r="102" spans="2:10" x14ac:dyDescent="0.25">
+        <v>888</v>
+      </c>
+      <c r="C101" s="33" t="s">
+        <v>1092</v>
+      </c>
+      <c r="D101" s="35">
+        <v>3703</v>
+      </c>
+      <c r="E101" t="s">
+        <v>682</v>
+      </c>
+      <c r="F101" s="26">
+        <v>2</v>
+      </c>
+      <c r="G101" s="26" t="s">
+        <v>1170</v>
+      </c>
+      <c r="H101" s="26">
+        <v>2</v>
+      </c>
+      <c r="I101" s="26" t="str">
+        <f t="shared" si="8"/>
+        <v>3,3</v>
+      </c>
+      <c r="J101" t="s">
+        <v>983</v>
+      </c>
+      <c r="L101" t="str">
+        <f t="shared" si="4"/>
+        <v>DPFC1_DslPrtcltFltrActvRgnrtnInhbtdDTI</v>
+      </c>
+      <c r="M101" t="str">
+        <f t="shared" si="5"/>
+        <v>GVL_J1939.DPFC1_DslPrtcltFltrActvRgnrtnInhbtdDTI</v>
+      </c>
+      <c r="N101" t="str">
+        <f t="shared" si="6"/>
+        <v>GVL_J1939.DPFC1_DslPrtcltFltrActvRgnrtnInhbtdDTI;</v>
+      </c>
+      <c r="O101" t="str">
+        <f t="shared" si="7"/>
+        <v>DPFC1_DslPrtcltFltrActvRgnrtnInhbtdDTI:USINT; // SPN:3703</v>
+      </c>
+    </row>
+    <row r="102" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A102">
+        <v>101</v>
+      </c>
       <c r="B102" t="s">
-        <v>938</v>
+        <v>888</v>
       </c>
       <c r="C102" t="s">
-        <v>1081</v>
-      </c>
-      <c r="H102" t="s">
-        <v>984</v>
-      </c>
-      <c r="J102" t="str">
-        <f t="shared" si="2"/>
-        <v>EngWasteOilReservoirLevel;</v>
-      </c>
-    </row>
-    <row r="103" spans="2:10" x14ac:dyDescent="0.25">
+        <v>1093</v>
+      </c>
+      <c r="D102" s="35">
+        <v>3704</v>
+      </c>
+      <c r="F102" s="26">
+        <v>2</v>
+      </c>
+      <c r="G102" s="26" t="s">
+        <v>1172</v>
+      </c>
+      <c r="H102" s="26">
+        <v>4</v>
+      </c>
+      <c r="I102" s="26" t="str">
+        <f t="shared" si="8"/>
+        <v>3,5</v>
+      </c>
+      <c r="J102" t="s">
+        <v>983</v>
+      </c>
+      <c r="L102" t="str">
+        <f t="shared" si="4"/>
+        <v>DPFC1_DslPrtcltFltrActvRgnrtnInhbtdDTC</v>
+      </c>
+      <c r="M102" t="str">
+        <f t="shared" si="5"/>
+        <v>GVL_J1939.DPFC1_DslPrtcltFltrActvRgnrtnInhbtdDTC</v>
+      </c>
+      <c r="N102" t="str">
+        <f t="shared" si="6"/>
+        <v>GVL_J1939.DPFC1_DslPrtcltFltrActvRgnrtnInhbtdDTC;</v>
+      </c>
+      <c r="O102" t="str">
+        <f t="shared" si="7"/>
+        <v>DPFC1_DslPrtcltFltrActvRgnrtnInhbtdDTC:USINT; // SPN:3704</v>
+      </c>
+    </row>
+    <row r="103" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A103">
+        <v>102</v>
+      </c>
       <c r="B103" t="s">
-        <v>938</v>
+        <v>888</v>
       </c>
       <c r="C103" t="s">
-        <v>1082</v>
-      </c>
-      <c r="H103" t="s">
-        <v>1051</v>
-      </c>
-      <c r="J103" t="str">
-        <f t="shared" si="2"/>
-        <v>EngOilFilterOutletPress;</v>
-      </c>
-    </row>
-    <row r="104" spans="2:10" x14ac:dyDescent="0.25">
+        <v>1094</v>
+      </c>
+      <c r="D103" s="35">
+        <v>3705</v>
+      </c>
+      <c r="F103" s="26">
+        <v>2</v>
+      </c>
+      <c r="G103" s="26" t="s">
+        <v>1173</v>
+      </c>
+      <c r="H103" s="26">
+        <v>6</v>
+      </c>
+      <c r="I103" s="26" t="str">
+        <f t="shared" si="8"/>
+        <v>3,7</v>
+      </c>
+      <c r="J103" t="s">
+        <v>983</v>
+      </c>
+      <c r="L103" t="str">
+        <f t="shared" si="4"/>
+        <v>DPFC1_DslPrtcltFltrActvRgnrtnInhb_0004</v>
+      </c>
+      <c r="M103" t="str">
+        <f t="shared" si="5"/>
+        <v>GVL_J1939.DPFC1_DslPrtcltFltrActvRgnrtnInhb_0004</v>
+      </c>
+      <c r="N103" t="str">
+        <f t="shared" si="6"/>
+        <v>GVL_J1939.DPFC1_DslPrtcltFltrActvRgnrtnInhb_0004;</v>
+      </c>
+      <c r="O103" t="str">
+        <f t="shared" si="7"/>
+        <v>DPFC1_DslPrtcltFltrActvRgnrtnInhb_0004:USINT; // SPN:3705</v>
+      </c>
+    </row>
+    <row r="104" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A104">
+        <v>103</v>
+      </c>
       <c r="B104" t="s">
-        <v>938</v>
+        <v>888</v>
       </c>
       <c r="C104" t="s">
-        <v>1083</v>
-      </c>
-      <c r="H104" t="s">
+        <v>1095</v>
+      </c>
+      <c r="D104" s="35">
+        <v>3706</v>
+      </c>
+      <c r="F104" s="26">
+        <v>3</v>
+      </c>
+      <c r="G104" s="26" t="s">
+        <v>1169</v>
+      </c>
+      <c r="H104" s="26">
+        <v>0</v>
+      </c>
+      <c r="I104" s="26" t="str">
+        <f t="shared" si="8"/>
+        <v>4,1</v>
+      </c>
+      <c r="J104" t="s">
         <v>983</v>
       </c>
-      <c r="J104" t="str">
-        <f t="shared" si="2"/>
-        <v>EngOilPrimingPumpSwitch;</v>
-      </c>
-    </row>
-    <row r="105" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="L104" t="str">
+        <f t="shared" si="4"/>
+        <v>DPFC1_DslPrtcltFltrActvRgnrtnInhb_0003</v>
+      </c>
+      <c r="M104" t="str">
+        <f t="shared" si="5"/>
+        <v>GVL_J1939.DPFC1_DslPrtcltFltrActvRgnrtnInhb_0003</v>
+      </c>
+      <c r="N104" t="str">
+        <f t="shared" si="6"/>
+        <v>GVL_J1939.DPFC1_DslPrtcltFltrActvRgnrtnInhb_0003;</v>
+      </c>
+      <c r="O104" t="str">
+        <f t="shared" si="7"/>
+        <v>DPFC1_DslPrtcltFltrActvRgnrtnInhb_0003:USINT; // SPN:3706</v>
+      </c>
+    </row>
+    <row r="105" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A105">
+        <v>104</v>
+      </c>
       <c r="B105" t="s">
-        <v>938</v>
+        <v>888</v>
       </c>
       <c r="C105" t="s">
-        <v>1084</v>
-      </c>
-      <c r="H105" t="s">
+        <v>1096</v>
+      </c>
+      <c r="D105" s="35">
+        <v>3707</v>
+      </c>
+      <c r="F105" s="26">
+        <v>3</v>
+      </c>
+      <c r="G105" s="26" t="s">
+        <v>1170</v>
+      </c>
+      <c r="H105" s="26">
+        <v>2</v>
+      </c>
+      <c r="I105" s="26" t="str">
+        <f t="shared" si="8"/>
+        <v>4,3</v>
+      </c>
+      <c r="J105" t="s">
         <v>983</v>
       </c>
-      <c r="J105" t="str">
-        <f t="shared" si="2"/>
-        <v>EngOilPrimingState;</v>
-      </c>
-    </row>
-    <row r="106" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="L105" t="str">
+        <f t="shared" si="4"/>
+        <v>DPFC1_DslPrtcltFltrActvRgnrtnInhbtdDTA</v>
+      </c>
+      <c r="M105" t="str">
+        <f t="shared" si="5"/>
+        <v>GVL_J1939.DPFC1_DslPrtcltFltrActvRgnrtnInhbtdDTA</v>
+      </c>
+      <c r="N105" t="str">
+        <f t="shared" si="6"/>
+        <v>GVL_J1939.DPFC1_DslPrtcltFltrActvRgnrtnInhbtdDTA;</v>
+      </c>
+      <c r="O105" t="str">
+        <f t="shared" si="7"/>
+        <v>DPFC1_DslPrtcltFltrActvRgnrtnInhbtdDTA:USINT; // SPN:3707</v>
+      </c>
+    </row>
+    <row r="106" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A106">
+        <v>105</v>
+      </c>
       <c r="B106" t="s">
-        <v>938</v>
+        <v>888</v>
       </c>
       <c r="C106" t="s">
-        <v>1085</v>
-      </c>
-      <c r="H106" t="s">
+        <v>1097</v>
+      </c>
+      <c r="D106" s="35">
+        <v>3708</v>
+      </c>
+      <c r="F106" s="26">
+        <v>3</v>
+      </c>
+      <c r="G106" s="26" t="s">
+        <v>1172</v>
+      </c>
+      <c r="H106" s="26">
+        <v>4</v>
+      </c>
+      <c r="I106" s="26" t="str">
+        <f t="shared" si="8"/>
+        <v>4,5</v>
+      </c>
+      <c r="J106" t="s">
         <v>983</v>
       </c>
-      <c r="J106" t="str">
-        <f t="shared" si="2"/>
-        <v>EngOilPreHeatedState;</v>
-      </c>
-    </row>
-    <row r="107" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="L106" t="str">
+        <f t="shared" si="4"/>
+        <v>DPFC1_DslPrtcltFltrActvRgnrtnInhbtdDTO</v>
+      </c>
+      <c r="M106" t="str">
+        <f t="shared" si="5"/>
+        <v>GVL_J1939.DPFC1_DslPrtcltFltrActvRgnrtnInhbtdDTO</v>
+      </c>
+      <c r="N106" t="str">
+        <f t="shared" si="6"/>
+        <v>GVL_J1939.DPFC1_DslPrtcltFltrActvRgnrtnInhbtdDTO;</v>
+      </c>
+      <c r="O106" t="str">
+        <f t="shared" si="7"/>
+        <v>DPFC1_DslPrtcltFltrActvRgnrtnInhbtdDTO:USINT; // SPN:3708</v>
+      </c>
+    </row>
+    <row r="107" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A107">
+        <v>106</v>
+      </c>
       <c r="B107" t="s">
-        <v>938</v>
+        <v>888</v>
       </c>
       <c r="C107" t="s">
-        <v>1086</v>
-      </c>
-      <c r="H107" t="s">
+        <v>1098</v>
+      </c>
+      <c r="D107" s="35">
+        <v>3709</v>
+      </c>
+      <c r="F107" s="26">
+        <v>3</v>
+      </c>
+      <c r="G107" s="26" t="s">
+        <v>1173</v>
+      </c>
+      <c r="H107" s="26">
+        <v>6</v>
+      </c>
+      <c r="I107" s="26" t="str">
+        <f t="shared" si="8"/>
+        <v>4,7</v>
+      </c>
+      <c r="J107" t="s">
         <v>983</v>
       </c>
-      <c r="J107" t="str">
-        <f t="shared" si="2"/>
-        <v>EngCoolantPreheatedState;</v>
-      </c>
-    </row>
-    <row r="108" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="L107" t="str">
+        <f t="shared" si="4"/>
+        <v>DPFC1_DslPrtcltFltrActvRgnrtnInhb_0002</v>
+      </c>
+      <c r="M107" t="str">
+        <f t="shared" si="5"/>
+        <v>GVL_J1939.DPFC1_DslPrtcltFltrActvRgnrtnInhb_0002</v>
+      </c>
+      <c r="N107" t="str">
+        <f t="shared" si="6"/>
+        <v>GVL_J1939.DPFC1_DslPrtcltFltrActvRgnrtnInhb_0002;</v>
+      </c>
+      <c r="O107" t="str">
+        <f t="shared" si="7"/>
+        <v>DPFC1_DslPrtcltFltrActvRgnrtnInhb_0002:USINT; // SPN:3709</v>
+      </c>
+    </row>
+    <row r="108" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A108">
+        <v>107</v>
+      </c>
       <c r="B108" t="s">
-        <v>938</v>
+        <v>888</v>
       </c>
       <c r="C108" t="s">
-        <v>1087</v>
-      </c>
-      <c r="H108" t="s">
+        <v>1099</v>
+      </c>
+      <c r="D108" s="35">
+        <v>3710</v>
+      </c>
+      <c r="F108" s="26">
+        <v>4</v>
+      </c>
+      <c r="G108" s="26" t="s">
+        <v>1169</v>
+      </c>
+      <c r="H108" s="26">
+        <v>0</v>
+      </c>
+      <c r="I108" s="26" t="str">
+        <f t="shared" si="8"/>
+        <v>5,1</v>
+      </c>
+      <c r="J108" t="s">
         <v>983</v>
       </c>
-      <c r="J108" t="str">
-        <f t="shared" si="2"/>
-        <v>EngVentilationStatus;</v>
-      </c>
-    </row>
-    <row r="109" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="L108" t="str">
+        <f t="shared" si="4"/>
+        <v>DPFC1_DslPrtcltFltrActvRgnrtnInhb_0001</v>
+      </c>
+      <c r="M108" t="str">
+        <f t="shared" si="5"/>
+        <v>GVL_J1939.DPFC1_DslPrtcltFltrActvRgnrtnInhb_0001</v>
+      </c>
+      <c r="N108" t="str">
+        <f t="shared" si="6"/>
+        <v>GVL_J1939.DPFC1_DslPrtcltFltrActvRgnrtnInhb_0001;</v>
+      </c>
+      <c r="O108" t="str">
+        <f t="shared" si="7"/>
+        <v>DPFC1_DslPrtcltFltrActvRgnrtnInhb_0001:USINT; // SPN:3710</v>
+      </c>
+    </row>
+    <row r="109" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A109">
+        <v>108</v>
+      </c>
       <c r="B109" t="s">
-        <v>938</v>
+        <v>888</v>
       </c>
       <c r="C109" t="s">
-        <v>1088</v>
-      </c>
-      <c r="H109" t="s">
+        <v>1100</v>
+      </c>
+      <c r="D109" s="35">
+        <v>3711</v>
+      </c>
+      <c r="F109" s="26">
+        <v>4</v>
+      </c>
+      <c r="G109" s="26" t="s">
+        <v>1170</v>
+      </c>
+      <c r="H109" s="26">
+        <v>2</v>
+      </c>
+      <c r="I109" s="26" t="str">
+        <f t="shared" si="8"/>
+        <v>5,3</v>
+      </c>
+      <c r="J109" t="s">
         <v>983</v>
       </c>
-      <c r="J109" t="str">
-        <f t="shared" si="2"/>
-        <v>FuelPumpPrimerStatus;</v>
-      </c>
-    </row>
-    <row r="110" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="J110" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="111" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="L109" t="str">
+        <f t="shared" si="4"/>
+        <v>DPFC1_DslPrtcltFltrActvRgnrtnInhbtdDTL</v>
+      </c>
+      <c r="M109" t="str">
+        <f t="shared" si="5"/>
+        <v>GVL_J1939.DPFC1_DslPrtcltFltrActvRgnrtnInhbtdDTL</v>
+      </c>
+      <c r="N109" t="str">
+        <f t="shared" si="6"/>
+        <v>GVL_J1939.DPFC1_DslPrtcltFltrActvRgnrtnInhbtdDTL;</v>
+      </c>
+      <c r="O109" t="str">
+        <f t="shared" si="7"/>
+        <v>DPFC1_DslPrtcltFltrActvRgnrtnInhbtdDTL:USINT; // SPN:3711</v>
+      </c>
+    </row>
+    <row r="110" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A110">
+        <v>109</v>
+      </c>
+      <c r="B110" t="s">
+        <v>888</v>
+      </c>
+      <c r="C110" t="s">
+        <v>1101</v>
+      </c>
+      <c r="D110" s="35">
+        <v>3712</v>
+      </c>
+      <c r="F110" s="26">
+        <v>4</v>
+      </c>
+      <c r="G110" s="26" t="s">
+        <v>1172</v>
+      </c>
+      <c r="H110" s="26">
+        <v>4</v>
+      </c>
+      <c r="I110" s="26" t="str">
+        <f t="shared" si="8"/>
+        <v>5,5</v>
+      </c>
+      <c r="J110" t="s">
+        <v>983</v>
+      </c>
+      <c r="L110" t="str">
+        <f t="shared" si="4"/>
+        <v>DPFC1_DslPrtcltFltrActvRgnrtnInhb_0000</v>
+      </c>
+      <c r="M110" t="str">
+        <f t="shared" si="5"/>
+        <v>GVL_J1939.DPFC1_DslPrtcltFltrActvRgnrtnInhb_0000</v>
+      </c>
+      <c r="N110" t="str">
+        <f t="shared" si="6"/>
+        <v>GVL_J1939.DPFC1_DslPrtcltFltrActvRgnrtnInhb_0000;</v>
+      </c>
+      <c r="O110" t="str">
+        <f t="shared" si="7"/>
+        <v>DPFC1_DslPrtcltFltrActvRgnrtnInhb_0000:USINT; // SPN:3712</v>
+      </c>
+    </row>
+    <row r="111" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A111">
+        <v>110</v>
+      </c>
       <c r="B111" t="s">
         <v>888</v>
       </c>
-      <c r="C111" s="33" t="s">
-        <v>1089</v>
-      </c>
-      <c r="D111" s="26">
-        <v>0</v>
-      </c>
-      <c r="E111" s="26" t="s">
-        <v>1179</v>
+      <c r="C111" t="s">
+        <v>1102</v>
+      </c>
+      <c r="D111" s="35">
+        <v>3713</v>
       </c>
       <c r="F111" s="26">
-        <v>0</v>
-      </c>
-      <c r="G111" s="26" t="str">
-        <f>_xlfn.CONCAT(D111+1,",",F111+1)</f>
-        <v>1,1</v>
-      </c>
-      <c r="H111" t="s">
+        <v>4</v>
+      </c>
+      <c r="G111" s="26" t="s">
+        <v>1173</v>
+      </c>
+      <c r="H111" s="26">
+        <v>6</v>
+      </c>
+      <c r="I111" s="26" t="str">
+        <f t="shared" si="8"/>
+        <v>5,7</v>
+      </c>
+      <c r="J111" t="s">
         <v>983</v>
       </c>
-      <c r="J111" t="str">
-        <f t="shared" si="2"/>
-        <v>DieselParticulateFilterLampCmd;</v>
-      </c>
-    </row>
-    <row r="112" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="L111" t="str">
+        <f t="shared" si="4"/>
+        <v>DPFC1_DslPrtcltFltrActvRgnrtnInhbtdDTS</v>
+      </c>
+      <c r="M111" t="str">
+        <f t="shared" si="5"/>
+        <v>GVL_J1939.DPFC1_DslPrtcltFltrActvRgnrtnInhbtdDTS</v>
+      </c>
+      <c r="N111" t="str">
+        <f t="shared" si="6"/>
+        <v>GVL_J1939.DPFC1_DslPrtcltFltrActvRgnrtnInhbtdDTS;</v>
+      </c>
+      <c r="O111" t="str">
+        <f t="shared" si="7"/>
+        <v>DPFC1_DslPrtcltFltrActvRgnrtnInhbtdDTS:USINT; // SPN:3713</v>
+      </c>
+    </row>
+    <row r="112" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A112">
+        <v>111</v>
+      </c>
       <c r="B112" t="s">
         <v>888</v>
       </c>
-      <c r="C112" t="s">
-        <v>1090</v>
-      </c>
-      <c r="D112" s="26">
-        <v>1</v>
-      </c>
-      <c r="E112" s="26" t="s">
-        <v>1180</v>
+      <c r="C112" s="33" t="s">
+        <v>1103</v>
+      </c>
+      <c r="D112" s="35">
+        <v>3714</v>
+      </c>
+      <c r="E112" t="s">
+        <v>682</v>
       </c>
       <c r="F112" s="26">
+        <v>5</v>
+      </c>
+      <c r="G112" s="26" t="s">
+        <v>1169</v>
+      </c>
+      <c r="H112" s="26">
         <v>0</v>
       </c>
-      <c r="G112" s="26" t="str">
-        <f t="shared" ref="G112:G133" si="3">_xlfn.CONCAT(D112+1,",",F112+1)</f>
-        <v>2,1</v>
-      </c>
-      <c r="H112" t="s">
+      <c r="I112" s="26" t="str">
+        <f t="shared" si="8"/>
+        <v>6,1</v>
+      </c>
+      <c r="J112" t="s">
         <v>983</v>
       </c>
-      <c r="J112" t="str">
-        <f t="shared" si="2"/>
-        <v>DslPrtcltFltrPssvRgnrtionStatus;</v>
-      </c>
-    </row>
-    <row r="113" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="L112" t="str">
+        <f t="shared" si="4"/>
+        <v>DPFC1_DslPrtcltFltrActvRgnrtnInhbtdDTT</v>
+      </c>
+      <c r="M112" t="str">
+        <f t="shared" si="5"/>
+        <v>GVL_J1939.DPFC1_DslPrtcltFltrActvRgnrtnInhbtdDTT</v>
+      </c>
+      <c r="N112" t="str">
+        <f t="shared" si="6"/>
+        <v>GVL_J1939.DPFC1_DslPrtcltFltrActvRgnrtnInhbtdDTT;</v>
+      </c>
+      <c r="O112" t="str">
+        <f t="shared" si="7"/>
+        <v>DPFC1_DslPrtcltFltrActvRgnrtnInhbtdDTT:USINT; // SPN:3714</v>
+      </c>
+    </row>
+    <row r="113" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A113">
+        <v>112</v>
+      </c>
       <c r="B113" t="s">
         <v>888</v>
       </c>
       <c r="C113" s="33" t="s">
-        <v>1091</v>
-      </c>
-      <c r="D113" s="26">
-        <v>1</v>
-      </c>
-      <c r="E113" s="26" t="s">
-        <v>1181</v>
+        <v>1104</v>
+      </c>
+      <c r="D113" s="35">
+        <v>3715</v>
+      </c>
+      <c r="E113" t="s">
+        <v>682</v>
       </c>
       <c r="F113" s="26">
+        <v>5</v>
+      </c>
+      <c r="G113" s="26" t="s">
+        <v>1170</v>
+      </c>
+      <c r="H113" s="26">
         <v>2</v>
       </c>
-      <c r="G113" s="26" t="str">
-        <f t="shared" si="3"/>
-        <v>2,3</v>
-      </c>
-      <c r="H113" t="s">
+      <c r="I113" s="26" t="str">
+        <f t="shared" si="8"/>
+        <v>6,3</v>
+      </c>
+      <c r="J113" t="s">
         <v>983</v>
       </c>
-      <c r="J113" t="str">
-        <f t="shared" si="2"/>
-        <v>DslPrtcltFltrActvRgnrtionStatus;</v>
-      </c>
-    </row>
-    <row r="114" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="L113" t="str">
+        <f t="shared" si="4"/>
+        <v>DPFC1_DslPrtcltFltrActvRgnrtnInhbtdDTP</v>
+      </c>
+      <c r="M113" t="str">
+        <f t="shared" si="5"/>
+        <v>GVL_J1939.DPFC1_DslPrtcltFltrActvRgnrtnInhbtdDTP</v>
+      </c>
+      <c r="N113" t="str">
+        <f t="shared" si="6"/>
+        <v>GVL_J1939.DPFC1_DslPrtcltFltrActvRgnrtnInhbtdDTP;</v>
+      </c>
+      <c r="O113" t="str">
+        <f t="shared" si="7"/>
+        <v>DPFC1_DslPrtcltFltrActvRgnrtnInhbtdDTP:USINT; // SPN:3715</v>
+      </c>
+    </row>
+    <row r="114" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A114">
+        <v>113</v>
+      </c>
       <c r="B114" t="s">
         <v>888</v>
       </c>
-      <c r="C114" s="33" t="s">
-        <v>1092</v>
-      </c>
-      <c r="D114" s="26">
-        <v>1</v>
-      </c>
-      <c r="E114" s="26" t="s">
-        <v>1182</v>
+      <c r="C114" t="s">
+        <v>1105</v>
+      </c>
+      <c r="D114" s="35">
+        <v>3716</v>
       </c>
       <c r="F114" s="26">
+        <v>5</v>
+      </c>
+      <c r="G114" s="26" t="s">
+        <v>1172</v>
+      </c>
+      <c r="H114" s="26">
         <v>4</v>
       </c>
-      <c r="G114" s="26" t="str">
-        <f t="shared" si="3"/>
-        <v>2,5</v>
-      </c>
-      <c r="H114" t="s">
+      <c r="I114" s="26" t="str">
+        <f t="shared" si="8"/>
+        <v>6,5</v>
+      </c>
+      <c r="J114" t="s">
         <v>983</v>
       </c>
-      <c r="J114" t="str">
-        <f t="shared" si="2"/>
-        <v>DieselParticulateFilterStatus;</v>
-      </c>
-    </row>
-    <row r="115" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="L114" t="str">
+        <f t="shared" si="4"/>
+        <v>DPFC1_DslPrtcltFltrActvRgnrtnInhbtdDTE</v>
+      </c>
+      <c r="M114" t="str">
+        <f t="shared" si="5"/>
+        <v>GVL_J1939.DPFC1_DslPrtcltFltrActvRgnrtnInhbtdDTE</v>
+      </c>
+      <c r="N114" t="str">
+        <f t="shared" si="6"/>
+        <v>GVL_J1939.DPFC1_DslPrtcltFltrActvRgnrtnInhbtdDTE;</v>
+      </c>
+      <c r="O114" t="str">
+        <f t="shared" si="7"/>
+        <v>DPFC1_DslPrtcltFltrActvRgnrtnInhbtdDTE:USINT; // SPN:3716</v>
+      </c>
+    </row>
+    <row r="115" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A115">
+        <v>114</v>
+      </c>
       <c r="B115" t="s">
         <v>888</v>
       </c>
       <c r="C115" t="s">
-        <v>1093</v>
-      </c>
-      <c r="D115" s="26">
-        <v>2</v>
-      </c>
-      <c r="E115" s="26" t="s">
-        <v>1180</v>
+        <v>1106</v>
+      </c>
+      <c r="D115" s="35">
+        <v>3717</v>
       </c>
       <c r="F115" s="26">
-        <v>0</v>
-      </c>
-      <c r="G115" s="26" t="str">
-        <f t="shared" si="3"/>
-        <v>3,1</v>
-      </c>
-      <c r="H115" t="s">
+        <v>5</v>
+      </c>
+      <c r="G115" s="26" t="s">
+        <v>1173</v>
+      </c>
+      <c r="H115" s="26">
+        <v>6</v>
+      </c>
+      <c r="I115" s="26" t="str">
+        <f t="shared" si="8"/>
+        <v>6,7</v>
+      </c>
+      <c r="J115" t="s">
         <v>983</v>
       </c>
-      <c r="J115" t="str">
-        <f t="shared" si="2"/>
-        <v>DslPrtcltFltrActvRgnrtnInhbtdStt;</v>
-      </c>
-    </row>
-    <row r="116" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="L115" t="str">
+        <f t="shared" si="4"/>
+        <v>DPFC1_DslPrtcltFltrActvRgnrtnInhbtdDTV</v>
+      </c>
+      <c r="M115" t="str">
+        <f t="shared" si="5"/>
+        <v>GVL_J1939.DPFC1_DslPrtcltFltrActvRgnrtnInhbtdDTV</v>
+      </c>
+      <c r="N115" t="str">
+        <f t="shared" si="6"/>
+        <v>GVL_J1939.DPFC1_DslPrtcltFltrActvRgnrtnInhbtdDTV;</v>
+      </c>
+      <c r="O115" t="str">
+        <f t="shared" si="7"/>
+        <v>DPFC1_DslPrtcltFltrActvRgnrtnInhbtdDTV:USINT; // SPN:3717</v>
+      </c>
+    </row>
+    <row r="116" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A116">
+        <v>115</v>
+      </c>
       <c r="B116" t="s">
         <v>888</v>
       </c>
-      <c r="C116" s="33" t="s">
-        <v>1094</v>
-      </c>
-      <c r="D116" s="26">
-        <v>2</v>
-      </c>
-      <c r="E116" s="26" t="s">
-        <v>1181</v>
+      <c r="C116" t="s">
+        <v>1107</v>
+      </c>
+      <c r="D116" s="35">
+        <v>3718</v>
       </c>
       <c r="F116" s="26">
-        <v>2</v>
-      </c>
-      <c r="G116" s="26" t="str">
-        <f t="shared" si="3"/>
-        <v>3,3</v>
-      </c>
-      <c r="H116" t="s">
+        <v>6</v>
+      </c>
+      <c r="G116" s="26" t="s">
+        <v>1169</v>
+      </c>
+      <c r="H116" s="26">
+        <v>0</v>
+      </c>
+      <c r="I116" s="26" t="str">
+        <f t="shared" si="8"/>
+        <v>7,1</v>
+      </c>
+      <c r="J116" t="s">
         <v>983</v>
       </c>
-      <c r="J116" t="str">
-        <f t="shared" si="2"/>
-        <v>DslPrtcltFltrActvRgnrtnInhbtdDTI;</v>
-      </c>
-    </row>
-    <row r="117" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="L116" t="str">
+        <f t="shared" si="4"/>
+        <v>DPFC1_DslPrtcltFltrAtmtcActvRgnrtnIntt</v>
+      </c>
+      <c r="M116" t="str">
+        <f t="shared" si="5"/>
+        <v>GVL_J1939.DPFC1_DslPrtcltFltrAtmtcActvRgnrtnIntt</v>
+      </c>
+      <c r="N116" t="str">
+        <f t="shared" si="6"/>
+        <v>GVL_J1939.DPFC1_DslPrtcltFltrAtmtcActvRgnrtnIntt;</v>
+      </c>
+      <c r="O116" t="str">
+        <f t="shared" si="7"/>
+        <v>DPFC1_DslPrtcltFltrAtmtcActvRgnrtnIntt:USINT; // SPN:3718</v>
+      </c>
+    </row>
+    <row r="117" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A117">
+        <v>116</v>
+      </c>
       <c r="B117" t="s">
         <v>888</v>
       </c>
       <c r="C117" t="s">
-        <v>1095</v>
-      </c>
-      <c r="D117" s="26">
+        <v>1108</v>
+      </c>
+      <c r="D117" s="35">
+        <v>3698</v>
+      </c>
+      <c r="F117" s="26">
+        <v>6</v>
+      </c>
+      <c r="G117" s="26" t="s">
+        <v>1174</v>
+      </c>
+      <c r="H117" s="26">
         <v>2</v>
       </c>
-      <c r="E117" s="26" t="s">
-        <v>1183</v>
-      </c>
-      <c r="F117" s="26">
-        <v>4</v>
-      </c>
-      <c r="G117" s="26" t="str">
-        <f t="shared" si="3"/>
-        <v>3,5</v>
-      </c>
-      <c r="H117" t="s">
+      <c r="I117" s="26" t="str">
+        <f t="shared" si="8"/>
+        <v>7,3</v>
+      </c>
+      <c r="J117" t="s">
         <v>983</v>
       </c>
-      <c r="J117" t="str">
-        <f t="shared" si="2"/>
-        <v>DslPrtcltFltrActvRgnrtnInhbtdDTC;</v>
-      </c>
-    </row>
-    <row r="118" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="L117" t="str">
+        <f t="shared" si="4"/>
+        <v>DPFC1_ExhaustSystemHighTempLampCmd</v>
+      </c>
+      <c r="M117" t="str">
+        <f t="shared" si="5"/>
+        <v>GVL_J1939.DPFC1_ExhaustSystemHighTempLampCmd</v>
+      </c>
+      <c r="N117" t="str">
+        <f t="shared" si="6"/>
+        <v>GVL_J1939.DPFC1_ExhaustSystemHighTempLampCmd;</v>
+      </c>
+      <c r="O117" t="str">
+        <f t="shared" si="7"/>
+        <v>DPFC1_ExhaustSystemHighTempLampCmd:USINT; // SPN:3698</v>
+      </c>
+    </row>
+    <row r="118" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A118">
+        <v>117</v>
+      </c>
       <c r="B118" t="s">
         <v>888</v>
       </c>
       <c r="C118" t="s">
-        <v>1096</v>
-      </c>
-      <c r="D118" s="26">
-        <v>2</v>
-      </c>
-      <c r="E118" s="26" t="s">
-        <v>1184</v>
+        <v>1109</v>
+      </c>
+      <c r="D118" s="35">
+        <v>4175</v>
       </c>
       <c r="F118" s="26">
         <v>6</v>
       </c>
-      <c r="G118" s="26" t="str">
-        <f t="shared" si="3"/>
-        <v>3,7</v>
-      </c>
-      <c r="H118" t="s">
+      <c r="G118" s="26" t="s">
+        <v>1175</v>
+      </c>
+      <c r="H118" s="26">
+        <v>5</v>
+      </c>
+      <c r="I118" s="26" t="str">
+        <f t="shared" si="8"/>
+        <v>7,6</v>
+      </c>
+      <c r="J118" t="s">
         <v>983</v>
       </c>
-      <c r="J118" t="str">
-        <f t="shared" si="2"/>
-        <v>DslPrtcltFltrActvRgnrtnInhb_0004;</v>
-      </c>
-    </row>
-    <row r="119" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="L118" t="str">
+        <f t="shared" si="4"/>
+        <v>DPFC1_DslPrtcltFltrActvRgnrtnFrcdStts</v>
+      </c>
+      <c r="M118" t="str">
+        <f t="shared" si="5"/>
+        <v>GVL_J1939.DPFC1_DslPrtcltFltrActvRgnrtnFrcdStts</v>
+      </c>
+      <c r="N118" t="str">
+        <f t="shared" si="6"/>
+        <v>GVL_J1939.DPFC1_DslPrtcltFltrActvRgnrtnFrcdStts;</v>
+      </c>
+      <c r="O118" t="str">
+        <f t="shared" si="7"/>
+        <v>DPFC1_DslPrtcltFltrActvRgnrtnFrcdStts:USINT; // SPN:4175</v>
+      </c>
+    </row>
+    <row r="119" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A119">
+        <v>118</v>
+      </c>
       <c r="B119" t="s">
-        <v>888</v>
+        <v>935</v>
       </c>
       <c r="C119" t="s">
-        <v>1097</v>
-      </c>
-      <c r="D119" s="26">
+        <v>1110</v>
+      </c>
+      <c r="D119" s="35">
+        <v>3241</v>
+      </c>
+      <c r="J119" t="s">
+        <v>984</v>
+      </c>
+      <c r="L119" t="str">
+        <f t="shared" si="4"/>
+        <v>AT1IG2_Aftertreatment1ExhaustGasTemp1</v>
+      </c>
+      <c r="M119" t="str">
+        <f t="shared" si="5"/>
+        <v>GVL_J1939.AT1IG2_Aftertreatment1ExhaustGasTemp1</v>
+      </c>
+      <c r="N119" t="str">
+        <f t="shared" si="6"/>
+        <v>GVL_J1939.AT1IG2_Aftertreatment1ExhaustGasTemp1;</v>
+      </c>
+      <c r="O119" t="str">
+        <f t="shared" si="7"/>
+        <v>AT1IG2_Aftertreatment1ExhaustGasTemp1:REAL; // SPN:3241</v>
+      </c>
+    </row>
+    <row r="120" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A120">
+        <v>119</v>
+      </c>
+      <c r="B120" t="s">
+        <v>935</v>
+      </c>
+      <c r="C120" t="s">
+        <v>1111</v>
+      </c>
+      <c r="D120" s="35">
+        <v>3242</v>
+      </c>
+      <c r="E120" t="s">
+        <v>682</v>
+      </c>
+      <c r="J120" t="s">
+        <v>984</v>
+      </c>
+      <c r="L120" t="str">
+        <f t="shared" si="4"/>
+        <v>AT1IG2_Aftrtrtmnt1DslPrtcltFltrInt_0000</v>
+      </c>
+      <c r="M120" t="str">
+        <f t="shared" si="5"/>
+        <v>GVL_J1939.AT1IG2_Aftrtrtmnt1DslPrtcltFltrInt_0000</v>
+      </c>
+      <c r="N120" t="str">
+        <f t="shared" si="6"/>
+        <v>GVL_J1939.AT1IG2_Aftrtrtmnt1DslPrtcltFltrInt_0000;</v>
+      </c>
+      <c r="O120" t="str">
+        <f t="shared" si="7"/>
+        <v>AT1IG2_Aftrtrtmnt1DslPrtcltFltrInt_0000:REAL; // SPN:3242</v>
+      </c>
+    </row>
+    <row r="121" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A121">
+        <v>120</v>
+      </c>
+      <c r="B121" t="s">
+        <v>935</v>
+      </c>
+      <c r="C121" t="s">
+        <v>1112</v>
+      </c>
+      <c r="D121" s="35">
+        <v>3243</v>
+      </c>
+      <c r="J121" t="s">
+        <v>983</v>
+      </c>
+      <c r="L121" t="str">
+        <f t="shared" si="4"/>
+        <v>AT1IG2_Aftrtrtmnt1ExhstGsTmp1PrlmnryFMI</v>
+      </c>
+      <c r="M121" t="str">
+        <f t="shared" si="5"/>
+        <v>GVL_J1939.AT1IG2_Aftrtrtmnt1ExhstGsTmp1PrlmnryFMI</v>
+      </c>
+      <c r="N121" t="str">
+        <f t="shared" si="6"/>
+        <v>GVL_J1939.AT1IG2_Aftrtrtmnt1ExhstGsTmp1PrlmnryFMI;</v>
+      </c>
+      <c r="O121" t="str">
+        <f t="shared" si="7"/>
+        <v>AT1IG2_Aftrtrtmnt1ExhstGsTmp1PrlmnryFMI:USINT; // SPN:3243</v>
+      </c>
+    </row>
+    <row r="122" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A122">
+        <v>121</v>
+      </c>
+      <c r="B122" t="s">
+        <v>935</v>
+      </c>
+      <c r="C122" t="s">
+        <v>1113</v>
+      </c>
+      <c r="D122" s="35">
+        <v>3244</v>
+      </c>
+      <c r="J122" t="s">
+        <v>983</v>
+      </c>
+      <c r="L122" t="str">
+        <f t="shared" si="4"/>
+        <v>AT1IG2_Aftrtrtmnt1DslPrtcltFltrIntkGsTm</v>
+      </c>
+      <c r="M122" t="str">
+        <f t="shared" si="5"/>
+        <v>GVL_J1939.AT1IG2_Aftrtrtmnt1DslPrtcltFltrIntkGsTm</v>
+      </c>
+      <c r="N122" t="str">
+        <f t="shared" si="6"/>
+        <v>GVL_J1939.AT1IG2_Aftrtrtmnt1DslPrtcltFltrIntkGsTm;</v>
+      </c>
+      <c r="O122" t="str">
+        <f t="shared" si="7"/>
+        <v>AT1IG2_Aftrtrtmnt1DslPrtcltFltrIntkGsTm:USINT; // SPN:3244</v>
+      </c>
+    </row>
+    <row r="123" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A123">
+        <v>122</v>
+      </c>
+      <c r="B123" t="s">
+        <v>1123</v>
+      </c>
+      <c r="C123" t="s">
+        <v>1114</v>
+      </c>
+      <c r="D123" s="35">
+        <v>1761</v>
+      </c>
+      <c r="E123" t="s">
+        <v>682</v>
+      </c>
+      <c r="J123" t="s">
+        <v>984</v>
+      </c>
+      <c r="L123" t="str">
+        <f t="shared" si="4"/>
+        <v>AT1T1I_Aftrtrtmnt1SCRCatalystTankLevel</v>
+      </c>
+      <c r="M123" t="str">
+        <f t="shared" si="5"/>
+        <v>GVL_J1939.AT1T1I_Aftrtrtmnt1SCRCatalystTankLevel</v>
+      </c>
+      <c r="N123" t="str">
+        <f t="shared" si="6"/>
+        <v>GVL_J1939.AT1T1I_Aftrtrtmnt1SCRCatalystTankLevel;</v>
+      </c>
+      <c r="O123" t="str">
+        <f t="shared" si="7"/>
+        <v>AT1T1I_Aftrtrtmnt1SCRCatalystTankLevel:REAL; // SPN:1761</v>
+      </c>
+    </row>
+    <row r="124" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A124">
+        <v>123</v>
+      </c>
+      <c r="B124" t="s">
+        <v>1123</v>
+      </c>
+      <c r="C124" t="s">
+        <v>1115</v>
+      </c>
+      <c r="D124" s="35">
+        <v>3031</v>
+      </c>
+      <c r="E124" t="s">
+        <v>682</v>
+      </c>
+      <c r="J124" t="s">
+        <v>985</v>
+      </c>
+      <c r="L124" t="str">
+        <f t="shared" si="4"/>
+        <v>AT1T1I_Aftrtrtment1SCRCatalystTankTemp</v>
+      </c>
+      <c r="M124" t="str">
+        <f t="shared" si="5"/>
+        <v>GVL_J1939.AT1T1I_Aftrtrtment1SCRCatalystTankTemp</v>
+      </c>
+      <c r="N124" t="str">
+        <f t="shared" si="6"/>
+        <v>GVL_J1939.AT1T1I_Aftrtrtment1SCRCatalystTankTemp;</v>
+      </c>
+      <c r="O124" t="str">
+        <f t="shared" si="7"/>
+        <v>AT1T1I_Aftrtrtment1SCRCatalystTankTemp:INT; // SPN:3031</v>
+      </c>
+    </row>
+    <row r="125" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A125">
+        <v>124</v>
+      </c>
+      <c r="B125" t="s">
+        <v>1123</v>
+      </c>
+      <c r="C125" t="s">
+        <v>1116</v>
+      </c>
+      <c r="D125" s="35">
+        <v>3517</v>
+      </c>
+      <c r="J125" t="s">
+        <v>984</v>
+      </c>
+      <c r="L125" t="str">
+        <f t="shared" si="4"/>
+        <v>AT1T1I_Aftrtrtmnt1SCRCtalystTankLevel2</v>
+      </c>
+      <c r="M125" t="str">
+        <f t="shared" si="5"/>
+        <v>GVL_J1939.AT1T1I_Aftrtrtmnt1SCRCtalystTankLevel2</v>
+      </c>
+      <c r="N125" t="str">
+        <f t="shared" si="6"/>
+        <v>GVL_J1939.AT1T1I_Aftrtrtmnt1SCRCtalystTankLevel2;</v>
+      </c>
+      <c r="O125" t="str">
+        <f t="shared" si="7"/>
+        <v>AT1T1I_Aftrtrtmnt1SCRCtalystTankLevel2:REAL; // SPN:3517</v>
+      </c>
+    </row>
+    <row r="126" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A126">
+        <v>125</v>
+      </c>
+      <c r="B126" t="s">
+        <v>1123</v>
+      </c>
+      <c r="C126" t="s">
+        <v>1117</v>
+      </c>
+      <c r="D126" s="35">
+        <v>3532</v>
+      </c>
+      <c r="J126" t="s">
+        <v>983</v>
+      </c>
+      <c r="L126" t="str">
+        <f t="shared" si="4"/>
+        <v>AT1T1I_Aftrtrtmnt1SCRCtlystTnkLvlPrlmnr</v>
+      </c>
+      <c r="M126" t="str">
+        <f t="shared" si="5"/>
+        <v>GVL_J1939.AT1T1I_Aftrtrtmnt1SCRCtlystTnkLvlPrlmnr</v>
+      </c>
+      <c r="N126" t="str">
+        <f t="shared" si="6"/>
+        <v>GVL_J1939.AT1T1I_Aftrtrtmnt1SCRCtlystTnkLvlPrlmnr;</v>
+      </c>
+      <c r="O126" t="str">
+        <f t="shared" si="7"/>
+        <v>AT1T1I_Aftrtrtmnt1SCRCtlystTnkLvlPrlmnr:USINT; // SPN:3532</v>
+      </c>
+    </row>
+    <row r="127" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A127">
+        <v>126</v>
+      </c>
+      <c r="B127" t="s">
+        <v>1123</v>
+      </c>
+      <c r="C127" t="s">
+        <v>1118</v>
+      </c>
+      <c r="D127" s="35">
+        <v>5245</v>
+      </c>
+      <c r="E127" t="s">
+        <v>682</v>
+      </c>
+      <c r="J127" t="s">
+        <v>983</v>
+      </c>
+      <c r="L127" t="str">
+        <f t="shared" si="4"/>
+        <v>AT1T1I_Aftrtrtmnt1DEFTnkLwLvlIndicator</v>
+      </c>
+      <c r="M127" t="str">
+        <f t="shared" si="5"/>
+        <v>GVL_J1939.AT1T1I_Aftrtrtmnt1DEFTnkLwLvlIndicator</v>
+      </c>
+      <c r="N127" t="str">
+        <f t="shared" si="6"/>
+        <v>GVL_J1939.AT1T1I_Aftrtrtmnt1DEFTnkLwLvlIndicator;</v>
+      </c>
+      <c r="O127" t="str">
+        <f t="shared" si="7"/>
+        <v>AT1T1I_Aftrtrtmnt1DEFTnkLwLvlIndicator:USINT; // SPN:5245</v>
+      </c>
+    </row>
+    <row r="128" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A128">
+        <v>127</v>
+      </c>
+      <c r="B128" t="s">
+        <v>1123</v>
+      </c>
+      <c r="C128" t="s">
+        <v>1119</v>
+      </c>
+      <c r="D128" s="35">
+        <v>4365</v>
+      </c>
+      <c r="J128" t="s">
+        <v>983</v>
+      </c>
+      <c r="L128" t="str">
+        <f t="shared" si="4"/>
+        <v>AT1T1I_Aftrtrtmnt1SCRCtlystRgntTnk1TmpP</v>
+      </c>
+      <c r="M128" t="str">
+        <f t="shared" si="5"/>
+        <v>GVL_J1939.AT1T1I_Aftrtrtmnt1SCRCtlystRgntTnk1TmpP</v>
+      </c>
+      <c r="N128" t="str">
+        <f t="shared" si="6"/>
+        <v>GVL_J1939.AT1T1I_Aftrtrtmnt1SCRCtlystRgntTnk1TmpP;</v>
+      </c>
+      <c r="O128" t="str">
+        <f t="shared" si="7"/>
+        <v>AT1T1I_Aftrtrtmnt1SCRCtlystRgntTnk1TmpP:USINT; // SPN:4365</v>
+      </c>
+    </row>
+    <row r="129" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A129">
+        <v>128</v>
+      </c>
+      <c r="B129" t="s">
+        <v>1123</v>
+      </c>
+      <c r="C129" t="s">
+        <v>1120</v>
+      </c>
+      <c r="D129" s="35">
+        <v>5246</v>
+      </c>
+      <c r="E129" t="s">
+        <v>682</v>
+      </c>
+      <c r="J129" t="s">
+        <v>983</v>
+      </c>
+      <c r="L129" t="str">
+        <f t="shared" si="4"/>
+        <v>AT1T1I_AftrtrtmntSCROprtrIndcmntSvrity</v>
+      </c>
+      <c r="M129" t="str">
+        <f t="shared" si="5"/>
+        <v>GVL_J1939.AT1T1I_AftrtrtmntSCROprtrIndcmntSvrity</v>
+      </c>
+      <c r="N129" t="str">
+        <f t="shared" si="6"/>
+        <v>GVL_J1939.AT1T1I_AftrtrtmntSCROprtrIndcmntSvrity;</v>
+      </c>
+      <c r="O129" t="str">
+        <f t="shared" si="7"/>
+        <v>AT1T1I_AftrtrtmntSCROprtrIndcmntSvrity:USINT; // SPN:5246</v>
+      </c>
+    </row>
+    <row r="130" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A130">
+        <v>129</v>
+      </c>
+      <c r="B130" t="s">
+        <v>1123</v>
+      </c>
+      <c r="C130" t="s">
+        <v>1121</v>
+      </c>
+      <c r="D130" s="35">
+        <v>3363</v>
+      </c>
+      <c r="J130" t="s">
+        <v>984</v>
+      </c>
+      <c r="L130" t="str">
+        <f t="shared" si="4"/>
+        <v>AT1T1I_Aftrtrtmnt1SCRCtalystTankHeater</v>
+      </c>
+      <c r="M130" t="str">
+        <f t="shared" si="5"/>
+        <v>GVL_J1939.AT1T1I_Aftrtrtmnt1SCRCtalystTankHeater</v>
+      </c>
+      <c r="N130" t="str">
+        <f t="shared" si="6"/>
+        <v>GVL_J1939.AT1T1I_Aftrtrtmnt1SCRCtalystTankHeater;</v>
+      </c>
+      <c r="O130" t="str">
+        <f t="shared" si="7"/>
+        <v>AT1T1I_Aftrtrtmnt1SCRCtalystTankHeater:REAL; // SPN:3363</v>
+      </c>
+    </row>
+    <row r="131" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A131">
+        <v>130</v>
+      </c>
+      <c r="B131" t="s">
+        <v>1123</v>
+      </c>
+      <c r="C131" t="s">
+        <v>1122</v>
+      </c>
+      <c r="D131" s="35">
+        <v>4366</v>
+      </c>
+      <c r="J131" t="s">
+        <v>983</v>
+      </c>
+      <c r="L131" t="str">
+        <f t="shared" ref="L131:L171" si="9">IF(C131&lt;&gt;"",_xlfn.CONCAT(B131,"_",C131),"")</f>
+        <v>AT1T1I_Aftrtrtmnt1SCRCtlystRgntTnk1HtrP</v>
+      </c>
+      <c r="M131" t="str">
+        <f t="shared" ref="M131:M171" si="10">_xlfn.CONCAT($M$1,L131)</f>
+        <v>GVL_J1939.AT1T1I_Aftrtrtmnt1SCRCtlystRgntTnk1HtrP</v>
+      </c>
+      <c r="N131" t="str">
+        <f t="shared" ref="N131:N171" si="11">_xlfn.CONCAT(M131,";")</f>
+        <v>GVL_J1939.AT1T1I_Aftrtrtmnt1SCRCtlystRgntTnk1HtrP;</v>
+      </c>
+      <c r="O131" t="str">
+        <f t="shared" ref="O131:O171" si="12">_xlfn.CONCAT(L131,":",J131,"; // SPN:",D131)</f>
+        <v>AT1T1I_Aftrtrtmnt1SCRCtlystRgntTnk1HtrP:USINT; // SPN:4366</v>
+      </c>
+    </row>
+    <row r="132" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A132">
+        <v>140</v>
+      </c>
+      <c r="B132" t="s">
+        <v>940</v>
+      </c>
+      <c r="C132" t="s">
+        <v>1124</v>
+      </c>
+      <c r="D132" s="35">
+        <v>4331</v>
+      </c>
+      <c r="J132" t="s">
+        <v>984</v>
+      </c>
+      <c r="L132" t="str">
+        <f t="shared" si="9"/>
+        <v>A1SCRDSI1_Aftrtrtmnt1SCRActlDsngRgntQntty</v>
+      </c>
+      <c r="M132" t="str">
+        <f t="shared" si="10"/>
+        <v>GVL_J1939.A1SCRDSI1_Aftrtrtmnt1SCRActlDsngRgntQntty</v>
+      </c>
+      <c r="N132" t="str">
+        <f t="shared" si="11"/>
+        <v>GVL_J1939.A1SCRDSI1_Aftrtrtmnt1SCRActlDsngRgntQntty;</v>
+      </c>
+      <c r="O132" t="str">
+        <f t="shared" si="12"/>
+        <v>A1SCRDSI1_Aftrtrtmnt1SCRActlDsngRgntQntty:REAL; // SPN:4331</v>
+      </c>
+    </row>
+    <row r="133" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A133">
+        <v>141</v>
+      </c>
+      <c r="B133" t="s">
+        <v>940</v>
+      </c>
+      <c r="C133" t="s">
+        <v>1125</v>
+      </c>
+      <c r="D133" s="35">
+        <v>4332</v>
+      </c>
+      <c r="E133" t="s">
+        <v>682</v>
+      </c>
+      <c r="J133" t="s">
+        <v>983</v>
+      </c>
+      <c r="L133" t="str">
+        <f t="shared" si="9"/>
+        <v>A1SCRDSI1_Aftertreatment1SCRSystemState</v>
+      </c>
+      <c r="M133" t="str">
+        <f t="shared" si="10"/>
+        <v>GVL_J1939.A1SCRDSI1_Aftertreatment1SCRSystemState</v>
+      </c>
+      <c r="N133" t="str">
+        <f t="shared" si="11"/>
+        <v>GVL_J1939.A1SCRDSI1_Aftertreatment1SCRSystemState;</v>
+      </c>
+      <c r="O133" t="str">
+        <f t="shared" si="12"/>
+        <v>A1SCRDSI1_Aftertreatment1SCRSystemState:USINT; // SPN:4332</v>
+      </c>
+    </row>
+    <row r="134" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A134">
+        <v>142</v>
+      </c>
+      <c r="B134" t="s">
+        <v>940</v>
+      </c>
+      <c r="C134" t="s">
+        <v>1126</v>
+      </c>
+      <c r="D134" s="35">
+        <v>4333</v>
+      </c>
+      <c r="J134" t="s">
+        <v>984</v>
+      </c>
+      <c r="L134" t="str">
+        <f t="shared" si="9"/>
+        <v>A1SCRDSI1_Aftrtrtmnt1SCRActlRgntQnttyOfInt</v>
+      </c>
+      <c r="M134" t="str">
+        <f t="shared" si="10"/>
+        <v>GVL_J1939.A1SCRDSI1_Aftrtrtmnt1SCRActlRgntQnttyOfInt</v>
+      </c>
+      <c r="N134" t="str">
+        <f t="shared" si="11"/>
+        <v>GVL_J1939.A1SCRDSI1_Aftrtrtmnt1SCRActlRgntQnttyOfInt;</v>
+      </c>
+      <c r="O134" t="str">
+        <f t="shared" si="12"/>
+        <v>A1SCRDSI1_Aftrtrtmnt1SCRActlRgntQnttyOfInt:REAL; // SPN:4333</v>
+      </c>
+    </row>
+    <row r="135" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A135">
+        <v>143</v>
+      </c>
+      <c r="B135" t="s">
+        <v>940</v>
+      </c>
+      <c r="C135" t="s">
+        <v>1127</v>
+      </c>
+      <c r="D135" s="35">
+        <v>4334</v>
+      </c>
+      <c r="J135" t="s">
+        <v>1049</v>
+      </c>
+      <c r="L135" t="str">
+        <f t="shared" si="9"/>
+        <v>A1SCRDSI1_Aftrtrtmnt1SCRDsngRgentAbsPress</v>
+      </c>
+      <c r="M135" t="str">
+        <f t="shared" si="10"/>
+        <v>GVL_J1939.A1SCRDSI1_Aftrtrtmnt1SCRDsngRgentAbsPress</v>
+      </c>
+      <c r="N135" t="str">
+        <f t="shared" si="11"/>
+        <v>GVL_J1939.A1SCRDSI1_Aftrtrtmnt1SCRDsngRgentAbsPress;</v>
+      </c>
+      <c r="O135" t="str">
+        <f t="shared" si="12"/>
+        <v>A1SCRDSI1_Aftrtrtmnt1SCRDsngRgentAbsPress:UINT; // SPN:4334</v>
+      </c>
+    </row>
+    <row r="136" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A136">
+        <v>144</v>
+      </c>
+      <c r="B136" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C136" t="s">
+        <v>1129</v>
+      </c>
+      <c r="D136" s="35">
+        <v>4360</v>
+      </c>
+      <c r="E136" t="s">
+        <v>682</v>
+      </c>
+      <c r="J136" t="s">
+        <v>984</v>
+      </c>
+      <c r="L136" t="str">
+        <f t="shared" si="9"/>
+        <v>A1SCREGT_Aftrtrtmnt1SCRCtlystIntkGasTemp</v>
+      </c>
+      <c r="M136" t="str">
+        <f t="shared" si="10"/>
+        <v>GVL_J1939.A1SCREGT_Aftrtrtmnt1SCRCtlystIntkGasTemp</v>
+      </c>
+      <c r="N136" t="str">
+        <f t="shared" si="11"/>
+        <v>GVL_J1939.A1SCREGT_Aftrtrtmnt1SCRCtlystIntkGasTemp;</v>
+      </c>
+      <c r="O136" t="str">
+        <f t="shared" si="12"/>
+        <v>A1SCREGT_Aftrtrtmnt1SCRCtlystIntkGasTemp:REAL; // SPN:4360</v>
+      </c>
+    </row>
+    <row r="137" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A137">
+        <v>145</v>
+      </c>
+      <c r="B137" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C137" t="s">
+        <v>1130</v>
+      </c>
+      <c r="D137" s="35">
+        <v>4361</v>
+      </c>
+      <c r="J137" t="s">
+        <v>983</v>
+      </c>
+      <c r="L137" t="str">
+        <f t="shared" si="9"/>
+        <v>A1SCREGT_Aftrtrtmnt1SCRCtlystIntkGsTmpPrl</v>
+      </c>
+      <c r="M137" t="str">
+        <f t="shared" si="10"/>
+        <v>GVL_J1939.A1SCREGT_Aftrtrtmnt1SCRCtlystIntkGsTmpPrl</v>
+      </c>
+      <c r="N137" t="str">
+        <f t="shared" si="11"/>
+        <v>GVL_J1939.A1SCREGT_Aftrtrtmnt1SCRCtlystIntkGsTmpPrl;</v>
+      </c>
+      <c r="O137" t="str">
+        <f t="shared" si="12"/>
+        <v>A1SCREGT_Aftrtrtmnt1SCRCtlystIntkGsTmpPrl:USINT; // SPN:4361</v>
+      </c>
+    </row>
+    <row r="138" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A138">
+        <v>146</v>
+      </c>
+      <c r="B138" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C138" t="s">
+        <v>1131</v>
+      </c>
+      <c r="D138" s="35">
+        <v>4363</v>
+      </c>
+      <c r="J138" t="s">
+        <v>984</v>
+      </c>
+      <c r="L138" t="str">
+        <f t="shared" si="9"/>
+        <v>A1SCREGT_Aftrtrtmnt1SCRCtlystOtltGasTemp</v>
+      </c>
+      <c r="M138" t="str">
+        <f t="shared" si="10"/>
+        <v>GVL_J1939.A1SCREGT_Aftrtrtmnt1SCRCtlystOtltGasTemp</v>
+      </c>
+      <c r="N138" t="str">
+        <f t="shared" si="11"/>
+        <v>GVL_J1939.A1SCREGT_Aftrtrtmnt1SCRCtlystOtltGasTemp;</v>
+      </c>
+      <c r="O138" t="str">
+        <f t="shared" si="12"/>
+        <v>A1SCREGT_Aftrtrtmnt1SCRCtlystOtltGasTemp:REAL; // SPN:4363</v>
+      </c>
+    </row>
+    <row r="139" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A139">
+        <v>147</v>
+      </c>
+      <c r="B139" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C139" t="s">
+        <v>1132</v>
+      </c>
+      <c r="D139" s="35">
+        <v>4362</v>
+      </c>
+      <c r="J139" t="s">
+        <v>983</v>
+      </c>
+      <c r="L139" t="str">
+        <f t="shared" si="9"/>
+        <v>A1SCREGT_Aftrtrtmnt1SCRCtlystOtltGsTmpPrl</v>
+      </c>
+      <c r="M139" t="str">
+        <f t="shared" si="10"/>
+        <v>GVL_J1939.A1SCREGT_Aftrtrtmnt1SCRCtlystOtltGsTmpPrl</v>
+      </c>
+      <c r="N139" t="str">
+        <f t="shared" si="11"/>
+        <v>GVL_J1939.A1SCREGT_Aftrtrtmnt1SCRCtlystOtltGsTmpPrl;</v>
+      </c>
+      <c r="O139" t="str">
+        <f t="shared" si="12"/>
+        <v>A1SCREGT_Aftrtrtmnt1SCRCtlystOtltGsTmpPrl:USINT; // SPN:4362</v>
+      </c>
+    </row>
+    <row r="140" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A140">
+        <v>148</v>
+      </c>
+      <c r="B140" t="s">
+        <v>950</v>
+      </c>
+      <c r="C140" t="s">
+        <v>1133</v>
+      </c>
+      <c r="D140" s="35">
+        <v>4765</v>
+      </c>
+      <c r="E140" t="s">
+        <v>682</v>
+      </c>
+      <c r="J140" t="s">
+        <v>984</v>
+      </c>
+      <c r="L140" t="str">
+        <f t="shared" si="9"/>
+        <v>A1DOC_Aftrtrtmnt1DslOxdtnCtlystIn_0000</v>
+      </c>
+      <c r="M140" t="str">
+        <f t="shared" si="10"/>
+        <v>GVL_J1939.A1DOC_Aftrtrtmnt1DslOxdtnCtlystIn_0000</v>
+      </c>
+      <c r="N140" t="str">
+        <f t="shared" si="11"/>
+        <v>GVL_J1939.A1DOC_Aftrtrtmnt1DslOxdtnCtlystIn_0000;</v>
+      </c>
+      <c r="O140" t="str">
+        <f t="shared" si="12"/>
+        <v>A1DOC_Aftrtrtmnt1DslOxdtnCtlystIn_0000:REAL; // SPN:4765</v>
+      </c>
+    </row>
+    <row r="141" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A141">
+        <v>149</v>
+      </c>
+      <c r="B141" t="s">
+        <v>950</v>
+      </c>
+      <c r="C141" t="s">
+        <v>1134</v>
+      </c>
+      <c r="D141" s="35">
+        <v>4766</v>
+      </c>
+      <c r="J141" t="s">
+        <v>984</v>
+      </c>
+      <c r="L141" t="str">
+        <f t="shared" si="9"/>
+        <v>A1DOC_Aftrtrtmnt1DslOxdtnCtlystOt_0000</v>
+      </c>
+      <c r="M141" t="str">
+        <f t="shared" si="10"/>
+        <v>GVL_J1939.A1DOC_Aftrtrtmnt1DslOxdtnCtlystOt_0000</v>
+      </c>
+      <c r="N141" t="str">
+        <f t="shared" si="11"/>
+        <v>GVL_J1939.A1DOC_Aftrtrtmnt1DslOxdtnCtlystOt_0000;</v>
+      </c>
+      <c r="O141" t="str">
+        <f t="shared" si="12"/>
+        <v>A1DOC_Aftrtrtmnt1DslOxdtnCtlystOt_0000:REAL; // SPN:4766</v>
+      </c>
+    </row>
+    <row r="142" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A142">
+        <v>150</v>
+      </c>
+      <c r="B142" t="s">
+        <v>950</v>
+      </c>
+      <c r="C142" t="s">
+        <v>1135</v>
+      </c>
+      <c r="D142" s="35">
+        <v>4767</v>
+      </c>
+      <c r="J142" t="s">
+        <v>984</v>
+      </c>
+      <c r="L142" t="str">
+        <f t="shared" si="9"/>
+        <v>A1DOC_Aftrtrtmnt1DslOxdtnCtlystDffPrss</v>
+      </c>
+      <c r="M142" t="str">
+        <f t="shared" si="10"/>
+        <v>GVL_J1939.A1DOC_Aftrtrtmnt1DslOxdtnCtlystDffPrss</v>
+      </c>
+      <c r="N142" t="str">
+        <f t="shared" si="11"/>
+        <v>GVL_J1939.A1DOC_Aftrtrtmnt1DslOxdtnCtlystDffPrss;</v>
+      </c>
+      <c r="O142" t="str">
+        <f t="shared" si="12"/>
+        <v>A1DOC_Aftrtrtmnt1DslOxdtnCtlystDffPrss:REAL; // SPN:4767</v>
+      </c>
+    </row>
+    <row r="143" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A143">
+        <v>151</v>
+      </c>
+      <c r="B143" t="s">
+        <v>950</v>
+      </c>
+      <c r="C143" t="s">
+        <v>1136</v>
+      </c>
+      <c r="D143" s="35">
+        <v>4768</v>
+      </c>
+      <c r="J143" t="s">
+        <v>983</v>
+      </c>
+      <c r="L143" t="str">
+        <f t="shared" si="9"/>
+        <v>A1DOC_Aftrtrtmnt1DslOxdtnCtlystIntkGsT</v>
+      </c>
+      <c r="M143" t="str">
+        <f t="shared" si="10"/>
+        <v>GVL_J1939.A1DOC_Aftrtrtmnt1DslOxdtnCtlystIntkGsT</v>
+      </c>
+      <c r="N143" t="str">
+        <f t="shared" si="11"/>
+        <v>GVL_J1939.A1DOC_Aftrtrtmnt1DslOxdtnCtlystIntkGsT;</v>
+      </c>
+      <c r="O143" t="str">
+        <f t="shared" si="12"/>
+        <v>A1DOC_Aftrtrtmnt1DslOxdtnCtlystIntkGsT:USINT; // SPN:4768</v>
+      </c>
+    </row>
+    <row r="144" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A144">
+        <v>152</v>
+      </c>
+      <c r="B144" t="s">
+        <v>950</v>
+      </c>
+      <c r="C144" t="s">
+        <v>1137</v>
+      </c>
+      <c r="D144" s="35">
+        <v>4769</v>
+      </c>
+      <c r="J144" t="s">
+        <v>983</v>
+      </c>
+      <c r="L144" t="str">
+        <f t="shared" si="9"/>
+        <v>A1DOC_Aftrtrtmnt1DslOxdtnCtlystOtltGsT</v>
+      </c>
+      <c r="M144" t="str">
+        <f t="shared" si="10"/>
+        <v>GVL_J1939.A1DOC_Aftrtrtmnt1DslOxdtnCtlystOtltGsT</v>
+      </c>
+      <c r="N144" t="str">
+        <f t="shared" si="11"/>
+        <v>GVL_J1939.A1DOC_Aftrtrtmnt1DslOxdtnCtlystOtltGsT;</v>
+      </c>
+      <c r="O144" t="str">
+        <f t="shared" si="12"/>
+        <v>A1DOC_Aftrtrtmnt1DslOxdtnCtlystOtltGsT:USINT; // SPN:4769</v>
+      </c>
+    </row>
+    <row r="145" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A145">
+        <v>153</v>
+      </c>
+      <c r="B145" t="s">
+        <v>950</v>
+      </c>
+      <c r="C145" t="s">
+        <v>1138</v>
+      </c>
+      <c r="D145" s="35">
+        <v>4770</v>
+      </c>
+      <c r="J145" t="s">
+        <v>983</v>
+      </c>
+      <c r="L145" t="str">
+        <f t="shared" si="9"/>
+        <v>A1DOC_Aftrtrtmnt1DslOxdtnCtlystDf_0000</v>
+      </c>
+      <c r="M145" t="str">
+        <f t="shared" si="10"/>
+        <v>GVL_J1939.A1DOC_Aftrtrtmnt1DslOxdtnCtlystDf_0000</v>
+      </c>
+      <c r="N145" t="str">
+        <f t="shared" si="11"/>
+        <v>GVL_J1939.A1DOC_Aftrtrtmnt1DslOxdtnCtlystDf_0000;</v>
+      </c>
+      <c r="O145" t="str">
+        <f t="shared" si="12"/>
+        <v>A1DOC_Aftrtrtmnt1DslOxdtnCtlystDf_0000:USINT; // SPN:4770</v>
+      </c>
+    </row>
+    <row r="146" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A146">
+        <v>154</v>
+      </c>
+      <c r="B146" t="s">
+        <v>1139</v>
+      </c>
+      <c r="C146" t="s">
+        <v>1140</v>
+      </c>
+      <c r="D146" s="35">
+        <v>97</v>
+      </c>
+      <c r="E146" t="s">
+        <v>682</v>
+      </c>
+      <c r="J146" t="s">
+        <v>983</v>
+      </c>
+      <c r="L146" t="str">
+        <f t="shared" si="9"/>
+        <v>WFI_WaterInFuelIndicator</v>
+      </c>
+      <c r="M146" t="str">
+        <f t="shared" si="10"/>
+        <v>GVL_J1939.WFI_WaterInFuelIndicator</v>
+      </c>
+      <c r="N146" t="str">
+        <f t="shared" si="11"/>
+        <v>GVL_J1939.WFI_WaterInFuelIndicator;</v>
+      </c>
+      <c r="O146" t="str">
+        <f t="shared" si="12"/>
+        <v>WFI_WaterInFuelIndicator:USINT; // SPN:97</v>
+      </c>
+    </row>
+    <row r="147" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A147">
+        <v>155</v>
+      </c>
+      <c r="B147" t="s">
+        <v>961</v>
+      </c>
+      <c r="C147" t="s">
+        <v>1141</v>
+      </c>
+      <c r="D147" s="35">
+        <v>5077</v>
+      </c>
+      <c r="J147" t="s">
+        <v>983</v>
+      </c>
+      <c r="K147">
+        <v>1</v>
+      </c>
+      <c r="L147" t="str">
+        <f t="shared" si="9"/>
+        <v>DLCC1_EngProtectLampCmd</v>
+      </c>
+      <c r="M147" t="str">
+        <f t="shared" si="10"/>
+        <v>GVL_J1939.DLCC1_EngProtectLampCmd</v>
+      </c>
+      <c r="N147" t="str">
+        <f t="shared" si="11"/>
+        <v>GVL_J1939.DLCC1_EngProtectLampCmd;</v>
+      </c>
+      <c r="O147" t="str">
+        <f t="shared" si="12"/>
+        <v>DLCC1_EngProtectLampCmd:USINT; // SPN:5077</v>
+      </c>
+    </row>
+    <row r="148" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A148">
+        <v>156</v>
+      </c>
+      <c r="B148" t="s">
+        <v>961</v>
+      </c>
+      <c r="C148" t="s">
+        <v>1142</v>
+      </c>
+      <c r="D148" s="35">
+        <v>5078</v>
+      </c>
+      <c r="J148" t="s">
+        <v>983</v>
+      </c>
+      <c r="K148">
+        <v>2</v>
+      </c>
+      <c r="L148" t="str">
+        <f t="shared" si="9"/>
+        <v>DLCC1_EngAmberWarningLampCmd</v>
+      </c>
+      <c r="M148" t="str">
+        <f t="shared" si="10"/>
+        <v>GVL_J1939.DLCC1_EngAmberWarningLampCmd</v>
+      </c>
+      <c r="N148" t="str">
+        <f t="shared" si="11"/>
+        <v>GVL_J1939.DLCC1_EngAmberWarningLampCmd;</v>
+      </c>
+      <c r="O148" t="str">
+        <f t="shared" si="12"/>
+        <v>DLCC1_EngAmberWarningLampCmd:USINT; // SPN:5078</v>
+      </c>
+    </row>
+    <row r="149" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A149">
+        <v>157</v>
+      </c>
+      <c r="B149" t="s">
+        <v>961</v>
+      </c>
+      <c r="C149" t="s">
+        <v>1143</v>
+      </c>
+      <c r="D149" s="35">
+        <v>5079</v>
+      </c>
+      <c r="J149" t="s">
+        <v>983</v>
+      </c>
+      <c r="K149">
         <v>3</v>
       </c>
-      <c r="E119" s="26" t="s">
-        <v>1180</v>
-      </c>
-      <c r="F119" s="26">
-        <v>0</v>
-      </c>
-      <c r="G119" s="26" t="str">
-        <f t="shared" si="3"/>
-        <v>4,1</v>
-      </c>
-      <c r="H119" t="s">
+      <c r="L149" t="str">
+        <f t="shared" si="9"/>
+        <v>DLCC1_EngRedStopLampCmd</v>
+      </c>
+      <c r="M149" t="str">
+        <f t="shared" si="10"/>
+        <v>GVL_J1939.DLCC1_EngRedStopLampCmd</v>
+      </c>
+      <c r="N149" t="str">
+        <f t="shared" si="11"/>
+        <v>GVL_J1939.DLCC1_EngRedStopLampCmd;</v>
+      </c>
+      <c r="O149" t="str">
+        <f t="shared" si="12"/>
+        <v>DLCC1_EngRedStopLampCmd:USINT; // SPN:5079</v>
+      </c>
+    </row>
+    <row r="150" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A150">
+        <v>158</v>
+      </c>
+      <c r="B150" t="s">
+        <v>961</v>
+      </c>
+      <c r="C150" t="s">
+        <v>1144</v>
+      </c>
+      <c r="D150" s="35">
+        <v>5080</v>
+      </c>
+      <c r="J150" t="s">
         <v>983</v>
       </c>
-      <c r="J119" t="str">
-        <f t="shared" si="2"/>
-        <v>DslPrtcltFltrActvRgnrtnInhb_0003;</v>
-      </c>
-    </row>
-    <row r="120" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B120" t="s">
-        <v>888</v>
-      </c>
-      <c r="C120" t="s">
-        <v>1098</v>
-      </c>
-      <c r="D120" s="26">
+      <c r="K150">
+        <v>4</v>
+      </c>
+      <c r="L150" t="str">
+        <f t="shared" si="9"/>
+        <v>DLCC1_OBDMalfunctionIndicatorLampCmd</v>
+      </c>
+      <c r="M150" t="str">
+        <f t="shared" si="10"/>
+        <v>GVL_J1939.DLCC1_OBDMalfunctionIndicatorLampCmd</v>
+      </c>
+      <c r="N150" t="str">
+        <f t="shared" si="11"/>
+        <v>GVL_J1939.DLCC1_OBDMalfunctionIndicatorLampCmd;</v>
+      </c>
+      <c r="O150" t="str">
+        <f t="shared" si="12"/>
+        <v>DLCC1_OBDMalfunctionIndicatorLampCmd:USINT; // SPN:5080</v>
+      </c>
+    </row>
+    <row r="151" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A151">
+        <v>159</v>
+      </c>
+      <c r="B151" t="s">
+        <v>961</v>
+      </c>
+      <c r="C151" t="s">
+        <v>1145</v>
+      </c>
+      <c r="D151" s="35">
+        <v>5081</v>
+      </c>
+      <c r="J151" t="s">
+        <v>983</v>
+      </c>
+      <c r="K151">
+        <v>5</v>
+      </c>
+      <c r="L151" t="str">
+        <f t="shared" si="9"/>
+        <v>DLCC1_EngBrakeActiveLampCmd</v>
+      </c>
+      <c r="M151" t="str">
+        <f t="shared" si="10"/>
+        <v>GVL_J1939.DLCC1_EngBrakeActiveLampCmd</v>
+      </c>
+      <c r="N151" t="str">
+        <f t="shared" si="11"/>
+        <v>GVL_J1939.DLCC1_EngBrakeActiveLampCmd;</v>
+      </c>
+      <c r="O151" t="str">
+        <f t="shared" si="12"/>
+        <v>DLCC1_EngBrakeActiveLampCmd:USINT; // SPN:5081</v>
+      </c>
+    </row>
+    <row r="152" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A152">
+        <v>160</v>
+      </c>
+      <c r="B152" t="s">
+        <v>961</v>
+      </c>
+      <c r="C152" t="s">
+        <v>1146</v>
+      </c>
+      <c r="D152" s="35">
+        <v>3987</v>
+      </c>
+      <c r="J152" t="s">
+        <v>983</v>
+      </c>
+      <c r="K152">
+        <v>6</v>
+      </c>
+      <c r="L152" t="str">
+        <f t="shared" si="9"/>
+        <v>DLCC1_CmprssnBrkEnblSwtchIndctrLmpCmd</v>
+      </c>
+      <c r="M152" t="str">
+        <f t="shared" si="10"/>
+        <v>GVL_J1939.DLCC1_CmprssnBrkEnblSwtchIndctrLmpCmd</v>
+      </c>
+      <c r="N152" t="str">
+        <f t="shared" si="11"/>
+        <v>GVL_J1939.DLCC1_CmprssnBrkEnblSwtchIndctrLmpCmd;</v>
+      </c>
+      <c r="O152" t="str">
+        <f t="shared" si="12"/>
+        <v>DLCC1_CmprssnBrkEnblSwtchIndctrLmpCmd:USINT; // SPN:3987</v>
+      </c>
+    </row>
+    <row r="153" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A153">
+        <v>161</v>
+      </c>
+      <c r="B153" t="s">
+        <v>961</v>
+      </c>
+      <c r="C153" t="s">
+        <v>1147</v>
+      </c>
+      <c r="D153" s="35">
+        <v>5082</v>
+      </c>
+      <c r="J153" t="s">
+        <v>983</v>
+      </c>
+      <c r="K153">
+        <v>7</v>
+      </c>
+      <c r="L153" t="str">
+        <f t="shared" si="9"/>
+        <v>DLCC1_EngOilPressLowLampCmd</v>
+      </c>
+      <c r="M153" t="str">
+        <f t="shared" si="10"/>
+        <v>GVL_J1939.DLCC1_EngOilPressLowLampCmd</v>
+      </c>
+      <c r="N153" t="str">
+        <f t="shared" si="11"/>
+        <v>GVL_J1939.DLCC1_EngOilPressLowLampCmd;</v>
+      </c>
+      <c r="O153" t="str">
+        <f t="shared" si="12"/>
+        <v>DLCC1_EngOilPressLowLampCmd:USINT; // SPN:5082</v>
+      </c>
+    </row>
+    <row r="154" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A154">
+        <v>162</v>
+      </c>
+      <c r="B154" t="s">
+        <v>961</v>
+      </c>
+      <c r="C154" t="s">
+        <v>1148</v>
+      </c>
+      <c r="D154" s="35">
+        <v>5083</v>
+      </c>
+      <c r="J154" t="s">
+        <v>983</v>
+      </c>
+      <c r="K154">
+        <v>8</v>
+      </c>
+      <c r="L154" t="str">
+        <f t="shared" si="9"/>
+        <v>DLCC1_EngCoolantTempHighLampCmd</v>
+      </c>
+      <c r="M154" t="str">
+        <f t="shared" si="10"/>
+        <v>GVL_J1939.DLCC1_EngCoolantTempHighLampCmd</v>
+      </c>
+      <c r="N154" t="str">
+        <f t="shared" si="11"/>
+        <v>GVL_J1939.DLCC1_EngCoolantTempHighLampCmd;</v>
+      </c>
+      <c r="O154" t="str">
+        <f t="shared" si="12"/>
+        <v>DLCC1_EngCoolantTempHighLampCmd:USINT; // SPN:5083</v>
+      </c>
+    </row>
+    <row r="155" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A155">
+        <v>163</v>
+      </c>
+      <c r="B155" t="s">
+        <v>961</v>
+      </c>
+      <c r="C155" t="s">
+        <v>1149</v>
+      </c>
+      <c r="D155" s="35">
+        <v>5084</v>
+      </c>
+      <c r="J155" t="s">
+        <v>983</v>
+      </c>
+      <c r="K155">
+        <v>9</v>
+      </c>
+      <c r="L155" t="str">
+        <f t="shared" si="9"/>
+        <v>DLCC1_EngCoolantLevelLowLampCmd</v>
+      </c>
+      <c r="M155" t="str">
+        <f t="shared" si="10"/>
+        <v>GVL_J1939.DLCC1_EngCoolantLevelLowLampCmd</v>
+      </c>
+      <c r="N155" t="str">
+        <f t="shared" si="11"/>
+        <v>GVL_J1939.DLCC1_EngCoolantLevelLowLampCmd;</v>
+      </c>
+      <c r="O155" t="str">
+        <f t="shared" si="12"/>
+        <v>DLCC1_EngCoolantLevelLowLampCmd:USINT; // SPN:5084</v>
+      </c>
+    </row>
+    <row r="156" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A156">
+        <v>164</v>
+      </c>
+      <c r="B156" t="s">
+        <v>961</v>
+      </c>
+      <c r="C156" t="s">
+        <v>1150</v>
+      </c>
+      <c r="D156" s="35">
+        <v>5085</v>
+      </c>
+      <c r="J156" t="s">
+        <v>983</v>
+      </c>
+      <c r="K156">
+        <v>10</v>
+      </c>
+      <c r="L156" t="str">
+        <f t="shared" si="9"/>
+        <v>DLCC1_EngIdleManagementActiveLampCmd</v>
+      </c>
+      <c r="M156" t="str">
+        <f t="shared" si="10"/>
+        <v>GVL_J1939.DLCC1_EngIdleManagementActiveLampCmd</v>
+      </c>
+      <c r="N156" t="str">
+        <f t="shared" si="11"/>
+        <v>GVL_J1939.DLCC1_EngIdleManagementActiveLampCmd;</v>
+      </c>
+      <c r="O156" t="str">
+        <f t="shared" si="12"/>
+        <v>DLCC1_EngIdleManagementActiveLampCmd:USINT; // SPN:5085</v>
+      </c>
+    </row>
+    <row r="157" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A157">
+        <v>165</v>
+      </c>
+      <c r="B157" t="s">
+        <v>961</v>
+      </c>
+      <c r="C157" t="s">
+        <v>1151</v>
+      </c>
+      <c r="D157" s="35">
+        <v>5086</v>
+      </c>
+      <c r="E157" t="s">
+        <v>682</v>
+      </c>
+      <c r="J157" t="s">
+        <v>983</v>
+      </c>
+      <c r="K157">
+        <v>11</v>
+      </c>
+      <c r="L157" t="str">
+        <f t="shared" si="9"/>
+        <v>DLCC1_EngAirFilterRestrictionLampCmd</v>
+      </c>
+      <c r="M157" t="str">
+        <f t="shared" si="10"/>
+        <v>GVL_J1939.DLCC1_EngAirFilterRestrictionLampCmd</v>
+      </c>
+      <c r="N157" t="str">
+        <f t="shared" si="11"/>
+        <v>GVL_J1939.DLCC1_EngAirFilterRestrictionLampCmd;</v>
+      </c>
+      <c r="O157" t="str">
+        <f t="shared" si="12"/>
+        <v>DLCC1_EngAirFilterRestrictionLampCmd:USINT; // SPN:5086</v>
+      </c>
+    </row>
+    <row r="158" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A158">
+        <v>166</v>
+      </c>
+      <c r="B158" t="s">
+        <v>961</v>
+      </c>
+      <c r="C158" t="s">
+        <v>1152</v>
+      </c>
+      <c r="D158" s="35">
+        <v>5469</v>
+      </c>
+      <c r="J158" t="s">
+        <v>983</v>
+      </c>
+      <c r="K158">
+        <v>12</v>
+      </c>
+      <c r="L158" t="str">
+        <f t="shared" si="9"/>
+        <v>DLCC1_EngFuelFilterRestrictedLampCmd</v>
+      </c>
+      <c r="M158" t="str">
+        <f t="shared" si="10"/>
+        <v>GVL_J1939.DLCC1_EngFuelFilterRestrictedLampCmd</v>
+      </c>
+      <c r="N158" t="str">
+        <f t="shared" si="11"/>
+        <v>GVL_J1939.DLCC1_EngFuelFilterRestrictedLampCmd;</v>
+      </c>
+      <c r="O158" t="str">
+        <f t="shared" si="12"/>
+        <v>DLCC1_EngFuelFilterRestrictedLampCmd:USINT; // SPN:5469</v>
+      </c>
+    </row>
+    <row r="159" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A159">
+        <v>167</v>
+      </c>
+      <c r="B159" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C159" t="s">
+        <v>1154</v>
+      </c>
+      <c r="D159" s="35">
+        <v>5093</v>
+      </c>
+      <c r="J159" t="s">
+        <v>983</v>
+      </c>
+      <c r="K159">
+        <v>1</v>
+      </c>
+      <c r="L159" t="str">
+        <f t="shared" si="9"/>
+        <v>DLCD1_EngProtectLampData</v>
+      </c>
+      <c r="M159" t="str">
+        <f t="shared" si="10"/>
+        <v>GVL_J1939.DLCD1_EngProtectLampData</v>
+      </c>
+      <c r="N159" t="str">
+        <f t="shared" si="11"/>
+        <v>GVL_J1939.DLCD1_EngProtectLampData;</v>
+      </c>
+      <c r="O159" t="str">
+        <f t="shared" si="12"/>
+        <v>DLCD1_EngProtectLampData:USINT; // SPN:5093</v>
+      </c>
+    </row>
+    <row r="160" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A160">
+        <v>168</v>
+      </c>
+      <c r="B160" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C160" t="s">
+        <v>1155</v>
+      </c>
+      <c r="D160" s="35">
+        <v>5094</v>
+      </c>
+      <c r="J160" t="s">
+        <v>983</v>
+      </c>
+      <c r="K160">
+        <v>2</v>
+      </c>
+      <c r="L160" t="str">
+        <f t="shared" si="9"/>
+        <v>DLCD1_EngAmberWarningLampData</v>
+      </c>
+      <c r="M160" t="str">
+        <f t="shared" si="10"/>
+        <v>GVL_J1939.DLCD1_EngAmberWarningLampData</v>
+      </c>
+      <c r="N160" t="str">
+        <f t="shared" si="11"/>
+        <v>GVL_J1939.DLCD1_EngAmberWarningLampData;</v>
+      </c>
+      <c r="O160" t="str">
+        <f t="shared" si="12"/>
+        <v>DLCD1_EngAmberWarningLampData:USINT; // SPN:5094</v>
+      </c>
+    </row>
+    <row r="161" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A161">
+        <v>169</v>
+      </c>
+      <c r="B161" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C161" t="s">
+        <v>1156</v>
+      </c>
+      <c r="D161" s="35">
+        <v>5095</v>
+      </c>
+      <c r="J161" t="s">
+        <v>983</v>
+      </c>
+      <c r="K161">
         <v>3</v>
       </c>
-      <c r="E120" s="26" t="s">
-        <v>1181</v>
-      </c>
-      <c r="F120" s="26">
-        <v>2</v>
-      </c>
-      <c r="G120" s="26" t="str">
-        <f t="shared" si="3"/>
-        <v>4,3</v>
-      </c>
-      <c r="H120" t="s">
+      <c r="L161" t="str">
+        <f t="shared" si="9"/>
+        <v>DLCD1_EngRedStopLampData</v>
+      </c>
+      <c r="M161" t="str">
+        <f t="shared" si="10"/>
+        <v>GVL_J1939.DLCD1_EngRedStopLampData</v>
+      </c>
+      <c r="N161" t="str">
+        <f t="shared" si="11"/>
+        <v>GVL_J1939.DLCD1_EngRedStopLampData;</v>
+      </c>
+      <c r="O161" t="str">
+        <f t="shared" si="12"/>
+        <v>DLCD1_EngRedStopLampData:USINT; // SPN:5095</v>
+      </c>
+    </row>
+    <row r="162" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A162">
+        <v>170</v>
+      </c>
+      <c r="B162" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C162" t="s">
+        <v>1157</v>
+      </c>
+      <c r="D162" s="35">
+        <v>5096</v>
+      </c>
+      <c r="J162" t="s">
         <v>983</v>
       </c>
-      <c r="J120" t="str">
-        <f t="shared" si="2"/>
-        <v>DslPrtcltFltrActvRgnrtnInhbtdDTA;</v>
-      </c>
-    </row>
-    <row r="121" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B121" t="s">
-        <v>888</v>
-      </c>
-      <c r="C121" t="s">
-        <v>1099</v>
-      </c>
-      <c r="D121" s="26">
-        <v>3</v>
-      </c>
-      <c r="E121" s="26" t="s">
-        <v>1183</v>
-      </c>
-      <c r="F121" s="26">
+      <c r="K162">
         <v>4</v>
       </c>
-      <c r="G121" s="26" t="str">
-        <f t="shared" si="3"/>
-        <v>4,5</v>
-      </c>
-      <c r="H121" t="s">
+      <c r="L162" t="str">
+        <f t="shared" si="9"/>
+        <v>DLCD1_OBDMalfunctionIndicatorLampData</v>
+      </c>
+      <c r="M162" t="str">
+        <f t="shared" si="10"/>
+        <v>GVL_J1939.DLCD1_OBDMalfunctionIndicatorLampData</v>
+      </c>
+      <c r="N162" t="str">
+        <f t="shared" si="11"/>
+        <v>GVL_J1939.DLCD1_OBDMalfunctionIndicatorLampData;</v>
+      </c>
+      <c r="O162" t="str">
+        <f t="shared" si="12"/>
+        <v>DLCD1_OBDMalfunctionIndicatorLampData:USINT; // SPN:5096</v>
+      </c>
+    </row>
+    <row r="163" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A163">
+        <v>171</v>
+      </c>
+      <c r="B163" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C163" t="s">
+        <v>1158</v>
+      </c>
+      <c r="D163" s="35">
+        <v>5097</v>
+      </c>
+      <c r="J163" t="s">
         <v>983</v>
       </c>
-      <c r="J121" t="str">
-        <f t="shared" si="2"/>
-        <v>DslPrtcltFltrActvRgnrtnInhbtdDTO;</v>
-      </c>
-    </row>
-    <row r="122" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B122" t="s">
-        <v>888</v>
-      </c>
-      <c r="C122" t="s">
-        <v>1100</v>
-      </c>
-      <c r="D122" s="26">
-        <v>3</v>
-      </c>
-      <c r="E122" s="26" t="s">
-        <v>1184</v>
-      </c>
-      <c r="F122" s="26">
+      <c r="K163">
+        <v>5</v>
+      </c>
+      <c r="L163" t="str">
+        <f t="shared" si="9"/>
+        <v>DLCD1_EngBrakeActiveLampData</v>
+      </c>
+      <c r="M163" t="str">
+        <f t="shared" si="10"/>
+        <v>GVL_J1939.DLCD1_EngBrakeActiveLampData</v>
+      </c>
+      <c r="N163" t="str">
+        <f t="shared" si="11"/>
+        <v>GVL_J1939.DLCD1_EngBrakeActiveLampData;</v>
+      </c>
+      <c r="O163" t="str">
+        <f t="shared" si="12"/>
+        <v>DLCD1_EngBrakeActiveLampData:USINT; // SPN:5097</v>
+      </c>
+    </row>
+    <row r="164" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A164">
+        <v>172</v>
+      </c>
+      <c r="B164" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C164" t="s">
+        <v>1159</v>
+      </c>
+      <c r="D164" s="35">
+        <v>5098</v>
+      </c>
+      <c r="J164" t="s">
+        <v>983</v>
+      </c>
+      <c r="K164">
         <v>6</v>
       </c>
-      <c r="G122" s="26" t="str">
-        <f t="shared" si="3"/>
-        <v>4,7</v>
-      </c>
-      <c r="H122" t="s">
+      <c r="L164" t="str">
+        <f t="shared" si="9"/>
+        <v>DLCD1_CmprssnBrkEnblSwtchIndctrLmpDta</v>
+      </c>
+      <c r="M164" t="str">
+        <f t="shared" si="10"/>
+        <v>GVL_J1939.DLCD1_CmprssnBrkEnblSwtchIndctrLmpDta</v>
+      </c>
+      <c r="N164" t="str">
+        <f t="shared" si="11"/>
+        <v>GVL_J1939.DLCD1_CmprssnBrkEnblSwtchIndctrLmpDta;</v>
+      </c>
+      <c r="O164" t="str">
+        <f t="shared" si="12"/>
+        <v>DLCD1_CmprssnBrkEnblSwtchIndctrLmpDta:USINT; // SPN:5098</v>
+      </c>
+    </row>
+    <row r="165" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A165">
+        <v>173</v>
+      </c>
+      <c r="B165" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C165" t="s">
+        <v>1160</v>
+      </c>
+      <c r="D165" s="35">
+        <v>5099</v>
+      </c>
+      <c r="E165" t="s">
+        <v>682</v>
+      </c>
+      <c r="J165" t="s">
         <v>983</v>
       </c>
-      <c r="J122" t="str">
-        <f t="shared" si="2"/>
-        <v>DslPrtcltFltrActvRgnrtnInhb_0002;</v>
-      </c>
-    </row>
-    <row r="123" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B123" t="s">
-        <v>888</v>
-      </c>
-      <c r="C123" t="s">
-        <v>1101</v>
-      </c>
-      <c r="D123" s="26">
-        <v>4</v>
-      </c>
-      <c r="E123" s="26" t="s">
-        <v>1180</v>
-      </c>
-      <c r="F123" s="26">
-        <v>0</v>
-      </c>
-      <c r="G123" s="26" t="str">
-        <f t="shared" si="3"/>
-        <v>5,1</v>
-      </c>
-      <c r="H123" t="s">
+      <c r="K165">
+        <v>7</v>
+      </c>
+      <c r="L165" t="str">
+        <f t="shared" si="9"/>
+        <v>DLCD1_EngOilPressLowLampData</v>
+      </c>
+      <c r="M165" t="str">
+        <f t="shared" si="10"/>
+        <v>GVL_J1939.DLCD1_EngOilPressLowLampData</v>
+      </c>
+      <c r="N165" t="str">
+        <f t="shared" si="11"/>
+        <v>GVL_J1939.DLCD1_EngOilPressLowLampData;</v>
+      </c>
+      <c r="O165" t="str">
+        <f t="shared" si="12"/>
+        <v>DLCD1_EngOilPressLowLampData:USINT; // SPN:5099</v>
+      </c>
+    </row>
+    <row r="166" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A166">
+        <v>174</v>
+      </c>
+      <c r="B166" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C166" t="s">
+        <v>1161</v>
+      </c>
+      <c r="D166" s="35">
+        <v>5100</v>
+      </c>
+      <c r="J166" t="s">
         <v>983</v>
       </c>
-      <c r="J123" t="str">
-        <f t="shared" si="2"/>
-        <v>DslPrtcltFltrActvRgnrtnInhb_0001;</v>
-      </c>
-    </row>
-    <row r="124" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B124" t="s">
-        <v>888</v>
-      </c>
-      <c r="C124" t="s">
-        <v>1102</v>
-      </c>
-      <c r="D124" s="26">
-        <v>4</v>
-      </c>
-      <c r="E124" s="26" t="s">
-        <v>1181</v>
-      </c>
-      <c r="F124" s="26">
-        <v>2</v>
-      </c>
-      <c r="G124" s="26" t="str">
-        <f t="shared" si="3"/>
-        <v>5,3</v>
-      </c>
-      <c r="H124" t="s">
+      <c r="K166">
+        <v>8</v>
+      </c>
+      <c r="L166" t="str">
+        <f t="shared" si="9"/>
+        <v>DLCD1_EngCoolantTempHighLampData</v>
+      </c>
+      <c r="M166" t="str">
+        <f t="shared" si="10"/>
+        <v>GVL_J1939.DLCD1_EngCoolantTempHighLampData</v>
+      </c>
+      <c r="N166" t="str">
+        <f t="shared" si="11"/>
+        <v>GVL_J1939.DLCD1_EngCoolantTempHighLampData;</v>
+      </c>
+      <c r="O166" t="str">
+        <f t="shared" si="12"/>
+        <v>DLCD1_EngCoolantTempHighLampData:USINT; // SPN:5100</v>
+      </c>
+    </row>
+    <row r="167" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A167">
+        <v>175</v>
+      </c>
+      <c r="B167" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C167" t="s">
+        <v>1162</v>
+      </c>
+      <c r="D167" s="35">
+        <v>5101</v>
+      </c>
+      <c r="E167" t="s">
+        <v>682</v>
+      </c>
+      <c r="J167" t="s">
         <v>983</v>
       </c>
-      <c r="J124" t="str">
-        <f t="shared" si="2"/>
-        <v>DslPrtcltFltrActvRgnrtnInhbtdDTL;</v>
-      </c>
-    </row>
-    <row r="125" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B125" t="s">
-        <v>888</v>
-      </c>
-      <c r="C125" t="s">
-        <v>1103</v>
-      </c>
-      <c r="D125" s="26">
-        <v>4</v>
-      </c>
-      <c r="E125" s="26" t="s">
-        <v>1183</v>
-      </c>
-      <c r="F125" s="26">
-        <v>4</v>
-      </c>
-      <c r="G125" s="26" t="str">
-        <f t="shared" si="3"/>
-        <v>5,5</v>
-      </c>
-      <c r="H125" t="s">
+      <c r="K167">
+        <v>9</v>
+      </c>
+      <c r="L167" t="str">
+        <f t="shared" si="9"/>
+        <v>DLCD1_EngCoolantLevelLowLampData</v>
+      </c>
+      <c r="M167" t="str">
+        <f t="shared" si="10"/>
+        <v>GVL_J1939.DLCD1_EngCoolantLevelLowLampData</v>
+      </c>
+      <c r="N167" t="str">
+        <f t="shared" si="11"/>
+        <v>GVL_J1939.DLCD1_EngCoolantLevelLowLampData;</v>
+      </c>
+      <c r="O167" t="str">
+        <f t="shared" si="12"/>
+        <v>DLCD1_EngCoolantLevelLowLampData:USINT; // SPN:5101</v>
+      </c>
+    </row>
+    <row r="168" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A168">
+        <v>176</v>
+      </c>
+      <c r="B168" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C168" t="s">
+        <v>1163</v>
+      </c>
+      <c r="D168" s="35">
+        <v>5102</v>
+      </c>
+      <c r="J168" t="s">
         <v>983</v>
       </c>
-      <c r="J125" t="str">
-        <f t="shared" si="2"/>
-        <v>DslPrtcltFltrActvRgnrtnInhb_0000;</v>
-      </c>
-    </row>
-    <row r="126" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B126" t="s">
-        <v>888</v>
-      </c>
-      <c r="C126" t="s">
-        <v>1104</v>
-      </c>
-      <c r="D126" s="26">
-        <v>4</v>
-      </c>
-      <c r="E126" s="26" t="s">
-        <v>1184</v>
-      </c>
-      <c r="F126" s="26">
-        <v>6</v>
-      </c>
-      <c r="G126" s="26" t="str">
-        <f t="shared" si="3"/>
-        <v>5,7</v>
-      </c>
-      <c r="H126" t="s">
+      <c r="K168">
+        <v>10</v>
+      </c>
+      <c r="L168" t="str">
+        <f t="shared" si="9"/>
+        <v>DLCD1_EngIdleManagementActiveLampData</v>
+      </c>
+      <c r="M168" t="str">
+        <f t="shared" si="10"/>
+        <v>GVL_J1939.DLCD1_EngIdleManagementActiveLampData</v>
+      </c>
+      <c r="N168" t="str">
+        <f t="shared" si="11"/>
+        <v>GVL_J1939.DLCD1_EngIdleManagementActiveLampData;</v>
+      </c>
+      <c r="O168" t="str">
+        <f t="shared" si="12"/>
+        <v>DLCD1_EngIdleManagementActiveLampData:USINT; // SPN:5102</v>
+      </c>
+    </row>
+    <row r="169" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A169">
+        <v>177</v>
+      </c>
+      <c r="B169" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C169" t="s">
+        <v>1164</v>
+      </c>
+      <c r="D169" s="35">
+        <v>5103</v>
+      </c>
+      <c r="J169" t="s">
         <v>983</v>
       </c>
-      <c r="J126" t="str">
-        <f t="shared" si="2"/>
-        <v>DslPrtcltFltrActvRgnrtnInhbtdDTS;</v>
-      </c>
-    </row>
-    <row r="127" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B127" t="s">
-        <v>888</v>
-      </c>
-      <c r="C127" s="33" t="s">
-        <v>1105</v>
-      </c>
-      <c r="D127" s="26">
-        <v>5</v>
-      </c>
-      <c r="E127" s="26" t="s">
-        <v>1180</v>
-      </c>
-      <c r="F127" s="26">
-        <v>0</v>
-      </c>
-      <c r="G127" s="26" t="str">
-        <f t="shared" si="3"/>
-        <v>6,1</v>
-      </c>
-      <c r="H127" t="s">
+      <c r="K169">
+        <v>11</v>
+      </c>
+      <c r="L169" t="str">
+        <f t="shared" si="9"/>
+        <v>DLCD1_EngAirFilterRestrictionLampData</v>
+      </c>
+      <c r="M169" t="str">
+        <f t="shared" si="10"/>
+        <v>GVL_J1939.DLCD1_EngAirFilterRestrictionLampData</v>
+      </c>
+      <c r="N169" t="str">
+        <f t="shared" si="11"/>
+        <v>GVL_J1939.DLCD1_EngAirFilterRestrictionLampData;</v>
+      </c>
+      <c r="O169" t="str">
+        <f t="shared" si="12"/>
+        <v>DLCD1_EngAirFilterRestrictionLampData:USINT; // SPN:5103</v>
+      </c>
+    </row>
+    <row r="170" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A170">
+        <v>178</v>
+      </c>
+      <c r="B170" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C170" t="s">
+        <v>1165</v>
+      </c>
+      <c r="D170" s="35">
+        <v>5470</v>
+      </c>
+      <c r="J170" t="s">
         <v>983</v>
       </c>
-      <c r="J127" t="str">
-        <f t="shared" si="2"/>
-        <v>DslPrtcltFltrActvRgnrtnInhbtdDTT;</v>
-      </c>
-    </row>
-    <row r="128" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B128" t="s">
-        <v>888</v>
-      </c>
-      <c r="C128" s="33" t="s">
-        <v>1106</v>
-      </c>
-      <c r="D128" s="26">
-        <v>5</v>
-      </c>
-      <c r="E128" s="26" t="s">
-        <v>1181</v>
-      </c>
-      <c r="F128" s="26">
-        <v>2</v>
-      </c>
-      <c r="G128" s="26" t="str">
-        <f t="shared" si="3"/>
-        <v>6,3</v>
-      </c>
-      <c r="H128" t="s">
+      <c r="K170">
+        <v>12</v>
+      </c>
+      <c r="L170" t="str">
+        <f t="shared" si="9"/>
+        <v>DLCD1_EngFuelFilterRestrictedLampData</v>
+      </c>
+      <c r="M170" t="str">
+        <f t="shared" si="10"/>
+        <v>GVL_J1939.DLCD1_EngFuelFilterRestrictedLampData</v>
+      </c>
+      <c r="N170" t="str">
+        <f t="shared" si="11"/>
+        <v>GVL_J1939.DLCD1_EngFuelFilterRestrictedLampData;</v>
+      </c>
+      <c r="O170" t="str">
+        <f t="shared" si="12"/>
+        <v>DLCD1_EngFuelFilterRestrictedLampData:USINT; // SPN:5470</v>
+      </c>
+    </row>
+    <row r="171" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A171">
+        <v>179</v>
+      </c>
+      <c r="B171" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C171" t="s">
+        <v>1166</v>
+      </c>
+      <c r="D171" s="35">
+        <v>5416</v>
+      </c>
+      <c r="J171" t="s">
         <v>983</v>
       </c>
-      <c r="J128" t="str">
-        <f t="shared" si="2"/>
-        <v>DslPrtcltFltrActvRgnrtnInhbtdDTP;</v>
-      </c>
-    </row>
-    <row r="129" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B129" t="s">
-        <v>888</v>
-      </c>
-      <c r="C129" t="s">
-        <v>1107</v>
-      </c>
-      <c r="D129" s="26">
-        <v>5</v>
-      </c>
-      <c r="E129" s="26" t="s">
-        <v>1183</v>
-      </c>
-      <c r="F129" s="26">
-        <v>4</v>
-      </c>
-      <c r="G129" s="26" t="str">
-        <f t="shared" si="3"/>
-        <v>6,5</v>
-      </c>
-      <c r="H129" t="s">
-        <v>983</v>
-      </c>
-      <c r="J129" t="str">
-        <f t="shared" si="2"/>
-        <v>DslPrtcltFltrActvRgnrtnInhbtdDTE;</v>
-      </c>
-    </row>
-    <row r="130" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B130" t="s">
-        <v>888</v>
-      </c>
-      <c r="C130" t="s">
-        <v>1108</v>
-      </c>
-      <c r="D130" s="26">
-        <v>5</v>
-      </c>
-      <c r="E130" s="26" t="s">
-        <v>1184</v>
-      </c>
-      <c r="F130" s="26">
-        <v>6</v>
-      </c>
-      <c r="G130" s="26" t="str">
-        <f t="shared" si="3"/>
-        <v>6,7</v>
-      </c>
-      <c r="H130" t="s">
-        <v>983</v>
-      </c>
-      <c r="J130" t="str">
-        <f t="shared" si="2"/>
-        <v>DslPrtcltFltrActvRgnrtnInhbtdDTV;</v>
-      </c>
-    </row>
-    <row r="131" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B131" t="s">
-        <v>888</v>
-      </c>
-      <c r="C131" t="s">
-        <v>1109</v>
-      </c>
-      <c r="D131" s="26">
-        <v>6</v>
-      </c>
-      <c r="E131" s="26" t="s">
-        <v>1180</v>
-      </c>
-      <c r="F131" s="26">
-        <v>0</v>
-      </c>
-      <c r="G131" s="26" t="str">
-        <f t="shared" si="3"/>
-        <v>7,1</v>
-      </c>
-      <c r="H131" t="s">
-        <v>983</v>
-      </c>
-      <c r="J131" t="str">
-        <f t="shared" si="2"/>
-        <v>DslPrtcltFltrAtmtcActvRgnrtnIntt;</v>
-      </c>
-    </row>
-    <row r="132" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B132" t="s">
-        <v>888</v>
-      </c>
-      <c r="C132" t="s">
-        <v>1110</v>
-      </c>
-      <c r="D132" s="26">
-        <v>6</v>
-      </c>
-      <c r="E132" s="26" t="s">
-        <v>1185</v>
-      </c>
-      <c r="F132" s="26">
-        <v>2</v>
-      </c>
-      <c r="G132" s="26" t="str">
-        <f t="shared" si="3"/>
-        <v>7,3</v>
-      </c>
-      <c r="H132" t="s">
-        <v>983</v>
-      </c>
-      <c r="J132" t="str">
-        <f t="shared" ref="J132:J195" si="4">IF(C132&lt;&gt;"",_xlfn.CONCAT(C132,";"),"")</f>
-        <v>ExhaustSystemHighTempLampCmd;</v>
-      </c>
-    </row>
-    <row r="133" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B133" t="s">
-        <v>888</v>
-      </c>
-      <c r="C133" t="s">
-        <v>1111</v>
-      </c>
-      <c r="D133" s="26">
-        <v>6</v>
-      </c>
-      <c r="E133" s="26" t="s">
-        <v>1186</v>
-      </c>
-      <c r="F133" s="26">
-        <v>5</v>
-      </c>
-      <c r="G133" s="26" t="str">
-        <f t="shared" si="3"/>
-        <v>7,6</v>
-      </c>
-      <c r="H133" t="s">
-        <v>983</v>
-      </c>
-      <c r="J133" t="str">
-        <f t="shared" si="4"/>
-        <v>DslPrtcltFltrActvRgnrtnFrcdStts;</v>
-      </c>
-    </row>
-    <row r="134" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="J134" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="135" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B135" t="s">
-        <v>935</v>
-      </c>
-      <c r="C135" t="s">
-        <v>1112</v>
-      </c>
-      <c r="H135" t="s">
-        <v>984</v>
-      </c>
-      <c r="J135" t="str">
-        <f t="shared" si="4"/>
-        <v>Aftertreatment1ExhaustGasTemp1;</v>
-      </c>
-    </row>
-    <row r="136" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B136" t="s">
-        <v>935</v>
-      </c>
-      <c r="C136" t="s">
-        <v>1113</v>
-      </c>
-      <c r="H136" t="s">
-        <v>984</v>
-      </c>
-      <c r="J136" t="str">
-        <f t="shared" si="4"/>
-        <v>Aftrtrtmnt1DslPrtcltFltrInt_0000;</v>
-      </c>
-    </row>
-    <row r="137" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B137" t="s">
-        <v>935</v>
-      </c>
-      <c r="C137" t="s">
-        <v>1114</v>
-      </c>
-      <c r="H137" t="s">
-        <v>983</v>
-      </c>
-      <c r="J137" t="str">
-        <f t="shared" si="4"/>
-        <v>Aftrtrtmnt1ExhstGsTmp1PrlmnryFMI;</v>
-      </c>
-    </row>
-    <row r="138" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B138" t="s">
-        <v>935</v>
-      </c>
-      <c r="C138" t="s">
-        <v>1115</v>
-      </c>
-      <c r="H138" t="s">
-        <v>983</v>
-      </c>
-      <c r="J138" t="str">
-        <f t="shared" si="4"/>
-        <v>Aftrtrtmnt1DslPrtcltFltrIntkGsTm;</v>
-      </c>
-    </row>
-    <row r="139" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="J139" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="140" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B140" t="s">
-        <v>1134</v>
-      </c>
-      <c r="C140" t="s">
-        <v>1116</v>
-      </c>
-      <c r="H140" t="s">
-        <v>984</v>
-      </c>
-      <c r="J140" t="str">
-        <f t="shared" si="4"/>
-        <v>Aftrtrtmnt1SCRCatalystTankLevel;</v>
-      </c>
-    </row>
-    <row r="141" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B141" t="s">
-        <v>1134</v>
-      </c>
-      <c r="C141" t="s">
-        <v>1117</v>
-      </c>
-      <c r="H141" t="s">
-        <v>985</v>
-      </c>
-      <c r="J141" t="str">
-        <f t="shared" si="4"/>
-        <v>Aftrtrtment1SCRCatalystTankTemp;</v>
-      </c>
-    </row>
-    <row r="142" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B142" t="s">
-        <v>1134</v>
-      </c>
-      <c r="C142" t="s">
-        <v>1118</v>
-      </c>
-      <c r="H142" t="s">
-        <v>984</v>
-      </c>
-      <c r="J142" t="str">
-        <f t="shared" si="4"/>
-        <v>Aftrtrtmnt1SCRCtalystTankLevel2;</v>
-      </c>
-    </row>
-    <row r="143" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B143" t="s">
-        <v>1134</v>
-      </c>
-      <c r="C143" t="s">
-        <v>1119</v>
-      </c>
-      <c r="H143" t="s">
-        <v>983</v>
-      </c>
-      <c r="J143" t="str">
-        <f t="shared" si="4"/>
-        <v>Aftrtrtmnt1SCRCtlystTnkLvlPrlmnr;</v>
-      </c>
-    </row>
-    <row r="144" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B144" t="s">
-        <v>1134</v>
-      </c>
-      <c r="C144" t="s">
-        <v>1120</v>
-      </c>
-      <c r="H144" t="s">
-        <v>983</v>
-      </c>
-      <c r="J144" t="str">
-        <f t="shared" si="4"/>
-        <v>Aftrtrtmnt1DEFTnkLwLvlIndicator;</v>
-      </c>
-    </row>
-    <row r="145" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B145" t="s">
-        <v>1134</v>
-      </c>
-      <c r="C145" t="s">
-        <v>1121</v>
-      </c>
-      <c r="H145" t="s">
-        <v>983</v>
-      </c>
-      <c r="J145" t="str">
-        <f t="shared" si="4"/>
-        <v>Aftrtrtmnt1SCRCtlystRgntTnk1TmpP;</v>
-      </c>
-    </row>
-    <row r="146" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B146" t="s">
-        <v>1134</v>
-      </c>
-      <c r="C146" t="s">
-        <v>1122</v>
-      </c>
-      <c r="H146" t="s">
-        <v>983</v>
-      </c>
-      <c r="J146" t="str">
-        <f t="shared" si="4"/>
-        <v>AftrtrtmntSCROprtrIndcmntSvrity;</v>
-      </c>
-    </row>
-    <row r="147" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B147" t="s">
-        <v>1134</v>
-      </c>
-      <c r="C147" t="s">
-        <v>1123</v>
-      </c>
-      <c r="H147" t="s">
-        <v>984</v>
-      </c>
-      <c r="J147" t="str">
-        <f t="shared" si="4"/>
-        <v>Aftrtrtmnt1SCRCtalystTankHeater;</v>
-      </c>
-    </row>
-    <row r="148" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B148" t="s">
-        <v>1134</v>
-      </c>
-      <c r="C148" t="s">
-        <v>1124</v>
-      </c>
-      <c r="H148" t="s">
-        <v>983</v>
-      </c>
-      <c r="J148" t="str">
-        <f t="shared" si="4"/>
-        <v>Aftrtrtmnt1SCRCtlystRgntTnk1HtrP;</v>
-      </c>
-    </row>
-    <row r="149" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B149" t="s">
-        <v>1134</v>
-      </c>
-      <c r="C149" t="s">
-        <v>1125</v>
-      </c>
-      <c r="H149" t="s">
-        <v>984</v>
-      </c>
-      <c r="J149" t="str">
-        <f t="shared" si="4"/>
-        <v>Aftrtrtmnt1SCRCatalystTankLevel_1;</v>
-      </c>
-    </row>
-    <row r="150" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B150" t="s">
-        <v>1134</v>
-      </c>
-      <c r="C150" t="s">
-        <v>1126</v>
-      </c>
-      <c r="H150" t="s">
-        <v>985</v>
-      </c>
-      <c r="J150" t="str">
-        <f t="shared" si="4"/>
-        <v>Aftrtrtment1SCRCatalystTankTemp_1;</v>
-      </c>
-    </row>
-    <row r="151" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B151" t="s">
-        <v>1134</v>
-      </c>
-      <c r="C151" t="s">
-        <v>1127</v>
-      </c>
-      <c r="H151" t="s">
-        <v>984</v>
-      </c>
-      <c r="J151" t="str">
-        <f t="shared" si="4"/>
-        <v>Aftrtrtmnt1SCRCtalystTankLevel2_1;</v>
-      </c>
-    </row>
-    <row r="152" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B152" t="s">
-        <v>1134</v>
-      </c>
-      <c r="C152" t="s">
-        <v>1128</v>
-      </c>
-      <c r="H152" t="s">
-        <v>983</v>
-      </c>
-      <c r="J152" t="str">
-        <f t="shared" si="4"/>
-        <v>Aftrtrtmnt1SCRCtlystTnkLvlPrlmnr_1;</v>
-      </c>
-    </row>
-    <row r="153" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B153" t="s">
-        <v>1134</v>
-      </c>
-      <c r="C153" t="s">
-        <v>1129</v>
-      </c>
-      <c r="H153" t="s">
-        <v>983</v>
-      </c>
-      <c r="J153" t="str">
-        <f t="shared" si="4"/>
-        <v>Aftrtrtmnt1DEFTnkLwLvlIndicator_1;</v>
-      </c>
-    </row>
-    <row r="154" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B154" t="s">
-        <v>1134</v>
-      </c>
-      <c r="C154" t="s">
-        <v>1130</v>
-      </c>
-      <c r="H154" t="s">
-        <v>983</v>
-      </c>
-      <c r="J154" t="str">
-        <f t="shared" si="4"/>
-        <v>Aftrtrtmnt1SCRCtlystRgntTnk1TmpP_1;</v>
-      </c>
-    </row>
-    <row r="155" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B155" t="s">
-        <v>1134</v>
-      </c>
-      <c r="C155" t="s">
-        <v>1131</v>
-      </c>
-      <c r="H155" t="s">
-        <v>983</v>
-      </c>
-      <c r="J155" t="str">
-        <f t="shared" si="4"/>
-        <v>AftrtrtmntSCROprtrIndcmntSvrity_1;</v>
-      </c>
-    </row>
-    <row r="156" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B156" t="s">
-        <v>1134</v>
-      </c>
-      <c r="C156" t="s">
-        <v>1132</v>
-      </c>
-      <c r="H156" t="s">
-        <v>984</v>
-      </c>
-      <c r="J156" t="str">
-        <f t="shared" si="4"/>
-        <v>Aftrtrtmnt1SCRCtalystTankHeater_1;</v>
-      </c>
-    </row>
-    <row r="157" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B157" t="s">
-        <v>1134</v>
-      </c>
-      <c r="C157" t="s">
-        <v>1133</v>
-      </c>
-      <c r="H157" t="s">
-        <v>983</v>
-      </c>
-      <c r="J157" t="str">
-        <f t="shared" si="4"/>
-        <v>Aftrtrtmnt1SCRCtlystRgntTnk1HtrP_1;</v>
-      </c>
-    </row>
-    <row r="158" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="J158" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="159" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B159" t="s">
-        <v>940</v>
-      </c>
-      <c r="C159" t="s">
-        <v>1135</v>
-      </c>
-      <c r="H159" t="s">
-        <v>984</v>
-      </c>
-      <c r="J159" t="str">
-        <f t="shared" si="4"/>
-        <v>Aftrtrtmnt1SCRActlDsngRgntQntty;</v>
-      </c>
-    </row>
-    <row r="160" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B160" t="s">
-        <v>940</v>
-      </c>
-      <c r="C160" t="s">
-        <v>1136</v>
-      </c>
-      <c r="H160" t="s">
-        <v>983</v>
-      </c>
-      <c r="J160" t="str">
-        <f t="shared" si="4"/>
-        <v>Aftertreatment1SCRSystemState;</v>
-      </c>
-    </row>
-    <row r="161" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B161" t="s">
-        <v>940</v>
-      </c>
-      <c r="C161" t="s">
-        <v>1137</v>
-      </c>
-      <c r="H161" t="s">
-        <v>984</v>
-      </c>
-      <c r="J161" t="str">
-        <f t="shared" si="4"/>
-        <v>Aftrtrtmnt1SCRActlRgntQnttyOfInt;</v>
-      </c>
-    </row>
-    <row r="162" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B162" t="s">
-        <v>940</v>
-      </c>
-      <c r="C162" t="s">
-        <v>1138</v>
-      </c>
-      <c r="H162" t="s">
-        <v>1051</v>
-      </c>
-      <c r="J162" t="str">
-        <f t="shared" si="4"/>
-        <v>Aftrtrtmnt1SCRDsngRgentAbsPress;</v>
-      </c>
-    </row>
-    <row r="163" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="J163" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="164" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B164" t="s">
-        <v>1139</v>
-      </c>
-      <c r="C164" t="s">
-        <v>1140</v>
-      </c>
-      <c r="H164" t="s">
-        <v>984</v>
-      </c>
-      <c r="J164" t="str">
-        <f t="shared" si="4"/>
-        <v>Aftrtrtmnt1SCRCtlystIntkGasTemp;</v>
-      </c>
-    </row>
-    <row r="165" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B165" t="s">
-        <v>1139</v>
-      </c>
-      <c r="C165" t="s">
-        <v>1141</v>
-      </c>
-      <c r="H165" t="s">
-        <v>983</v>
-      </c>
-      <c r="J165" t="str">
-        <f t="shared" si="4"/>
-        <v>Aftrtrtmnt1SCRCtlystIntkGsTmpPrl;</v>
-      </c>
-    </row>
-    <row r="166" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B166" t="s">
-        <v>1139</v>
-      </c>
-      <c r="C166" t="s">
-        <v>1142</v>
-      </c>
-      <c r="H166" t="s">
-        <v>984</v>
-      </c>
-      <c r="J166" t="str">
-        <f t="shared" si="4"/>
-        <v>Aftrtrtmnt1SCRCtlystOtltGasTemp;</v>
-      </c>
-    </row>
-    <row r="167" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B167" t="s">
-        <v>1139</v>
-      </c>
-      <c r="C167" t="s">
-        <v>1143</v>
-      </c>
-      <c r="H167" t="s">
-        <v>983</v>
-      </c>
-      <c r="J167" t="str">
-        <f t="shared" si="4"/>
-        <v>Aftrtrtmnt1SCRCtlystOtltGsTmpPrl;</v>
-      </c>
-    </row>
-    <row r="168" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="J168" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="169" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B169" t="s">
-        <v>950</v>
-      </c>
-      <c r="C169" t="s">
-        <v>1144</v>
-      </c>
-      <c r="H169" t="s">
-        <v>984</v>
-      </c>
-      <c r="J169" t="str">
-        <f t="shared" si="4"/>
-        <v>Aftrtrtmnt1DslOxdtnCtlystIn_0000;</v>
-      </c>
-    </row>
-    <row r="170" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B170" t="s">
-        <v>950</v>
-      </c>
-      <c r="C170" t="s">
-        <v>1145</v>
-      </c>
-      <c r="H170" t="s">
-        <v>984</v>
-      </c>
-      <c r="J170" t="str">
-        <f t="shared" si="4"/>
-        <v>Aftrtrtmnt1DslOxdtnCtlystOt_0000;</v>
-      </c>
-    </row>
-    <row r="171" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B171" t="s">
-        <v>950</v>
-      </c>
-      <c r="C171" t="s">
-        <v>1146</v>
-      </c>
-      <c r="H171" t="s">
-        <v>984</v>
-      </c>
-      <c r="J171" t="str">
-        <f t="shared" si="4"/>
-        <v>Aftrtrtmnt1DslOxdtnCtlystDffPrss;</v>
-      </c>
-    </row>
-    <row r="172" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B172" t="s">
-        <v>950</v>
-      </c>
-      <c r="C172" t="s">
-        <v>1147</v>
-      </c>
-      <c r="H172" t="s">
-        <v>983</v>
-      </c>
-      <c r="J172" t="str">
-        <f t="shared" si="4"/>
-        <v>Aftrtrtmnt1DslOxdtnCtlystIntkGsT;</v>
-      </c>
-    </row>
-    <row r="173" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B173" t="s">
-        <v>950</v>
-      </c>
-      <c r="C173" t="s">
-        <v>1148</v>
-      </c>
-      <c r="H173" t="s">
-        <v>983</v>
-      </c>
-      <c r="J173" t="str">
-        <f t="shared" si="4"/>
-        <v>Aftrtrtmnt1DslOxdtnCtlystOtltGsT;</v>
-      </c>
-    </row>
-    <row r="174" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B174" t="s">
-        <v>950</v>
-      </c>
-      <c r="C174" t="s">
-        <v>1149</v>
-      </c>
-      <c r="H174" t="s">
-        <v>983</v>
-      </c>
-      <c r="J174" t="str">
-        <f t="shared" si="4"/>
-        <v>Aftrtrtmnt1DslOxdtnCtlystDf_0000;</v>
-      </c>
-    </row>
-    <row r="175" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="J175" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="176" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B176" t="s">
-        <v>1150</v>
-      </c>
-      <c r="C176" t="s">
-        <v>1151</v>
-      </c>
-      <c r="H176" t="s">
-        <v>983</v>
-      </c>
-      <c r="J176" t="str">
-        <f t="shared" si="4"/>
-        <v>WaterInFuelIndicator;</v>
-      </c>
-    </row>
-    <row r="177" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="J177" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="178" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B178" t="s">
-        <v>961</v>
-      </c>
-      <c r="C178" t="s">
-        <v>1152</v>
-      </c>
-      <c r="H178" t="s">
-        <v>983</v>
-      </c>
-      <c r="I178">
-        <v>1</v>
-      </c>
-      <c r="J178" t="str">
-        <f t="shared" si="4"/>
-        <v>EngProtectLampCmd;</v>
-      </c>
-    </row>
-    <row r="179" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B179" t="s">
-        <v>961</v>
-      </c>
-      <c r="C179" t="s">
-        <v>1153</v>
-      </c>
-      <c r="H179" t="s">
-        <v>983</v>
-      </c>
-      <c r="I179">
-        <v>2</v>
-      </c>
-      <c r="J179" t="str">
-        <f t="shared" si="4"/>
-        <v>EngAmberWarningLampCmd;</v>
-      </c>
-    </row>
-    <row r="180" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B180" t="s">
-        <v>961</v>
-      </c>
-      <c r="C180" t="s">
-        <v>1154</v>
-      </c>
-      <c r="H180" t="s">
-        <v>983</v>
-      </c>
-      <c r="I180">
-        <v>3</v>
-      </c>
-      <c r="J180" t="str">
-        <f t="shared" si="4"/>
-        <v>EngRedStopLampCmd;</v>
-      </c>
-    </row>
-    <row r="181" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B181" t="s">
-        <v>961</v>
-      </c>
-      <c r="C181" t="s">
-        <v>1155</v>
-      </c>
-      <c r="H181" t="s">
-        <v>983</v>
-      </c>
-      <c r="I181">
-        <v>4</v>
-      </c>
-      <c r="J181" t="str">
-        <f t="shared" si="4"/>
-        <v>OBDMalfunctionIndicatorLampCmd;</v>
-      </c>
-    </row>
-    <row r="182" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B182" t="s">
-        <v>961</v>
-      </c>
-      <c r="C182" t="s">
-        <v>1156</v>
-      </c>
-      <c r="H182" t="s">
-        <v>983</v>
-      </c>
-      <c r="I182">
-        <v>5</v>
-      </c>
-      <c r="J182" t="str">
-        <f t="shared" si="4"/>
-        <v>EngBrakeActiveLampCmd;</v>
-      </c>
-    </row>
-    <row r="183" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B183" t="s">
-        <v>961</v>
-      </c>
-      <c r="C183" t="s">
-        <v>1157</v>
-      </c>
-      <c r="H183" t="s">
-        <v>983</v>
-      </c>
-      <c r="I183">
-        <v>6</v>
-      </c>
-      <c r="J183" t="str">
-        <f t="shared" si="4"/>
-        <v>CmprssnBrkEnblSwtchIndctrLmpCmd;</v>
-      </c>
-    </row>
-    <row r="184" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B184" t="s">
-        <v>961</v>
-      </c>
-      <c r="C184" t="s">
-        <v>1158</v>
-      </c>
-      <c r="H184" t="s">
-        <v>983</v>
-      </c>
-      <c r="I184">
-        <v>7</v>
-      </c>
-      <c r="J184" t="str">
-        <f t="shared" si="4"/>
-        <v>EngOilPressLowLampCmd;</v>
-      </c>
-    </row>
-    <row r="185" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B185" t="s">
-        <v>961</v>
-      </c>
-      <c r="C185" t="s">
-        <v>1159</v>
-      </c>
-      <c r="H185" t="s">
-        <v>983</v>
-      </c>
-      <c r="I185">
-        <v>8</v>
-      </c>
-      <c r="J185" t="str">
-        <f t="shared" si="4"/>
-        <v>EngCoolantTempHighLampCmd;</v>
-      </c>
-    </row>
-    <row r="186" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B186" t="s">
-        <v>961</v>
-      </c>
-      <c r="C186" t="s">
-        <v>1160</v>
-      </c>
-      <c r="H186" t="s">
-        <v>983</v>
-      </c>
-      <c r="I186">
-        <v>9</v>
-      </c>
-      <c r="J186" t="str">
-        <f t="shared" si="4"/>
-        <v>EngCoolantLevelLowLampCmd;</v>
-      </c>
-    </row>
-    <row r="187" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B187" t="s">
-        <v>961</v>
-      </c>
-      <c r="C187" t="s">
-        <v>1161</v>
-      </c>
-      <c r="H187" t="s">
-        <v>983</v>
-      </c>
-      <c r="I187">
-        <v>10</v>
-      </c>
-      <c r="J187" t="str">
-        <f t="shared" si="4"/>
-        <v>EngIdleManagementActiveLampCmd;</v>
-      </c>
-    </row>
-    <row r="188" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B188" t="s">
-        <v>961</v>
-      </c>
-      <c r="C188" t="s">
-        <v>1162</v>
-      </c>
-      <c r="H188" t="s">
-        <v>983</v>
-      </c>
-      <c r="I188">
-        <v>11</v>
-      </c>
-      <c r="J188" t="str">
-        <f t="shared" si="4"/>
-        <v>EngAirFilterRestrictionLampCmd;</v>
-      </c>
-    </row>
-    <row r="189" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B189" t="s">
-        <v>961</v>
-      </c>
-      <c r="C189" t="s">
-        <v>1163</v>
-      </c>
-      <c r="H189" t="s">
-        <v>983</v>
-      </c>
-      <c r="I189">
-        <v>12</v>
-      </c>
-      <c r="J189" t="str">
-        <f t="shared" si="4"/>
-        <v>EngFuelFilterRestrictedLampCmd;</v>
-      </c>
-    </row>
-    <row r="190" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="J190" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="191" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B191" t="s">
-        <v>1164</v>
-      </c>
-      <c r="C191" t="s">
-        <v>1165</v>
-      </c>
-      <c r="H191" t="s">
-        <v>983</v>
-      </c>
-      <c r="I191">
-        <v>1</v>
-      </c>
-      <c r="J191" t="str">
-        <f t="shared" si="4"/>
-        <v>EngProtectLampData;</v>
-      </c>
-    </row>
-    <row r="192" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B192" t="s">
-        <v>1164</v>
-      </c>
-      <c r="C192" t="s">
-        <v>1166</v>
-      </c>
-      <c r="H192" t="s">
-        <v>983</v>
-      </c>
-      <c r="I192">
-        <v>2</v>
-      </c>
-      <c r="J192" t="str">
-        <f t="shared" si="4"/>
-        <v>EngAmberWarningLampData;</v>
-      </c>
-    </row>
-    <row r="193" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B193" t="s">
-        <v>1164</v>
-      </c>
-      <c r="C193" t="s">
-        <v>1167</v>
-      </c>
-      <c r="H193" t="s">
-        <v>983</v>
-      </c>
-      <c r="I193">
-        <v>3</v>
-      </c>
-      <c r="J193" t="str">
-        <f t="shared" si="4"/>
-        <v>EngRedStopLampData;</v>
-      </c>
-    </row>
-    <row r="194" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B194" t="s">
-        <v>1164</v>
-      </c>
-      <c r="C194" t="s">
-        <v>1168</v>
-      </c>
-      <c r="H194" t="s">
-        <v>983</v>
-      </c>
-      <c r="I194">
-        <v>4</v>
-      </c>
-      <c r="J194" t="str">
-        <f t="shared" si="4"/>
-        <v>OBDMalfunctionIndicatorLampData;</v>
-      </c>
-    </row>
-    <row r="195" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B195" t="s">
-        <v>1164</v>
-      </c>
-      <c r="C195" t="s">
-        <v>1169</v>
-      </c>
-      <c r="H195" t="s">
-        <v>983</v>
-      </c>
-      <c r="I195">
-        <v>5</v>
-      </c>
-      <c r="J195" t="str">
-        <f t="shared" si="4"/>
-        <v>EngBrakeActiveLampData;</v>
-      </c>
-    </row>
-    <row r="196" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B196" t="s">
-        <v>1164</v>
-      </c>
-      <c r="C196" t="s">
-        <v>1170</v>
-      </c>
-      <c r="H196" t="s">
-        <v>983</v>
-      </c>
-      <c r="I196">
-        <v>6</v>
-      </c>
-      <c r="J196" t="str">
-        <f t="shared" ref="J196:J203" si="5">IF(C196&lt;&gt;"",_xlfn.CONCAT(C196,";"),"")</f>
-        <v>CmprssnBrkEnblSwtchIndctrLmpDta;</v>
-      </c>
-    </row>
-    <row r="197" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B197" t="s">
-        <v>1164</v>
-      </c>
-      <c r="C197" t="s">
-        <v>1171</v>
-      </c>
-      <c r="H197" t="s">
-        <v>983</v>
-      </c>
-      <c r="I197">
-        <v>7</v>
-      </c>
-      <c r="J197" t="str">
-        <f t="shared" si="5"/>
-        <v>EngOilPressLowLampData;</v>
-      </c>
-    </row>
-    <row r="198" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B198" t="s">
-        <v>1164</v>
-      </c>
-      <c r="C198" t="s">
-        <v>1172</v>
-      </c>
-      <c r="H198" t="s">
-        <v>983</v>
-      </c>
-      <c r="I198">
-        <v>8</v>
-      </c>
-      <c r="J198" t="str">
-        <f t="shared" si="5"/>
-        <v>EngCoolantTempHighLampData;</v>
-      </c>
-    </row>
-    <row r="199" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B199" t="s">
-        <v>1164</v>
-      </c>
-      <c r="C199" t="s">
-        <v>1173</v>
-      </c>
-      <c r="H199" t="s">
-        <v>983</v>
-      </c>
-      <c r="I199">
-        <v>9</v>
-      </c>
-      <c r="J199" t="str">
-        <f t="shared" si="5"/>
-        <v>EngCoolantLevelLowLampData;</v>
-      </c>
-    </row>
-    <row r="200" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B200" t="s">
-        <v>1164</v>
-      </c>
-      <c r="C200" t="s">
-        <v>1174</v>
-      </c>
-      <c r="H200" t="s">
-        <v>983</v>
-      </c>
-      <c r="I200">
-        <v>10</v>
-      </c>
-      <c r="J200" t="str">
-        <f t="shared" si="5"/>
-        <v>EngIdleManagementActiveLampData;</v>
-      </c>
-    </row>
-    <row r="201" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B201" t="s">
-        <v>1164</v>
-      </c>
-      <c r="C201" t="s">
-        <v>1175</v>
-      </c>
-      <c r="H201" t="s">
-        <v>983</v>
-      </c>
-      <c r="I201">
-        <v>11</v>
-      </c>
-      <c r="J201" t="str">
-        <f t="shared" si="5"/>
-        <v>EngAirFilterRestrictionLampData;</v>
-      </c>
-    </row>
-    <row r="202" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B202" t="s">
-        <v>1164</v>
-      </c>
-      <c r="C202" t="s">
-        <v>1176</v>
-      </c>
-      <c r="H202" t="s">
-        <v>983</v>
-      </c>
-      <c r="I202">
-        <v>12</v>
-      </c>
-      <c r="J202" t="str">
-        <f t="shared" si="5"/>
-        <v>EngFuelFilterRestrictedLampData;</v>
-      </c>
-    </row>
-    <row r="203" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B203" t="s">
-        <v>1164</v>
-      </c>
-      <c r="C203" t="s">
-        <v>1177</v>
-      </c>
-      <c r="H203" t="s">
-        <v>983</v>
-      </c>
-      <c r="I203">
+      <c r="K171">
         <v>13</v>
       </c>
-      <c r="J203" t="str">
-        <f t="shared" si="5"/>
-        <v>EngWaitToStartLampData;</v>
+      <c r="L171" t="str">
+        <f t="shared" si="9"/>
+        <v>DLCD1_EngWaitToStartLampData</v>
+      </c>
+      <c r="M171" t="str">
+        <f t="shared" si="10"/>
+        <v>GVL_J1939.DLCD1_EngWaitToStartLampData</v>
+      </c>
+      <c r="N171" t="str">
+        <f t="shared" si="11"/>
+        <v>GVL_J1939.DLCD1_EngWaitToStartLampData;</v>
+      </c>
+      <c r="O171" t="str">
+        <f t="shared" si="12"/>
+        <v>DLCD1_EngWaitToStartLampData:USINT; // SPN:5416</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:W171" xr:uid="{67835F87-8E16-4012-B1FC-4AA8A57E1B78}">
+    <filterColumn colId="4">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c96d9849-7071-4555-8535-ee11c374d0f7">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3f324c86-ae15-4ed4-b4a2-09335a7d28ef" xsi:nil="true"/>
-    <SharedWithUsers xmlns="3f324c86-ae15-4ed4-b4a2-09335a7d28ef">
-      <UserInfo>
-        <DisplayName>Noel Loughran</DisplayName>
-        <AccountId>19</AccountId>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -28693,27 +31540,27 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c96d9849-7071-4555-8535-ee11c374d0f7">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3f324c86-ae15-4ed4-b4a2-09335a7d28ef" xsi:nil="true"/>
+    <SharedWithUsers xmlns="3f324c86-ae15-4ed4-b4a2-09335a7d28ef">
+      <UserInfo>
+        <DisplayName>Noel Loughran</DisplayName>
+        <AccountId>19</AccountId>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7DE4EA8D-9182-4C6A-B31C-49373749A7AE}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3E59E7C-5896-4162-AB70-9CA3CEB6A0FE}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="3f324c86-ae15-4ed4-b4a2-09335a7d28ef"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="c96d9849-7071-4555-8535-ee11c374d0f7"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -28738,9 +31585,18 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3E59E7C-5896-4162-AB70-9CA3CEB6A0FE}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7DE4EA8D-9182-4C6A-B31C-49373749A7AE}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="3f324c86-ae15-4ed4-b4a2-09335a7d28ef"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="c96d9849-7071-4555-8535-ee11c374d0f7"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/T620X_IO.xlsx
+++ b/T620X_IO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\dev_plc\MTech\MTech_T620X_Trommel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49464D75-6129-474D-9E3A-402C8D09734C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CE95135-CF38-414E-8EEB-23CC7FBCAA2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="5280" windowWidth="29040" windowHeight="15720" tabRatio="857" activeTab="7" xr2:uid="{2FCBBB71-3591-49CF-88C3-9E3184A7626E}"/>
+    <workbookView xWindow="38280" yWindow="5280" windowWidth="29040" windowHeight="15720" tabRatio="857" activeTab="9" xr2:uid="{2FCBBB71-3591-49CF-88C3-9E3184A7626E}"/>
   </bookViews>
   <sheets>
     <sheet name="IO" sheetId="11" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="ALARMS" sheetId="24" r:id="rId5"/>
     <sheet name="ALARMS_IO" sheetId="31" r:id="rId6"/>
     <sheet name="SNAGS" sheetId="33" r:id="rId7"/>
-    <sheet name="Sheet2" sheetId="37" r:id="rId8"/>
+    <sheet name="DPF Symbol Logic" sheetId="37" r:id="rId8"/>
     <sheet name="  C3.6 PGNs" sheetId="35" r:id="rId9"/>
     <sheet name="C3.6 PGNS -12 doc" sheetId="36" r:id="rId10"/>
   </sheets>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3144" uniqueCount="1186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3150" uniqueCount="1188">
   <si>
     <t>PLC Name</t>
   </si>
@@ -3609,6 +3609,12 @@
   </si>
   <si>
     <t>GVL_Engine.MILamp=FALSE</t>
+  </si>
+  <si>
+    <t>Engine hours  request</t>
+  </si>
+  <si>
+    <t>Method for setting speed a bit random ….?</t>
   </si>
 </sst>
 </file>
@@ -10753,7 +10759,7 @@
     <col min="7" max="7" width="5.140625" style="26" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="2" style="26" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="8.140625" style="26" customWidth="1"/>
-    <col min="12" max="12" width="43.28515625" customWidth="1"/>
+    <col min="12" max="12" width="43.28515625" hidden="1" customWidth="1"/>
     <col min="13" max="13" width="50.28515625" customWidth="1"/>
     <col min="14" max="14" width="44" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="49" bestFit="1" customWidth="1"/>
@@ -12444,7 +12450,7 @@
         <v>682</v>
       </c>
       <c r="J49" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="L49" t="str">
         <f t="shared" si="0"/>
@@ -12460,7 +12466,7 @@
       </c>
       <c r="O49" t="str">
         <f t="shared" si="3"/>
-        <v>ET1_EngCoolantTemp:REAL; // SPN:1637</v>
+        <v>ET1_EngCoolantTemp:INT; // SPN:1637</v>
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
@@ -13822,7 +13828,7 @@
         <v>EFS_EngOilFilterOutletPress:UINT; // SPN:3549</v>
       </c>
     </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>89</v>
       </c>
@@ -13834,9 +13840,6 @@
       </c>
       <c r="D90" s="35">
         <v>3550</v>
-      </c>
-      <c r="E90" t="s">
-        <v>682</v>
       </c>
       <c r="J90" t="s">
         <v>983</v>
@@ -13858,7 +13861,7 @@
         <v>EFS_EngOilPrimingPumpSwitch:USINT; // SPN:3550</v>
       </c>
     </row>
-    <row r="91" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>90</v>
       </c>
@@ -13870,6 +13873,9 @@
       </c>
       <c r="D91" s="35">
         <v>3551</v>
+      </c>
+      <c r="E91" t="s">
+        <v>682</v>
       </c>
       <c r="J91" t="s">
         <v>983</v>
@@ -31089,6 +31095,9 @@
       <c r="C90" t="s">
         <v>865</v>
       </c>
+      <c r="D90" t="s">
+        <v>589</v>
+      </c>
     </row>
     <row r="91" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B91" t="s">
@@ -31112,6 +31121,25 @@
       </c>
       <c r="C93" t="s">
         <v>864</v>
+      </c>
+    </row>
+    <row r="95" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B95" t="s">
+        <v>669</v>
+      </c>
+      <c r="C95" t="s">
+        <v>1186</v>
+      </c>
+      <c r="D95" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="96" spans="2:5" s="33" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B96" s="33" t="s">
+        <v>573</v>
+      </c>
+      <c r="C96" s="33" t="s">
+        <v>1187</v>
       </c>
     </row>
     <row r="108" spans="2:5" x14ac:dyDescent="0.25">
@@ -31982,33 +32010,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c96d9849-7071-4555-8535-ee11c374d0f7">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3f324c86-ae15-4ed4-b4a2-09335a7d28ef" xsi:nil="true"/>
-    <SharedWithUsers xmlns="3f324c86-ae15-4ed4-b4a2-09335a7d28ef">
-      <UserInfo>
-        <DisplayName>Noel Loughran</DisplayName>
-        <AccountId>19</AccountId>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007A9F7729ADF49144A01A6175DD599202" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3f00ebe7287476f312414df31db46304">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c96d9849-7071-4555-8535-ee11c374d0f7" xmlns:ns3="3f324c86-ae15-4ed4-b4a2-09335a7d28ef" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8f2e969a0d0c60cbdf6bd0d859a86451" ns2:_="" ns3:_="">
     <xsd:import namespace="c96d9849-7071-4555-8535-ee11c374d0f7"/>
@@ -32231,32 +32232,34 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7DE4EA8D-9182-4C6A-B31C-49373749A7AE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="3f324c86-ae15-4ed4-b4a2-09335a7d28ef"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="c96d9849-7071-4555-8535-ee11c374d0f7"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3E59E7C-5896-4162-AB70-9CA3CEB6A0FE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c96d9849-7071-4555-8535-ee11c374d0f7">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3f324c86-ae15-4ed4-b4a2-09335a7d28ef" xsi:nil="true"/>
+    <SharedWithUsers xmlns="3f324c86-ae15-4ed4-b4a2-09335a7d28ef">
+      <UserInfo>
+        <DisplayName>Noel Loughran</DisplayName>
+        <AccountId>19</AccountId>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6596B7D1-B3E6-40CB-B05E-2E959D1A2B6D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -32273,4 +32276,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3E59E7C-5896-4162-AB70-9CA3CEB6A0FE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7DE4EA8D-9182-4C6A-B31C-49373749A7AE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="3f324c86-ae15-4ed4-b4a2-09335a7d28ef"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="c96d9849-7071-4555-8535-ee11c374d0f7"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/T620X_IO.xlsx
+++ b/T620X_IO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\dev_plc\MTech\MTech_T620X_Trommel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{709D9869-B1E7-44F9-A3DD-A3FA48B7EEC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09B68600-DA9A-48D9-AF99-48653C91BDB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="5280" windowWidth="29040" windowHeight="15720" tabRatio="857" activeTab="7" xr2:uid="{2FCBBB71-3591-49CF-88C3-9E3184A7626E}"/>
+    <workbookView xWindow="38280" yWindow="5280" windowWidth="29040" windowHeight="15720" tabRatio="857" activeTab="4" xr2:uid="{2FCBBB71-3591-49CF-88C3-9E3184A7626E}"/>
   </bookViews>
   <sheets>
     <sheet name="IO" sheetId="11" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2686" uniqueCount="936">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2687" uniqueCount="937">
   <si>
     <t>PLC Name</t>
   </si>
@@ -2857,6 +2857,9 @@
   </si>
   <si>
     <t>Hydraulic Oil level Low Alarm</t>
+  </si>
+  <si>
+    <t>CollectConveyor_RectIcon_FB.Fill_Colour</t>
   </si>
 </sst>
 </file>
@@ -18049,7 +18052,6 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A526D88A-D53C-48FF-978F-7E496FB8AA8D}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:E131"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -18073,7 +18075,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="2" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -18087,7 +18089,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="3" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -18101,7 +18103,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="4" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -18115,7 +18117,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="5" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -18129,7 +18131,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="6" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -18146,7 +18148,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="7" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -18160,7 +18162,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="8" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -18174,7 +18176,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="9" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -18188,7 +18190,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="10" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -18202,7 +18204,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -18216,7 +18218,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -18230,7 +18232,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -18244,7 +18246,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="14" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -18258,7 +18260,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="15" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -18272,7 +18274,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="16" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -18286,7 +18288,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="17" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -18300,7 +18302,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="18" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -18314,7 +18316,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="19" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -18331,7 +18333,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="20" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -18345,7 +18347,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="21" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -18359,7 +18361,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="22" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -18373,7 +18375,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="23" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -18390,7 +18392,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="24" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
@@ -18404,7 +18406,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="25" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -18418,7 +18420,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="26" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -18432,7 +18434,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="27" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
@@ -18446,7 +18448,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="28" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
@@ -18463,7 +18465,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="29" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
@@ -18491,7 +18493,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="31" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
@@ -18508,7 +18510,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="32" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
@@ -18522,7 +18524,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="33" spans="1:5" s="33" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" s="33" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
@@ -18539,7 +18541,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="34" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
@@ -18556,7 +18558,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="35" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
@@ -18573,7 +18575,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="36" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
@@ -18587,7 +18589,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="37" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
@@ -18601,7 +18603,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="38" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
@@ -18615,7 +18617,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="39" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
@@ -18632,7 +18634,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="40" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
@@ -18649,7 +18651,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="41" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
@@ -18663,7 +18665,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="42" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
@@ -18691,7 +18693,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="44" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
@@ -18705,7 +18707,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="45" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
@@ -18722,7 +18724,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="46" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>45</v>
       </c>
@@ -18736,7 +18738,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="47" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>46</v>
       </c>
@@ -18750,7 +18752,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="48" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
@@ -18764,7 +18766,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="49" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
@@ -18778,7 +18780,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="50" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>49</v>
       </c>
@@ -18795,7 +18797,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="51" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>50</v>
       </c>
@@ -18809,7 +18811,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="52" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>51</v>
       </c>
@@ -18826,7 +18828,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="53" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>52</v>
       </c>
@@ -18840,7 +18842,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="54" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>53</v>
       </c>
@@ -18854,7 +18856,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="55" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>54</v>
       </c>
@@ -18868,7 +18870,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="56" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>55</v>
       </c>
@@ -18893,7 +18895,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="58" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>57</v>
       </c>
@@ -18907,7 +18909,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="59" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>58</v>
       </c>
@@ -18924,7 +18926,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="60" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>59</v>
       </c>
@@ -18938,7 +18940,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="61" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>60</v>
       </c>
@@ -18952,7 +18954,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="62" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>61</v>
       </c>
@@ -18966,7 +18968,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="63" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>62</v>
       </c>
@@ -18997,7 +18999,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="65" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>64</v>
       </c>
@@ -19028,7 +19030,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="67" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>66</v>
       </c>
@@ -19045,7 +19047,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="68" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>67</v>
       </c>
@@ -19059,7 +19061,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="69" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>69</v>
       </c>
@@ -19076,7 +19078,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="70" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>70</v>
       </c>
@@ -19090,7 +19092,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="71" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>71</v>
       </c>
@@ -19134,8 +19136,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="75" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="76" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B76" t="s">
         <v>570</v>
       </c>
@@ -19154,8 +19155,6 @@
         <v>567</v>
       </c>
     </row>
-    <row r="78" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="79" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B80" t="s">
         <v>552</v>
@@ -19175,8 +19174,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="82" spans="2:5" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="83" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B83" t="s">
         <v>555</v>
       </c>
@@ -19187,7 +19185,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="84" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C84" t="s">
         <v>579</v>
       </c>
@@ -19198,8 +19196,6 @@
         <v>580</v>
       </c>
     </row>
-    <row r="85" spans="2:5" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="86" spans="2:5" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="87" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B87" t="s">
         <v>288</v>
@@ -19208,7 +19204,6 @@
         <v>581</v>
       </c>
     </row>
-    <row r="88" spans="2:5" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="89" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B89" t="s">
         <v>570</v>
@@ -19217,7 +19212,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="90" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B90" t="s">
         <v>288</v>
       </c>
@@ -19228,7 +19223,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="91" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B91" t="s">
         <v>288</v>
       </c>
@@ -19255,8 +19250,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="94" spans="2:5" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="95" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B95" t="s">
         <v>390</v>
       </c>
@@ -19275,17 +19269,11 @@
         <v>908</v>
       </c>
     </row>
-    <row r="97" spans="2:5" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="98" spans="2:5" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="99" spans="2:5" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="100" spans="2:5" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="101" spans="2:5" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="102" spans="2:5" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="103" spans="2:5" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="104" spans="2:5" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="105" spans="2:5" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="106" spans="2:5" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="107" spans="2:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="102" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E102" t="s">
+        <v>936</v>
+      </c>
+    </row>
     <row r="108" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B108" t="s">
         <v>555</v>
@@ -19294,8 +19282,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="109" spans="2:5" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="110" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C110" t="s">
         <v>558</v>
       </c>
@@ -19316,7 +19303,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="113" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C113" t="s">
         <v>560</v>
       </c>
@@ -19324,7 +19311,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="114" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C114" t="s">
         <v>563</v>
       </c>
@@ -19332,7 +19319,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="115" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C115" t="s">
         <v>561</v>
       </c>
@@ -19340,9 +19327,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="116" spans="2:5" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="117" spans="2:5" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="118" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C118" t="s">
         <v>558</v>
       </c>
@@ -19363,7 +19348,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="121" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C121" t="s">
         <v>560</v>
       </c>
@@ -19371,7 +19356,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="122" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C122" t="s">
         <v>563</v>
       </c>
@@ -19379,7 +19364,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="123" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C123" t="s">
         <v>561</v>
       </c>
@@ -19387,10 +19372,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="124" spans="2:5" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="125" spans="2:5" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="126" spans="2:5" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="127" spans="2:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B127">
         <v>1</v>
       </c>
@@ -19412,7 +19394,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="129" spans="2:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B129">
         <v>3</v>
       </c>
@@ -19423,7 +19405,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="130" spans="2:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B130">
         <v>4</v>
       </c>
@@ -19434,7 +19416,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="131" spans="2:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B131">
         <v>5</v>
       </c>
@@ -19446,16 +19428,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E131" xr:uid="{A526D88A-D53C-48FF-978F-7E496FB8AA8D}">
-    <filterColumn colId="2">
-      <customFilters>
-        <customFilter operator="notEqual" val=" "/>
-      </customFilters>
-    </filterColumn>
-    <filterColumn colId="3">
-      <filters blank="1"/>
-    </filterColumn>
-  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -26830,6 +26802,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="c96d9849-7071-4555-8535-ee11c374d0f7">
@@ -26845,15 +26826,6 @@
     </SharedWithUsers>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -26876,6 +26848,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3E59E7C-5896-4162-AB70-9CA3CEB6A0FE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7DE4EA8D-9182-4C6A-B31C-49373749A7AE}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="3f324c86-ae15-4ed4-b4a2-09335a7d28ef"/>
@@ -26890,12 +26870,4 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3E59E7C-5896-4162-AB70-9CA3CEB6A0FE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/T620X_IO.xlsx
+++ b/T620X_IO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\dev_plc\MTech\MTech_T620X_Trommel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09B68600-DA9A-48D9-AF99-48653C91BDB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56B040C4-30AF-46E9-923D-8F0941E25534}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="5280" windowWidth="29040" windowHeight="15720" tabRatio="857" activeTab="4" xr2:uid="{2FCBBB71-3591-49CF-88C3-9E3184A7626E}"/>
   </bookViews>
@@ -22,11 +22,12 @@
     <sheet name="  C3.6 PGNs" sheetId="35" r:id="rId7"/>
     <sheet name="C3.6 PGNS -12 doc" sheetId="36" r:id="rId8"/>
     <sheet name="DPF Symbol Logic" sheetId="37" r:id="rId9"/>
+    <sheet name="SEQ" sheetId="39" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'C3.6 PGNS -12 doc'!$A$1:$X$171</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">IO!$A$1:$AP$78</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">SNAGS!$A$1:$E$131</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">SNAGS!$A$1:$E$99</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -49,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2687" uniqueCount="937">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2696" uniqueCount="939">
   <si>
     <t>PLC Name</t>
   </si>
@@ -1245,9 +1246,6 @@
     <t>Knob white/green on the footer - setup mode flash in mimic</t>
   </si>
   <si>
-    <t>better lines! Show ecu symbol on the engine can link</t>
-  </si>
-  <si>
     <t>Access to the min/max Valve mA settings,</t>
   </si>
   <si>
@@ -1791,15 +1789,6 @@
     <t>Radial mode - swap buttons 2+3</t>
   </si>
   <si>
-    <t>collection has to be started first?</t>
-  </si>
-  <si>
-    <t>fix up the naming on the milla amp settings on the radial</t>
-  </si>
-  <si>
-    <t>Alarms Page to cover all the shutdowns</t>
-  </si>
-  <si>
     <t>FAN Settings on Screen - add the counters to the screen</t>
   </si>
   <si>
@@ -2859,7 +2848,25 @@
     <t>Hydraulic Oil level Low Alarm</t>
   </si>
   <si>
-    <t>CollectConveyor_RectIcon_FB.Fill_Colour</t>
+    <t>Radial mode - show the stockpile direction</t>
+  </si>
+  <si>
+    <t>fix up the naming on the milla amp settings on the radial page for radial</t>
+  </si>
+  <si>
+    <t>dual names for both modes (stockpile is side coveyor)</t>
+  </si>
+  <si>
+    <t>Basic Page listing all the alrms anad interlocks - highlight logic</t>
+  </si>
+  <si>
+    <t>Check the logic for this - could be a lot more simple when tracking started</t>
+  </si>
+  <si>
+    <t>Alarms Page to cover all the shutdowns / interlocks / main alarm</t>
+  </si>
+  <si>
+    <t>better lines! Show ecu symbol on the engine can link - maybe just schamtic style</t>
   </si>
 </sst>
 </file>
@@ -4387,7 +4394,7 @@
         <v>CHASSIS.IN0102</v>
       </c>
       <c r="K4" s="19" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="L4" s="19" t="str">
         <f t="shared" si="7"/>
@@ -4463,7 +4470,7 @@
         <v>CHASSIS.IN0103</v>
       </c>
       <c r="K5" s="19" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="L5" s="19" t="str">
         <f t="shared" si="7"/>
@@ -4539,7 +4546,7 @@
         <v>CHASSIS.IN0200</v>
       </c>
       <c r="K6" s="19" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="L6" s="19" t="str">
         <f t="shared" si="7"/>
@@ -5892,7 +5899,7 @@
         <v>CHASSIS.IN0502</v>
       </c>
       <c r="K24" s="32" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="L24" s="19" t="str">
         <f t="shared" si="7"/>
@@ -5968,7 +5975,7 @@
         <v>CHASSIS.IN0503</v>
       </c>
       <c r="K25" s="32" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="L25" s="19" t="str">
         <f t="shared" si="7"/>
@@ -6681,7 +6688,7 @@
         <v>CHASSIS.OUT0000.Init(Machine_IO.Outputs.TAILCONVSPD_MA);</v>
       </c>
       <c r="V34" s="2" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="35" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -6842,7 +6849,7 @@
         <v>CHASSIS.OUT0002.Init(Machine_IO.Outputs.SIDECONVSPD_MA);</v>
       </c>
       <c r="V36" s="2" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="37" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -7003,7 +7010,7 @@
         <v>CHASSIS.OUT0004.Init(Machine_IO.Outputs.SIDETRANSFERSPD_MA);</v>
       </c>
       <c r="V38" s="2" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="39" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -7243,7 +7250,7 @@
         <v>CHASSIS.OUT0007.Init(Machine_IO.Outputs.COLLECTIONCONVSPD_MA);</v>
       </c>
       <c r="V41" s="2" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="42" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -7325,7 +7332,7 @@
         <v>CHASSIS.OUT0008.Init(Machine_IO.Outputs.COLLECTIONCONVON_OP);</v>
       </c>
       <c r="V42" s="2" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="43" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -7486,7 +7493,7 @@
         <v>CHASSIS.OUT0100.Init(Machine_IO.Outputs.DRUMSPD_MA_RAMP_LIMIT);</v>
       </c>
       <c r="V44" s="4" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="45" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -7647,7 +7654,7 @@
         <v>CHASSIS.OUT0102.Init(Machine_IO.Outputs.FEEDERSPD_MA);</v>
       </c>
       <c r="V46" s="2" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="47" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -8045,7 +8052,7 @@
         <v>CHASSIS.OUT0107.Init(Machine_IO.Outputs.SIDECONVON_OP);</v>
       </c>
       <c r="V51" s="4" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.2">
@@ -9602,7 +9609,7 @@
         <v>AUX.OP6</v>
       </c>
       <c r="K73" s="19" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="L73" s="19" t="str">
         <f t="shared" si="44"/>
@@ -9671,7 +9678,7 @@
         <v>AUX.OP7</v>
       </c>
       <c r="K74" s="19" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="L74" s="19" t="str">
         <f t="shared" si="44"/>
@@ -9987,6 +9994,174 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094488" right="0.23622047244094488" top="0.19685039370078741" bottom="0.19685039370078741" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup scale="71" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{153C88B4-F11D-4FCC-AB21-D805B4E115CA}">
+  <dimension ref="A1:D24"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="55.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="43.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>554</v>
+      </c>
+      <c r="B1" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>557</v>
+      </c>
+      <c r="C3" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>558</v>
+      </c>
+      <c r="D4" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>559</v>
+      </c>
+      <c r="C6" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>562</v>
+      </c>
+      <c r="C7" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>560</v>
+      </c>
+      <c r="C8" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>557</v>
+      </c>
+      <c r="C11" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>558</v>
+      </c>
+      <c r="D12" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
+        <v>559</v>
+      </c>
+      <c r="C14" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
+        <v>562</v>
+      </c>
+      <c r="C15" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>560</v>
+      </c>
+      <c r="C16" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>1</v>
+      </c>
+      <c r="B20" t="s">
+        <v>576</v>
+      </c>
+      <c r="C20" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>2</v>
+      </c>
+      <c r="B21" t="s">
+        <v>575</v>
+      </c>
+      <c r="D21" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>3</v>
+      </c>
+      <c r="B22" t="s">
+        <v>574</v>
+      </c>
+      <c r="C22" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>4</v>
+      </c>
+      <c r="B23" t="s">
+        <v>573</v>
+      </c>
+      <c r="C23" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>5</v>
+      </c>
+      <c r="B24" t="s">
+        <v>577</v>
+      </c>
+      <c r="C24" t="s">
+        <v>561</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -10005,7 +10180,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C2" t="str">
         <f>_xlfn.CONCAT("IF CODE = ",A2," THEN&lt;cr&gt;&lt;t&gt;TEXT:='",B2,"';&lt;cr&gt;END_IF;")</f>
@@ -10017,7 +10192,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C3" t="str">
         <f t="shared" ref="C3:C66" si="0">_xlfn.CONCAT("IF CODE = ",A3," THEN&lt;cr&gt;&lt;t&gt;TEXT:='",B3,"';&lt;cr&gt;END_IF;")</f>
@@ -10029,7 +10204,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C4" t="str">
         <f t="shared" si="0"/>
@@ -10041,7 +10216,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C5" t="str">
         <f t="shared" si="0"/>
@@ -10053,7 +10228,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C6" t="str">
         <f t="shared" si="0"/>
@@ -10065,7 +10240,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C7" t="str">
         <f t="shared" si="0"/>
@@ -10077,7 +10252,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C8" t="str">
         <f t="shared" si="0"/>
@@ -10089,7 +10264,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C9" t="str">
         <f t="shared" si="0"/>
@@ -10101,7 +10276,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C10" t="str">
         <f t="shared" si="0"/>
@@ -10113,7 +10288,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C11" t="str">
         <f t="shared" si="0"/>
@@ -10125,7 +10300,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C12" t="str">
         <f t="shared" si="0"/>
@@ -10137,7 +10312,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C13" t="str">
         <f t="shared" si="0"/>
@@ -10149,7 +10324,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C14" t="str">
         <f t="shared" si="0"/>
@@ -10161,7 +10336,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C15" t="str">
         <f t="shared" si="0"/>
@@ -10173,7 +10348,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C16" t="str">
         <f t="shared" si="0"/>
@@ -10185,7 +10360,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C17" t="str">
         <f t="shared" si="0"/>
@@ -10197,7 +10372,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C18" t="str">
         <f t="shared" si="0"/>
@@ -10209,7 +10384,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C19" t="str">
         <f t="shared" si="0"/>
@@ -10221,7 +10396,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C20" t="str">
         <f t="shared" si="0"/>
@@ -10233,7 +10408,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C21" t="str">
         <f t="shared" si="0"/>
@@ -10245,7 +10420,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C22" t="str">
         <f t="shared" si="0"/>
@@ -10257,7 +10432,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C23" t="str">
         <f t="shared" si="0"/>
@@ -10269,7 +10444,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C24" t="str">
         <f t="shared" si="0"/>
@@ -10281,7 +10456,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C25" t="str">
         <f t="shared" si="0"/>
@@ -10293,7 +10468,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C26" t="str">
         <f t="shared" si="0"/>
@@ -10305,7 +10480,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C27" t="str">
         <f t="shared" si="0"/>
@@ -10317,7 +10492,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C28" t="str">
         <f t="shared" si="0"/>
@@ -10329,7 +10504,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C29" t="str">
         <f t="shared" si="0"/>
@@ -10341,7 +10516,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C30" t="str">
         <f t="shared" si="0"/>
@@ -10353,7 +10528,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C31" t="str">
         <f t="shared" si="0"/>
@@ -10365,7 +10540,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C32" t="str">
         <f t="shared" si="0"/>
@@ -10377,7 +10552,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C33" t="str">
         <f t="shared" si="0"/>
@@ -10389,7 +10564,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C34" t="str">
         <f t="shared" si="0"/>
@@ -10401,7 +10576,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C35" t="str">
         <f t="shared" si="0"/>
@@ -10413,7 +10588,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C36" t="str">
         <f t="shared" si="0"/>
@@ -10425,7 +10600,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C37" t="str">
         <f t="shared" si="0"/>
@@ -10437,7 +10612,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C38" t="str">
         <f t="shared" si="0"/>
@@ -10449,7 +10624,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C39" t="str">
         <f t="shared" si="0"/>
@@ -10461,7 +10636,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C40" t="str">
         <f t="shared" si="0"/>
@@ -10473,7 +10648,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C41" t="str">
         <f t="shared" si="0"/>
@@ -10485,7 +10660,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C42" t="str">
         <f t="shared" si="0"/>
@@ -10497,7 +10672,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C43" t="str">
         <f t="shared" si="0"/>
@@ -10509,7 +10684,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C44" t="str">
         <f t="shared" si="0"/>
@@ -10521,7 +10696,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C45" t="str">
         <f t="shared" si="0"/>
@@ -10533,7 +10708,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C46" t="str">
         <f t="shared" si="0"/>
@@ -10545,7 +10720,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C47" t="str">
         <f t="shared" si="0"/>
@@ -10557,7 +10732,7 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C48" t="str">
         <f t="shared" si="0"/>
@@ -10569,7 +10744,7 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C49" t="str">
         <f t="shared" si="0"/>
@@ -10581,7 +10756,7 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C50" t="str">
         <f t="shared" si="0"/>
@@ -10593,7 +10768,7 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C51" t="str">
         <f t="shared" si="0"/>
@@ -10605,7 +10780,7 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C52" t="str">
         <f t="shared" si="0"/>
@@ -10617,7 +10792,7 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C53" t="str">
         <f t="shared" si="0"/>
@@ -10629,7 +10804,7 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C54" t="str">
         <f t="shared" si="0"/>
@@ -10641,7 +10816,7 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C55" t="str">
         <f t="shared" si="0"/>
@@ -10653,7 +10828,7 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C56" t="str">
         <f t="shared" si="0"/>
@@ -10665,7 +10840,7 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C57" t="str">
         <f t="shared" si="0"/>
@@ -10677,7 +10852,7 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C58" t="str">
         <f t="shared" si="0"/>
@@ -10689,7 +10864,7 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C59" t="str">
         <f t="shared" si="0"/>
@@ -10701,7 +10876,7 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C60" t="str">
         <f t="shared" si="0"/>
@@ -10713,7 +10888,7 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C61" t="str">
         <f t="shared" si="0"/>
@@ -10725,7 +10900,7 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C62" t="str">
         <f t="shared" si="0"/>
@@ -10737,7 +10912,7 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C63" t="str">
         <f t="shared" si="0"/>
@@ -10749,7 +10924,7 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C64" t="str">
         <f t="shared" si="0"/>
@@ -10761,7 +10936,7 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C65" t="str">
         <f t="shared" si="0"/>
@@ -10773,7 +10948,7 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C66" t="str">
         <f t="shared" si="0"/>
@@ -10785,7 +10960,7 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C67" t="str">
         <f t="shared" ref="C67:C130" si="1">_xlfn.CONCAT("IF CODE = ",A67," THEN&lt;cr&gt;&lt;t&gt;TEXT:='",B67,"';&lt;cr&gt;END_IF;")</f>
@@ -10797,7 +10972,7 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C68" t="str">
         <f t="shared" si="1"/>
@@ -10809,7 +10984,7 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C69" t="str">
         <f t="shared" si="1"/>
@@ -10821,7 +10996,7 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C70" t="str">
         <f t="shared" si="1"/>
@@ -10833,7 +11008,7 @@
         <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C71" t="str">
         <f t="shared" si="1"/>
@@ -10845,7 +11020,7 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C72" t="str">
         <f t="shared" si="1"/>
@@ -10857,7 +11032,7 @@
         <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C73" t="str">
         <f t="shared" si="1"/>
@@ -10869,7 +11044,7 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C74" t="str">
         <f t="shared" si="1"/>
@@ -10881,7 +11056,7 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C75" t="str">
         <f t="shared" si="1"/>
@@ -10893,7 +11068,7 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C76" t="str">
         <f t="shared" si="1"/>
@@ -10905,7 +11080,7 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C77" t="str">
         <f t="shared" si="1"/>
@@ -10917,7 +11092,7 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C78" t="str">
         <f t="shared" si="1"/>
@@ -10929,7 +11104,7 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C79" t="str">
         <f t="shared" si="1"/>
@@ -10941,7 +11116,7 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C80" t="str">
         <f t="shared" si="1"/>
@@ -10953,7 +11128,7 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C81" t="str">
         <f t="shared" si="1"/>
@@ -10965,7 +11140,7 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C82" t="str">
         <f t="shared" si="1"/>
@@ -10977,7 +11152,7 @@
         <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C83" t="str">
         <f t="shared" si="1"/>
@@ -10989,7 +11164,7 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C84" t="str">
         <f t="shared" si="1"/>
@@ -11001,7 +11176,7 @@
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C85" t="str">
         <f t="shared" si="1"/>
@@ -11013,7 +11188,7 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C86" t="str">
         <f t="shared" si="1"/>
@@ -11025,7 +11200,7 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C87" t="str">
         <f t="shared" si="1"/>
@@ -11037,7 +11212,7 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C88" t="str">
         <f t="shared" si="1"/>
@@ -11049,7 +11224,7 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C89" t="str">
         <f t="shared" si="1"/>
@@ -11061,7 +11236,7 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C90" t="str">
         <f t="shared" si="1"/>
@@ -11073,7 +11248,7 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C91" t="str">
         <f t="shared" si="1"/>
@@ -11085,7 +11260,7 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C92" t="str">
         <f t="shared" si="1"/>
@@ -11097,7 +11272,7 @@
         <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C93" t="str">
         <f t="shared" si="1"/>
@@ -11109,7 +11284,7 @@
         <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C94" t="str">
         <f t="shared" si="1"/>
@@ -11121,7 +11296,7 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C95" t="str">
         <f t="shared" si="1"/>
@@ -11133,7 +11308,7 @@
         <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C96" t="str">
         <f t="shared" si="1"/>
@@ -11145,7 +11320,7 @@
         <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C97" t="str">
         <f t="shared" si="1"/>
@@ -11157,7 +11332,7 @@
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C98" t="str">
         <f t="shared" si="1"/>
@@ -11169,7 +11344,7 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C99" t="str">
         <f t="shared" si="1"/>
@@ -11181,7 +11356,7 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C100" t="str">
         <f t="shared" si="1"/>
@@ -11193,7 +11368,7 @@
         <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C101" t="str">
         <f t="shared" si="1"/>
@@ -11205,7 +11380,7 @@
         <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C102" t="str">
         <f t="shared" si="1"/>
@@ -11217,7 +11392,7 @@
         <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C103" t="str">
         <f t="shared" si="1"/>
@@ -11229,7 +11404,7 @@
         <v>102</v>
       </c>
       <c r="B104" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C104" t="str">
         <f t="shared" si="1"/>
@@ -11241,7 +11416,7 @@
         <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C105" t="str">
         <f t="shared" si="1"/>
@@ -11253,7 +11428,7 @@
         <v>104</v>
       </c>
       <c r="B106" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C106" t="str">
         <f t="shared" si="1"/>
@@ -11265,7 +11440,7 @@
         <v>105</v>
       </c>
       <c r="B107" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C107" t="str">
         <f t="shared" si="1"/>
@@ -11277,7 +11452,7 @@
         <v>106</v>
       </c>
       <c r="B108" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C108" t="str">
         <f t="shared" si="1"/>
@@ -11289,7 +11464,7 @@
         <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C109" t="str">
         <f t="shared" si="1"/>
@@ -11301,7 +11476,7 @@
         <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C110" t="str">
         <f t="shared" si="1"/>
@@ -11313,7 +11488,7 @@
         <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C111" t="str">
         <f t="shared" si="1"/>
@@ -11325,7 +11500,7 @@
         <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C112" t="str">
         <f t="shared" si="1"/>
@@ -11337,7 +11512,7 @@
         <v>111</v>
       </c>
       <c r="B113" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C113" t="str">
         <f t="shared" si="1"/>
@@ -11349,7 +11524,7 @@
         <v>112</v>
       </c>
       <c r="B114" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C114" t="str">
         <f t="shared" si="1"/>
@@ -11361,7 +11536,7 @@
         <v>113</v>
       </c>
       <c r="B115" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C115" t="str">
         <f t="shared" si="1"/>
@@ -11373,7 +11548,7 @@
         <v>114</v>
       </c>
       <c r="B116" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C116" t="str">
         <f t="shared" si="1"/>
@@ -11385,7 +11560,7 @@
         <v>115</v>
       </c>
       <c r="B117" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C117" t="str">
         <f t="shared" si="1"/>
@@ -11397,7 +11572,7 @@
         <v>116</v>
       </c>
       <c r="B118" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C118" t="str">
         <f t="shared" si="1"/>
@@ -11409,7 +11584,7 @@
         <v>117</v>
       </c>
       <c r="B119" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C119" t="str">
         <f t="shared" si="1"/>
@@ -11421,7 +11596,7 @@
         <v>118</v>
       </c>
       <c r="B120" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C120" t="str">
         <f t="shared" si="1"/>
@@ -11433,7 +11608,7 @@
         <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="C121" t="str">
         <f t="shared" si="1"/>
@@ -11445,7 +11620,7 @@
         <v>120</v>
       </c>
       <c r="B122" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C122" t="str">
         <f t="shared" si="1"/>
@@ -11457,7 +11632,7 @@
         <v>121</v>
       </c>
       <c r="B123" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C123" t="str">
         <f t="shared" si="1"/>
@@ -11469,7 +11644,7 @@
         <v>122</v>
       </c>
       <c r="B124" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C124" t="str">
         <f t="shared" si="1"/>
@@ -11481,7 +11656,7 @@
         <v>123</v>
       </c>
       <c r="B125" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C125" t="str">
         <f t="shared" si="1"/>
@@ -11493,7 +11668,7 @@
         <v>124</v>
       </c>
       <c r="B126" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C126" t="str">
         <f t="shared" si="1"/>
@@ -11505,7 +11680,7 @@
         <v>125</v>
       </c>
       <c r="B127" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C127" t="str">
         <f t="shared" si="1"/>
@@ -11517,7 +11692,7 @@
         <v>126</v>
       </c>
       <c r="B128" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C128" t="str">
         <f t="shared" si="1"/>
@@ -11529,7 +11704,7 @@
         <v>127</v>
       </c>
       <c r="B129" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C129" t="str">
         <f t="shared" si="1"/>
@@ -11541,7 +11716,7 @@
         <v>128</v>
       </c>
       <c r="B130" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C130" t="str">
         <f t="shared" si="1"/>
@@ -11553,7 +11728,7 @@
         <v>129</v>
       </c>
       <c r="B131" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C131" t="str">
         <f t="shared" ref="C131:C135" si="2">_xlfn.CONCAT("IF CODE = ",A131," THEN&lt;cr&gt;&lt;t&gt;TEXT:='",B131,"';&lt;cr&gt;END_IF;")</f>
@@ -11565,7 +11740,7 @@
         <v>130</v>
       </c>
       <c r="B132" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C132" t="str">
         <f t="shared" si="2"/>
@@ -11577,7 +11752,7 @@
         <v>131</v>
       </c>
       <c r="B133" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C133" t="str">
         <f t="shared" si="2"/>
@@ -11589,7 +11764,7 @@
         <v>132</v>
       </c>
       <c r="B134" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C134" t="str">
         <f t="shared" si="2"/>
@@ -11601,7 +11776,7 @@
         <v>133</v>
       </c>
       <c r="B135" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C135" t="str">
         <f t="shared" si="2"/>
@@ -18052,7 +18227,8 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A526D88A-D53C-48FF-978F-7E496FB8AA8D}">
-  <dimension ref="A1:E131"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:E89"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="20.42578125" customWidth="1"/>
@@ -18075,7 +18251,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -18089,7 +18265,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -18103,7 +18279,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -18117,7 +18293,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -18131,7 +18307,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -18148,7 +18324,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -18162,7 +18338,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -18176,7 +18352,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -18190,7 +18366,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -18204,7 +18380,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -18218,7 +18394,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -18232,7 +18408,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -18246,7 +18422,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -18260,7 +18436,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -18274,7 +18450,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -18288,7 +18464,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -18302,7 +18478,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -18316,7 +18492,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -18333,7 +18509,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -18347,7 +18523,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -18361,7 +18537,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -18375,7 +18551,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -18392,7 +18568,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
@@ -18406,7 +18582,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -18420,7 +18596,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -18434,7 +18610,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
@@ -18448,7 +18624,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
@@ -18465,7 +18641,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
@@ -18479,7 +18655,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
@@ -18489,11 +18665,14 @@
       <c r="C30" t="s">
         <v>292</v>
       </c>
+      <c r="D30" t="s">
+        <v>310</v>
+      </c>
       <c r="E30" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
@@ -18510,7 +18689,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
@@ -18524,7 +18703,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="33" spans="1:5" s="33" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" s="33" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
@@ -18541,7 +18720,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
@@ -18558,7 +18737,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
@@ -18575,7 +18754,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
@@ -18589,7 +18768,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
@@ -18603,7 +18782,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
@@ -18617,7 +18796,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
@@ -18634,7 +18813,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
@@ -18651,7 +18830,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
@@ -18665,7 +18844,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
@@ -18690,10 +18869,10 @@
         <v>351</v>
       </c>
       <c r="E43" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
@@ -18707,7 +18886,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
@@ -18724,7 +18903,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>45</v>
       </c>
@@ -18738,7 +18917,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>46</v>
       </c>
@@ -18752,7 +18931,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
@@ -18766,7 +18945,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
@@ -18780,7 +18959,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>49</v>
       </c>
@@ -18794,10 +18973,10 @@
         <v>375</v>
       </c>
       <c r="E50" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>50</v>
       </c>
@@ -18811,7 +18990,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>51</v>
       </c>
@@ -18828,7 +19007,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>52</v>
       </c>
@@ -18842,7 +19021,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>53</v>
       </c>
@@ -18856,7 +19035,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>54</v>
       </c>
@@ -18870,7 +19049,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>55</v>
       </c>
@@ -18895,7 +19074,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>57</v>
       </c>
@@ -18909,7 +19088,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>58</v>
       </c>
@@ -18926,7 +19105,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>59</v>
       </c>
@@ -18934,13 +19113,13 @@
         <v>386</v>
       </c>
       <c r="C60" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="D60" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>60</v>
       </c>
@@ -18954,7 +19133,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>61</v>
       </c>
@@ -18968,7 +19147,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>62</v>
       </c>
@@ -18982,12 +19161,12 @@
         <v>375</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="C64" t="s">
         <v>393</v>
@@ -18996,10 +19175,10 @@
         <v>310</v>
       </c>
       <c r="E64" s="33" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>64</v>
       </c>
@@ -19013,10 +19192,10 @@
         <v>311</v>
       </c>
       <c r="E65" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>65</v>
       </c>
@@ -19030,7 +19209,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>66</v>
       </c>
@@ -19038,16 +19217,16 @@
         <v>288</v>
       </c>
       <c r="C67" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D67" t="s">
         <v>375</v>
       </c>
       <c r="E67" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>67</v>
       </c>
@@ -19055,90 +19234,116 @@
         <v>288</v>
       </c>
       <c r="C68" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D68" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B69" t="s">
+        <v>538</v>
+      </c>
+      <c r="C69" t="s">
         <v>539</v>
-      </c>
-      <c r="C69" t="s">
-        <v>540</v>
       </c>
       <c r="D69" t="s">
         <v>310</v>
       </c>
       <c r="E69" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B70" t="s">
         <v>294</v>
       </c>
       <c r="C70" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="D70" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C71" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="D71" t="s">
         <v>310</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>71</v>
+      </c>
       <c r="B72" t="s">
         <v>294</v>
       </c>
       <c r="C72" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="E72" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>72</v>
+      </c>
       <c r="B73" t="s">
         <v>294</v>
       </c>
       <c r="C73" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>73</v>
+      </c>
       <c r="B74" t="s">
         <v>294</v>
       </c>
       <c r="C74" t="s">
+        <v>571</v>
+      </c>
+      <c r="E74" t="s">
         <v>572</v>
       </c>
-      <c r="E74" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="75" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>74</v>
+      </c>
+      <c r="B75" t="s">
+        <v>569</v>
+      </c>
+      <c r="C75" t="s">
+        <v>565</v>
+      </c>
+      <c r="D75" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>75</v>
+      </c>
       <c r="B76" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C76" t="s">
         <v>566</v>
@@ -19148,286 +19353,190 @@
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>76</v>
+      </c>
       <c r="B77" t="s">
-        <v>570</v>
+        <v>551</v>
       </c>
       <c r="C77" t="s">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+        <v>552</v>
+      </c>
+      <c r="E77" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>77</v>
+      </c>
+      <c r="B78" t="s">
+        <v>551</v>
+      </c>
+      <c r="C78" t="s">
+        <v>553</v>
+      </c>
+      <c r="D78" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>78</v>
+      </c>
+      <c r="B79" t="s">
+        <v>290</v>
+      </c>
+      <c r="C79" t="s">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>79</v>
+      </c>
       <c r="B80" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="C80" t="s">
-        <v>553</v>
-      </c>
-      <c r="E80" t="s">
+        <v>555</v>
+      </c>
+      <c r="D80" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>80</v>
+      </c>
+      <c r="B81" t="s">
+        <v>551</v>
+      </c>
+      <c r="C81" t="s">
+        <v>578</v>
+      </c>
+      <c r="D81" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>81</v>
+      </c>
+      <c r="B82" t="s">
+        <v>288</v>
+      </c>
+      <c r="C82" t="s">
+        <v>933</v>
+      </c>
+      <c r="E82" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>82</v>
+      </c>
+      <c r="B83" t="s">
         <v>569</v>
       </c>
-    </row>
-    <row r="81" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B81" t="s">
-        <v>552</v>
-      </c>
-      <c r="C81" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="83" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B83" t="s">
-        <v>555</v>
-      </c>
       <c r="C83" t="s">
-        <v>556</v>
-      </c>
-      <c r="D83" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="84" spans="2:5" x14ac:dyDescent="0.25">
+        <v>937</v>
+      </c>
+      <c r="E83" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>83</v>
+      </c>
+      <c r="B84" t="s">
+        <v>288</v>
+      </c>
       <c r="C84" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="D84" t="s">
         <v>310</v>
       </c>
-      <c r="E84" t="s">
+    </row>
+    <row r="85" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>84</v>
+      </c>
+      <c r="B85" t="s">
+        <v>288</v>
+      </c>
+      <c r="C85" t="s">
+        <v>579</v>
+      </c>
+      <c r="D85" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>85</v>
+      </c>
+      <c r="B86" t="s">
+        <v>587</v>
+      </c>
+      <c r="C86" t="s">
         <v>580</v>
       </c>
-    </row>
-    <row r="87" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="D86" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>86</v>
+      </c>
       <c r="B87" t="s">
-        <v>288</v>
+        <v>587</v>
       </c>
       <c r="C87" t="s">
         <v>581</v>
       </c>
-    </row>
-    <row r="89" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B89" t="s">
-        <v>570</v>
-      </c>
-      <c r="C89" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="90" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B90" t="s">
-        <v>288</v>
-      </c>
-      <c r="C90" t="s">
-        <v>586</v>
-      </c>
-      <c r="D90" t="s">
+      <c r="D87" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="91" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B91" t="s">
-        <v>288</v>
-      </c>
-      <c r="C91" t="s">
-        <v>583</v>
-      </c>
-      <c r="D91" t="s">
+    <row r="88" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>87</v>
+      </c>
+      <c r="B88" t="s">
+        <v>390</v>
+      </c>
+      <c r="C88" t="s">
+        <v>903</v>
+      </c>
+      <c r="D88" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="92" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B92" t="s">
-        <v>591</v>
-      </c>
-      <c r="C92" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="93" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B93" t="s">
-        <v>591</v>
-      </c>
-      <c r="C93" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="95" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B95" t="s">
-        <v>390</v>
-      </c>
-      <c r="C95" t="s">
-        <v>907</v>
-      </c>
-      <c r="D95" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="96" spans="2:5" s="33" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B96" s="33" t="s">
+    <row r="89" spans="1:5" s="33" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>88</v>
+      </c>
+      <c r="B89" s="33" t="s">
         <v>294</v>
       </c>
-      <c r="C96" s="33" t="s">
-        <v>908</v>
-      </c>
-    </row>
-    <row r="102" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="E102" t="s">
+      <c r="C89" s="33" t="s">
+        <v>904</v>
+      </c>
+      <c r="E89" s="33" t="s">
         <v>936</v>
       </c>
     </row>
-    <row r="108" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B108" t="s">
-        <v>555</v>
-      </c>
-      <c r="C108" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="110" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C110" t="s">
-        <v>558</v>
-      </c>
-      <c r="D110" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="111" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C111" t="s">
-        <v>559</v>
-      </c>
-      <c r="E111" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="112" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C112" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="113" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C113" t="s">
-        <v>560</v>
-      </c>
-      <c r="D113" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="114" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C114" t="s">
-        <v>563</v>
-      </c>
-      <c r="D114" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="115" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C115" t="s">
-        <v>561</v>
-      </c>
-      <c r="D115" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="118" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C118" t="s">
-        <v>558</v>
-      </c>
-      <c r="D118" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="119" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C119" t="s">
-        <v>559</v>
-      </c>
-      <c r="E119" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="120" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C120" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="121" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C121" t="s">
-        <v>560</v>
-      </c>
-      <c r="D121" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="122" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C122" t="s">
-        <v>563</v>
-      </c>
-      <c r="D122" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="123" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C123" t="s">
-        <v>561</v>
-      </c>
-      <c r="D123" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="127" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B127">
-        <v>1</v>
-      </c>
-      <c r="C127" t="s">
-        <v>577</v>
-      </c>
-      <c r="D127" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="128" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B128">
-        <v>2</v>
-      </c>
-      <c r="C128" t="s">
-        <v>576</v>
-      </c>
-      <c r="E128" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="129" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B129">
-        <v>3</v>
-      </c>
-      <c r="C129" t="s">
-        <v>575</v>
-      </c>
-      <c r="D129" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="130" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B130">
-        <v>4</v>
-      </c>
-      <c r="C130" t="s">
-        <v>574</v>
-      </c>
-      <c r="D130" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="131" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B131">
-        <v>5</v>
-      </c>
-      <c r="C131" t="s">
-        <v>578</v>
-      </c>
-      <c r="D131" t="s">
-        <v>562</v>
-      </c>
-    </row>
   </sheetData>
+  <autoFilter ref="A1:E99" xr:uid="{A526D88A-D53C-48FF-978F-7E496FB8AA8D}">
+    <filterColumn colId="3">
+      <filters blank="1"/>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -19449,7 +19558,7 @@
         <v>101</v>
       </c>
       <c r="C2" t="s">
-        <v>920</v>
+        <v>916</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -19460,7 +19569,7 @@
         <v>102</v>
       </c>
       <c r="C3" t="s">
-        <v>921</v>
+        <v>917</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -19476,79 +19585,79 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>922</v>
+        <v>918</v>
       </c>
       <c r="B5">
         <v>104</v>
       </c>
       <c r="C5" t="s">
-        <v>935</v>
+        <v>931</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>923</v>
+        <v>919</v>
       </c>
       <c r="B6">
         <v>105</v>
       </c>
       <c r="C6" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="B7">
         <v>106</v>
       </c>
       <c r="C7" t="s">
-        <v>929</v>
+        <v>925</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>925</v>
+        <v>921</v>
       </c>
       <c r="B8">
         <v>107</v>
       </c>
       <c r="C8" t="s">
-        <v>933</v>
+        <v>929</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>926</v>
+        <v>922</v>
       </c>
       <c r="B9">
         <v>108</v>
       </c>
       <c r="C9" t="s">
-        <v>930</v>
+        <v>926</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>927</v>
+        <v>923</v>
       </c>
       <c r="B10">
         <v>109</v>
       </c>
       <c r="C10" t="s">
-        <v>931</v>
+        <v>927</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>928</v>
+        <v>924</v>
       </c>
       <c r="B11">
         <v>110</v>
       </c>
       <c r="C11" t="s">
-        <v>932</v>
+        <v>928</v>
       </c>
     </row>
   </sheetData>
@@ -19569,319 +19678,319 @@
   <sheetData>
     <row r="1" spans="1:7" s="38" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="38" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="B1" s="39" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="C1" s="39" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="D1" s="40" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="E1" s="40"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="B2" s="35" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="C2" s="35" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="D2" s="26">
         <f>HEX2DEC(C2)</f>
         <v>61444</v>
       </c>
       <c r="F2" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>678</v>
+        <v>674</v>
       </c>
       <c r="B3" s="35" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="C3" s="35" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
       <c r="D3" s="26">
         <f>HEX2DEC(C3)</f>
         <v>61443</v>
       </c>
       <c r="F3" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="B4" s="35" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="C4" s="35" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="D4" s="26">
         <f>HEX2DEC(C4)</f>
         <v>65247</v>
       </c>
       <c r="F4" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="B5" s="35" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="C5" s="35" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="D5" s="26">
         <f>HEX2DEC(C5)</f>
         <v>64981</v>
       </c>
       <c r="F5" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="B6" s="35" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="C6" s="35" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="D6" s="26">
         <f t="shared" ref="D6:D7" si="0">HEX2DEC(C6)</f>
         <v>65262</v>
       </c>
       <c r="F6" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="B7" s="35" t="s">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="C7" s="35" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="D7" s="26">
         <f t="shared" si="0"/>
         <v>65263</v>
       </c>
       <c r="F7" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="36" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="B8" s="36" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="C8" s="35" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="D8" s="26">
         <f t="shared" ref="D8:D17" si="1">HEX2DEC(C8)</f>
         <v>65253</v>
       </c>
       <c r="F8" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="G8" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="35" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="B9" s="35" t="s">
         <v>285</v>
       </c>
       <c r="C9" s="35" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="D9" s="26">
         <f t="shared" si="1"/>
         <v>65226</v>
       </c>
       <c r="F9" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="35" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="B10" s="35" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="C10" s="35" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="D10" s="26">
         <f t="shared" si="1"/>
         <v>65227</v>
       </c>
       <c r="F10" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
       <c r="B11" s="35" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="D11" s="26">
         <f t="shared" si="1"/>
         <v>65243</v>
       </c>
       <c r="F11" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="B12" s="35" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="C12" s="35" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="D12" s="26">
         <f t="shared" si="1"/>
         <v>65266</v>
       </c>
       <c r="F12" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="B13" s="35" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="C13" s="35" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="D13" s="26">
         <f t="shared" si="1"/>
         <v>65257</v>
       </c>
       <c r="F13" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="G13" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="B14" s="35" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="C14" s="35" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="D14" s="26">
         <f t="shared" si="1"/>
         <v>65269</v>
       </c>
       <c r="F14" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>633</v>
+        <v>629</v>
       </c>
       <c r="B15" s="35" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="C15" s="35" t="s">
-        <v>634</v>
+        <v>630</v>
       </c>
       <c r="D15" s="26">
         <f t="shared" si="1"/>
         <v>65270</v>
       </c>
       <c r="F15" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="B16" s="35" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="C16" s="35" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="D16" s="26">
         <f t="shared" si="1"/>
         <v>65271</v>
       </c>
       <c r="F16" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="B17" s="35" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="C17" s="35" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="D17" s="26">
         <f t="shared" si="1"/>
         <v>65130</v>
       </c>
       <c r="F17" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="43" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="B19" s="44" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="C19" s="44">
         <v>0</v>
@@ -19892,18 +20001,18 @@
       </c>
       <c r="E19" s="45"/>
       <c r="F19" s="43" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="43" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="B20" s="44" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="C20" s="44" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="D20" s="45">
         <f>HEX2DEC(C20)</f>
@@ -19911,15 +20020,15 @@
       </c>
       <c r="E20" s="45"/>
       <c r="F20" s="43" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="43" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="B21" s="44" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="C21" s="44">
         <v>8500</v>
@@ -19930,18 +20039,18 @@
       </c>
       <c r="E21" s="45"/>
       <c r="F21" s="43" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="43" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="B22" s="44" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="C22" s="44" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="D22" s="45">
         <f>HEX2DEC(C22)</f>
@@ -19949,144 +20058,144 @@
       </c>
       <c r="E22" s="45"/>
       <c r="F22" s="43" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="B24" s="35" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="C24" s="35" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="D24" s="26">
         <f>HEX2DEC(C24)</f>
         <v>64892</v>
       </c>
       <c r="F24" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="B25" s="35" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="C25" s="35" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="D25" s="26">
         <f>HEX2DEC(C25)</f>
         <v>64948</v>
       </c>
       <c r="F25" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>639</v>
+        <v>635</v>
       </c>
       <c r="B26" s="35" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="C26" s="35" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="D26" s="26">
         <f>HEX2DEC(C26)</f>
         <v>65110</v>
       </c>
       <c r="F26" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="B27" s="35" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="C27" s="35" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="D27" s="26">
         <f t="shared" ref="D27:D38" si="2">HEX2DEC(C27)</f>
         <v>61475</v>
       </c>
       <c r="F27" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
       <c r="B28" s="35" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="C28" s="35" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="D28" s="26">
         <f t="shared" si="2"/>
         <v>65110</v>
       </c>
       <c r="F28" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="B29" s="35" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="C29" s="35" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="D29" s="26">
         <f t="shared" si="2"/>
         <v>64830</v>
       </c>
       <c r="F29" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
       <c r="B30" s="35" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="C30" s="35" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="D30" s="26">
         <f t="shared" si="2"/>
         <v>64800</v>
       </c>
       <c r="F30" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="33" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
       <c r="B31" s="41" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="C31" s="41" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
       <c r="D31" s="42">
         <f t="shared" si="2"/>
@@ -20094,113 +20203,113 @@
       </c>
       <c r="E31" s="42"/>
       <c r="F31" s="33" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="B33" s="35" t="s">
-        <v>677</v>
+        <v>673</v>
       </c>
       <c r="C33" s="35" t="s">
-        <v>676</v>
+        <v>672</v>
       </c>
       <c r="D33" s="26">
         <f t="shared" si="2"/>
         <v>65279</v>
       </c>
       <c r="F33" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="B34" s="35" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="C34" s="35" t="s">
-        <v>683</v>
+        <v>679</v>
       </c>
       <c r="D34" s="26">
         <f t="shared" si="2"/>
         <v>64775</v>
       </c>
       <c r="F34" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="B35" s="35" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="C35" s="35" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
       <c r="D35" s="26">
         <f t="shared" si="2"/>
         <v>64773</v>
       </c>
       <c r="F35" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
       <c r="B37" s="35" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
       <c r="C37" s="35" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="D37" s="26">
         <f t="shared" si="2"/>
         <v>65242</v>
       </c>
       <c r="F37" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="G37" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="B38" s="35" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="C38" s="35" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
       <c r="D38" s="26">
         <f t="shared" si="2"/>
         <v>65259</v>
       </c>
       <c r="F38" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="G38" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="37" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>888</v>
+        <v>884</v>
       </c>
       <c r="D42" s="26">
         <v>61473</v>
@@ -20249,23 +20358,23 @@
         <v>2</v>
       </c>
       <c r="B1" s="27" t="s">
-        <v>899</v>
+        <v>895</v>
       </c>
       <c r="E1" s="46" t="s">
+        <v>894</v>
+      </c>
+      <c r="F1" s="27" t="s">
         <v>898</v>
-      </c>
-      <c r="F1" s="27" t="s">
-        <v>902</v>
       </c>
       <c r="G1" s="28"/>
       <c r="H1" s="28"/>
       <c r="I1" s="28"/>
       <c r="J1" s="28"/>
       <c r="K1" s="27" t="s">
-        <v>900</v>
+        <v>896</v>
       </c>
       <c r="N1" s="27" t="s">
-        <v>901</v>
+        <v>897</v>
       </c>
     </row>
     <row r="2" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
@@ -20273,13 +20382,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="C2" t="s">
-        <v>695</v>
+        <v>691</v>
       </c>
       <c r="K2" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="M2" t="str">
         <f>IF(C2&lt;&gt;"",_xlfn.CONCAT(B2,"_",C2),"")</f>
@@ -20303,13 +20412,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="C3" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="K3" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="M3" t="str">
         <f t="shared" ref="M3:M66" si="0">IF(C3&lt;&gt;"",_xlfn.CONCAT(B3,"_",C3),"")</f>
@@ -20333,13 +20442,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="C4" t="s">
-        <v>696</v>
+        <v>692</v>
       </c>
       <c r="K4" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="M4" t="str">
         <f t="shared" si="0"/>
@@ -20363,13 +20472,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="C5" t="s">
-        <v>697</v>
+        <v>693</v>
       </c>
       <c r="K5" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="M5" t="str">
         <f t="shared" si="0"/>
@@ -20393,13 +20502,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="C6" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="K6" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="M6" t="str">
         <f t="shared" si="0"/>
@@ -20423,13 +20532,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="C7" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="K7" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="M7" t="str">
         <f t="shared" si="0"/>
@@ -20453,13 +20562,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="C8" t="s">
+        <v>696</v>
+      </c>
+      <c r="K8" t="s">
         <v>700</v>
-      </c>
-      <c r="K8" t="s">
-        <v>704</v>
       </c>
       <c r="M8" t="str">
         <f t="shared" si="0"/>
@@ -20481,10 +20590,10 @@
         <v>285</v>
       </c>
       <c r="V8" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="X8" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
     </row>
     <row r="9" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
@@ -20492,13 +20601,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="C9" t="s">
+        <v>697</v>
+      </c>
+      <c r="K9" t="s">
         <v>701</v>
-      </c>
-      <c r="K9" t="s">
-        <v>705</v>
       </c>
       <c r="M9" t="str">
         <f t="shared" si="0"/>
@@ -20520,10 +20629,10 @@
         <v>285</v>
       </c>
       <c r="V9" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="X9" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
     </row>
     <row r="10" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
@@ -20531,13 +20640,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="C10" t="s">
-        <v>702</v>
+        <v>698</v>
       </c>
       <c r="K10" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="M10" t="str">
         <f t="shared" si="0"/>
@@ -20559,10 +20668,10 @@
         <v>285</v>
       </c>
       <c r="V10" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="X10" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
     </row>
     <row r="11" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
@@ -20570,13 +20679,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="C11" t="s">
-        <v>703</v>
+        <v>699</v>
       </c>
       <c r="K11" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="M11" t="str">
         <f t="shared" si="0"/>
@@ -20598,10 +20707,10 @@
         <v>285</v>
       </c>
       <c r="V11" t="s">
-        <v>718</v>
+        <v>714</v>
       </c>
       <c r="X11" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
     </row>
     <row r="12" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
@@ -20609,16 +20718,16 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="C12" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="E12" s="35">
         <v>899</v>
       </c>
       <c r="K12" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="M12" t="str">
         <f t="shared" si="0"/>
@@ -20640,10 +20749,10 @@
         <v>285</v>
       </c>
       <c r="V12" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="X12" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
     </row>
     <row r="13" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
@@ -20651,16 +20760,16 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="C13" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="E13" s="35">
         <v>4154</v>
       </c>
       <c r="K13" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="M13" t="str">
         <f t="shared" si="0"/>
@@ -20682,10 +20791,10 @@
         <v>285</v>
       </c>
       <c r="V13" t="s">
-        <v>720</v>
+        <v>716</v>
       </c>
       <c r="X13" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
     </row>
     <row r="14" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
@@ -20693,16 +20802,16 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="C14" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="E14" s="35">
         <v>512</v>
       </c>
       <c r="K14" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="M14" t="str">
         <f t="shared" si="0"/>
@@ -20724,10 +20833,10 @@
         <v>285</v>
       </c>
       <c r="V14" t="s">
-        <v>721</v>
+        <v>717</v>
       </c>
       <c r="X14" t="s">
-        <v>726</v>
+        <v>722</v>
       </c>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.25">
@@ -20735,19 +20844,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="C15" t="s">
-        <v>710</v>
+        <v>706</v>
       </c>
       <c r="E15" s="35">
         <v>513</v>
       </c>
       <c r="F15" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K15" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="M15" t="str">
         <f t="shared" si="0"/>
@@ -20769,10 +20878,10 @@
         <v>285</v>
       </c>
       <c r="V15" t="s">
+        <v>718</v>
+      </c>
+      <c r="X15" t="s">
         <v>722</v>
-      </c>
-      <c r="X15" t="s">
-        <v>726</v>
       </c>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.25">
@@ -20780,19 +20889,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="C16" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="E16" s="35">
         <v>190</v>
       </c>
       <c r="F16" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K16" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="M16" t="str">
         <f t="shared" si="0"/>
@@ -20814,10 +20923,10 @@
         <v>285</v>
       </c>
       <c r="V16" t="s">
-        <v>723</v>
+        <v>719</v>
       </c>
       <c r="X16" t="s">
-        <v>726</v>
+        <v>722</v>
       </c>
     </row>
     <row r="17" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
@@ -20825,16 +20934,16 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="C17" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="E17" s="35">
         <v>1483</v>
       </c>
       <c r="K17" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="M17" t="str">
         <f t="shared" si="0"/>
@@ -20856,10 +20965,10 @@
         <v>285</v>
       </c>
       <c r="V17" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="X17" t="s">
-        <v>726</v>
+        <v>722</v>
       </c>
     </row>
     <row r="18" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
@@ -20867,16 +20976,16 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="C18" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="E18" s="35">
         <v>1675</v>
       </c>
       <c r="K18" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="M18" t="str">
         <f t="shared" si="0"/>
@@ -20898,10 +21007,10 @@
         <v>285</v>
       </c>
       <c r="V18" t="s">
-        <v>725</v>
+        <v>721</v>
       </c>
       <c r="X18" t="s">
-        <v>726</v>
+        <v>722</v>
       </c>
     </row>
     <row r="19" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
@@ -20909,16 +21018,16 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="C19" t="s">
-        <v>714</v>
+        <v>710</v>
       </c>
       <c r="E19" s="35">
         <v>2432</v>
       </c>
       <c r="K19" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="M19" t="str">
         <f t="shared" si="0"/>
@@ -20942,16 +21051,16 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="C20" t="s">
-        <v>727</v>
+        <v>723</v>
       </c>
       <c r="E20" s="35">
         <v>588</v>
       </c>
       <c r="K20" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="M20" t="str">
         <f t="shared" si="0"/>
@@ -20975,16 +21084,16 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="C21" t="s">
-        <v>728</v>
+        <v>724</v>
       </c>
       <c r="E21" s="35">
         <v>559</v>
       </c>
       <c r="K21" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="M21" t="str">
         <f t="shared" si="0"/>
@@ -21008,16 +21117,16 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="C22" t="s">
-        <v>729</v>
+        <v>725</v>
       </c>
       <c r="E22" s="35">
         <v>1437</v>
       </c>
       <c r="K22" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="M22" t="str">
         <f t="shared" si="0"/>
@@ -21041,16 +21150,16 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="C23" t="s">
-        <v>730</v>
+        <v>726</v>
       </c>
       <c r="E23" s="35">
         <v>2970</v>
       </c>
       <c r="K23" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="M23" t="str">
         <f t="shared" si="0"/>
@@ -21074,16 +21183,16 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="C24" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="E24" s="35">
         <v>91</v>
       </c>
       <c r="K24" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="M24" t="str">
         <f t="shared" si="0"/>
@@ -21107,19 +21216,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="C25" t="s">
-        <v>732</v>
+        <v>728</v>
       </c>
       <c r="E25" s="35">
         <v>92</v>
       </c>
       <c r="F25" t="s">
-        <v>897</v>
+        <v>893</v>
       </c>
       <c r="K25" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="M25" t="str">
         <f t="shared" si="0"/>
@@ -21143,16 +21252,16 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="C26" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="E26" s="35">
         <v>974</v>
       </c>
       <c r="K26" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="M26" t="str">
         <f t="shared" si="0"/>
@@ -21176,16 +21285,16 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="C27" t="s">
-        <v>734</v>
+        <v>730</v>
       </c>
       <c r="E27" s="35">
         <v>29</v>
       </c>
       <c r="K27" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="M27" t="str">
         <f t="shared" si="0"/>
@@ -21209,16 +21318,16 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="C28" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="E28" s="35">
         <v>2979</v>
       </c>
       <c r="K28" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="M28" t="str">
         <f t="shared" si="0"/>
@@ -21242,16 +21351,16 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="C29" t="s">
-        <v>736</v>
+        <v>732</v>
       </c>
       <c r="E29" s="35">
         <v>5021</v>
       </c>
       <c r="K29" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="M29" t="str">
         <f t="shared" si="0"/>
@@ -21275,16 +21384,16 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="C30" t="s">
-        <v>737</v>
+        <v>733</v>
       </c>
       <c r="E30" s="35">
         <v>5399</v>
       </c>
       <c r="K30" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="M30" t="str">
         <f t="shared" si="0"/>
@@ -21308,19 +21417,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="C31" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="E31" s="35">
         <v>5400</v>
       </c>
       <c r="F31" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K31" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="M31" t="str">
         <f t="shared" si="0"/>
@@ -21344,19 +21453,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="C32" t="s">
-        <v>739</v>
+        <v>735</v>
       </c>
       <c r="E32" s="35">
         <v>3357</v>
       </c>
       <c r="F32" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K32" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="M32" t="str">
         <f t="shared" si="0"/>
@@ -21380,16 +21489,16 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="C33" t="s">
-        <v>740</v>
+        <v>736</v>
       </c>
       <c r="E33" s="35">
         <v>5398</v>
       </c>
       <c r="K33" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="M33" t="str">
         <f t="shared" si="0"/>
@@ -21413,19 +21522,19 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="C34" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="E34" s="35">
         <v>514</v>
       </c>
       <c r="F34" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K34" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="M34" t="str">
         <f t="shared" si="0"/>
@@ -21449,19 +21558,19 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="C35" t="s">
-        <v>742</v>
+        <v>738</v>
       </c>
       <c r="E35" s="35">
         <v>515</v>
       </c>
       <c r="F35" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K35" t="s">
-        <v>750</v>
+        <v>746</v>
       </c>
       <c r="M35" t="str">
         <f t="shared" si="0"/>
@@ -21485,16 +21594,16 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="C36" t="s">
-        <v>743</v>
+        <v>739</v>
       </c>
       <c r="E36" s="35">
         <v>519</v>
       </c>
       <c r="K36" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="M36" t="str">
         <f t="shared" si="0"/>
@@ -21518,16 +21627,16 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="C37" t="s">
-        <v>744</v>
+        <v>740</v>
       </c>
       <c r="E37" s="35">
         <v>2978</v>
       </c>
       <c r="K37" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="M37" t="str">
         <f t="shared" si="0"/>
@@ -21551,16 +21660,16 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="C38" t="s">
-        <v>745</v>
+        <v>741</v>
       </c>
       <c r="E38" s="35">
         <v>3236</v>
       </c>
       <c r="K38" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="M38" t="str">
         <f t="shared" si="0"/>
@@ -21584,16 +21693,16 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="C39" t="s">
-        <v>746</v>
+        <v>742</v>
       </c>
       <c r="E39" s="35">
         <v>3237</v>
       </c>
       <c r="K39" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="M39" t="str">
         <f t="shared" si="0"/>
@@ -21617,16 +21726,16 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="C40" t="s">
-        <v>747</v>
+        <v>743</v>
       </c>
       <c r="E40" s="35">
         <v>3238</v>
       </c>
       <c r="K40" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="M40" t="str">
         <f t="shared" si="0"/>
@@ -21650,16 +21759,16 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="C41" t="s">
-        <v>748</v>
+        <v>744</v>
       </c>
       <c r="E41" s="35">
         <v>3239</v>
       </c>
       <c r="K41" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="M41" t="str">
         <f t="shared" si="0"/>
@@ -21683,16 +21792,16 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="C42" t="s">
-        <v>749</v>
+        <v>745</v>
       </c>
       <c r="E42" s="35">
         <v>3240</v>
       </c>
       <c r="K42" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="M42" t="str">
         <f t="shared" si="0"/>
@@ -21716,16 +21825,16 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="C43" t="s">
-        <v>751</v>
+        <v>747</v>
       </c>
       <c r="E43" s="35">
         <v>2789</v>
       </c>
       <c r="K43" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="M43" t="str">
         <f t="shared" si="0"/>
@@ -21749,16 +21858,16 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="C44" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
       <c r="E44" s="35">
         <v>2790</v>
       </c>
       <c r="K44" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="M44" t="str">
         <f t="shared" si="0"/>
@@ -21782,19 +21891,19 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="C45" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="E45" s="35">
         <v>2791</v>
       </c>
       <c r="F45" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K45" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="M45" t="str">
         <f t="shared" si="0"/>
@@ -21818,16 +21927,16 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="C46" t="s">
-        <v>754</v>
+        <v>750</v>
       </c>
       <c r="E46" s="35">
         <v>2792</v>
       </c>
       <c r="K46" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="M46" t="str">
         <f t="shared" si="0"/>
@@ -21851,16 +21960,16 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="C47" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="E47" s="35">
         <v>5457</v>
       </c>
       <c r="K47" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="M47" t="str">
         <f t="shared" si="0"/>
@@ -21884,16 +21993,16 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="C48" t="s">
-        <v>756</v>
+        <v>752</v>
       </c>
       <c r="E48" s="35">
         <v>2795</v>
       </c>
       <c r="K48" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="M48" t="str">
         <f t="shared" si="0"/>
@@ -21917,19 +22026,19 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="C49" t="s">
-        <v>757</v>
+        <v>753</v>
       </c>
       <c r="E49" s="35">
         <v>1637</v>
       </c>
       <c r="F49" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K49" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="M49" t="str">
         <f t="shared" si="0"/>
@@ -21953,19 +22062,19 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="C50" t="s">
-        <v>758</v>
+        <v>754</v>
       </c>
       <c r="E50" s="35">
         <v>174</v>
       </c>
       <c r="F50" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K50" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="M50" t="str">
         <f t="shared" si="0"/>
@@ -21989,16 +22098,16 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="C51" t="s">
-        <v>759</v>
+        <v>755</v>
       </c>
       <c r="E51" s="35">
         <v>175</v>
       </c>
       <c r="K51" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="M51" t="str">
         <f t="shared" si="0"/>
@@ -22022,16 +22131,16 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="C52" t="s">
-        <v>760</v>
+        <v>756</v>
       </c>
       <c r="E52" s="35">
         <v>176</v>
       </c>
       <c r="K52" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="M52" t="str">
         <f t="shared" si="0"/>
@@ -22055,16 +22164,16 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="C53" t="s">
-        <v>761</v>
+        <v>757</v>
       </c>
       <c r="E53" s="35">
         <v>52</v>
       </c>
       <c r="K53" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="M53" t="str">
         <f t="shared" si="0"/>
@@ -22088,16 +22197,16 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="C54" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="E54" s="35">
         <v>1134</v>
       </c>
       <c r="K54" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="M54" t="str">
         <f t="shared" si="0"/>
@@ -22121,16 +22230,16 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>771</v>
+        <v>767</v>
       </c>
       <c r="C55" t="s">
-        <v>763</v>
+        <v>759</v>
       </c>
       <c r="E55" s="35">
         <v>94</v>
       </c>
       <c r="K55" t="s">
-        <v>770</v>
+        <v>766</v>
       </c>
       <c r="M55" t="str">
         <f t="shared" si="0"/>
@@ -22154,16 +22263,16 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>771</v>
+        <v>767</v>
       </c>
       <c r="C56" t="s">
-        <v>764</v>
+        <v>760</v>
       </c>
       <c r="E56" s="35">
         <v>22</v>
       </c>
       <c r="K56" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="M56" t="str">
         <f t="shared" si="0"/>
@@ -22187,16 +22296,16 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>771</v>
+        <v>767</v>
       </c>
       <c r="C57" t="s">
-        <v>765</v>
+        <v>761</v>
       </c>
       <c r="E57" s="35">
         <v>98</v>
       </c>
       <c r="K57" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="M57" t="str">
         <f t="shared" si="0"/>
@@ -22220,19 +22329,19 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>771</v>
+        <v>767</v>
       </c>
       <c r="C58" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
       <c r="E58" s="35">
         <v>100</v>
       </c>
       <c r="F58" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K58" t="s">
-        <v>770</v>
+        <v>766</v>
       </c>
       <c r="M58" t="str">
         <f t="shared" si="0"/>
@@ -22256,16 +22365,16 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>771</v>
+        <v>767</v>
       </c>
       <c r="C59" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
       <c r="E59" s="35">
         <v>101</v>
       </c>
       <c r="K59" t="s">
-        <v>750</v>
+        <v>746</v>
       </c>
       <c r="M59" t="str">
         <f t="shared" si="0"/>
@@ -22289,16 +22398,16 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>771</v>
+        <v>767</v>
       </c>
       <c r="C60" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
       <c r="E60" s="35">
         <v>109</v>
       </c>
       <c r="K60" t="s">
-        <v>770</v>
+        <v>766</v>
       </c>
       <c r="M60" t="str">
         <f t="shared" si="0"/>
@@ -22322,19 +22431,19 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>771</v>
+        <v>767</v>
       </c>
       <c r="C61" t="s">
-        <v>769</v>
+        <v>765</v>
       </c>
       <c r="E61" s="35">
         <v>111</v>
       </c>
       <c r="F61" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K61" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="M61" t="str">
         <f t="shared" si="0"/>
@@ -22358,16 +22467,16 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
       <c r="C62" t="s">
-        <v>772</v>
+        <v>768</v>
       </c>
       <c r="E62" s="35">
         <v>164</v>
       </c>
       <c r="K62" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="M62" t="str">
         <f t="shared" si="0"/>
@@ -22391,19 +22500,19 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
       <c r="C63" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="E63" s="35">
         <v>157</v>
       </c>
       <c r="F63" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K63" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="M63" t="str">
         <f t="shared" si="0"/>
@@ -22427,16 +22536,16 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
       <c r="C64" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
       <c r="E64" s="35">
         <v>156</v>
       </c>
       <c r="K64" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="M64" t="str">
         <f t="shared" si="0"/>
@@ -22460,16 +22569,16 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
       <c r="C65" t="s">
-        <v>775</v>
+        <v>771</v>
       </c>
       <c r="E65" s="35">
         <v>1349</v>
       </c>
       <c r="K65" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="M65" t="str">
         <f t="shared" si="0"/>
@@ -22493,16 +22602,16 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="C66" t="s">
-        <v>777</v>
+        <v>773</v>
       </c>
       <c r="E66" s="35">
         <v>182</v>
       </c>
       <c r="K66" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="M66" t="str">
         <f t="shared" si="0"/>
@@ -22526,19 +22635,19 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="C67" t="s">
-        <v>778</v>
+        <v>774</v>
       </c>
       <c r="E67" s="35">
         <v>250</v>
       </c>
       <c r="F67" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K67" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="M67" t="str">
         <f t="shared" ref="M67:M130" si="4">IF(C67&lt;&gt;"",_xlfn.CONCAT(B67,"_",C67),"")</f>
@@ -22562,19 +22671,19 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="C68" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
       <c r="E68" s="35">
         <v>108</v>
       </c>
       <c r="F68" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K68" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="M68" t="str">
         <f t="shared" si="4"/>
@@ -22598,16 +22707,16 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="C69" t="s">
-        <v>780</v>
+        <v>776</v>
       </c>
       <c r="E69" s="35">
         <v>170</v>
       </c>
       <c r="K69" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="M69" t="str">
         <f t="shared" si="4"/>
@@ -22631,19 +22740,19 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="C70" t="s">
-        <v>781</v>
+        <v>777</v>
       </c>
       <c r="E70" s="35">
         <v>171</v>
       </c>
       <c r="F70" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K70" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="M70" t="str">
         <f t="shared" si="4"/>
@@ -22667,19 +22776,19 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="C71" t="s">
-        <v>782</v>
+        <v>778</v>
       </c>
       <c r="E71" s="35">
         <v>172</v>
       </c>
       <c r="F71" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K71" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="M71" t="str">
         <f t="shared" si="4"/>
@@ -22703,16 +22812,16 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="C72" t="s">
-        <v>783</v>
+        <v>779</v>
       </c>
       <c r="E72" s="35">
         <v>79</v>
       </c>
       <c r="K72" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="M72" t="str">
         <f t="shared" si="4"/>
@@ -22736,16 +22845,16 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>791</v>
+        <v>787</v>
       </c>
       <c r="C73" t="s">
-        <v>784</v>
+        <v>780</v>
       </c>
       <c r="E73" s="35">
         <v>81</v>
       </c>
       <c r="K73" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="M73" t="str">
         <f t="shared" si="4"/>
@@ -22769,19 +22878,19 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>791</v>
+        <v>787</v>
       </c>
       <c r="C74" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
       <c r="E74" s="35">
         <v>102</v>
       </c>
       <c r="F74" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K74" t="s">
-        <v>770</v>
+        <v>766</v>
       </c>
       <c r="M74" t="str">
         <f t="shared" si="4"/>
@@ -22805,19 +22914,19 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>791</v>
+        <v>787</v>
       </c>
       <c r="C75" t="s">
-        <v>786</v>
+        <v>782</v>
       </c>
       <c r="E75" s="35">
         <v>105</v>
       </c>
       <c r="F75" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K75" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="M75" t="str">
         <f t="shared" si="4"/>
@@ -22841,19 +22950,19 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>791</v>
+        <v>787</v>
       </c>
       <c r="C76" t="s">
-        <v>787</v>
+        <v>783</v>
       </c>
       <c r="E76" s="35">
         <v>106</v>
       </c>
       <c r="F76" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K76" t="s">
-        <v>770</v>
+        <v>766</v>
       </c>
       <c r="M76" t="str">
         <f t="shared" si="4"/>
@@ -22877,16 +22986,16 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>791</v>
+        <v>787</v>
       </c>
       <c r="C77" t="s">
-        <v>788</v>
+        <v>784</v>
       </c>
       <c r="E77" s="35">
         <v>107</v>
       </c>
       <c r="K77" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="M77" t="str">
         <f t="shared" si="4"/>
@@ -22910,16 +23019,16 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>791</v>
+        <v>787</v>
       </c>
       <c r="C78" t="s">
-        <v>789</v>
+        <v>785</v>
       </c>
       <c r="E78" s="35">
         <v>173</v>
       </c>
       <c r="K78" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="M78" t="str">
         <f t="shared" si="4"/>
@@ -22943,16 +23052,16 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>791</v>
+        <v>787</v>
       </c>
       <c r="C79" t="s">
-        <v>790</v>
+        <v>786</v>
       </c>
       <c r="E79" s="35">
         <v>112</v>
       </c>
       <c r="K79" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="M79" t="str">
         <f t="shared" si="4"/>
@@ -22976,16 +23085,16 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="C80" t="s">
-        <v>792</v>
+        <v>788</v>
       </c>
       <c r="E80" s="35">
         <v>114</v>
       </c>
       <c r="K80" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="M80" t="str">
         <f t="shared" si="4"/>
@@ -23009,16 +23118,16 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="C81" t="s">
-        <v>793</v>
+        <v>789</v>
       </c>
       <c r="E81" s="35">
         <v>115</v>
       </c>
       <c r="K81" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="M81" t="str">
         <f t="shared" si="4"/>
@@ -23042,16 +23151,16 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="C82" t="s">
-        <v>794</v>
+        <v>790</v>
       </c>
       <c r="E82" s="35">
         <v>167</v>
       </c>
       <c r="K82" t="s">
-        <v>750</v>
+        <v>746</v>
       </c>
       <c r="M82" t="str">
         <f t="shared" si="4"/>
@@ -23075,19 +23184,19 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="C83" t="s">
-        <v>795</v>
+        <v>791</v>
       </c>
       <c r="E83" s="35">
         <v>168</v>
       </c>
       <c r="F83" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K83" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="M83" t="str">
         <f t="shared" si="4"/>
@@ -23111,19 +23220,19 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="C84" t="s">
-        <v>796</v>
+        <v>792</v>
       </c>
       <c r="E84" s="35">
         <v>158</v>
       </c>
       <c r="F84" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K84" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="M84" t="str">
         <f t="shared" si="4"/>
@@ -23147,16 +23256,16 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="C85" t="s">
-        <v>797</v>
+        <v>793</v>
       </c>
       <c r="E85" s="35">
         <v>1380</v>
       </c>
       <c r="K85" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="M85" t="str">
         <f t="shared" si="4"/>
@@ -23180,16 +23289,16 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="C86" t="s">
-        <v>798</v>
+        <v>794</v>
       </c>
       <c r="E86" s="35">
         <v>1381</v>
       </c>
       <c r="K86" t="s">
-        <v>770</v>
+        <v>766</v>
       </c>
       <c r="M86" t="str">
         <f t="shared" si="4"/>
@@ -23213,16 +23322,16 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="C87" t="s">
-        <v>799</v>
+        <v>795</v>
       </c>
       <c r="E87" s="35">
         <v>1382</v>
       </c>
       <c r="K87" t="s">
-        <v>770</v>
+        <v>766</v>
       </c>
       <c r="M87" t="str">
         <f t="shared" si="4"/>
@@ -23246,16 +23355,16 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="C88" t="s">
-        <v>800</v>
+        <v>796</v>
       </c>
       <c r="E88" s="35">
         <v>3548</v>
       </c>
       <c r="K88" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="M88" t="str">
         <f t="shared" si="4"/>
@@ -23279,16 +23388,16 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="C89" t="s">
-        <v>801</v>
+        <v>797</v>
       </c>
       <c r="E89" s="35">
         <v>3549</v>
       </c>
       <c r="K89" t="s">
-        <v>770</v>
+        <v>766</v>
       </c>
       <c r="M89" t="str">
         <f t="shared" si="4"/>
@@ -23312,16 +23421,16 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="C90" t="s">
-        <v>802</v>
+        <v>798</v>
       </c>
       <c r="E90" s="35">
         <v>3550</v>
       </c>
       <c r="K90" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="M90" t="str">
         <f t="shared" si="4"/>
@@ -23345,19 +23454,19 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="C91" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
       <c r="E91" s="35">
         <v>3551</v>
       </c>
       <c r="F91" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K91" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="M91" t="str">
         <f t="shared" si="4"/>
@@ -23381,16 +23490,16 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="C92" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="E92" s="35">
         <v>3552</v>
       </c>
       <c r="K92" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="M92" t="str">
         <f t="shared" si="4"/>
@@ -23414,16 +23523,16 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="C93" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
       <c r="E93" s="35">
         <v>3553</v>
       </c>
       <c r="K93" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="M93" t="str">
         <f t="shared" si="4"/>
@@ -23447,16 +23556,16 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="C94" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="E94" s="35">
         <v>3554</v>
       </c>
       <c r="K94" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="M94" t="str">
         <f t="shared" si="4"/>
@@ -23480,19 +23589,19 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="C95" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
       <c r="E95" s="35">
         <v>4083</v>
       </c>
       <c r="F95" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K95" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="M95" t="str">
         <f t="shared" si="4"/>
@@ -23516,25 +23625,25 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="C96" s="33" t="s">
-        <v>808</v>
+        <v>804</v>
       </c>
       <c r="D96" s="33" t="s">
-        <v>909</v>
+        <v>905</v>
       </c>
       <c r="E96" s="41">
         <v>3697</v>
       </c>
       <c r="F96" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="G96" s="26">
         <v>0</v>
       </c>
       <c r="H96" s="26" t="s">
-        <v>889</v>
+        <v>885</v>
       </c>
       <c r="I96" s="26">
         <v>0</v>
@@ -23544,7 +23653,7 @@
         <v>1,1</v>
       </c>
       <c r="K96" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="M96" t="str">
         <f t="shared" si="4"/>
@@ -23568,10 +23677,10 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="C97" t="s">
-        <v>809</v>
+        <v>805</v>
       </c>
       <c r="E97" s="35">
         <v>3699</v>
@@ -23580,7 +23689,7 @@
         <v>1</v>
       </c>
       <c r="H97" s="26" t="s">
-        <v>890</v>
+        <v>886</v>
       </c>
       <c r="I97" s="26">
         <v>0</v>
@@ -23590,7 +23699,7 @@
         <v>2,1</v>
       </c>
       <c r="K97" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="M97" t="str">
         <f t="shared" si="4"/>
@@ -23614,25 +23723,25 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="C98" s="33" t="s">
-        <v>810</v>
+        <v>806</v>
       </c>
       <c r="D98" s="33" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="E98" s="35">
         <v>3700</v>
       </c>
       <c r="F98" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="G98" s="26">
         <v>1</v>
       </c>
       <c r="H98" s="26" t="s">
-        <v>891</v>
+        <v>887</v>
       </c>
       <c r="I98" s="26">
         <v>2</v>
@@ -23642,7 +23751,7 @@
         <v>2,3</v>
       </c>
       <c r="K98" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="M98" t="str">
         <f t="shared" si="4"/>
@@ -23666,23 +23775,23 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="C99" s="33" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="D99" s="33"/>
       <c r="E99" s="35">
         <v>3701</v>
       </c>
       <c r="F99" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="G99" s="26">
         <v>1</v>
       </c>
       <c r="H99" s="26" t="s">
-        <v>892</v>
+        <v>888</v>
       </c>
       <c r="I99" s="26">
         <v>4</v>
@@ -23692,7 +23801,7 @@
         <v>2,5</v>
       </c>
       <c r="K99" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="M99" t="str">
         <f t="shared" si="4"/>
@@ -23716,10 +23825,10 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="C100" t="s">
-        <v>812</v>
+        <v>808</v>
       </c>
       <c r="E100" s="35">
         <v>3702</v>
@@ -23728,7 +23837,7 @@
         <v>2</v>
       </c>
       <c r="H100" s="26" t="s">
-        <v>890</v>
+        <v>886</v>
       </c>
       <c r="I100" s="26">
         <v>0</v>
@@ -23738,7 +23847,7 @@
         <v>3,1</v>
       </c>
       <c r="K100" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="M100" t="str">
         <f t="shared" si="4"/>
@@ -23762,25 +23871,25 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="C101" s="33" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
       <c r="D101" s="33" t="s">
-        <v>911</v>
+        <v>907</v>
       </c>
       <c r="E101" s="35">
         <v>3703</v>
       </c>
       <c r="F101" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="G101" s="26">
         <v>2</v>
       </c>
       <c r="H101" s="26" t="s">
-        <v>891</v>
+        <v>887</v>
       </c>
       <c r="I101" s="26">
         <v>2</v>
@@ -23790,7 +23899,7 @@
         <v>3,3</v>
       </c>
       <c r="K101" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="M101" t="str">
         <f t="shared" si="4"/>
@@ -23814,10 +23923,10 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="C102" t="s">
-        <v>814</v>
+        <v>810</v>
       </c>
       <c r="E102" s="35">
         <v>3704</v>
@@ -23826,7 +23935,7 @@
         <v>2</v>
       </c>
       <c r="H102" s="26" t="s">
-        <v>893</v>
+        <v>889</v>
       </c>
       <c r="I102" s="26">
         <v>4</v>
@@ -23836,7 +23945,7 @@
         <v>3,5</v>
       </c>
       <c r="K102" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="M102" t="str">
         <f t="shared" si="4"/>
@@ -23860,10 +23969,10 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="C103" t="s">
-        <v>815</v>
+        <v>811</v>
       </c>
       <c r="E103" s="35">
         <v>3705</v>
@@ -23872,7 +23981,7 @@
         <v>2</v>
       </c>
       <c r="H103" s="26" t="s">
-        <v>894</v>
+        <v>890</v>
       </c>
       <c r="I103" s="26">
         <v>6</v>
@@ -23882,7 +23991,7 @@
         <v>3,7</v>
       </c>
       <c r="K103" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="M103" t="str">
         <f t="shared" si="4"/>
@@ -23906,10 +24015,10 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="C104" t="s">
-        <v>816</v>
+        <v>812</v>
       </c>
       <c r="E104" s="35">
         <v>3706</v>
@@ -23918,7 +24027,7 @@
         <v>3</v>
       </c>
       <c r="H104" s="26" t="s">
-        <v>890</v>
+        <v>886</v>
       </c>
       <c r="I104" s="26">
         <v>0</v>
@@ -23928,7 +24037,7 @@
         <v>4,1</v>
       </c>
       <c r="K104" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="M104" t="str">
         <f t="shared" si="4"/>
@@ -23952,10 +24061,10 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="C105" t="s">
-        <v>817</v>
+        <v>813</v>
       </c>
       <c r="E105" s="35">
         <v>3707</v>
@@ -23964,7 +24073,7 @@
         <v>3</v>
       </c>
       <c r="H105" s="26" t="s">
-        <v>891</v>
+        <v>887</v>
       </c>
       <c r="I105" s="26">
         <v>2</v>
@@ -23974,7 +24083,7 @@
         <v>4,3</v>
       </c>
       <c r="K105" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="M105" t="str">
         <f t="shared" si="4"/>
@@ -23998,10 +24107,10 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="C106" t="s">
-        <v>818</v>
+        <v>814</v>
       </c>
       <c r="E106" s="35">
         <v>3708</v>
@@ -24010,7 +24119,7 @@
         <v>3</v>
       </c>
       <c r="H106" s="26" t="s">
-        <v>893</v>
+        <v>889</v>
       </c>
       <c r="I106" s="26">
         <v>4</v>
@@ -24020,7 +24129,7 @@
         <v>4,5</v>
       </c>
       <c r="K106" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="M106" t="str">
         <f t="shared" si="4"/>
@@ -24044,10 +24153,10 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="C107" t="s">
-        <v>819</v>
+        <v>815</v>
       </c>
       <c r="E107" s="35">
         <v>3709</v>
@@ -24056,7 +24165,7 @@
         <v>3</v>
       </c>
       <c r="H107" s="26" t="s">
-        <v>894</v>
+        <v>890</v>
       </c>
       <c r="I107" s="26">
         <v>6</v>
@@ -24066,7 +24175,7 @@
         <v>4,7</v>
       </c>
       <c r="K107" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="M107" t="str">
         <f t="shared" si="4"/>
@@ -24090,10 +24199,10 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="C108" t="s">
-        <v>820</v>
+        <v>816</v>
       </c>
       <c r="E108" s="35">
         <v>3710</v>
@@ -24102,7 +24211,7 @@
         <v>4</v>
       </c>
       <c r="H108" s="26" t="s">
-        <v>890</v>
+        <v>886</v>
       </c>
       <c r="I108" s="26">
         <v>0</v>
@@ -24112,7 +24221,7 @@
         <v>5,1</v>
       </c>
       <c r="K108" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="M108" t="str">
         <f t="shared" si="4"/>
@@ -24136,10 +24245,10 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="C109" t="s">
-        <v>821</v>
+        <v>817</v>
       </c>
       <c r="E109" s="35">
         <v>3711</v>
@@ -24148,7 +24257,7 @@
         <v>4</v>
       </c>
       <c r="H109" s="26" t="s">
-        <v>891</v>
+        <v>887</v>
       </c>
       <c r="I109" s="26">
         <v>2</v>
@@ -24158,7 +24267,7 @@
         <v>5,3</v>
       </c>
       <c r="K109" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="M109" t="str">
         <f t="shared" si="4"/>
@@ -24182,10 +24291,10 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="C110" t="s">
-        <v>822</v>
+        <v>818</v>
       </c>
       <c r="E110" s="35">
         <v>3712</v>
@@ -24194,7 +24303,7 @@
         <v>4</v>
       </c>
       <c r="H110" s="26" t="s">
-        <v>893</v>
+        <v>889</v>
       </c>
       <c r="I110" s="26">
         <v>4</v>
@@ -24204,7 +24313,7 @@
         <v>5,5</v>
       </c>
       <c r="K110" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="M110" t="str">
         <f t="shared" si="4"/>
@@ -24228,10 +24337,10 @@
         <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="C111" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="E111" s="35">
         <v>3713</v>
@@ -24240,7 +24349,7 @@
         <v>4</v>
       </c>
       <c r="H111" s="26" t="s">
-        <v>894</v>
+        <v>890</v>
       </c>
       <c r="I111" s="26">
         <v>6</v>
@@ -24250,7 +24359,7 @@
         <v>5,7</v>
       </c>
       <c r="K111" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="M111" t="str">
         <f t="shared" si="4"/>
@@ -24274,25 +24383,25 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="C112" s="33" t="s">
-        <v>824</v>
+        <v>820</v>
       </c>
       <c r="D112" s="33" t="s">
-        <v>912</v>
+        <v>908</v>
       </c>
       <c r="E112" s="35">
         <v>3714</v>
       </c>
       <c r="F112" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="G112" s="26">
         <v>5</v>
       </c>
       <c r="H112" s="26" t="s">
-        <v>890</v>
+        <v>886</v>
       </c>
       <c r="I112" s="26">
         <v>0</v>
@@ -24302,7 +24411,7 @@
         <v>6,1</v>
       </c>
       <c r="K112" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="M112" t="str">
         <f t="shared" si="4"/>
@@ -24326,25 +24435,25 @@
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="C113" s="33" t="s">
-        <v>825</v>
+        <v>821</v>
       </c>
       <c r="D113" s="33" t="s">
-        <v>913</v>
+        <v>909</v>
       </c>
       <c r="E113" s="35">
         <v>3715</v>
       </c>
       <c r="F113" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="G113" s="26">
         <v>5</v>
       </c>
       <c r="H113" s="26" t="s">
-        <v>891</v>
+        <v>887</v>
       </c>
       <c r="I113" s="26">
         <v>2</v>
@@ -24354,7 +24463,7 @@
         <v>6,3</v>
       </c>
       <c r="K113" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="M113" t="str">
         <f t="shared" si="4"/>
@@ -24378,10 +24487,10 @@
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="C114" t="s">
-        <v>826</v>
+        <v>822</v>
       </c>
       <c r="E114" s="35">
         <v>3716</v>
@@ -24390,7 +24499,7 @@
         <v>5</v>
       </c>
       <c r="H114" s="26" t="s">
-        <v>893</v>
+        <v>889</v>
       </c>
       <c r="I114" s="26">
         <v>4</v>
@@ -24400,7 +24509,7 @@
         <v>6,5</v>
       </c>
       <c r="K114" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="M114" t="str">
         <f t="shared" si="4"/>
@@ -24424,10 +24533,10 @@
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="C115" t="s">
-        <v>827</v>
+        <v>823</v>
       </c>
       <c r="E115" s="35">
         <v>3717</v>
@@ -24436,7 +24545,7 @@
         <v>5</v>
       </c>
       <c r="H115" s="26" t="s">
-        <v>894</v>
+        <v>890</v>
       </c>
       <c r="I115" s="26">
         <v>6</v>
@@ -24446,7 +24555,7 @@
         <v>6,7</v>
       </c>
       <c r="K115" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="M115" t="str">
         <f t="shared" si="4"/>
@@ -24470,10 +24579,10 @@
         <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="C116" t="s">
-        <v>828</v>
+        <v>824</v>
       </c>
       <c r="E116" s="35">
         <v>3718</v>
@@ -24482,7 +24591,7 @@
         <v>6</v>
       </c>
       <c r="H116" s="26" t="s">
-        <v>890</v>
+        <v>886</v>
       </c>
       <c r="I116" s="26">
         <v>0</v>
@@ -24492,7 +24601,7 @@
         <v>7,1</v>
       </c>
       <c r="K116" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="M116" t="str">
         <f t="shared" si="4"/>
@@ -24516,10 +24625,10 @@
         <v>116</v>
       </c>
       <c r="B117" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="C117" t="s">
-        <v>829</v>
+        <v>825</v>
       </c>
       <c r="E117" s="35">
         <v>3698</v>
@@ -24528,7 +24637,7 @@
         <v>6</v>
       </c>
       <c r="H117" s="26" t="s">
-        <v>895</v>
+        <v>891</v>
       </c>
       <c r="I117" s="26">
         <v>2</v>
@@ -24538,7 +24647,7 @@
         <v>7,3</v>
       </c>
       <c r="K117" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="M117" t="str">
         <f t="shared" si="4"/>
@@ -24562,10 +24671,10 @@
         <v>117</v>
       </c>
       <c r="B118" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="C118" t="s">
-        <v>830</v>
+        <v>826</v>
       </c>
       <c r="E118" s="35">
         <v>4175</v>
@@ -24574,7 +24683,7 @@
         <v>6</v>
       </c>
       <c r="H118" s="26" t="s">
-        <v>896</v>
+        <v>892</v>
       </c>
       <c r="I118" s="26">
         <v>5</v>
@@ -24584,7 +24693,7 @@
         <v>7,6</v>
       </c>
       <c r="K118" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="M118" t="str">
         <f t="shared" si="4"/>
@@ -24608,16 +24717,16 @@
         <v>118</v>
       </c>
       <c r="B119" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="C119" t="s">
-        <v>831</v>
+        <v>827</v>
       </c>
       <c r="E119" s="35">
         <v>3241</v>
       </c>
       <c r="K119" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="M119" t="str">
         <f t="shared" si="4"/>
@@ -24641,19 +24750,19 @@
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="C120" t="s">
-        <v>832</v>
+        <v>828</v>
       </c>
       <c r="E120" s="35">
         <v>3242</v>
       </c>
       <c r="F120" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K120" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="M120" t="str">
         <f t="shared" si="4"/>
@@ -24677,16 +24786,16 @@
         <v>120</v>
       </c>
       <c r="B121" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="C121" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="E121" s="35">
         <v>3243</v>
       </c>
       <c r="K121" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="M121" t="str">
         <f t="shared" si="4"/>
@@ -24710,16 +24819,16 @@
         <v>121</v>
       </c>
       <c r="B122" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="C122" t="s">
-        <v>834</v>
+        <v>830</v>
       </c>
       <c r="E122" s="35">
         <v>3244</v>
       </c>
       <c r="K122" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="M122" t="str">
         <f t="shared" si="4"/>
@@ -24743,19 +24852,19 @@
         <v>122</v>
       </c>
       <c r="B123" t="s">
-        <v>844</v>
+        <v>840</v>
       </c>
       <c r="C123" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="E123" s="35">
         <v>1761</v>
       </c>
       <c r="F123" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K123" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="M123" t="str">
         <f t="shared" si="4"/>
@@ -24779,19 +24888,19 @@
         <v>123</v>
       </c>
       <c r="B124" t="s">
-        <v>844</v>
+        <v>840</v>
       </c>
       <c r="C124" t="s">
-        <v>836</v>
+        <v>832</v>
       </c>
       <c r="E124" s="35">
         <v>3031</v>
       </c>
       <c r="F124" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K124" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="M124" t="str">
         <f t="shared" si="4"/>
@@ -24815,16 +24924,16 @@
         <v>124</v>
       </c>
       <c r="B125" t="s">
-        <v>844</v>
+        <v>840</v>
       </c>
       <c r="C125" t="s">
-        <v>837</v>
+        <v>833</v>
       </c>
       <c r="E125" s="35">
         <v>3517</v>
       </c>
       <c r="K125" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="M125" t="str">
         <f t="shared" si="4"/>
@@ -24848,16 +24957,16 @@
         <v>125</v>
       </c>
       <c r="B126" t="s">
-        <v>844</v>
+        <v>840</v>
       </c>
       <c r="C126" t="s">
-        <v>838</v>
+        <v>834</v>
       </c>
       <c r="E126" s="35">
         <v>3532</v>
       </c>
       <c r="K126" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="M126" t="str">
         <f t="shared" si="4"/>
@@ -24881,19 +24990,19 @@
         <v>126</v>
       </c>
       <c r="B127" t="s">
-        <v>844</v>
+        <v>840</v>
       </c>
       <c r="C127" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="E127" s="35">
         <v>5245</v>
       </c>
       <c r="F127" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K127" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="M127" t="str">
         <f t="shared" si="4"/>
@@ -24917,16 +25026,16 @@
         <v>127</v>
       </c>
       <c r="B128" t="s">
-        <v>844</v>
+        <v>840</v>
       </c>
       <c r="C128" t="s">
-        <v>840</v>
+        <v>836</v>
       </c>
       <c r="E128" s="35">
         <v>4365</v>
       </c>
       <c r="K128" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="M128" t="str">
         <f t="shared" si="4"/>
@@ -24950,19 +25059,19 @@
         <v>128</v>
       </c>
       <c r="B129" t="s">
-        <v>844</v>
+        <v>840</v>
       </c>
       <c r="C129" t="s">
-        <v>841</v>
+        <v>837</v>
       </c>
       <c r="E129" s="35">
         <v>5246</v>
       </c>
       <c r="F129" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K129" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="M129" t="str">
         <f t="shared" si="4"/>
@@ -24986,16 +25095,16 @@
         <v>129</v>
       </c>
       <c r="B130" t="s">
-        <v>844</v>
+        <v>840</v>
       </c>
       <c r="C130" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="E130" s="35">
         <v>3363</v>
       </c>
       <c r="K130" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="M130" t="str">
         <f t="shared" si="4"/>
@@ -25019,16 +25128,16 @@
         <v>130</v>
       </c>
       <c r="B131" t="s">
-        <v>844</v>
+        <v>840</v>
       </c>
       <c r="C131" t="s">
-        <v>843</v>
+        <v>839</v>
       </c>
       <c r="E131" s="35">
         <v>4366</v>
       </c>
       <c r="K131" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="M131" t="str">
         <f t="shared" ref="M131:M171" si="9">IF(C131&lt;&gt;"",_xlfn.CONCAT(B131,"_",C131),"")</f>
@@ -25052,16 +25161,16 @@
         <v>140</v>
       </c>
       <c r="B132" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="C132" t="s">
-        <v>845</v>
+        <v>841</v>
       </c>
       <c r="E132" s="35">
         <v>4331</v>
       </c>
       <c r="K132" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="M132" t="str">
         <f t="shared" si="9"/>
@@ -25085,19 +25194,19 @@
         <v>141</v>
       </c>
       <c r="B133" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="C133" t="s">
-        <v>846</v>
+        <v>842</v>
       </c>
       <c r="E133" s="35">
         <v>4332</v>
       </c>
       <c r="F133" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K133" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="M133" t="str">
         <f t="shared" si="9"/>
@@ -25121,16 +25230,16 @@
         <v>142</v>
       </c>
       <c r="B134" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="C134" t="s">
-        <v>847</v>
+        <v>843</v>
       </c>
       <c r="E134" s="35">
         <v>4333</v>
       </c>
       <c r="K134" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="M134" t="str">
         <f t="shared" si="9"/>
@@ -25154,16 +25263,16 @@
         <v>143</v>
       </c>
       <c r="B135" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="C135" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
       <c r="E135" s="35">
         <v>4334</v>
       </c>
       <c r="K135" t="s">
-        <v>770</v>
+        <v>766</v>
       </c>
       <c r="M135" t="str">
         <f t="shared" si="9"/>
@@ -25187,19 +25296,19 @@
         <v>144</v>
       </c>
       <c r="B136" t="s">
-        <v>849</v>
+        <v>845</v>
       </c>
       <c r="C136" t="s">
-        <v>850</v>
+        <v>846</v>
       </c>
       <c r="E136" s="35">
         <v>4360</v>
       </c>
       <c r="F136" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K136" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="M136" t="str">
         <f t="shared" si="9"/>
@@ -25223,16 +25332,16 @@
         <v>145</v>
       </c>
       <c r="B137" t="s">
-        <v>849</v>
+        <v>845</v>
       </c>
       <c r="C137" t="s">
-        <v>851</v>
+        <v>847</v>
       </c>
       <c r="E137" s="35">
         <v>4361</v>
       </c>
       <c r="K137" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="M137" t="str">
         <f t="shared" si="9"/>
@@ -25256,16 +25365,16 @@
         <v>146</v>
       </c>
       <c r="B138" t="s">
-        <v>849</v>
+        <v>845</v>
       </c>
       <c r="C138" t="s">
-        <v>852</v>
+        <v>848</v>
       </c>
       <c r="E138" s="35">
         <v>4363</v>
       </c>
       <c r="K138" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="M138" t="str">
         <f t="shared" si="9"/>
@@ -25289,16 +25398,16 @@
         <v>147</v>
       </c>
       <c r="B139" t="s">
+        <v>845</v>
+      </c>
+      <c r="C139" t="s">
         <v>849</v>
-      </c>
-      <c r="C139" t="s">
-        <v>853</v>
       </c>
       <c r="E139" s="35">
         <v>4362</v>
       </c>
       <c r="K139" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="M139" t="str">
         <f t="shared" si="9"/>
@@ -25322,19 +25431,19 @@
         <v>148</v>
       </c>
       <c r="B140" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="C140" t="s">
-        <v>854</v>
+        <v>850</v>
       </c>
       <c r="E140" s="35">
         <v>4765</v>
       </c>
       <c r="F140" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K140" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="M140" t="str">
         <f t="shared" si="9"/>
@@ -25358,16 +25467,16 @@
         <v>149</v>
       </c>
       <c r="B141" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="C141" t="s">
-        <v>855</v>
+        <v>851</v>
       </c>
       <c r="E141" s="35">
         <v>4766</v>
       </c>
       <c r="K141" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="M141" t="str">
         <f t="shared" si="9"/>
@@ -25391,16 +25500,16 @@
         <v>150</v>
       </c>
       <c r="B142" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="C142" t="s">
-        <v>856</v>
+        <v>852</v>
       </c>
       <c r="E142" s="35">
         <v>4767</v>
       </c>
       <c r="K142" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="M142" t="str">
         <f t="shared" si="9"/>
@@ -25424,16 +25533,16 @@
         <v>151</v>
       </c>
       <c r="B143" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="C143" t="s">
-        <v>857</v>
+        <v>853</v>
       </c>
       <c r="E143" s="35">
         <v>4768</v>
       </c>
       <c r="K143" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="M143" t="str">
         <f t="shared" si="9"/>
@@ -25457,16 +25566,16 @@
         <v>152</v>
       </c>
       <c r="B144" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="C144" t="s">
-        <v>858</v>
+        <v>854</v>
       </c>
       <c r="E144" s="35">
         <v>4769</v>
       </c>
       <c r="K144" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="M144" t="str">
         <f t="shared" si="9"/>
@@ -25490,16 +25599,16 @@
         <v>153</v>
       </c>
       <c r="B145" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="C145" t="s">
-        <v>859</v>
+        <v>855</v>
       </c>
       <c r="E145" s="35">
         <v>4770</v>
       </c>
       <c r="K145" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="M145" t="str">
         <f t="shared" si="9"/>
@@ -25523,19 +25632,19 @@
         <v>154</v>
       </c>
       <c r="B146" t="s">
-        <v>860</v>
+        <v>856</v>
       </c>
       <c r="C146" t="s">
-        <v>861</v>
+        <v>857</v>
       </c>
       <c r="E146" s="35">
         <v>97</v>
       </c>
       <c r="F146" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K146" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="M146" t="str">
         <f t="shared" si="9"/>
@@ -25559,16 +25668,16 @@
         <v>155</v>
       </c>
       <c r="B147" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="C147" t="s">
-        <v>862</v>
+        <v>858</v>
       </c>
       <c r="E147" s="35">
         <v>5077</v>
       </c>
       <c r="K147" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="L147">
         <v>1</v>
@@ -25595,16 +25704,16 @@
         <v>156</v>
       </c>
       <c r="B148" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="C148" t="s">
-        <v>863</v>
+        <v>859</v>
       </c>
       <c r="E148" s="35">
         <v>5078</v>
       </c>
       <c r="K148" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="L148">
         <v>2</v>
@@ -25631,16 +25740,16 @@
         <v>157</v>
       </c>
       <c r="B149" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="C149" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="E149" s="35">
         <v>5079</v>
       </c>
       <c r="K149" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="L149">
         <v>3</v>
@@ -25667,16 +25776,16 @@
         <v>158</v>
       </c>
       <c r="B150" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="C150" t="s">
-        <v>865</v>
+        <v>861</v>
       </c>
       <c r="E150" s="35">
         <v>5080</v>
       </c>
       <c r="K150" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="L150">
         <v>4</v>
@@ -25703,16 +25812,16 @@
         <v>159</v>
       </c>
       <c r="B151" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="C151" t="s">
-        <v>866</v>
+        <v>862</v>
       </c>
       <c r="E151" s="35">
         <v>5081</v>
       </c>
       <c r="K151" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="L151">
         <v>5</v>
@@ -25739,16 +25848,16 @@
         <v>160</v>
       </c>
       <c r="B152" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="C152" t="s">
-        <v>867</v>
+        <v>863</v>
       </c>
       <c r="E152" s="35">
         <v>3987</v>
       </c>
       <c r="K152" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="L152">
         <v>6</v>
@@ -25775,16 +25884,16 @@
         <v>161</v>
       </c>
       <c r="B153" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="C153" t="s">
-        <v>868</v>
+        <v>864</v>
       </c>
       <c r="E153" s="35">
         <v>5082</v>
       </c>
       <c r="K153" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="L153">
         <v>7</v>
@@ -25811,16 +25920,16 @@
         <v>162</v>
       </c>
       <c r="B154" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="C154" t="s">
-        <v>869</v>
+        <v>865</v>
       </c>
       <c r="E154" s="35">
         <v>5083</v>
       </c>
       <c r="K154" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="L154">
         <v>8</v>
@@ -25847,16 +25956,16 @@
         <v>163</v>
       </c>
       <c r="B155" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="C155" t="s">
-        <v>870</v>
+        <v>866</v>
       </c>
       <c r="E155" s="35">
         <v>5084</v>
       </c>
       <c r="K155" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="L155">
         <v>9</v>
@@ -25883,16 +25992,16 @@
         <v>164</v>
       </c>
       <c r="B156" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="C156" t="s">
-        <v>871</v>
+        <v>867</v>
       </c>
       <c r="E156" s="35">
         <v>5085</v>
       </c>
       <c r="K156" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="L156">
         <v>10</v>
@@ -25919,19 +26028,19 @@
         <v>165</v>
       </c>
       <c r="B157" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="C157" t="s">
-        <v>872</v>
+        <v>868</v>
       </c>
       <c r="E157" s="35">
         <v>5086</v>
       </c>
       <c r="F157" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K157" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="L157">
         <v>11</v>
@@ -25958,16 +26067,16 @@
         <v>166</v>
       </c>
       <c r="B158" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="C158" t="s">
-        <v>873</v>
+        <v>869</v>
       </c>
       <c r="E158" s="35">
         <v>5469</v>
       </c>
       <c r="K158" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="L158">
         <v>12</v>
@@ -25994,16 +26103,16 @@
         <v>167</v>
       </c>
       <c r="B159" t="s">
-        <v>874</v>
+        <v>870</v>
       </c>
       <c r="C159" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="E159" s="35">
         <v>5093</v>
       </c>
       <c r="K159" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="L159">
         <v>1</v>
@@ -26030,16 +26139,16 @@
         <v>168</v>
       </c>
       <c r="B160" t="s">
-        <v>874</v>
+        <v>870</v>
       </c>
       <c r="C160" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="E160" s="35">
         <v>5094</v>
       </c>
       <c r="K160" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="L160">
         <v>2</v>
@@ -26066,16 +26175,16 @@
         <v>169</v>
       </c>
       <c r="B161" t="s">
-        <v>874</v>
+        <v>870</v>
       </c>
       <c r="C161" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="E161" s="35">
         <v>5095</v>
       </c>
       <c r="K161" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="L161">
         <v>3</v>
@@ -26102,16 +26211,16 @@
         <v>170</v>
       </c>
       <c r="B162" t="s">
+        <v>870</v>
+      </c>
+      <c r="C162" t="s">
         <v>874</v>
-      </c>
-      <c r="C162" t="s">
-        <v>878</v>
       </c>
       <c r="E162" s="35">
         <v>5096</v>
       </c>
       <c r="K162" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="L162">
         <v>4</v>
@@ -26138,16 +26247,16 @@
         <v>171</v>
       </c>
       <c r="B163" t="s">
-        <v>874</v>
+        <v>870</v>
       </c>
       <c r="C163" t="s">
-        <v>879</v>
+        <v>875</v>
       </c>
       <c r="E163" s="35">
         <v>5097</v>
       </c>
       <c r="K163" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="L163">
         <v>5</v>
@@ -26174,16 +26283,16 @@
         <v>172</v>
       </c>
       <c r="B164" t="s">
-        <v>874</v>
+        <v>870</v>
       </c>
       <c r="C164" t="s">
-        <v>880</v>
+        <v>876</v>
       </c>
       <c r="E164" s="35">
         <v>5098</v>
       </c>
       <c r="K164" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="L164">
         <v>6</v>
@@ -26210,19 +26319,19 @@
         <v>173</v>
       </c>
       <c r="B165" t="s">
-        <v>874</v>
+        <v>870</v>
       </c>
       <c r="C165" t="s">
-        <v>881</v>
+        <v>877</v>
       </c>
       <c r="E165" s="35">
         <v>5099</v>
       </c>
       <c r="F165" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K165" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="L165">
         <v>7</v>
@@ -26249,16 +26358,16 @@
         <v>174</v>
       </c>
       <c r="B166" t="s">
-        <v>874</v>
+        <v>870</v>
       </c>
       <c r="C166" t="s">
-        <v>882</v>
+        <v>878</v>
       </c>
       <c r="E166" s="35">
         <v>5100</v>
       </c>
       <c r="K166" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="L166">
         <v>8</v>
@@ -26285,19 +26394,19 @@
         <v>175</v>
       </c>
       <c r="B167" t="s">
-        <v>874</v>
+        <v>870</v>
       </c>
       <c r="C167" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
       <c r="E167" s="35">
         <v>5101</v>
       </c>
       <c r="F167" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K167" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="L167">
         <v>9</v>
@@ -26324,16 +26433,16 @@
         <v>176</v>
       </c>
       <c r="B168" t="s">
-        <v>874</v>
+        <v>870</v>
       </c>
       <c r="C168" t="s">
-        <v>884</v>
+        <v>880</v>
       </c>
       <c r="E168" s="35">
         <v>5102</v>
       </c>
       <c r="K168" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="L168">
         <v>10</v>
@@ -26360,16 +26469,16 @@
         <v>177</v>
       </c>
       <c r="B169" t="s">
-        <v>874</v>
+        <v>870</v>
       </c>
       <c r="C169" t="s">
-        <v>885</v>
+        <v>881</v>
       </c>
       <c r="E169" s="35">
         <v>5103</v>
       </c>
       <c r="K169" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="L169">
         <v>11</v>
@@ -26396,16 +26505,16 @@
         <v>178</v>
       </c>
       <c r="B170" t="s">
-        <v>874</v>
+        <v>870</v>
       </c>
       <c r="C170" t="s">
-        <v>886</v>
+        <v>882</v>
       </c>
       <c r="E170" s="35">
         <v>5470</v>
       </c>
       <c r="K170" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="L170">
         <v>12</v>
@@ -26432,16 +26541,16 @@
         <v>179</v>
       </c>
       <c r="B171" t="s">
-        <v>874</v>
+        <v>870</v>
       </c>
       <c r="C171" t="s">
-        <v>887</v>
+        <v>883</v>
       </c>
       <c r="E171" s="35">
         <v>5416</v>
       </c>
       <c r="K171" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="L171">
         <v>13</v>
@@ -26487,24 +26596,24 @@
   <sheetData>
     <row r="2" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C2" s="33" t="s">
-        <v>909</v>
+        <v>905</v>
       </c>
       <c r="D2" s="41">
         <v>3697</v>
       </c>
       <c r="E2" t="s">
-        <v>914</v>
+        <v>910</v>
       </c>
     </row>
     <row r="3" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C3" s="33" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="D3" s="35">
         <v>3700</v>
       </c>
       <c r="E3" t="s">
-        <v>915</v>
+        <v>911</v>
       </c>
     </row>
     <row r="4" spans="3:5" x14ac:dyDescent="0.25">
@@ -26513,63 +26622,63 @@
         <v>3701</v>
       </c>
       <c r="E4" t="s">
-        <v>916</v>
+        <v>912</v>
       </c>
     </row>
     <row r="5" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C5" s="33" t="s">
-        <v>911</v>
+        <v>907</v>
       </c>
       <c r="D5" s="35">
         <v>3703</v>
       </c>
       <c r="E5" t="s">
-        <v>917</v>
+        <v>913</v>
       </c>
     </row>
     <row r="6" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C6" s="33" t="s">
-        <v>912</v>
+        <v>908</v>
       </c>
       <c r="D6" s="35">
         <v>3714</v>
       </c>
       <c r="E6" t="s">
-        <v>918</v>
+        <v>914</v>
       </c>
     </row>
     <row r="7" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C7" s="33" t="s">
-        <v>913</v>
+        <v>909</v>
       </c>
       <c r="D7" s="35">
         <v>3715</v>
       </c>
       <c r="E7" t="s">
-        <v>919</v>
+        <v>915</v>
       </c>
     </row>
     <row r="10" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E10" t="s">
-        <v>903</v>
+        <v>899</v>
       </c>
     </row>
     <row r="14" spans="3:5" ht="255" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="15" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E15" t="s">
-        <v>904</v>
+        <v>900</v>
       </c>
     </row>
     <row r="18" spans="5:5" ht="409.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="20" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E20" t="s">
-        <v>905</v>
+        <v>901</v>
       </c>
     </row>
     <row r="23" spans="5:5" ht="205.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="25" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E25" t="s">
-        <v>906</v>
+        <v>902</v>
       </c>
     </row>
   </sheetData>
@@ -26579,6 +26688,33 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c96d9849-7071-4555-8535-ee11c374d0f7">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3f324c86-ae15-4ed4-b4a2-09335a7d28ef" xsi:nil="true"/>
+    <SharedWithUsers xmlns="3f324c86-ae15-4ed4-b4a2-09335a7d28ef">
+      <UserInfo>
+        <DisplayName>Noel Loughran</DisplayName>
+        <AccountId>19</AccountId>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007A9F7729ADF49144A01A6175DD599202" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3f00ebe7287476f312414df31db46304">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c96d9849-7071-4555-8535-ee11c374d0f7" xmlns:ns3="3f324c86-ae15-4ed4-b4a2-09335a7d28ef" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8f2e969a0d0c60cbdf6bd0d859a86451" ns2:_="" ns3:_="">
     <xsd:import namespace="c96d9849-7071-4555-8535-ee11c374d0f7"/>
@@ -26801,34 +26937,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7DE4EA8D-9182-4C6A-B31C-49373749A7AE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="3f324c86-ae15-4ed4-b4a2-09335a7d28ef"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="c96d9849-7071-4555-8535-ee11c374d0f7"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c96d9849-7071-4555-8535-ee11c374d0f7">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3f324c86-ae15-4ed4-b4a2-09335a7d28ef" xsi:nil="true"/>
-    <SharedWithUsers xmlns="3f324c86-ae15-4ed4-b4a2-09335a7d28ef">
-      <UserInfo>
-        <DisplayName>Noel Loughran</DisplayName>
-        <AccountId>19</AccountId>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3E59E7C-5896-4162-AB70-9CA3CEB6A0FE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6596B7D1-B3E6-40CB-B05E-2E959D1A2B6D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -26845,29 +26979,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3E59E7C-5896-4162-AB70-9CA3CEB6A0FE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7DE4EA8D-9182-4C6A-B31C-49373749A7AE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="3f324c86-ae15-4ed4-b4a2-09335a7d28ef"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="c96d9849-7071-4555-8535-ee11c374d0f7"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/T620X_IO.xlsx
+++ b/T620X_IO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\dev_plc\MTech\MTech_T620X_Trommel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56B040C4-30AF-46E9-923D-8F0941E25534}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C00B3BF4-C8BA-42A6-AD44-D4C6D28929F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="5280" windowWidth="29040" windowHeight="15720" tabRatio="857" activeTab="4" xr2:uid="{2FCBBB71-3591-49CF-88C3-9E3184A7626E}"/>
   </bookViews>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2696" uniqueCount="939">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2698" uniqueCount="940">
   <si>
     <t>PLC Name</t>
   </si>
@@ -2867,6 +2867,9 @@
   </si>
   <si>
     <t>better lines! Show ecu symbol on the engine can link - maybe just schamtic style</t>
+  </si>
+  <si>
+    <t>Better Drum Pressure Display, move counter to interlocks page</t>
   </si>
 </sst>
 </file>
@@ -18228,7 +18231,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A526D88A-D53C-48FF-978F-7E496FB8AA8D}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:E89"/>
+  <dimension ref="A1:E90"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="20.42578125" customWidth="1"/>
@@ -19529,6 +19532,14 @@
       </c>
       <c r="E89" s="33" t="s">
         <v>936</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B90" t="s">
+        <v>290</v>
+      </c>
+      <c r="C90" t="s">
+        <v>939</v>
       </c>
     </row>
   </sheetData>
@@ -26706,15 +26717,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007A9F7729ADF49144A01A6175DD599202" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3f00ebe7287476f312414df31db46304">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c96d9849-7071-4555-8535-ee11c374d0f7" xmlns:ns3="3f324c86-ae15-4ed4-b4a2-09335a7d28ef" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8f2e969a0d0c60cbdf6bd0d859a86451" ns2:_="" ns3:_="">
     <xsd:import namespace="c96d9849-7071-4555-8535-ee11c374d0f7"/>
@@ -26937,6 +26939,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7DE4EA8D-9182-4C6A-B31C-49373749A7AE}">
   <ds:schemaRefs>
@@ -26955,14 +26966,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3E59E7C-5896-4162-AB70-9CA3CEB6A0FE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6596B7D1-B3E6-40CB-B05E-2E959D1A2B6D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -26979,4 +26982,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3E59E7C-5896-4162-AB70-9CA3CEB6A0FE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/T620X_IO.xlsx
+++ b/T620X_IO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\dev_plc\MTech\MTech_T620X_Trommel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C00B3BF4-C8BA-42A6-AD44-D4C6D28929F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{304F2CB8-F26E-4C3D-8BC2-B5D9DBEBE6FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="5280" windowWidth="29040" windowHeight="15720" tabRatio="857" activeTab="4" xr2:uid="{2FCBBB71-3591-49CF-88C3-9E3184A7626E}"/>
   </bookViews>
@@ -27,7 +27,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'C3.6 PGNS -12 doc'!$A$1:$X$171</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">IO!$A$1:$AP$78</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">SNAGS!$A$1:$E$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">SNAGS!$A$1:$E$98</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2698" uniqueCount="940">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2718" uniqueCount="950">
   <si>
     <t>PLC Name</t>
   </si>
@@ -1708,9 +1708,6 @@
     <t>RADIAL_MODE</t>
   </si>
   <si>
-    <t>Starting tracks stops auto radial mode?</t>
-  </si>
-  <si>
     <t>Reset the radial timeout if mode changed?</t>
   </si>
   <si>
@@ -2870,6 +2867,39 @@
   </si>
   <si>
     <t>Better Drum Pressure Display, move counter to interlocks page</t>
+  </si>
+  <si>
+    <t>Very unrelaible color setting!</t>
+  </si>
+  <si>
+    <t>Starting tracks stops auto radial  / standard mode?</t>
+  </si>
+  <si>
+    <t>is the radial left right speed controlled via ma?</t>
+  </si>
+  <si>
+    <t>radial meant to work of the remote control in auto mode?</t>
+  </si>
+  <si>
+    <t>sets the autoshutdown - what if you wanted to use it manually when auto running?</t>
+  </si>
+  <si>
+    <t>Jacklegs raise/lower sets the autoo shutodwn ?</t>
+  </si>
+  <si>
+    <t>not just ignore them in auto?</t>
+  </si>
+  <si>
+    <t>side conv up down  meant to work of the remote control in auto mode?</t>
+  </si>
+  <si>
+    <t>RADIAL</t>
+  </si>
+  <si>
+    <t>JACKLEGS</t>
+  </si>
+  <si>
+    <t>SIDE_CONV</t>
   </si>
 </sst>
 </file>
@@ -10012,100 +10042,100 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B1" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C3" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="D4" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C6" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C7" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
+        <v>559</v>
+      </c>
+      <c r="C8" t="s">
         <v>560</v>
-      </c>
-      <c r="C8" t="s">
-        <v>561</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C11" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="D12" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C14" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C15" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
+        <v>559</v>
+      </c>
+      <c r="C16" t="s">
         <v>560</v>
-      </c>
-      <c r="C16" t="s">
-        <v>561</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -10113,10 +10143,10 @@
         <v>1</v>
       </c>
       <c r="B20" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C20" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -10124,10 +10154,10 @@
         <v>2</v>
       </c>
       <c r="B21" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="D21" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -10135,10 +10165,10 @@
         <v>3</v>
       </c>
       <c r="B22" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C22" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -10146,10 +10176,10 @@
         <v>4</v>
       </c>
       <c r="B23" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C23" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -10157,10 +10187,10 @@
         <v>5</v>
       </c>
       <c r="B24" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C24" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
   </sheetData>
@@ -18231,7 +18261,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A526D88A-D53C-48FF-978F-7E496FB8AA8D}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:E90"/>
+  <dimension ref="A1:E94"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="20.42578125" customWidth="1"/>
@@ -18672,7 +18702,7 @@
         <v>310</v>
       </c>
       <c r="E30" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="31" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
@@ -18872,7 +18902,7 @@
         <v>351</v>
       </c>
       <c r="E43" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
     </row>
     <row r="44" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
@@ -19066,7 +19096,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>56</v>
       </c>
@@ -19075,6 +19105,12 @@
       </c>
       <c r="C57" t="s">
         <v>379</v>
+      </c>
+      <c r="D57" t="s">
+        <v>311</v>
+      </c>
+      <c r="E57" t="s">
+        <v>939</v>
       </c>
     </row>
     <row r="58" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
@@ -19169,7 +19205,7 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C64" t="s">
         <v>393</v>
@@ -19178,7 +19214,7 @@
         <v>310</v>
       </c>
       <c r="E64" s="33" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="65" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
@@ -19195,7 +19231,7 @@
         <v>311</v>
       </c>
       <c r="E65" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="66" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
@@ -19288,7 +19324,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>71</v>
       </c>
@@ -19296,13 +19332,16 @@
         <v>294</v>
       </c>
       <c r="C72" t="s">
-        <v>567</v>
+        <v>566</v>
+      </c>
+      <c r="D72" t="s">
+        <v>311</v>
       </c>
       <c r="E72" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>72</v>
       </c>
@@ -19310,10 +19349,13 @@
         <v>294</v>
       </c>
       <c r="C73" t="s">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+        <v>585</v>
+      </c>
+      <c r="D73" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>73</v>
       </c>
@@ -19321,10 +19363,13 @@
         <v>294</v>
       </c>
       <c r="C74" t="s">
+        <v>570</v>
+      </c>
+      <c r="D74" t="s">
+        <v>311</v>
+      </c>
+      <c r="E74" t="s">
         <v>571</v>
-      </c>
-      <c r="E74" t="s">
-        <v>572</v>
       </c>
     </row>
     <row r="75" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
@@ -19332,10 +19377,10 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="C75" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="D75" t="s">
         <v>310</v>
@@ -19346,10 +19391,10 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="C76" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="D76" t="s">
         <v>310</v>
@@ -19363,10 +19408,10 @@
         <v>551</v>
       </c>
       <c r="C77" t="s">
-        <v>552</v>
+        <v>940</v>
       </c>
       <c r="E77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="78" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
@@ -19377,13 +19422,13 @@
         <v>551</v>
       </c>
       <c r="C78" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="D78" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>78</v>
       </c>
@@ -19391,7 +19436,10 @@
         <v>290</v>
       </c>
       <c r="C79" t="s">
-        <v>932</v>
+        <v>931</v>
+      </c>
+      <c r="D79" t="s">
+        <v>310</v>
       </c>
     </row>
     <row r="80" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
@@ -19399,10 +19447,10 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
+        <v>553</v>
+      </c>
+      <c r="C80" t="s">
         <v>554</v>
-      </c>
-      <c r="C80" t="s">
-        <v>555</v>
       </c>
       <c r="D80" t="s">
         <v>310</v>
@@ -19416,13 +19464,13 @@
         <v>551</v>
       </c>
       <c r="C81" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D81" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>81</v>
       </c>
@@ -19430,24 +19478,30 @@
         <v>288</v>
       </c>
       <c r="C82" t="s">
+        <v>932</v>
+      </c>
+      <c r="D82" t="s">
+        <v>310</v>
+      </c>
+      <c r="E82" t="s">
         <v>933</v>
       </c>
-      <c r="E82" t="s">
-        <v>934</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="83" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="C83" t="s">
-        <v>937</v>
+        <v>936</v>
+      </c>
+      <c r="D83" t="s">
+        <v>311</v>
       </c>
       <c r="E83" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
     </row>
     <row r="84" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
@@ -19458,7 +19512,7 @@
         <v>288</v>
       </c>
       <c r="C84" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="D84" t="s">
         <v>310</v>
@@ -19472,7 +19526,7 @@
         <v>288</v>
       </c>
       <c r="C85" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="D85" t="s">
         <v>310</v>
@@ -19483,10 +19537,10 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C86" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="D86" t="s">
         <v>310</v>
@@ -19497,10 +19551,10 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C87" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="D87" t="s">
         <v>310</v>
@@ -19514,7 +19568,7 @@
         <v>390</v>
       </c>
       <c r="C88" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="D88" t="s">
         <v>310</v>
@@ -19528,22 +19582,66 @@
         <v>294</v>
       </c>
       <c r="C89" s="33" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="E89" s="33" t="s">
-        <v>936</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="B90" t="s">
         <v>290</v>
       </c>
       <c r="C90" t="s">
-        <v>939</v>
+        <v>938</v>
+      </c>
+      <c r="D90" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B91" t="s">
+        <v>947</v>
+      </c>
+      <c r="C91" t="s">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B92" t="s">
+        <v>947</v>
+      </c>
+      <c r="C92" t="s">
+        <v>942</v>
+      </c>
+      <c r="E92" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B93" t="s">
+        <v>948</v>
+      </c>
+      <c r="C93" t="s">
+        <v>944</v>
+      </c>
+      <c r="E93" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B94" t="s">
+        <v>949</v>
+      </c>
+      <c r="C94" t="s">
+        <v>946</v>
+      </c>
+      <c r="E94" t="s">
+        <v>943</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E99" xr:uid="{A526D88A-D53C-48FF-978F-7E496FB8AA8D}">
+  <autoFilter ref="A1:E98" xr:uid="{A526D88A-D53C-48FF-978F-7E496FB8AA8D}">
     <filterColumn colId="3">
       <filters blank="1"/>
     </filterColumn>
@@ -19569,7 +19667,7 @@
         <v>101</v>
       </c>
       <c r="C2" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -19580,7 +19678,7 @@
         <v>102</v>
       </c>
       <c r="C3" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -19596,79 +19694,79 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="B5">
         <v>104</v>
       </c>
       <c r="C5" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="B6">
         <v>105</v>
       </c>
       <c r="C6" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="B7">
         <v>106</v>
       </c>
       <c r="C7" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="B8">
         <v>107</v>
       </c>
       <c r="C8" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="B9">
         <v>108</v>
       </c>
       <c r="C9" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="B10">
         <v>109</v>
       </c>
       <c r="C10" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="B11">
         <v>110</v>
       </c>
       <c r="C11" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
     </row>
   </sheetData>
@@ -19689,319 +19787,319 @@
   <sheetData>
     <row r="1" spans="1:7" s="38" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="38" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B1" s="39" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="C1" s="39" t="s">
+        <v>597</v>
+      </c>
+      <c r="D1" s="40" t="s">
         <v>598</v>
-      </c>
-      <c r="D1" s="40" t="s">
-        <v>599</v>
       </c>
       <c r="E1" s="40"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B2" s="35" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="C2" s="35" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="D2" s="26">
         <f>HEX2DEC(C2)</f>
         <v>61444</v>
       </c>
       <c r="F2" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>673</v>
+      </c>
+      <c r="B3" s="35" t="s">
         <v>674</v>
       </c>
-      <c r="B3" s="35" t="s">
+      <c r="C3" s="35" t="s">
         <v>675</v>
-      </c>
-      <c r="C3" s="35" t="s">
-        <v>676</v>
       </c>
       <c r="D3" s="26">
         <f>HEX2DEC(C3)</f>
         <v>61443</v>
       </c>
       <c r="F3" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>613</v>
+      </c>
+      <c r="B4" s="35" t="s">
         <v>614</v>
       </c>
-      <c r="B4" s="35" t="s">
+      <c r="C4" s="35" t="s">
         <v>615</v>
-      </c>
-      <c r="C4" s="35" t="s">
-        <v>616</v>
       </c>
       <c r="D4" s="26">
         <f>HEX2DEC(C4)</f>
         <v>65247</v>
       </c>
       <c r="F4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>661</v>
+      </c>
+      <c r="B5" s="35" t="s">
         <v>662</v>
       </c>
-      <c r="B5" s="35" t="s">
+      <c r="C5" s="35" t="s">
         <v>663</v>
-      </c>
-      <c r="C5" s="35" t="s">
-        <v>664</v>
       </c>
       <c r="D5" s="26">
         <f>HEX2DEC(C5)</f>
         <v>64981</v>
       </c>
       <c r="F5" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="B6" s="35" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="C6" s="35" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="D6" s="26">
         <f t="shared" ref="D6:D7" si="0">HEX2DEC(C6)</f>
         <v>65262</v>
       </c>
       <c r="F6" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B7" s="35" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="C7" s="35" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="D7" s="26">
         <f t="shared" si="0"/>
         <v>65263</v>
       </c>
       <c r="F7" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="36" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B8" s="36" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C8" s="35" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="D8" s="26">
         <f t="shared" ref="D8:D17" si="1">HEX2DEC(C8)</f>
         <v>65253</v>
       </c>
       <c r="F8" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G8" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="35" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B9" s="35" t="s">
         <v>285</v>
       </c>
       <c r="C9" s="35" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="D9" s="26">
         <f t="shared" si="1"/>
         <v>65226</v>
       </c>
       <c r="F9" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="35" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B10" s="35" t="s">
+        <v>602</v>
+      </c>
+      <c r="C10" s="35" t="s">
         <v>603</v>
-      </c>
-      <c r="C10" s="35" t="s">
-        <v>604</v>
       </c>
       <c r="D10" s="26">
         <f t="shared" si="1"/>
         <v>65227</v>
       </c>
       <c r="F10" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>632</v>
+      </c>
+      <c r="B11" s="35" t="s">
+        <v>688</v>
+      </c>
+      <c r="C11" s="35" t="s">
         <v>633</v>
-      </c>
-      <c r="B11" s="35" t="s">
-        <v>689</v>
-      </c>
-      <c r="C11" s="35" t="s">
-        <v>634</v>
       </c>
       <c r="D11" s="26">
         <f t="shared" si="1"/>
         <v>65243</v>
       </c>
       <c r="F11" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B12" s="35" t="s">
+        <v>623</v>
+      </c>
+      <c r="C12" s="35" t="s">
         <v>624</v>
-      </c>
-      <c r="C12" s="35" t="s">
-        <v>625</v>
       </c>
       <c r="D12" s="26">
         <f t="shared" si="1"/>
         <v>65266</v>
       </c>
       <c r="F12" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B13" s="35" t="s">
+        <v>619</v>
+      </c>
+      <c r="C13" s="35" t="s">
         <v>620</v>
-      </c>
-      <c r="C13" s="35" t="s">
-        <v>621</v>
       </c>
       <c r="D13" s="26">
         <f t="shared" si="1"/>
         <v>65257</v>
       </c>
       <c r="F13" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G13" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>626</v>
+      </c>
+      <c r="B14" s="35" t="s">
+        <v>646</v>
+      </c>
+      <c r="C14" s="35" t="s">
         <v>627</v>
-      </c>
-      <c r="B14" s="35" t="s">
-        <v>647</v>
-      </c>
-      <c r="C14" s="35" t="s">
-        <v>628</v>
       </c>
       <c r="D14" s="26">
         <f t="shared" si="1"/>
         <v>65269</v>
       </c>
       <c r="F14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>628</v>
+      </c>
+      <c r="B15" s="35" t="s">
+        <v>645</v>
+      </c>
+      <c r="C15" s="35" t="s">
         <v>629</v>
-      </c>
-      <c r="B15" s="35" t="s">
-        <v>646</v>
-      </c>
-      <c r="C15" s="35" t="s">
-        <v>630</v>
       </c>
       <c r="D15" s="26">
         <f t="shared" si="1"/>
         <v>65270</v>
       </c>
       <c r="F15" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>642</v>
+      </c>
+      <c r="B16" s="35" t="s">
+        <v>644</v>
+      </c>
+      <c r="C16" s="35" t="s">
         <v>643</v>
-      </c>
-      <c r="B16" s="35" t="s">
-        <v>645</v>
-      </c>
-      <c r="C16" s="35" t="s">
-        <v>644</v>
       </c>
       <c r="D16" s="26">
         <f t="shared" si="1"/>
         <v>65271</v>
       </c>
       <c r="F16" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B17" s="35" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C17" s="35" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="D17" s="26">
         <f t="shared" si="1"/>
         <v>65130</v>
       </c>
       <c r="F17" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="43" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B19" s="44" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C19" s="44">
         <v>0</v>
@@ -20012,18 +20110,18 @@
       </c>
       <c r="E19" s="45"/>
       <c r="F19" s="43" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="43" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B20" s="44" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C20" s="44" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D20" s="45">
         <f>HEX2DEC(C20)</f>
@@ -20031,15 +20129,15 @@
       </c>
       <c r="E20" s="45"/>
       <c r="F20" s="43" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="43" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B21" s="44" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C21" s="44">
         <v>8500</v>
@@ -20050,18 +20148,18 @@
       </c>
       <c r="E21" s="45"/>
       <c r="F21" s="43" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="43" t="s">
+        <v>607</v>
+      </c>
+      <c r="B22" s="44" t="s">
+        <v>606</v>
+      </c>
+      <c r="C22" s="44" t="s">
         <v>608</v>
-      </c>
-      <c r="B22" s="44" t="s">
-        <v>607</v>
-      </c>
-      <c r="C22" s="44" t="s">
-        <v>609</v>
       </c>
       <c r="D22" s="45">
         <f>HEX2DEC(C22)</f>
@@ -20069,144 +20167,144 @@
       </c>
       <c r="E22" s="45"/>
       <c r="F22" s="43" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B24" s="35" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C24" s="35" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="D24" s="26">
         <f>HEX2DEC(C24)</f>
         <v>64892</v>
       </c>
       <c r="F24" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>630</v>
+      </c>
+      <c r="B25" s="35" t="s">
+        <v>651</v>
+      </c>
+      <c r="C25" s="35" t="s">
         <v>631</v>
-      </c>
-      <c r="B25" s="35" t="s">
-        <v>652</v>
-      </c>
-      <c r="C25" s="35" t="s">
-        <v>632</v>
       </c>
       <c r="D25" s="26">
         <f>HEX2DEC(C25)</f>
         <v>64948</v>
       </c>
       <c r="F25" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>634</v>
+      </c>
+      <c r="B26" s="35" t="s">
+        <v>653</v>
+      </c>
+      <c r="C26" s="35" t="s">
         <v>635</v>
-      </c>
-      <c r="B26" s="35" t="s">
-        <v>654</v>
-      </c>
-      <c r="C26" s="35" t="s">
-        <v>636</v>
       </c>
       <c r="D26" s="26">
         <f>HEX2DEC(C26)</f>
         <v>65110</v>
       </c>
       <c r="F26" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>637</v>
+      </c>
+      <c r="B27" s="35" t="s">
+        <v>656</v>
+      </c>
+      <c r="C27" s="35" t="s">
         <v>638</v>
-      </c>
-      <c r="B27" s="35" t="s">
-        <v>657</v>
-      </c>
-      <c r="C27" s="35" t="s">
-        <v>639</v>
       </c>
       <c r="D27" s="26">
         <f t="shared" ref="D27:D38" si="2">HEX2DEC(C27)</f>
         <v>61475</v>
       </c>
       <c r="F27" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B28" s="35" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="C28" s="35" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="D28" s="26">
         <f t="shared" si="2"/>
         <v>65110</v>
       </c>
       <c r="F28" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>640</v>
+      </c>
+      <c r="B29" s="35" t="s">
+        <v>658</v>
+      </c>
+      <c r="C29" s="35" t="s">
         <v>641</v>
-      </c>
-      <c r="B29" s="35" t="s">
-        <v>659</v>
-      </c>
-      <c r="C29" s="35" t="s">
-        <v>642</v>
       </c>
       <c r="D29" s="26">
         <f t="shared" si="2"/>
         <v>64830</v>
       </c>
       <c r="F29" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>665</v>
+      </c>
+      <c r="B30" s="35" t="s">
         <v>666</v>
       </c>
-      <c r="B30" s="35" t="s">
-        <v>667</v>
-      </c>
       <c r="C30" s="35" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="D30" s="26">
         <f t="shared" si="2"/>
         <v>64800</v>
       </c>
       <c r="F30" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="33" t="s">
+        <v>667</v>
+      </c>
+      <c r="B31" s="41" t="s">
         <v>668</v>
       </c>
-      <c r="B31" s="41" t="s">
+      <c r="C31" s="41" t="s">
         <v>669</v>
-      </c>
-      <c r="C31" s="41" t="s">
-        <v>670</v>
       </c>
       <c r="D31" s="42">
         <f t="shared" si="2"/>
@@ -20214,113 +20312,113 @@
       </c>
       <c r="E31" s="42"/>
       <c r="F31" s="33" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>670</v>
+      </c>
+      <c r="B33" s="35" t="s">
+        <v>672</v>
+      </c>
+      <c r="C33" s="35" t="s">
         <v>671</v>
-      </c>
-      <c r="B33" s="35" t="s">
-        <v>673</v>
-      </c>
-      <c r="C33" s="35" t="s">
-        <v>672</v>
       </c>
       <c r="D33" s="26">
         <f t="shared" si="2"/>
         <v>65279</v>
       </c>
       <c r="F33" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>676</v>
+      </c>
+      <c r="B34" s="35" t="s">
         <v>677</v>
       </c>
-      <c r="B34" s="35" t="s">
+      <c r="C34" s="35" t="s">
         <v>678</v>
-      </c>
-      <c r="C34" s="35" t="s">
-        <v>679</v>
       </c>
       <c r="D34" s="26">
         <f t="shared" si="2"/>
         <v>64775</v>
       </c>
       <c r="F34" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
+        <v>679</v>
+      </c>
+      <c r="B35" s="35" t="s">
         <v>680</v>
       </c>
-      <c r="B35" s="35" t="s">
+      <c r="C35" s="35" t="s">
         <v>681</v>
-      </c>
-      <c r="C35" s="35" t="s">
-        <v>682</v>
       </c>
       <c r="D35" s="26">
         <f t="shared" si="2"/>
         <v>64773</v>
       </c>
       <c r="F35" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
+        <v>682</v>
+      </c>
+      <c r="B37" s="35" t="s">
+        <v>684</v>
+      </c>
+      <c r="C37" s="35" t="s">
         <v>683</v>
-      </c>
-      <c r="B37" s="35" t="s">
-        <v>685</v>
-      </c>
-      <c r="C37" s="35" t="s">
-        <v>684</v>
       </c>
       <c r="D37" s="26">
         <f t="shared" si="2"/>
         <v>65242</v>
       </c>
       <c r="F37" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G37" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>685</v>
+      </c>
+      <c r="B38" s="35" t="s">
+        <v>687</v>
+      </c>
+      <c r="C38" s="35" t="s">
         <v>686</v>
-      </c>
-      <c r="B38" s="35" t="s">
-        <v>688</v>
-      </c>
-      <c r="C38" s="35" t="s">
-        <v>687</v>
       </c>
       <c r="D38" s="26">
         <f t="shared" si="2"/>
         <v>65259</v>
       </c>
       <c r="F38" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G38" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="37" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="D42" s="26">
         <v>61473</v>
@@ -20369,23 +20467,23 @@
         <v>2</v>
       </c>
       <c r="B1" s="27" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="E1" s="46" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="F1" s="27" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="G1" s="28"/>
       <c r="H1" s="28"/>
       <c r="I1" s="28"/>
       <c r="J1" s="28"/>
       <c r="K1" s="27" t="s">
+        <v>895</v>
+      </c>
+      <c r="N1" s="27" t="s">
         <v>896</v>
-      </c>
-      <c r="N1" s="27" t="s">
-        <v>897</v>
       </c>
     </row>
     <row r="2" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
@@ -20393,13 +20491,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C2" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="K2" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="M2" t="str">
         <f>IF(C2&lt;&gt;"",_xlfn.CONCAT(B2,"_",C2),"")</f>
@@ -20423,13 +20521,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C3" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="K3" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="M3" t="str">
         <f t="shared" ref="M3:M66" si="0">IF(C3&lt;&gt;"",_xlfn.CONCAT(B3,"_",C3),"")</f>
@@ -20453,13 +20551,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C4" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="K4" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="M4" t="str">
         <f t="shared" si="0"/>
@@ -20483,13 +20581,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C5" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="K5" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="M5" t="str">
         <f t="shared" si="0"/>
@@ -20513,13 +20611,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C6" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="K6" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="M6" t="str">
         <f t="shared" si="0"/>
@@ -20543,13 +20641,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C7" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="K7" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="M7" t="str">
         <f t="shared" si="0"/>
@@ -20573,13 +20671,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C8" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="K8" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="M8" t="str">
         <f t="shared" si="0"/>
@@ -20601,10 +20699,10 @@
         <v>285</v>
       </c>
       <c r="V8" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="X8" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
     </row>
     <row r="9" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
@@ -20612,13 +20710,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C9" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="K9" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="M9" t="str">
         <f t="shared" si="0"/>
@@ -20640,10 +20738,10 @@
         <v>285</v>
       </c>
       <c r="V9" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="X9" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
     </row>
     <row r="10" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
@@ -20651,13 +20749,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C10" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="K10" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="M10" t="str">
         <f t="shared" si="0"/>
@@ -20679,10 +20777,10 @@
         <v>285</v>
       </c>
       <c r="V10" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="X10" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
     </row>
     <row r="11" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
@@ -20690,13 +20788,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C11" t="s">
+        <v>698</v>
+      </c>
+      <c r="K11" t="s">
         <v>699</v>
-      </c>
-      <c r="K11" t="s">
-        <v>700</v>
       </c>
       <c r="M11" t="str">
         <f t="shared" si="0"/>
@@ -20718,10 +20816,10 @@
         <v>285</v>
       </c>
       <c r="V11" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="X11" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
     </row>
     <row r="12" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
@@ -20729,16 +20827,16 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="C12" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="E12" s="35">
         <v>899</v>
       </c>
       <c r="K12" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="M12" t="str">
         <f t="shared" si="0"/>
@@ -20760,10 +20858,10 @@
         <v>285</v>
       </c>
       <c r="V12" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="X12" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
     </row>
     <row r="13" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
@@ -20771,16 +20869,16 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="C13" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="E13" s="35">
         <v>4154</v>
       </c>
       <c r="K13" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="M13" t="str">
         <f t="shared" si="0"/>
@@ -20802,10 +20900,10 @@
         <v>285</v>
       </c>
       <c r="V13" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="X13" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
     </row>
     <row r="14" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
@@ -20813,16 +20911,16 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="C14" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="E14" s="35">
         <v>512</v>
       </c>
       <c r="K14" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="M14" t="str">
         <f t="shared" si="0"/>
@@ -20844,10 +20942,10 @@
         <v>285</v>
       </c>
       <c r="V14" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="X14" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.25">
@@ -20855,10 +20953,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="C15" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="E15" s="35">
         <v>513</v>
@@ -20867,7 +20965,7 @@
         <v>402</v>
       </c>
       <c r="K15" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="M15" t="str">
         <f t="shared" si="0"/>
@@ -20889,10 +20987,10 @@
         <v>285</v>
       </c>
       <c r="V15" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="X15" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.25">
@@ -20900,10 +20998,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="C16" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="E16" s="35">
         <v>190</v>
@@ -20912,7 +21010,7 @@
         <v>402</v>
       </c>
       <c r="K16" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="M16" t="str">
         <f t="shared" si="0"/>
@@ -20934,10 +21032,10 @@
         <v>285</v>
       </c>
       <c r="V16" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="X16" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
     </row>
     <row r="17" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
@@ -20945,16 +21043,16 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="C17" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="E17" s="35">
         <v>1483</v>
       </c>
       <c r="K17" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="M17" t="str">
         <f t="shared" si="0"/>
@@ -20976,10 +21074,10 @@
         <v>285</v>
       </c>
       <c r="V17" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="X17" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
     </row>
     <row r="18" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
@@ -20987,16 +21085,16 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="C18" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="E18" s="35">
         <v>1675</v>
       </c>
       <c r="K18" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="M18" t="str">
         <f t="shared" si="0"/>
@@ -21018,10 +21116,10 @@
         <v>285</v>
       </c>
       <c r="V18" t="s">
+        <v>720</v>
+      </c>
+      <c r="X18" t="s">
         <v>721</v>
-      </c>
-      <c r="X18" t="s">
-        <v>722</v>
       </c>
     </row>
     <row r="19" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
@@ -21029,16 +21127,16 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="C19" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="E19" s="35">
         <v>2432</v>
       </c>
       <c r="K19" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="M19" t="str">
         <f t="shared" si="0"/>
@@ -21062,16 +21160,16 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="C20" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="E20" s="35">
         <v>588</v>
       </c>
       <c r="K20" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="M20" t="str">
         <f t="shared" si="0"/>
@@ -21095,16 +21193,16 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="C21" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="E21" s="35">
         <v>559</v>
       </c>
       <c r="K21" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="M21" t="str">
         <f t="shared" si="0"/>
@@ -21128,16 +21226,16 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="C22" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E22" s="35">
         <v>1437</v>
       </c>
       <c r="K22" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="M22" t="str">
         <f t="shared" si="0"/>
@@ -21161,16 +21259,16 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="C23" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="E23" s="35">
         <v>2970</v>
       </c>
       <c r="K23" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="M23" t="str">
         <f t="shared" si="0"/>
@@ -21194,16 +21292,16 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="C24" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="E24" s="35">
         <v>91</v>
       </c>
       <c r="K24" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="M24" t="str">
         <f t="shared" si="0"/>
@@ -21227,19 +21325,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="C25" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="E25" s="35">
         <v>92</v>
       </c>
       <c r="F25" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="K25" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="M25" t="str">
         <f t="shared" si="0"/>
@@ -21263,16 +21361,16 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="C26" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E26" s="35">
         <v>974</v>
       </c>
       <c r="K26" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="M26" t="str">
         <f t="shared" si="0"/>
@@ -21296,16 +21394,16 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="C27" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="E27" s="35">
         <v>29</v>
       </c>
       <c r="K27" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="M27" t="str">
         <f t="shared" si="0"/>
@@ -21329,16 +21427,16 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="C28" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="E28" s="35">
         <v>2979</v>
       </c>
       <c r="K28" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="M28" t="str">
         <f t="shared" si="0"/>
@@ -21362,16 +21460,16 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="C29" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="E29" s="35">
         <v>5021</v>
       </c>
       <c r="K29" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="M29" t="str">
         <f t="shared" si="0"/>
@@ -21395,16 +21493,16 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="C30" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="E30" s="35">
         <v>5399</v>
       </c>
       <c r="K30" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="M30" t="str">
         <f t="shared" si="0"/>
@@ -21428,10 +21526,10 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="C31" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="E31" s="35">
         <v>5400</v>
@@ -21440,7 +21538,7 @@
         <v>402</v>
       </c>
       <c r="K31" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="M31" t="str">
         <f t="shared" si="0"/>
@@ -21464,10 +21562,10 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="C32" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="E32" s="35">
         <v>3357</v>
@@ -21476,7 +21574,7 @@
         <v>402</v>
       </c>
       <c r="K32" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="M32" t="str">
         <f t="shared" si="0"/>
@@ -21500,16 +21598,16 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="C33" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="E33" s="35">
         <v>5398</v>
       </c>
       <c r="K33" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="M33" t="str">
         <f t="shared" si="0"/>
@@ -21533,10 +21631,10 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="C34" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="E34" s="35">
         <v>514</v>
@@ -21545,7 +21643,7 @@
         <v>402</v>
       </c>
       <c r="K34" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="M34" t="str">
         <f t="shared" si="0"/>
@@ -21569,10 +21667,10 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="C35" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="E35" s="35">
         <v>515</v>
@@ -21581,7 +21679,7 @@
         <v>402</v>
       </c>
       <c r="K35" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="M35" t="str">
         <f t="shared" si="0"/>
@@ -21605,16 +21703,16 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="C36" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="E36" s="35">
         <v>519</v>
       </c>
       <c r="K36" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="M36" t="str">
         <f t="shared" si="0"/>
@@ -21638,16 +21736,16 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="C37" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="E37" s="35">
         <v>2978</v>
       </c>
       <c r="K37" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="M37" t="str">
         <f t="shared" si="0"/>
@@ -21671,16 +21769,16 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="C38" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="E38" s="35">
         <v>3236</v>
       </c>
       <c r="K38" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="M38" t="str">
         <f t="shared" si="0"/>
@@ -21704,16 +21802,16 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="C39" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="E39" s="35">
         <v>3237</v>
       </c>
       <c r="K39" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="M39" t="str">
         <f t="shared" si="0"/>
@@ -21737,16 +21835,16 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="C40" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="E40" s="35">
         <v>3238</v>
       </c>
       <c r="K40" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="M40" t="str">
         <f t="shared" si="0"/>
@@ -21770,16 +21868,16 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="C41" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="E41" s="35">
         <v>3239</v>
       </c>
       <c r="K41" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="M41" t="str">
         <f t="shared" si="0"/>
@@ -21803,16 +21901,16 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="C42" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="E42" s="35">
         <v>3240</v>
       </c>
       <c r="K42" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="M42" t="str">
         <f t="shared" si="0"/>
@@ -21836,16 +21934,16 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="C43" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="E43" s="35">
         <v>2789</v>
       </c>
       <c r="K43" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="M43" t="str">
         <f t="shared" si="0"/>
@@ -21869,16 +21967,16 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="C44" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="E44" s="35">
         <v>2790</v>
       </c>
       <c r="K44" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="M44" t="str">
         <f t="shared" si="0"/>
@@ -21902,10 +22000,10 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="C45" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="E45" s="35">
         <v>2791</v>
@@ -21914,7 +22012,7 @@
         <v>402</v>
       </c>
       <c r="K45" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="M45" t="str">
         <f t="shared" si="0"/>
@@ -21938,16 +22036,16 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="C46" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="E46" s="35">
         <v>2792</v>
       </c>
       <c r="K46" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="M46" t="str">
         <f t="shared" si="0"/>
@@ -21971,16 +22069,16 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="C47" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="E47" s="35">
         <v>5457</v>
       </c>
       <c r="K47" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="M47" t="str">
         <f t="shared" si="0"/>
@@ -22004,16 +22102,16 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="C48" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="E48" s="35">
         <v>2795</v>
       </c>
       <c r="K48" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="M48" t="str">
         <f t="shared" si="0"/>
@@ -22037,10 +22135,10 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="C49" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="E49" s="35">
         <v>1637</v>
@@ -22049,7 +22147,7 @@
         <v>402</v>
       </c>
       <c r="K49" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="M49" t="str">
         <f t="shared" si="0"/>
@@ -22073,10 +22171,10 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="C50" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="E50" s="35">
         <v>174</v>
@@ -22085,7 +22183,7 @@
         <v>402</v>
       </c>
       <c r="K50" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="M50" t="str">
         <f t="shared" si="0"/>
@@ -22109,16 +22207,16 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="C51" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="E51" s="35">
         <v>175</v>
       </c>
       <c r="K51" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="M51" t="str">
         <f t="shared" si="0"/>
@@ -22142,16 +22240,16 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="C52" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="E52" s="35">
         <v>176</v>
       </c>
       <c r="K52" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="M52" t="str">
         <f t="shared" si="0"/>
@@ -22175,16 +22273,16 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="C53" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="E53" s="35">
         <v>52</v>
       </c>
       <c r="K53" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="M53" t="str">
         <f t="shared" si="0"/>
@@ -22208,16 +22306,16 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="C54" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="E54" s="35">
         <v>1134</v>
       </c>
       <c r="K54" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="M54" t="str">
         <f t="shared" si="0"/>
@@ -22241,16 +22339,16 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C55" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="E55" s="35">
         <v>94</v>
       </c>
       <c r="K55" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="M55" t="str">
         <f t="shared" si="0"/>
@@ -22274,16 +22372,16 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C56" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="E56" s="35">
         <v>22</v>
       </c>
       <c r="K56" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="M56" t="str">
         <f t="shared" si="0"/>
@@ -22307,16 +22405,16 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C57" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="E57" s="35">
         <v>98</v>
       </c>
       <c r="K57" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="M57" t="str">
         <f t="shared" si="0"/>
@@ -22340,10 +22438,10 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C58" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="E58" s="35">
         <v>100</v>
@@ -22352,7 +22450,7 @@
         <v>402</v>
       </c>
       <c r="K58" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="M58" t="str">
         <f t="shared" si="0"/>
@@ -22376,16 +22474,16 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C59" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E59" s="35">
         <v>101</v>
       </c>
       <c r="K59" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="M59" t="str">
         <f t="shared" si="0"/>
@@ -22409,16 +22507,16 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C60" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="E60" s="35">
         <v>109</v>
       </c>
       <c r="K60" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="M60" t="str">
         <f t="shared" si="0"/>
@@ -22442,10 +22540,10 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C61" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="E61" s="35">
         <v>111</v>
@@ -22454,7 +22552,7 @@
         <v>402</v>
       </c>
       <c r="K61" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="M61" t="str">
         <f t="shared" si="0"/>
@@ -22478,16 +22576,16 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="C62" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="E62" s="35">
         <v>164</v>
       </c>
       <c r="K62" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="M62" t="str">
         <f t="shared" si="0"/>
@@ -22511,10 +22609,10 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="C63" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="E63" s="35">
         <v>157</v>
@@ -22523,7 +22621,7 @@
         <v>402</v>
       </c>
       <c r="K63" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="M63" t="str">
         <f t="shared" si="0"/>
@@ -22547,16 +22645,16 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="C64" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="E64" s="35">
         <v>156</v>
       </c>
       <c r="K64" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="M64" t="str">
         <f t="shared" si="0"/>
@@ -22580,16 +22678,16 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="C65" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="E65" s="35">
         <v>1349</v>
       </c>
       <c r="K65" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="M65" t="str">
         <f t="shared" si="0"/>
@@ -22613,16 +22711,16 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="C66" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="E66" s="35">
         <v>182</v>
       </c>
       <c r="K66" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="M66" t="str">
         <f t="shared" si="0"/>
@@ -22646,10 +22744,10 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="C67" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="E67" s="35">
         <v>250</v>
@@ -22658,7 +22756,7 @@
         <v>402</v>
       </c>
       <c r="K67" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="M67" t="str">
         <f t="shared" ref="M67:M130" si="4">IF(C67&lt;&gt;"",_xlfn.CONCAT(B67,"_",C67),"")</f>
@@ -22682,10 +22780,10 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="C68" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="E68" s="35">
         <v>108</v>
@@ -22694,7 +22792,7 @@
         <v>402</v>
       </c>
       <c r="K68" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="M68" t="str">
         <f t="shared" si="4"/>
@@ -22718,16 +22816,16 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="C69" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="E69" s="35">
         <v>170</v>
       </c>
       <c r="K69" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="M69" t="str">
         <f t="shared" si="4"/>
@@ -22751,10 +22849,10 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="C70" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E70" s="35">
         <v>171</v>
@@ -22763,7 +22861,7 @@
         <v>402</v>
       </c>
       <c r="K70" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="M70" t="str">
         <f t="shared" si="4"/>
@@ -22787,10 +22885,10 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="C71" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="E71" s="35">
         <v>172</v>
@@ -22799,7 +22897,7 @@
         <v>402</v>
       </c>
       <c r="K71" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="M71" t="str">
         <f t="shared" si="4"/>
@@ -22823,16 +22921,16 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="C72" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="E72" s="35">
         <v>79</v>
       </c>
       <c r="K72" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="M72" t="str">
         <f t="shared" si="4"/>
@@ -22856,16 +22954,16 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C73" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="E73" s="35">
         <v>81</v>
       </c>
       <c r="K73" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="M73" t="str">
         <f t="shared" si="4"/>
@@ -22889,10 +22987,10 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C74" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="E74" s="35">
         <v>102</v>
@@ -22901,7 +22999,7 @@
         <v>402</v>
       </c>
       <c r="K74" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="M74" t="str">
         <f t="shared" si="4"/>
@@ -22925,10 +23023,10 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C75" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="E75" s="35">
         <v>105</v>
@@ -22937,7 +23035,7 @@
         <v>402</v>
       </c>
       <c r="K75" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="M75" t="str">
         <f t="shared" si="4"/>
@@ -22961,10 +23059,10 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C76" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="E76" s="35">
         <v>106</v>
@@ -22973,7 +23071,7 @@
         <v>402</v>
       </c>
       <c r="K76" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="M76" t="str">
         <f t="shared" si="4"/>
@@ -22997,16 +23095,16 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C77" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="E77" s="35">
         <v>107</v>
       </c>
       <c r="K77" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="M77" t="str">
         <f t="shared" si="4"/>
@@ -23030,16 +23128,16 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C78" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="E78" s="35">
         <v>173</v>
       </c>
       <c r="K78" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="M78" t="str">
         <f t="shared" si="4"/>
@@ -23063,16 +23161,16 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C79" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="E79" s="35">
         <v>112</v>
       </c>
       <c r="K79" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="M79" t="str">
         <f t="shared" si="4"/>
@@ -23096,16 +23194,16 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="C80" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="E80" s="35">
         <v>114</v>
       </c>
       <c r="K80" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="M80" t="str">
         <f t="shared" si="4"/>
@@ -23129,16 +23227,16 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="C81" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="E81" s="35">
         <v>115</v>
       </c>
       <c r="K81" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="M81" t="str">
         <f t="shared" si="4"/>
@@ -23162,16 +23260,16 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="C82" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="E82" s="35">
         <v>167</v>
       </c>
       <c r="K82" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="M82" t="str">
         <f t="shared" si="4"/>
@@ -23195,10 +23293,10 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="C83" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="E83" s="35">
         <v>168</v>
@@ -23207,7 +23305,7 @@
         <v>402</v>
       </c>
       <c r="K83" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="M83" t="str">
         <f t="shared" si="4"/>
@@ -23231,10 +23329,10 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="C84" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="E84" s="35">
         <v>158</v>
@@ -23243,7 +23341,7 @@
         <v>402</v>
       </c>
       <c r="K84" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="M84" t="str">
         <f t="shared" si="4"/>
@@ -23267,16 +23365,16 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C85" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="E85" s="35">
         <v>1380</v>
       </c>
       <c r="K85" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="M85" t="str">
         <f t="shared" si="4"/>
@@ -23300,16 +23398,16 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C86" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="E86" s="35">
         <v>1381</v>
       </c>
       <c r="K86" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="M86" t="str">
         <f t="shared" si="4"/>
@@ -23333,16 +23431,16 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C87" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="E87" s="35">
         <v>1382</v>
       </c>
       <c r="K87" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="M87" t="str">
         <f t="shared" si="4"/>
@@ -23366,16 +23464,16 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C88" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="E88" s="35">
         <v>3548</v>
       </c>
       <c r="K88" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="M88" t="str">
         <f t="shared" si="4"/>
@@ -23399,16 +23497,16 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C89" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="E89" s="35">
         <v>3549</v>
       </c>
       <c r="K89" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="M89" t="str">
         <f t="shared" si="4"/>
@@ -23432,16 +23530,16 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C90" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="E90" s="35">
         <v>3550</v>
       </c>
       <c r="K90" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="M90" t="str">
         <f t="shared" si="4"/>
@@ -23465,10 +23563,10 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C91" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="E91" s="35">
         <v>3551</v>
@@ -23477,7 +23575,7 @@
         <v>402</v>
       </c>
       <c r="K91" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="M91" t="str">
         <f t="shared" si="4"/>
@@ -23501,16 +23599,16 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C92" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="E92" s="35">
         <v>3552</v>
       </c>
       <c r="K92" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="M92" t="str">
         <f t="shared" si="4"/>
@@ -23534,16 +23632,16 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C93" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="E93" s="35">
         <v>3553</v>
       </c>
       <c r="K93" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="M93" t="str">
         <f t="shared" si="4"/>
@@ -23567,16 +23665,16 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C94" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="E94" s="35">
         <v>3554</v>
       </c>
       <c r="K94" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="M94" t="str">
         <f t="shared" si="4"/>
@@ -23600,10 +23698,10 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C95" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="E95" s="35">
         <v>4083</v>
@@ -23612,7 +23710,7 @@
         <v>402</v>
       </c>
       <c r="K95" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="M95" t="str">
         <f t="shared" si="4"/>
@@ -23636,13 +23734,13 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C96" s="33" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="D96" s="33" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="E96" s="41">
         <v>3697</v>
@@ -23654,7 +23752,7 @@
         <v>0</v>
       </c>
       <c r="H96" s="26" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="I96" s="26">
         <v>0</v>
@@ -23664,7 +23762,7 @@
         <v>1,1</v>
       </c>
       <c r="K96" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="M96" t="str">
         <f t="shared" si="4"/>
@@ -23688,10 +23786,10 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C97" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="E97" s="35">
         <v>3699</v>
@@ -23700,7 +23798,7 @@
         <v>1</v>
       </c>
       <c r="H97" s="26" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="I97" s="26">
         <v>0</v>
@@ -23710,7 +23808,7 @@
         <v>2,1</v>
       </c>
       <c r="K97" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="M97" t="str">
         <f t="shared" si="4"/>
@@ -23734,13 +23832,13 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C98" s="33" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="D98" s="33" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="E98" s="35">
         <v>3700</v>
@@ -23752,7 +23850,7 @@
         <v>1</v>
       </c>
       <c r="H98" s="26" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="I98" s="26">
         <v>2</v>
@@ -23762,7 +23860,7 @@
         <v>2,3</v>
       </c>
       <c r="K98" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="M98" t="str">
         <f t="shared" si="4"/>
@@ -23786,10 +23884,10 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C99" s="33" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="D99" s="33"/>
       <c r="E99" s="35">
@@ -23802,7 +23900,7 @@
         <v>1</v>
       </c>
       <c r="H99" s="26" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="I99" s="26">
         <v>4</v>
@@ -23812,7 +23910,7 @@
         <v>2,5</v>
       </c>
       <c r="K99" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="M99" t="str">
         <f t="shared" si="4"/>
@@ -23836,10 +23934,10 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C100" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="E100" s="35">
         <v>3702</v>
@@ -23848,7 +23946,7 @@
         <v>2</v>
       </c>
       <c r="H100" s="26" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="I100" s="26">
         <v>0</v>
@@ -23858,7 +23956,7 @@
         <v>3,1</v>
       </c>
       <c r="K100" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="M100" t="str">
         <f t="shared" si="4"/>
@@ -23882,13 +23980,13 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C101" s="33" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="D101" s="33" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="E101" s="35">
         <v>3703</v>
@@ -23900,7 +23998,7 @@
         <v>2</v>
       </c>
       <c r="H101" s="26" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="I101" s="26">
         <v>2</v>
@@ -23910,7 +24008,7 @@
         <v>3,3</v>
       </c>
       <c r="K101" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="M101" t="str">
         <f t="shared" si="4"/>
@@ -23934,10 +24032,10 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C102" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="E102" s="35">
         <v>3704</v>
@@ -23946,7 +24044,7 @@
         <v>2</v>
       </c>
       <c r="H102" s="26" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="I102" s="26">
         <v>4</v>
@@ -23956,7 +24054,7 @@
         <v>3,5</v>
       </c>
       <c r="K102" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="M102" t="str">
         <f t="shared" si="4"/>
@@ -23980,10 +24078,10 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C103" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="E103" s="35">
         <v>3705</v>
@@ -23992,7 +24090,7 @@
         <v>2</v>
       </c>
       <c r="H103" s="26" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="I103" s="26">
         <v>6</v>
@@ -24002,7 +24100,7 @@
         <v>3,7</v>
       </c>
       <c r="K103" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="M103" t="str">
         <f t="shared" si="4"/>
@@ -24026,10 +24124,10 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C104" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="E104" s="35">
         <v>3706</v>
@@ -24038,7 +24136,7 @@
         <v>3</v>
       </c>
       <c r="H104" s="26" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="I104" s="26">
         <v>0</v>
@@ -24048,7 +24146,7 @@
         <v>4,1</v>
       </c>
       <c r="K104" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="M104" t="str">
         <f t="shared" si="4"/>
@@ -24072,10 +24170,10 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C105" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="E105" s="35">
         <v>3707</v>
@@ -24084,7 +24182,7 @@
         <v>3</v>
       </c>
       <c r="H105" s="26" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="I105" s="26">
         <v>2</v>
@@ -24094,7 +24192,7 @@
         <v>4,3</v>
       </c>
       <c r="K105" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="M105" t="str">
         <f t="shared" si="4"/>
@@ -24118,10 +24216,10 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C106" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="E106" s="35">
         <v>3708</v>
@@ -24130,7 +24228,7 @@
         <v>3</v>
       </c>
       <c r="H106" s="26" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="I106" s="26">
         <v>4</v>
@@ -24140,7 +24238,7 @@
         <v>4,5</v>
       </c>
       <c r="K106" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="M106" t="str">
         <f t="shared" si="4"/>
@@ -24164,10 +24262,10 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C107" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="E107" s="35">
         <v>3709</v>
@@ -24176,7 +24274,7 @@
         <v>3</v>
       </c>
       <c r="H107" s="26" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="I107" s="26">
         <v>6</v>
@@ -24186,7 +24284,7 @@
         <v>4,7</v>
       </c>
       <c r="K107" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="M107" t="str">
         <f t="shared" si="4"/>
@@ -24210,10 +24308,10 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C108" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="E108" s="35">
         <v>3710</v>
@@ -24222,7 +24320,7 @@
         <v>4</v>
       </c>
       <c r="H108" s="26" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="I108" s="26">
         <v>0</v>
@@ -24232,7 +24330,7 @@
         <v>5,1</v>
       </c>
       <c r="K108" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="M108" t="str">
         <f t="shared" si="4"/>
@@ -24256,10 +24354,10 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C109" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="E109" s="35">
         <v>3711</v>
@@ -24268,7 +24366,7 @@
         <v>4</v>
       </c>
       <c r="H109" s="26" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="I109" s="26">
         <v>2</v>
@@ -24278,7 +24376,7 @@
         <v>5,3</v>
       </c>
       <c r="K109" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="M109" t="str">
         <f t="shared" si="4"/>
@@ -24302,10 +24400,10 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C110" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="E110" s="35">
         <v>3712</v>
@@ -24314,7 +24412,7 @@
         <v>4</v>
       </c>
       <c r="H110" s="26" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="I110" s="26">
         <v>4</v>
@@ -24324,7 +24422,7 @@
         <v>5,5</v>
       </c>
       <c r="K110" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="M110" t="str">
         <f t="shared" si="4"/>
@@ -24348,10 +24446,10 @@
         <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C111" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="E111" s="35">
         <v>3713</v>
@@ -24360,7 +24458,7 @@
         <v>4</v>
       </c>
       <c r="H111" s="26" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="I111" s="26">
         <v>6</v>
@@ -24370,7 +24468,7 @@
         <v>5,7</v>
       </c>
       <c r="K111" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="M111" t="str">
         <f t="shared" si="4"/>
@@ -24394,13 +24492,13 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C112" s="33" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="D112" s="33" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="E112" s="35">
         <v>3714</v>
@@ -24412,7 +24510,7 @@
         <v>5</v>
       </c>
       <c r="H112" s="26" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="I112" s="26">
         <v>0</v>
@@ -24422,7 +24520,7 @@
         <v>6,1</v>
       </c>
       <c r="K112" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="M112" t="str">
         <f t="shared" si="4"/>
@@ -24446,13 +24544,13 @@
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C113" s="33" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="D113" s="33" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="E113" s="35">
         <v>3715</v>
@@ -24464,7 +24562,7 @@
         <v>5</v>
       </c>
       <c r="H113" s="26" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="I113" s="26">
         <v>2</v>
@@ -24474,7 +24572,7 @@
         <v>6,3</v>
       </c>
       <c r="K113" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="M113" t="str">
         <f t="shared" si="4"/>
@@ -24498,10 +24596,10 @@
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C114" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="E114" s="35">
         <v>3716</v>
@@ -24510,7 +24608,7 @@
         <v>5</v>
       </c>
       <c r="H114" s="26" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="I114" s="26">
         <v>4</v>
@@ -24520,7 +24618,7 @@
         <v>6,5</v>
       </c>
       <c r="K114" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="M114" t="str">
         <f t="shared" si="4"/>
@@ -24544,10 +24642,10 @@
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C115" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="E115" s="35">
         <v>3717</v>
@@ -24556,7 +24654,7 @@
         <v>5</v>
       </c>
       <c r="H115" s="26" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="I115" s="26">
         <v>6</v>
@@ -24566,7 +24664,7 @@
         <v>6,7</v>
       </c>
       <c r="K115" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="M115" t="str">
         <f t="shared" si="4"/>
@@ -24590,10 +24688,10 @@
         <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C116" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="E116" s="35">
         <v>3718</v>
@@ -24602,7 +24700,7 @@
         <v>6</v>
       </c>
       <c r="H116" s="26" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="I116" s="26">
         <v>0</v>
@@ -24612,7 +24710,7 @@
         <v>7,1</v>
       </c>
       <c r="K116" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="M116" t="str">
         <f t="shared" si="4"/>
@@ -24636,10 +24734,10 @@
         <v>116</v>
       </c>
       <c r="B117" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C117" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="E117" s="35">
         <v>3698</v>
@@ -24648,7 +24746,7 @@
         <v>6</v>
       </c>
       <c r="H117" s="26" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="I117" s="26">
         <v>2</v>
@@ -24658,7 +24756,7 @@
         <v>7,3</v>
       </c>
       <c r="K117" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="M117" t="str">
         <f t="shared" si="4"/>
@@ -24682,10 +24780,10 @@
         <v>117</v>
       </c>
       <c r="B118" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C118" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="E118" s="35">
         <v>4175</v>
@@ -24694,7 +24792,7 @@
         <v>6</v>
       </c>
       <c r="H118" s="26" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="I118" s="26">
         <v>5</v>
@@ -24704,7 +24802,7 @@
         <v>7,6</v>
       </c>
       <c r="K118" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="M118" t="str">
         <f t="shared" si="4"/>
@@ -24728,16 +24826,16 @@
         <v>118</v>
       </c>
       <c r="B119" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C119" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="E119" s="35">
         <v>3241</v>
       </c>
       <c r="K119" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="M119" t="str">
         <f t="shared" si="4"/>
@@ -24761,10 +24859,10 @@
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C120" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="E120" s="35">
         <v>3242</v>
@@ -24773,7 +24871,7 @@
         <v>402</v>
       </c>
       <c r="K120" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="M120" t="str">
         <f t="shared" si="4"/>
@@ -24797,16 +24895,16 @@
         <v>120</v>
       </c>
       <c r="B121" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C121" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="E121" s="35">
         <v>3243</v>
       </c>
       <c r="K121" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="M121" t="str">
         <f t="shared" si="4"/>
@@ -24830,16 +24928,16 @@
         <v>121</v>
       </c>
       <c r="B122" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C122" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="E122" s="35">
         <v>3244</v>
       </c>
       <c r="K122" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="M122" t="str">
         <f t="shared" si="4"/>
@@ -24863,10 +24961,10 @@
         <v>122</v>
       </c>
       <c r="B123" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C123" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="E123" s="35">
         <v>1761</v>
@@ -24875,7 +24973,7 @@
         <v>402</v>
       </c>
       <c r="K123" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="M123" t="str">
         <f t="shared" si="4"/>
@@ -24899,10 +24997,10 @@
         <v>123</v>
       </c>
       <c r="B124" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C124" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="E124" s="35">
         <v>3031</v>
@@ -24911,7 +25009,7 @@
         <v>402</v>
       </c>
       <c r="K124" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="M124" t="str">
         <f t="shared" si="4"/>
@@ -24935,16 +25033,16 @@
         <v>124</v>
       </c>
       <c r="B125" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C125" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E125" s="35">
         <v>3517</v>
       </c>
       <c r="K125" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="M125" t="str">
         <f t="shared" si="4"/>
@@ -24968,16 +25066,16 @@
         <v>125</v>
       </c>
       <c r="B126" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C126" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="E126" s="35">
         <v>3532</v>
       </c>
       <c r="K126" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="M126" t="str">
         <f t="shared" si="4"/>
@@ -25001,10 +25099,10 @@
         <v>126</v>
       </c>
       <c r="B127" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C127" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="E127" s="35">
         <v>5245</v>
@@ -25013,7 +25111,7 @@
         <v>402</v>
       </c>
       <c r="K127" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="M127" t="str">
         <f t="shared" si="4"/>
@@ -25037,16 +25135,16 @@
         <v>127</v>
       </c>
       <c r="B128" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C128" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="E128" s="35">
         <v>4365</v>
       </c>
       <c r="K128" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="M128" t="str">
         <f t="shared" si="4"/>
@@ -25070,10 +25168,10 @@
         <v>128</v>
       </c>
       <c r="B129" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C129" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="E129" s="35">
         <v>5246</v>
@@ -25082,7 +25180,7 @@
         <v>402</v>
       </c>
       <c r="K129" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="M129" t="str">
         <f t="shared" si="4"/>
@@ -25106,16 +25204,16 @@
         <v>129</v>
       </c>
       <c r="B130" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C130" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="E130" s="35">
         <v>3363</v>
       </c>
       <c r="K130" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="M130" t="str">
         <f t="shared" si="4"/>
@@ -25139,16 +25237,16 @@
         <v>130</v>
       </c>
       <c r="B131" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C131" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="E131" s="35">
         <v>4366</v>
       </c>
       <c r="K131" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="M131" t="str">
         <f t="shared" ref="M131:M171" si="9">IF(C131&lt;&gt;"",_xlfn.CONCAT(B131,"_",C131),"")</f>
@@ -25172,16 +25270,16 @@
         <v>140</v>
       </c>
       <c r="B132" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C132" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="E132" s="35">
         <v>4331</v>
       </c>
       <c r="K132" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="M132" t="str">
         <f t="shared" si="9"/>
@@ -25205,10 +25303,10 @@
         <v>141</v>
       </c>
       <c r="B133" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C133" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="E133" s="35">
         <v>4332</v>
@@ -25217,7 +25315,7 @@
         <v>402</v>
       </c>
       <c r="K133" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="M133" t="str">
         <f t="shared" si="9"/>
@@ -25241,16 +25339,16 @@
         <v>142</v>
       </c>
       <c r="B134" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C134" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="E134" s="35">
         <v>4333</v>
       </c>
       <c r="K134" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="M134" t="str">
         <f t="shared" si="9"/>
@@ -25274,16 +25372,16 @@
         <v>143</v>
       </c>
       <c r="B135" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C135" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="E135" s="35">
         <v>4334</v>
       </c>
       <c r="K135" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="M135" t="str">
         <f t="shared" si="9"/>
@@ -25307,10 +25405,10 @@
         <v>144</v>
       </c>
       <c r="B136" t="s">
+        <v>844</v>
+      </c>
+      <c r="C136" t="s">
         <v>845</v>
-      </c>
-      <c r="C136" t="s">
-        <v>846</v>
       </c>
       <c r="E136" s="35">
         <v>4360</v>
@@ -25319,7 +25417,7 @@
         <v>402</v>
       </c>
       <c r="K136" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="M136" t="str">
         <f t="shared" si="9"/>
@@ -25343,16 +25441,16 @@
         <v>145</v>
       </c>
       <c r="B137" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C137" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="E137" s="35">
         <v>4361</v>
       </c>
       <c r="K137" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="M137" t="str">
         <f t="shared" si="9"/>
@@ -25376,16 +25474,16 @@
         <v>146</v>
       </c>
       <c r="B138" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C138" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="E138" s="35">
         <v>4363</v>
       </c>
       <c r="K138" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="M138" t="str">
         <f t="shared" si="9"/>
@@ -25409,16 +25507,16 @@
         <v>147</v>
       </c>
       <c r="B139" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C139" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="E139" s="35">
         <v>4362</v>
       </c>
       <c r="K139" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="M139" t="str">
         <f t="shared" si="9"/>
@@ -25442,10 +25540,10 @@
         <v>148</v>
       </c>
       <c r="B140" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C140" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="E140" s="35">
         <v>4765</v>
@@ -25454,7 +25552,7 @@
         <v>402</v>
       </c>
       <c r="K140" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="M140" t="str">
         <f t="shared" si="9"/>
@@ -25478,16 +25576,16 @@
         <v>149</v>
       </c>
       <c r="B141" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C141" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="E141" s="35">
         <v>4766</v>
       </c>
       <c r="K141" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="M141" t="str">
         <f t="shared" si="9"/>
@@ -25511,16 +25609,16 @@
         <v>150</v>
       </c>
       <c r="B142" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C142" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="E142" s="35">
         <v>4767</v>
       </c>
       <c r="K142" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="M142" t="str">
         <f t="shared" si="9"/>
@@ -25544,16 +25642,16 @@
         <v>151</v>
       </c>
       <c r="B143" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C143" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="E143" s="35">
         <v>4768</v>
       </c>
       <c r="K143" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="M143" t="str">
         <f t="shared" si="9"/>
@@ -25577,16 +25675,16 @@
         <v>152</v>
       </c>
       <c r="B144" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C144" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="E144" s="35">
         <v>4769</v>
       </c>
       <c r="K144" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="M144" t="str">
         <f t="shared" si="9"/>
@@ -25610,16 +25708,16 @@
         <v>153</v>
       </c>
       <c r="B145" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C145" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="E145" s="35">
         <v>4770</v>
       </c>
       <c r="K145" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="M145" t="str">
         <f t="shared" si="9"/>
@@ -25643,10 +25741,10 @@
         <v>154</v>
       </c>
       <c r="B146" t="s">
+        <v>855</v>
+      </c>
+      <c r="C146" t="s">
         <v>856</v>
-      </c>
-      <c r="C146" t="s">
-        <v>857</v>
       </c>
       <c r="E146" s="35">
         <v>97</v>
@@ -25655,7 +25753,7 @@
         <v>402</v>
       </c>
       <c r="K146" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="M146" t="str">
         <f t="shared" si="9"/>
@@ -25679,16 +25777,16 @@
         <v>155</v>
       </c>
       <c r="B147" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="C147" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="E147" s="35">
         <v>5077</v>
       </c>
       <c r="K147" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="L147">
         <v>1</v>
@@ -25715,16 +25813,16 @@
         <v>156</v>
       </c>
       <c r="B148" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="C148" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="E148" s="35">
         <v>5078</v>
       </c>
       <c r="K148" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="L148">
         <v>2</v>
@@ -25751,16 +25849,16 @@
         <v>157</v>
       </c>
       <c r="B149" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="C149" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="E149" s="35">
         <v>5079</v>
       </c>
       <c r="K149" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="L149">
         <v>3</v>
@@ -25787,16 +25885,16 @@
         <v>158</v>
       </c>
       <c r="B150" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="C150" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="E150" s="35">
         <v>5080</v>
       </c>
       <c r="K150" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="L150">
         <v>4</v>
@@ -25823,16 +25921,16 @@
         <v>159</v>
       </c>
       <c r="B151" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="C151" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="E151" s="35">
         <v>5081</v>
       </c>
       <c r="K151" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="L151">
         <v>5</v>
@@ -25859,16 +25957,16 @@
         <v>160</v>
       </c>
       <c r="B152" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="C152" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="E152" s="35">
         <v>3987</v>
       </c>
       <c r="K152" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="L152">
         <v>6</v>
@@ -25895,16 +25993,16 @@
         <v>161</v>
       </c>
       <c r="B153" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="C153" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="E153" s="35">
         <v>5082</v>
       </c>
       <c r="K153" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="L153">
         <v>7</v>
@@ -25931,16 +26029,16 @@
         <v>162</v>
       </c>
       <c r="B154" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="C154" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="E154" s="35">
         <v>5083</v>
       </c>
       <c r="K154" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="L154">
         <v>8</v>
@@ -25967,16 +26065,16 @@
         <v>163</v>
       </c>
       <c r="B155" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="C155" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="E155" s="35">
         <v>5084</v>
       </c>
       <c r="K155" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="L155">
         <v>9</v>
@@ -26003,16 +26101,16 @@
         <v>164</v>
       </c>
       <c r="B156" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="C156" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="E156" s="35">
         <v>5085</v>
       </c>
       <c r="K156" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="L156">
         <v>10</v>
@@ -26039,10 +26137,10 @@
         <v>165</v>
       </c>
       <c r="B157" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="C157" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="E157" s="35">
         <v>5086</v>
@@ -26051,7 +26149,7 @@
         <v>402</v>
       </c>
       <c r="K157" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="L157">
         <v>11</v>
@@ -26078,16 +26176,16 @@
         <v>166</v>
       </c>
       <c r="B158" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="C158" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="E158" s="35">
         <v>5469</v>
       </c>
       <c r="K158" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="L158">
         <v>12</v>
@@ -26114,16 +26212,16 @@
         <v>167</v>
       </c>
       <c r="B159" t="s">
+        <v>869</v>
+      </c>
+      <c r="C159" t="s">
         <v>870</v>
-      </c>
-      <c r="C159" t="s">
-        <v>871</v>
       </c>
       <c r="E159" s="35">
         <v>5093</v>
       </c>
       <c r="K159" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="L159">
         <v>1</v>
@@ -26150,16 +26248,16 @@
         <v>168</v>
       </c>
       <c r="B160" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="C160" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="E160" s="35">
         <v>5094</v>
       </c>
       <c r="K160" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="L160">
         <v>2</v>
@@ -26186,16 +26284,16 @@
         <v>169</v>
       </c>
       <c r="B161" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="C161" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="E161" s="35">
         <v>5095</v>
       </c>
       <c r="K161" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="L161">
         <v>3</v>
@@ -26222,16 +26320,16 @@
         <v>170</v>
       </c>
       <c r="B162" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="C162" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="E162" s="35">
         <v>5096</v>
       </c>
       <c r="K162" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="L162">
         <v>4</v>
@@ -26258,16 +26356,16 @@
         <v>171</v>
       </c>
       <c r="B163" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="C163" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="E163" s="35">
         <v>5097</v>
       </c>
       <c r="K163" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="L163">
         <v>5</v>
@@ -26294,16 +26392,16 @@
         <v>172</v>
       </c>
       <c r="B164" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="C164" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="E164" s="35">
         <v>5098</v>
       </c>
       <c r="K164" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="L164">
         <v>6</v>
@@ -26330,10 +26428,10 @@
         <v>173</v>
       </c>
       <c r="B165" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="C165" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="E165" s="35">
         <v>5099</v>
@@ -26342,7 +26440,7 @@
         <v>402</v>
       </c>
       <c r="K165" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="L165">
         <v>7</v>
@@ -26369,16 +26467,16 @@
         <v>174</v>
       </c>
       <c r="B166" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="C166" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="E166" s="35">
         <v>5100</v>
       </c>
       <c r="K166" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="L166">
         <v>8</v>
@@ -26405,10 +26503,10 @@
         <v>175</v>
       </c>
       <c r="B167" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="C167" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="E167" s="35">
         <v>5101</v>
@@ -26417,7 +26515,7 @@
         <v>402</v>
       </c>
       <c r="K167" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="L167">
         <v>9</v>
@@ -26444,16 +26542,16 @@
         <v>176</v>
       </c>
       <c r="B168" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="C168" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="E168" s="35">
         <v>5102</v>
       </c>
       <c r="K168" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="L168">
         <v>10</v>
@@ -26480,16 +26578,16 @@
         <v>177</v>
       </c>
       <c r="B169" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="C169" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="E169" s="35">
         <v>5103</v>
       </c>
       <c r="K169" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="L169">
         <v>11</v>
@@ -26516,16 +26614,16 @@
         <v>178</v>
       </c>
       <c r="B170" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="C170" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="E170" s="35">
         <v>5470</v>
       </c>
       <c r="K170" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="L170">
         <v>12</v>
@@ -26552,16 +26650,16 @@
         <v>179</v>
       </c>
       <c r="B171" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="C171" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="E171" s="35">
         <v>5416</v>
       </c>
       <c r="K171" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="L171">
         <v>13</v>
@@ -26607,24 +26705,24 @@
   <sheetData>
     <row r="2" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C2" s="33" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="D2" s="41">
         <v>3697</v>
       </c>
       <c r="E2" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="3" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C3" s="33" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="D3" s="35">
         <v>3700</v>
       </c>
       <c r="E3" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
     </row>
     <row r="4" spans="3:5" x14ac:dyDescent="0.25">
@@ -26633,63 +26731,63 @@
         <v>3701</v>
       </c>
       <c r="E4" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
     </row>
     <row r="5" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C5" s="33" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="D5" s="35">
         <v>3703</v>
       </c>
       <c r="E5" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="6" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C6" s="33" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D6" s="35">
         <v>3714</v>
       </c>
       <c r="E6" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="7" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C7" s="33" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="D7" s="35">
         <v>3715</v>
       </c>
       <c r="E7" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
     </row>
     <row r="10" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E10" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
     </row>
     <row r="14" spans="3:5" ht="255" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="15" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E15" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="18" spans="5:5" ht="409.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="20" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E20" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="23" spans="5:5" ht="205.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="25" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E25" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
     </row>
   </sheetData>
@@ -26699,21 +26797,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c96d9849-7071-4555-8535-ee11c374d0f7">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3f324c86-ae15-4ed4-b4a2-09335a7d28ef" xsi:nil="true"/>
-    <SharedWithUsers xmlns="3f324c86-ae15-4ed4-b4a2-09335a7d28ef">
-      <UserInfo>
-        <DisplayName>Noel Loughran</DisplayName>
-        <AccountId>19</AccountId>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -26940,27 +27029,27 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c96d9849-7071-4555-8535-ee11c374d0f7">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3f324c86-ae15-4ed4-b4a2-09335a7d28ef" xsi:nil="true"/>
+    <SharedWithUsers xmlns="3f324c86-ae15-4ed4-b4a2-09335a7d28ef">
+      <UserInfo>
+        <DisplayName>Noel Loughran</DisplayName>
+        <AccountId>19</AccountId>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7DE4EA8D-9182-4C6A-B31C-49373749A7AE}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3E59E7C-5896-4162-AB70-9CA3CEB6A0FE}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="3f324c86-ae15-4ed4-b4a2-09335a7d28ef"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="c96d9849-7071-4555-8535-ee11c374d0f7"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -26985,9 +27074,18 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3E59E7C-5896-4162-AB70-9CA3CEB6A0FE}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7DE4EA8D-9182-4C6A-B31C-49373749A7AE}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="3f324c86-ae15-4ed4-b4a2-09335a7d28ef"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="c96d9849-7071-4555-8535-ee11c374d0f7"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>